--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="183">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -247,6 +247,15 @@
     <t>Krzemińska Beata</t>
   </si>
   <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>matura 2026</t>
+  </si>
+  <si>
     <t>2FA|JA2</t>
   </si>
   <si>
@@ -268,6 +277,12 @@
     <t>Hudziec Agnieszka</t>
   </si>
   <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
@@ -328,9 +343,6 @@
     <t>1TFA</t>
   </si>
   <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
     <t>7, 13:15-14:00</t>
   </si>
   <si>
@@ -352,6 +364,12 @@
     <t>9, 14:55-15:40</t>
   </si>
   <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>matura w ZSL</t>
+  </si>
+  <si>
     <t>4TFB</t>
   </si>
   <si>
@@ -364,51 +382,87 @@
     <t>6</t>
   </si>
   <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>egzaminy zawodowe - delegowanie Bolesławiec</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
     <t>Zastępstwo</t>
   </si>
   <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>egzaminy zawodowe - delegowanie Bolesławiec</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>2CA</t>
+    <t>p. Danielewski, zajęcia z wychowawcą za lekcję 1</t>
   </si>
   <si>
     <t>Technologia gastronomiczna z towaroznawstwem</t>
   </si>
   <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
     <t>1TFB</t>
   </si>
   <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
     <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
   </si>
   <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>1K|JA2</t>
+  </si>
+  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
@@ -416,6 +470,30 @@
   </si>
   <si>
     <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
   </si>
   <si>
     <t>Godzina</t>
@@ -940,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{352c979e-749c-4481-acbe-fb3da5fa484d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e828a118-3a58-4f33-894e-5b4ef4379ca1}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -961,8 +1039,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{838f1b2b-f8b9-48c2-b462-8f0009504aec}">
-  <dimension ref="A1:I76"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f313652-e00a-4353-9301-443c2dc22fc6}">
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1622,25 +1700,25 @@
         <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1651,25 +1729,25 @@
         <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1677,25 +1755,25 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
         <v>19</v>
@@ -1706,28 +1784,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
         <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1735,22 +1813,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H27" t="s">
         <v>24</v>
@@ -1764,22 +1842,22 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
         <v>24</v>
@@ -1793,28 +1871,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
         <v>24</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1822,28 +1900,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I30" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -1851,25 +1929,25 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" t="s">
         <v>87</v>
       </c>
-      <c r="E31" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" t="s">
-        <v>88</v>
-      </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I31" t="s">
         <v>30</v>
@@ -1880,25 +1958,25 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" t="s">
         <v>90</v>
       </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" t="s">
-        <v>85</v>
-      </c>
       <c r="H32" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>49</v>
@@ -1909,25 +1987,25 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
         <v>30</v>
@@ -1938,25 +2016,25 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" t="s">
         <v>90</v>
       </c>
-      <c r="C34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" t="s">
-        <v>97</v>
-      </c>
       <c r="H34" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -1967,22 +2045,22 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="G35" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="H35" t="s">
         <v>24</v>
@@ -1996,28 +2074,28 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="H36" t="s">
         <v>24</v>
       </c>
       <c r="I36" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2025,22 +2103,22 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H37" t="s">
         <v>24</v>
@@ -2054,25 +2132,25 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I38" t="s">
         <v>30</v>
@@ -2083,22 +2161,22 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D39" t="s">
         <v>104</v>
       </c>
       <c r="E39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s">
         <v>105</v>
-      </c>
-      <c r="F39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G39" t="s">
-        <v>106</v>
       </c>
       <c r="H39" t="s">
         <v>24</v>
@@ -2112,28 +2190,28 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2141,28 +2219,28 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
         <v>108</v>
       </c>
-      <c r="C41" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" t="s">
-        <v>87</v>
-      </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H41" t="s">
         <v>24</v>
       </c>
       <c r="I41" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2170,13 +2248,13 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
         <v>52</v>
       </c>
       <c r="D42" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -2185,13 +2263,13 @@
         <v>54</v>
       </c>
       <c r="G42" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H42" t="s">
         <v>24</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2199,170 +2277,170 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H43" t="s">
         <v>24</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F44" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>113</v>
+      </c>
+      <c r="C45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" t="s">
         <v>111</v>
       </c>
-      <c r="B45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
-        <v>116</v>
-      </c>
-      <c r="E45" t="s">
-        <v>117</v>
-      </c>
-      <c r="F45" t="s">
-        <v>118</v>
-      </c>
-      <c r="G45" t="s">
-        <v>19</v>
-      </c>
       <c r="H45" t="s">
         <v>24</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G46" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H46" t="s">
         <v>24</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" t="s">
         <v>119</v>
       </c>
-      <c r="E47" t="s">
-        <v>73</v>
-      </c>
-      <c r="F47" t="s">
-        <v>120</v>
-      </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" t="s">
         <v>122</v>
       </c>
-      <c r="D48" t="s">
+      <c r="F48" t="s">
         <v>123</v>
       </c>
-      <c r="E48" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2370,57 +2448,57 @@
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
         <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s">
         <v>24</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D50" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" t="s">
         <v>125</v>
       </c>
-      <c r="E50" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" t="s">
-        <v>92</v>
-      </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -2428,28 +2506,28 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="F51" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="G51" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
@@ -2457,28 +2535,28 @@
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E52" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -2486,28 +2564,28 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
         <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="H53" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -2515,57 +2593,57 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
         <v>44</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s">
         <v>24</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E55" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -2573,28 +2651,28 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="F56" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H56" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -2602,54 +2680,54 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="F57" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="H57" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
         <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2660,260 +2738,260 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s">
         <v>24</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D60" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="F61" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G61" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="H61" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="E63" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="H63" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="H65" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F66" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G66" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="H66" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="E67" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="F67" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G67" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="H67" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -2921,57 +2999,57 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s">
         <v>119</v>
       </c>
-      <c r="E68" t="s">
-        <v>124</v>
-      </c>
-      <c r="F68" t="s">
-        <v>60</v>
-      </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="E69" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" t="s">
+        <v>125</v>
+      </c>
+      <c r="G69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" t="s">
         <v>126</v>
-      </c>
-      <c r="F69" t="s">
-        <v>118</v>
-      </c>
-      <c r="G69" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" t="s">
-        <v>24</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
@@ -2979,141 +3057,141 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D70" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="F70" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="G70" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H70" t="s">
         <v>24</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="F71" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="G71" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D72" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E72" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="F72" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="G72" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="H72" t="s">
         <v>24</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="G73" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E74" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="G74" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="H74" t="s">
         <v>24</v>
@@ -3124,28 +3202,28 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
         <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E75" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="F75" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G75" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="H75" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -3153,31 +3231,234 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
         <v>57</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="E76" t="s">
         <v>59</v>
       </c>
       <c r="F76" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="G76" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="H76" t="s">
         <v>24</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15">
+      <c r="A77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" t="s">
+        <v>93</v>
+      </c>
+      <c r="G77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15">
+      <c r="A78" t="s">
+        <v>117</v>
+      </c>
+      <c r="B78" t="s">
+        <v>107</v>
+      </c>
+      <c r="C78" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" t="s">
+        <v>121</v>
+      </c>
+      <c r="E78" t="s">
+        <v>149</v>
+      </c>
+      <c r="F78" t="s">
+        <v>123</v>
+      </c>
+      <c r="G78" t="s">
+        <v>140</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15">
+      <c r="A79" t="s">
+        <v>117</v>
+      </c>
+      <c r="B79" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" t="s">
+        <v>150</v>
+      </c>
+      <c r="D79" t="s">
+        <v>151</v>
+      </c>
+      <c r="E79" t="s">
+        <v>59</v>
+      </c>
+      <c r="F79" t="s">
+        <v>152</v>
+      </c>
+      <c r="G79" t="s">
+        <v>153</v>
+      </c>
+      <c r="H79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15">
+      <c r="A80" t="s">
+        <v>117</v>
+      </c>
+      <c r="B80" t="s">
+        <v>112</v>
+      </c>
+      <c r="C80" t="s">
+        <v>74</v>
+      </c>
+      <c r="D80" t="s">
+        <v>116</v>
+      </c>
+      <c r="E80" t="s">
+        <v>141</v>
+      </c>
+      <c r="F80" t="s">
+        <v>125</v>
+      </c>
+      <c r="G80" t="s">
+        <v>140</v>
+      </c>
+      <c r="H80" t="s">
+        <v>126</v>
+      </c>
+      <c r="I80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15">
+      <c r="A81" t="s">
+        <v>117</v>
+      </c>
+      <c r="B81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" t="s">
+        <v>36</v>
+      </c>
+      <c r="E81" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" t="s">
+        <v>155</v>
+      </c>
+      <c r="H81" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15">
+      <c r="A82" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" t="s">
+        <v>112</v>
+      </c>
+      <c r="C82" t="s">
+        <v>156</v>
+      </c>
+      <c r="D82" t="s">
+        <v>157</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" t="s">
+        <v>140</v>
+      </c>
+      <c r="H82" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15">
+      <c r="A83" t="s">
+        <v>117</v>
+      </c>
+      <c r="B83" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" t="s">
+        <v>150</v>
+      </c>
+      <c r="D83" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" t="s">
+        <v>152</v>
+      </c>
+      <c r="G83" t="s">
+        <v>153</v>
+      </c>
+      <c r="H83" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3188,8 +3469,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5d8667d0-df0a-4206-a8ae-cd66c9d63208}">
-  <dimension ref="A1:F29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5c8f8fe0-7300-4449-a3ce-a8e8dfa8e991}">
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3205,13 +3486,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3222,16 +3503,16 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -3242,16 +3523,16 @@
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -3262,16 +3543,16 @@
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -3282,16 +3563,16 @@
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -3302,16 +3583,16 @@
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -3322,16 +3603,16 @@
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -3342,16 +3623,16 @@
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -3362,16 +3643,16 @@
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -3382,16 +3663,16 @@
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -3402,16 +3683,16 @@
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -3422,16 +3703,16 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -3445,13 +3726,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
@@ -3465,13 +3746,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -3485,16 +3766,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -3505,16 +3786,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -3525,13 +3806,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C17" t="s">
         <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E17" t="s">
         <v>43</v>
@@ -3545,16 +3826,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E18" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
         <v>24</v>
@@ -3562,76 +3843,76 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -3642,16 +3923,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -3662,122 +3943,142 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" t="s">
         <v>74</v>
       </c>
-      <c r="D29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>121</v>
+      <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -9,23 +9,25 @@
   <sheets>
     <sheet name="Opis parametrów" sheetId="2" r:id="rId2"/>
     <sheet name="Oddziały" sheetId="3" r:id="rId3"/>
-    <sheet name="Dyżury" sheetId="4" r:id="rId4"/>
+    <sheet name="Dzienniki zajeć innych" sheetId="4" r:id="rId4"/>
+    <sheet name="Dyżury" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Oddziały!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dyżury!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dzienniki zajeć innych'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Dyżury!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="174">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 04.05.2026 (pon.) - 10.05.2026 (niedz.)</t>
+    <t>Okres: 11.05.2026 (pon.) - 17.05.2026 (niedz.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -55,517 +57,490 @@
     <t>Forma płatności</t>
   </si>
   <si>
-    <t>07.05.2026</t>
+    <t>11.05.2026</t>
   </si>
   <si>
     <t>1, 08:00-08:45</t>
   </si>
   <si>
-    <t>Antoszewska Joanna</t>
-  </si>
-  <si>
-    <t>4TFB|dz2</t>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Uczniowie przychodzą później</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>Organizacja sprzedaży</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>2, 08:50-09:35</t>
+  </si>
+  <si>
+    <t>Nowak Magdalena</t>
+  </si>
+  <si>
+    <t>1CA</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Filipiak Wiesław</t>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>Czukiewska Bożena</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>Informatyka</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
   </si>
   <si>
     <t>Wychowanie fizyczne</t>
   </si>
   <si>
-    <t>sg6</t>
-  </si>
-  <si>
-    <t>Uczniowie przychodzą później</t>
-  </si>
-  <si>
-    <t>matura</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>1TFB|JA1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Jaworska Edyta</t>
-  </si>
-  <si>
-    <t>3TFA|JA1</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
-  </si>
-  <si>
-    <t>prf2</t>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>matura ustna</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Marketing w działalności handlowej</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>Symulacyjna firma handlowa</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>Pracownia sprzedaży</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>Jastrzębska-Majtyka Agnieszka</t>
   </si>
   <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2, 08:50-09:35</t>
-  </si>
-  <si>
-    <t>3TH|JA2</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>Budowa i naprawa pojazdów samochodowych</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Ramut Marian</t>
+  </si>
+  <si>
+    <t>Obsługa klienta</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
   </si>
   <si>
     <t>Najwer Maciej</t>
   </si>
   <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>1TH|JA2</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>Historia i teraźniejszość</t>
-  </si>
-  <si>
-    <t>Nestoruk Lidia</t>
-  </si>
-  <si>
-    <t>4TFB|CH</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>4TH|CH</t>
-  </si>
-  <si>
-    <t>Nowak Magdalena</t>
+    <t>2TFA|JA1</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
   </si>
   <si>
     <t>1FC</t>
   </si>
   <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Filipiak Wiesław</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Taszycka Magdalena</t>
-  </si>
-  <si>
-    <t>1WB|JN1</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>Mikołajczak Sylwia</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>matura 2026</t>
-  </si>
-  <si>
-    <t>2FA|JA2</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>Podstawy fryzjerstwa</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>1WA</t>
-  </si>
-  <si>
-    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>prF3</t>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>1FC|JA2</t>
+  </si>
+  <si>
+    <t>1CB|JA2</t>
+  </si>
+  <si>
+    <t>1S|JA2</t>
+  </si>
+  <si>
+    <t>Godzina</t>
+  </si>
+  <si>
+    <t>Nauczyciel</t>
+  </si>
+  <si>
+    <t>Dziennik zajęć innych</t>
+  </si>
+  <si>
+    <t>Opis zajęć</t>
+  </si>
+  <si>
+    <t>08:50-10:20</t>
+  </si>
+  <si>
+    <t>Krystian Pietrowski - 3M - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>09:40-10:25</t>
+  </si>
+  <si>
+    <t>Mateusz Wisiński - 1TH - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>Przedmioty zawodowe</t>
+  </si>
+  <si>
+    <t>10:00-12:00</t>
+  </si>
+  <si>
+    <t>Kaszak Maria</t>
+  </si>
+  <si>
+    <t>T - współorganizowanie kształcenia uczniów</t>
+  </si>
+  <si>
+    <t>Współorganizowanie dla uczniów z orzeczeniem o potrzebie kształcenia specjalnego ze względu na diagnozę autyzmu.</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>11:25-12:10</t>
+  </si>
+  <si>
+    <t>Małgorzata Wiśniewska - 3CA - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>12:00-17:00</t>
+  </si>
+  <si>
+    <t>dziennik pedagoga specjalnego - Maria Kaszak</t>
+  </si>
+  <si>
+    <t>dyżur pedagoga specjalnego</t>
+  </si>
+  <si>
+    <t>14:55-15:40</t>
+  </si>
+  <si>
+    <t>przedmioty zawodowe</t>
+  </si>
+  <si>
+    <t>16:35-17:20</t>
+  </si>
+  <si>
+    <t>Katarzyna Majewska -  2S - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>Jęezyk polski</t>
+  </si>
+  <si>
+    <t>Miejsce dyżuru</t>
+  </si>
+  <si>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>Filiczak Agnieszka</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
+  </si>
+  <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>13:10-13:15</t>
   </si>
   <si>
     <t>Leńczowska Iwona</t>
   </si>
   <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>Biezmienow Małgorzata</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>lekcja otwarta - awans zawodowy</t>
-  </si>
-  <si>
-    <t>1S|JA2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>1S|JA1</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>1TFA</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>3TH</t>
-  </si>
-  <si>
-    <t>Fizyka</t>
-  </si>
-  <si>
-    <t>Biczysko Wojciech</t>
-  </si>
-  <si>
-    <t>Pietrycha Małgorzata</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>matura w ZSL</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>08.05.2026</t>
-  </si>
-  <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>egzaminy zawodowe - delegowanie Bolesławiec</t>
-  </si>
-  <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>p. Danielewski, zajęcia z wychowawcą za lekcję 1</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>Projektowanie fryzur</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
-  </si>
-  <si>
-    <t>1K|JA1</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
-    <t>1K|JA2</t>
-  </si>
-  <si>
-    <t>1WA|JN1</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>Wakat2 matematyka</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>Godzina</t>
-  </si>
-  <si>
-    <t>Nauczyciel</t>
-  </si>
-  <si>
-    <t>Miejsce dyżuru</t>
-  </si>
-  <si>
-    <t>04.05.2026</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
   </si>
   <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>17:20-17:25</t>
+  </si>
+  <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
     <t>parter</t>
   </si>
   <si>
-    <t>05.05.2026</t>
-  </si>
-  <si>
-    <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
     <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>06.05.2026</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
-  </si>
-  <si>
-    <t>08:45-08:50</t>
-  </si>
-  <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
-    <t>Dalach Krystyna</t>
-  </si>
-  <si>
-    <t>11:20-11:25</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
-    <t>bramka wejściowa</t>
-  </si>
-  <si>
-    <t>13:10-13:15</t>
   </si>
   <si>
     <t>14:50-14:55</t>
@@ -1018,7 +993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e828a118-3a58-4f33-894e-5b4ef4379ca1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{728d5060-ea1b-4af7-90af-e59786dd1e8f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1039,18 +1014,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{4f313652-e00a-4353-9301-443c2dc22fc6}">
-  <dimension ref="A1:I83"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ed3fbbd3-004b-4111-adbf-8a2f711f21c9}">
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="13.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="43.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="12.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1135,7 +1110,7 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -1146,7 +1121,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -1164,7 +1139,7 @@
         <v>29</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>30</v>
@@ -1175,25 +1150,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1204,28 +1179,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1233,28 +1208,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1262,25 +1237,25 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1291,25 +1266,25 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>30</v>
@@ -1320,25 +1295,25 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
@@ -1349,16 +1324,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -1378,28 +1353,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1407,28 +1382,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1436,28 +1411,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
         <v>50</v>
       </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" t="s">
-        <v>24</v>
-      </c>
       <c r="I14" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1465,28 +1440,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1494,28 +1469,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1523,28 +1498,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1552,25 +1527,25 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
         <v>30</v>
@@ -1581,22 +1556,22 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
         <v>66</v>
       </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
@@ -1610,28 +1585,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1639,25 +1614,25 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
         <v>30</v>
@@ -1668,25 +1643,25 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
         <v>30</v>
@@ -1697,28 +1672,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1726,28 +1701,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
         <v>65</v>
       </c>
-      <c r="C24" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1755,28 +1730,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1784,28 +1759,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1813,25 +1788,25 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
         <v>30</v>
@@ -1842,28 +1817,28 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -1871,28 +1846,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -1900,25 +1875,25 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G30" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
         <v>30</v>
@@ -1929,25 +1904,25 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
         <v>30</v>
@@ -1958,28 +1933,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -1987,65 +1962,65 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -2060,387 +2035,387 @@
         <v>28</v>
       </c>
       <c r="G35" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E41" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2448,57 +2423,57 @@
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G49" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="H49" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="F50" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H50" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -2506,25 +2481,25 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E51" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -2535,28 +2510,28 @@
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" t="s">
         <v>117</v>
       </c>
-      <c r="B52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" t="s">
-        <v>121</v>
-      </c>
       <c r="E52" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
@@ -2564,28 +2539,28 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E53" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="G53" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
@@ -2593,57 +2568,57 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D55" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="F55" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H55" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
@@ -2651,28 +2626,28 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="E56" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="H56" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
@@ -2680,54 +2655,54 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="E57" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="F57" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E58" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2738,727 +2713,31 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="G59" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="H59" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15">
-      <c r="A60" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" t="s">
-        <v>135</v>
-      </c>
-      <c r="E60" t="s">
-        <v>46</v>
-      </c>
-      <c r="F60" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60" t="s">
-        <v>90</v>
-      </c>
-      <c r="H60" t="s">
-        <v>126</v>
-      </c>
-      <c r="I60" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15">
-      <c r="A61" t="s">
-        <v>117</v>
-      </c>
-      <c r="B61" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" t="s">
-        <v>116</v>
-      </c>
-      <c r="E61" t="s">
-        <v>136</v>
-      </c>
-      <c r="F61" t="s">
-        <v>125</v>
-      </c>
-      <c r="G61" t="s">
-        <v>137</v>
-      </c>
-      <c r="H61" t="s">
-        <v>18</v>
-      </c>
-      <c r="I61" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15">
-      <c r="A62" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-      <c r="E62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" t="s">
-        <v>87</v>
-      </c>
-      <c r="G62" t="s">
-        <v>134</v>
-      </c>
-      <c r="H62" t="s">
-        <v>24</v>
-      </c>
-      <c r="I62" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15">
-      <c r="A63" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" t="s">
-        <v>129</v>
-      </c>
-      <c r="F63" t="s">
-        <v>97</v>
-      </c>
-      <c r="G63" t="s">
-        <v>138</v>
-      </c>
-      <c r="H63" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15">
-      <c r="A64" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" t="s">
-        <v>80</v>
-      </c>
-      <c r="C64" t="s">
-        <v>25</v>
-      </c>
-      <c r="D64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s">
-        <v>119</v>
-      </c>
-      <c r="G64" t="s">
-        <v>94</v>
-      </c>
-      <c r="H64" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15">
-      <c r="A65" t="s">
-        <v>117</v>
-      </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>127</v>
-      </c>
-      <c r="D65" t="s">
-        <v>116</v>
-      </c>
-      <c r="E65" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65" t="s">
-        <v>61</v>
-      </c>
-      <c r="H65" t="s">
-        <v>18</v>
-      </c>
-      <c r="I65" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15">
-      <c r="A66" t="s">
-        <v>117</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" t="s">
-        <v>82</v>
-      </c>
-      <c r="E66" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" t="s">
-        <v>139</v>
-      </c>
-      <c r="G66" t="s">
-        <v>134</v>
-      </c>
-      <c r="H66" t="s">
-        <v>24</v>
-      </c>
-      <c r="I66" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15">
-      <c r="A67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" t="s">
-        <v>96</v>
-      </c>
-      <c r="D67" t="s">
-        <v>121</v>
-      </c>
-      <c r="E67" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" t="s">
-        <v>97</v>
-      </c>
-      <c r="G67" t="s">
-        <v>140</v>
-      </c>
-      <c r="H67" t="s">
-        <v>18</v>
-      </c>
-      <c r="I67" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15">
-      <c r="A68" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" t="s">
-        <v>95</v>
-      </c>
-      <c r="C68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D68" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" t="s">
-        <v>119</v>
-      </c>
-      <c r="G68" t="s">
-        <v>94</v>
-      </c>
-      <c r="H68" t="s">
-        <v>24</v>
-      </c>
-      <c r="I68" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15">
-      <c r="A69" t="s">
-        <v>117</v>
-      </c>
-      <c r="B69" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" t="s">
-        <v>116</v>
-      </c>
-      <c r="E69" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" t="s">
-        <v>125</v>
-      </c>
-      <c r="G69" t="s">
-        <v>140</v>
-      </c>
-      <c r="H69" t="s">
-        <v>126</v>
-      </c>
-      <c r="I69" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15">
-      <c r="A70" t="s">
-        <v>117</v>
-      </c>
-      <c r="B70" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" t="s">
-        <v>58</v>
-      </c>
-      <c r="E70" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-      <c r="G70" t="s">
-        <v>61</v>
-      </c>
-      <c r="H70" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15">
-      <c r="A71" t="s">
-        <v>117</v>
-      </c>
-      <c r="B71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" t="s">
-        <v>127</v>
-      </c>
-      <c r="D71" t="s">
-        <v>124</v>
-      </c>
-      <c r="E71" t="s">
-        <v>73</v>
-      </c>
-      <c r="F71" t="s">
-        <v>93</v>
-      </c>
-      <c r="G71" t="s">
-        <v>91</v>
-      </c>
-      <c r="H71" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="15">
-      <c r="A72" t="s">
-        <v>117</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>120</v>
-      </c>
-      <c r="D72" t="s">
-        <v>142</v>
-      </c>
-      <c r="E72" t="s">
-        <v>143</v>
-      </c>
-      <c r="F72" t="s">
-        <v>144</v>
-      </c>
-      <c r="G72" t="s">
-        <v>145</v>
-      </c>
-      <c r="H72" t="s">
-        <v>24</v>
-      </c>
-      <c r="I72" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="15">
-      <c r="A73" t="s">
-        <v>117</v>
-      </c>
-      <c r="B73" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" t="s">
-        <v>146</v>
-      </c>
-      <c r="E73" t="s">
-        <v>143</v>
-      </c>
-      <c r="F73" t="s">
-        <v>144</v>
-      </c>
-      <c r="G73" t="s">
-        <v>145</v>
-      </c>
-      <c r="H73" t="s">
-        <v>24</v>
-      </c>
-      <c r="I73" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15">
-      <c r="A74" t="s">
-        <v>117</v>
-      </c>
-      <c r="B74" t="s">
-        <v>107</v>
-      </c>
-      <c r="C74" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" t="s">
-        <v>147</v>
-      </c>
-      <c r="E74" t="s">
-        <v>22</v>
-      </c>
-      <c r="F74" t="s">
-        <v>148</v>
-      </c>
-      <c r="G74" t="s">
-        <v>140</v>
-      </c>
-      <c r="H74" t="s">
-        <v>24</v>
-      </c>
-      <c r="I74" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15">
-      <c r="A75" t="s">
-        <v>117</v>
-      </c>
-      <c r="B75" t="s">
-        <v>107</v>
-      </c>
-      <c r="C75" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75" t="s">
-        <v>116</v>
-      </c>
-      <c r="E75" t="s">
-        <v>141</v>
-      </c>
-      <c r="F75" t="s">
-        <v>125</v>
-      </c>
-      <c r="G75" t="s">
-        <v>140</v>
-      </c>
-      <c r="H75" t="s">
-        <v>126</v>
-      </c>
-      <c r="I75" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15">
-      <c r="A76" t="s">
-        <v>117</v>
-      </c>
-      <c r="B76" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" t="s">
-        <v>130</v>
-      </c>
-      <c r="E76" t="s">
-        <v>59</v>
-      </c>
-      <c r="F76" t="s">
-        <v>60</v>
-      </c>
-      <c r="G76" t="s">
-        <v>61</v>
-      </c>
-      <c r="H76" t="s">
-        <v>24</v>
-      </c>
-      <c r="I76" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="15">
-      <c r="A77" t="s">
-        <v>117</v>
-      </c>
-      <c r="B77" t="s">
-        <v>107</v>
-      </c>
-      <c r="C77" t="s">
-        <v>127</v>
-      </c>
-      <c r="D77" t="s">
-        <v>36</v>
-      </c>
-      <c r="E77" t="s">
-        <v>73</v>
-      </c>
-      <c r="F77" t="s">
-        <v>93</v>
-      </c>
-      <c r="G77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H77" t="s">
-        <v>18</v>
-      </c>
-      <c r="I77" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="15">
-      <c r="A78" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" t="s">
-        <v>107</v>
-      </c>
-      <c r="C78" t="s">
-        <v>120</v>
-      </c>
-      <c r="D78" t="s">
-        <v>121</v>
-      </c>
-      <c r="E78" t="s">
-        <v>149</v>
-      </c>
-      <c r="F78" t="s">
-        <v>123</v>
-      </c>
-      <c r="G78" t="s">
-        <v>140</v>
-      </c>
-      <c r="H78" t="s">
-        <v>24</v>
-      </c>
-      <c r="I78" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="15">
-      <c r="A79" t="s">
-        <v>117</v>
-      </c>
-      <c r="B79" t="s">
-        <v>107</v>
-      </c>
-      <c r="C79" t="s">
-        <v>150</v>
-      </c>
-      <c r="D79" t="s">
-        <v>151</v>
-      </c>
-      <c r="E79" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" t="s">
-        <v>152</v>
-      </c>
-      <c r="G79" t="s">
-        <v>153</v>
-      </c>
-      <c r="H79" t="s">
-        <v>24</v>
-      </c>
-      <c r="I79" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="15">
-      <c r="A80" t="s">
-        <v>117</v>
-      </c>
-      <c r="B80" t="s">
-        <v>112</v>
-      </c>
-      <c r="C80" t="s">
-        <v>74</v>
-      </c>
-      <c r="D80" t="s">
-        <v>116</v>
-      </c>
-      <c r="E80" t="s">
-        <v>141</v>
-      </c>
-      <c r="F80" t="s">
-        <v>125</v>
-      </c>
-      <c r="G80" t="s">
-        <v>140</v>
-      </c>
-      <c r="H80" t="s">
-        <v>126</v>
-      </c>
-      <c r="I80" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="15">
-      <c r="A81" t="s">
-        <v>117</v>
-      </c>
-      <c r="B81" t="s">
-        <v>112</v>
-      </c>
-      <c r="C81" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" t="s">
-        <v>36</v>
-      </c>
-      <c r="E81" t="s">
-        <v>154</v>
-      </c>
-      <c r="F81" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" t="s">
-        <v>155</v>
-      </c>
-      <c r="H81" t="s">
-        <v>24</v>
-      </c>
-      <c r="I81" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="15">
-      <c r="A82" t="s">
-        <v>117</v>
-      </c>
-      <c r="B82" t="s">
-        <v>112</v>
-      </c>
-      <c r="C82" t="s">
-        <v>156</v>
-      </c>
-      <c r="D82" t="s">
-        <v>157</v>
-      </c>
-      <c r="E82" t="s">
-        <v>22</v>
-      </c>
-      <c r="F82" t="s">
-        <v>23</v>
-      </c>
-      <c r="G82" t="s">
-        <v>140</v>
-      </c>
-      <c r="H82" t="s">
-        <v>24</v>
-      </c>
-      <c r="I82" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="15">
-      <c r="A83" t="s">
-        <v>117</v>
-      </c>
-      <c r="B83" t="s">
-        <v>112</v>
-      </c>
-      <c r="C83" t="s">
-        <v>150</v>
-      </c>
-      <c r="D83" t="s">
-        <v>151</v>
-      </c>
-      <c r="E83" t="s">
-        <v>59</v>
-      </c>
-      <c r="F83" t="s">
-        <v>152</v>
-      </c>
-      <c r="G83" t="s">
-        <v>153</v>
-      </c>
-      <c r="H83" t="s">
-        <v>24</v>
-      </c>
-      <c r="I83" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3469,16 +2748,329 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5c8f8fe0-7300-4449-a3ce-a8e8dfa8e991}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f897b8ce-001a-413d-ab91-eaee882e3c59}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="17.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="105" customWidth="1"/>
+    <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="56.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{80a72044-a486-4099-8bf3-78095fc19ea4}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="43.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="12.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -3486,13 +3078,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3503,222 +3095,222 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" t="s">
         <v>163</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
@@ -3726,19 +3318,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
@@ -3746,19 +3338,19 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
@@ -3766,16 +3358,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -3783,19 +3375,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -3803,19 +3395,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -3823,76 +3415,76 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -3903,182 +3495,22 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15">
-      <c r="A23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" t="s">
-        <v>177</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15">
-      <c r="A24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15">
-      <c r="A25" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15">
-      <c r="A27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15">
-      <c r="A28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15">
-      <c r="A29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" t="s">
-        <v>169</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>166</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="170">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -126,243 +126,228 @@
     <t>1TH|JA2</t>
   </si>
   <si>
+    <t>Pracownia sprzedaży</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>matura ustna</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>Marketing w działalności handlowej</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>Chemia</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Hudziec Agnieszka</t>
+  </si>
+  <si>
+    <t>Symulacyjna firma handlowa</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Karczmarz, j. angielski za lekcję 2</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>p. Jarek, EDB za lekcję 1</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>Budowa i naprawa pojazdów samochodowych</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Ramut Marian</t>
+  </si>
+  <si>
+    <t>Obsługa klienta</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>2TH</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>2TFA|JA1</t>
+  </si>
+  <si>
     <t>Informatyka</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Taszycka Magdalena</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>matura ustna</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>Marketing w działalności handlowej</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>Chemia</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Hudziec Agnieszka</t>
-  </si>
-  <si>
-    <t>Symulacyjna firma handlowa</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>Stępień Krystyna</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>Pracownia sprzedaży</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>3S</t>
-  </si>
-  <si>
-    <t>Doradztwo zawodowe</t>
-  </si>
-  <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>Budowa i naprawa pojazdów samochodowych</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Ramut Marian</t>
-  </si>
-  <si>
-    <t>Obsługa klienta</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>12.05.2026</t>
-  </si>
-  <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>2TH</t>
-  </si>
-  <si>
-    <t>13.05.2026</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>2TFA|JA1</t>
-  </si>
-  <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
     <t>2CA</t>
   </si>
   <si>
@@ -492,6 +477,12 @@
     <t>Filiczak Agnieszka</t>
   </si>
   <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
@@ -532,9 +523,6 @@
   </si>
   <si>
     <t>17:20-17:25</t>
-  </si>
-  <si>
-    <t>08:45-08:50</t>
   </si>
   <si>
     <t>parter</t>
@@ -993,7 +981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{728d5060-ea1b-4af7-90af-e59786dd1e8f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{551f0f92-f846-4c78-a099-1e2b21f0704a}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1014,8 +1002,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ed3fbbd3-004b-4111-adbf-8a2f711f21c9}">
-  <dimension ref="A1:I59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{70c9ba4c-00e5-4de7-ac86-e2fa4987131c}">
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1025,7 +1013,7 @@
     <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="12.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1191,16 +1179,16 @@
         <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1214,22 +1202,22 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1266,7 +1254,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -1275,19 +1263,19 @@
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1295,25 +1283,25 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" t="s">
-        <v>50</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
@@ -1324,16 +1312,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -1353,22 +1341,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -1382,7 +1370,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -1391,19 +1379,19 @@
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1411,25 +1399,25 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
@@ -1440,22 +1428,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -1469,22 +1457,22 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -1498,7 +1486,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
@@ -1507,19 +1495,19 @@
         <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I17" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1527,25 +1515,25 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I18" t="s">
         <v>30</v>
@@ -1556,28 +1544,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1585,22 +1573,22 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H20" t="s">
         <v>18</v>
@@ -1614,22 +1602,22 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
         <v>18</v>
@@ -1643,7 +1631,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
@@ -1652,19 +1640,19 @@
         <v>33</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1672,22 +1660,22 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s">
         <v>18</v>
@@ -1701,22 +1689,22 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
@@ -1730,22 +1718,22 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
         <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
@@ -1759,10 +1747,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
@@ -1771,7 +1759,7 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -1788,22 +1776,22 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
@@ -1817,22 +1805,22 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
@@ -1846,22 +1834,22 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
@@ -1875,22 +1863,22 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
@@ -1904,28 +1892,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -1933,28 +1921,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="H32" t="s">
         <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -1962,22 +1950,22 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
@@ -1988,25 +1976,25 @@
     </row>
     <row r="34" spans="1:9" ht="15">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
@@ -2017,25 +2005,25 @@
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
@@ -2046,16 +2034,16 @@
     </row>
     <row r="36" spans="1:9" ht="15">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -2075,16 +2063,16 @@
     </row>
     <row r="37" spans="1:9" ht="15">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -2104,16 +2092,16 @@
     </row>
     <row r="38" spans="1:9" ht="15">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -2133,16 +2121,16 @@
     </row>
     <row r="39" spans="1:9" ht="15">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C39" t="s">
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -2162,25 +2150,25 @@
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
@@ -2191,16 +2179,16 @@
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2220,25 +2208,25 @@
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="F42" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
@@ -2249,16 +2237,16 @@
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2278,25 +2266,25 @@
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
         <v>109</v>
       </c>
-      <c r="B44" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" t="s">
-        <v>115</v>
-      </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2307,16 +2295,16 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2336,16 +2324,16 @@
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2365,16 +2353,16 @@
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2394,16 +2382,16 @@
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2423,25 +2411,25 @@
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
@@ -2452,25 +2440,25 @@
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="F50" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
@@ -2481,25 +2469,25 @@
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F51" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="G51" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
@@ -2510,25 +2498,25 @@
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="F52" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
@@ -2539,25 +2527,25 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" t="s">
+        <v>117</v>
+      </c>
+      <c r="D53" t="s">
         <v>118</v>
       </c>
-      <c r="B53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" t="s">
-        <v>115</v>
-      </c>
       <c r="E53" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F53" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2568,16 +2556,16 @@
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2597,25 +2585,25 @@
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D55" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" t="s">
         <v>115</v>
       </c>
-      <c r="E55" t="s">
-        <v>121</v>
-      </c>
-      <c r="F55" t="s">
-        <v>120</v>
-      </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
@@ -2626,16 +2614,16 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2655,25 +2643,25 @@
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
@@ -2684,25 +2672,25 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2713,30 +2701,88 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="F59" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G59" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" t="s">
+        <v>120</v>
+      </c>
+      <c r="E60" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
+      <c r="A61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" t="s">
+        <v>65</v>
+      </c>
+      <c r="H61" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2748,7 +2794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f897b8ce-001a-413d-ab91-eaee882e3c59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8bb464ea-0220-4d5f-b1ed-4e3dd856b841}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2768,16 +2814,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -2797,22 +2843,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -2826,22 +2872,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -2855,22 +2901,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -2884,22 +2930,22 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -2913,22 +2959,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -2942,22 +2988,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -2971,22 +3017,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -3000,22 +3046,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -3026,25 +3072,25 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -3061,13 +3107,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{80a72044-a486-4099-8bf3-78095fc19ea4}">
-  <dimension ref="A1:F22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e2cd59f7-7772-4c72-adb5-ae4fbb312891}">
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="12.8571428571429" customWidth="1"/>
@@ -3078,13 +3124,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3098,13 +3144,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -3118,16 +3164,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3138,16 +3184,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -3158,16 +3204,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -3178,16 +3224,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -3198,16 +3244,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3218,16 +3264,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3238,19 +3284,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
@@ -3258,19 +3304,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
@@ -3278,16 +3324,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3298,16 +3344,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -3318,16 +3364,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -3338,16 +3384,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>168</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -3358,16 +3404,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -3375,19 +3421,19 @@
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -3395,16 +3441,16 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -3415,16 +3461,16 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -3435,16 +3481,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -3455,16 +3501,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -3475,16 +3521,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -3495,21 +3541,41 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
       </c>
       <c r="F22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="197">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -261,7 +261,7 @@
     <t>1TH</t>
   </si>
   <si>
-    <t>40</t>
+    <t>30</t>
   </si>
   <si>
     <t>Kończyńska Małgorzata</t>
@@ -327,18 +327,78 @@
     <t>12.05.2026</t>
   </si>
   <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
     <t>2CB</t>
   </si>
   <si>
+    <t>1TFB|JA2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>1CA|JA1</t>
+  </si>
+  <si>
     <t>3FA</t>
   </si>
   <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
     <t>2TH</t>
   </si>
   <si>
     <t>13.05.2026</t>
   </si>
   <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
     <t>Najwer Maciej</t>
   </si>
   <si>
@@ -351,12 +411,24 @@
     <t>2CA</t>
   </si>
   <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
     <t>4TFB</t>
   </si>
   <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
     <t>14.05.2026</t>
   </si>
   <si>
@@ -378,7 +450,13 @@
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
-    <t>1WA|JN2</t>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>1FC|JA2</t>
@@ -480,9 +558,6 @@
     <t>08:45-08:50</t>
   </si>
   <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
     <t>09:35-09:40</t>
   </si>
   <si>
@@ -523,6 +598,12 @@
   </si>
   <si>
     <t>17:20-17:25</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
   </si>
   <si>
     <t>parter</t>
@@ -981,7 +1062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{551f0f92-f846-4c78-a099-1e2b21f0704a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7ceaa7f1-38ec-4126-bf9b-15760bf391e8}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1002,13 +1083,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{70c9ba4c-00e5-4de7-ac86-e2fa4987131c}">
-  <dimension ref="A1:I61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bdb85dd4-cd08-44cf-a54d-c9a7bfbb1365}">
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="22.5714285714286" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
@@ -2037,28 +2118,28 @@
         <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2066,28 +2147,28 @@
         <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2095,28 +2176,28 @@
         <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2124,129 +2205,129 @@
         <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s">
         <v>103</v>
-      </c>
-      <c r="E39" t="s">
-        <v>27</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s">
         <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="H40" t="s">
         <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="H41" t="s">
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G42" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H42" t="s">
         <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2255,36 +2336,36 @@
         <v>28</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H44" t="s">
         <v>18</v>
@@ -2295,16 +2376,16 @@
     </row>
     <row r="45" spans="1:9" ht="15">
       <c r="A45" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2313,56 +2394,56 @@
         <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H45" t="s">
         <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H46" t="s">
         <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
       <c r="A47" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2371,27 +2452,27 @@
         <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="H47" t="s">
         <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2400,172 +2481,172 @@
         <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="H48" t="s">
         <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
       <c r="A49" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" t="s">
         <v>103</v>
-      </c>
-      <c r="E49" t="s">
-        <v>27</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
       <c r="A50" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B50" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s">
         <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F51" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="G51" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s">
         <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E52" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="F52" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" t="s">
         <v>118</v>
       </c>
-      <c r="E53" t="s">
-        <v>107</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" t="s">
-        <v>65</v>
-      </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2574,33 +2655,33 @@
         <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E55" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="G55" t="s">
         <v>65</v>
@@ -2614,16 +2695,16 @@
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s">
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2632,33 +2713,33 @@
         <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E57" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="G57" t="s">
         <v>65</v>
@@ -2672,16 +2753,16 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2690,99 +2771,592 @@
         <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E59" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E60" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="G60" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15">
+      <c r="A63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" t="s">
+        <v>118</v>
+      </c>
+      <c r="H63" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15">
+      <c r="A64" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>129</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" t="s">
+        <v>118</v>
+      </c>
+      <c r="H64" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15">
+      <c r="A65" t="s">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" t="s">
+        <v>43</v>
+      </c>
+      <c r="F65" t="s">
+        <v>139</v>
+      </c>
+      <c r="G65" t="s">
+        <v>65</v>
+      </c>
+      <c r="H65" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15">
+      <c r="A66" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" t="s">
+        <v>129</v>
+      </c>
+      <c r="E66" t="s">
+        <v>140</v>
+      </c>
+      <c r="F66" t="s">
+        <v>139</v>
+      </c>
+      <c r="G66" t="s">
+        <v>65</v>
+      </c>
+      <c r="H66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15">
+      <c r="A67" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" t="s">
+        <v>131</v>
+      </c>
+      <c r="E67" t="s">
+        <v>127</v>
+      </c>
+      <c r="F67" t="s">
+        <v>62</v>
+      </c>
+      <c r="G67" t="s">
+        <v>65</v>
+      </c>
+      <c r="H67" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15">
+      <c r="A68" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>136</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15">
+      <c r="A69" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" t="s">
+        <v>140</v>
+      </c>
+      <c r="F69" t="s">
+        <v>139</v>
+      </c>
+      <c r="G69" t="s">
+        <v>65</v>
+      </c>
+      <c r="H69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>128</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15">
+      <c r="A71" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>144</v>
+      </c>
+      <c r="G71" t="s">
+        <v>141</v>
+      </c>
+      <c r="H71" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15">
+      <c r="A72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72" t="s">
+        <v>129</v>
+      </c>
+      <c r="E72" t="s">
+        <v>140</v>
+      </c>
+      <c r="F72" t="s">
+        <v>139</v>
+      </c>
+      <c r="G72" t="s">
+        <v>65</v>
+      </c>
+      <c r="H72" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15">
+      <c r="A73" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>35</v>
+      </c>
+      <c r="E73" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" t="s">
+        <v>118</v>
+      </c>
+      <c r="H73" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="15">
+      <c r="A74" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" t="s">
+        <v>130</v>
+      </c>
+      <c r="D74" t="s">
+        <v>131</v>
+      </c>
+      <c r="E74" t="s">
+        <v>132</v>
+      </c>
+      <c r="F74" t="s">
+        <v>133</v>
+      </c>
+      <c r="G74" t="s">
+        <v>134</v>
+      </c>
+      <c r="H74" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" t="s">
+        <v>143</v>
+      </c>
+      <c r="E75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" t="s">
+        <v>144</v>
+      </c>
+      <c r="G75" t="s">
+        <v>141</v>
+      </c>
+      <c r="H75" t="s">
+        <v>18</v>
+      </c>
+      <c r="I75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15">
+      <c r="A76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" t="s">
+        <v>141</v>
+      </c>
+      <c r="D76" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" t="s">
+        <v>127</v>
+      </c>
+      <c r="F76" t="s">
+        <v>62</v>
+      </c>
+      <c r="G76" t="s">
+        <v>65</v>
+      </c>
+      <c r="H76" t="s">
+        <v>18</v>
+      </c>
+      <c r="I76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15">
+      <c r="A77" t="s">
+        <v>137</v>
+      </c>
+      <c r="B77" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" t="s">
+        <v>141</v>
+      </c>
+      <c r="D77" t="s">
+        <v>146</v>
+      </c>
+      <c r="E77" t="s">
+        <v>127</v>
+      </c>
+      <c r="F77" t="s">
+        <v>62</v>
+      </c>
+      <c r="G77" t="s">
+        <v>65</v>
+      </c>
+      <c r="H77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15">
+      <c r="A78" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" t="s">
         <v>99</v>
       </c>
-      <c r="C61" t="s">
-        <v>117</v>
-      </c>
-      <c r="D61" t="s">
-        <v>121</v>
-      </c>
-      <c r="E61" t="s">
-        <v>107</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="C78" t="s">
+        <v>141</v>
+      </c>
+      <c r="D78" t="s">
+        <v>147</v>
+      </c>
+      <c r="E78" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" t="s">
         <v>62</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G78" t="s">
         <v>65</v>
       </c>
-      <c r="H61" t="s">
-        <v>18</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="H78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2794,7 +3368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8bb464ea-0220-4d5f-b1ed-4e3dd856b841}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{972f1bbd-8d49-4d98-8c5b-73bc18370b74}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2814,16 +3388,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -2843,13 +3417,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -2872,16 +3446,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -2901,19 +3475,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
@@ -2930,13 +3504,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -2959,19 +3533,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
         <v>65</v>
@@ -2988,16 +3562,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3017,16 +3591,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3046,13 +3620,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -3072,19 +3646,19 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -3107,8 +3681,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e2cd59f7-7772-4c72-adb5-ae4fbb312891}">
-  <dimension ref="A1:F23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cc4d609e-a055-433c-89aa-62d0ba00b098}">
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3124,13 +3698,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3144,13 +3718,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -3164,16 +3738,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3184,13 +3758,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -3204,13 +3778,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -3224,13 +3798,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -3244,16 +3818,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3264,16 +3838,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3284,13 +3858,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -3304,13 +3878,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -3324,16 +3898,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3344,16 +3918,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -3364,16 +3938,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -3384,13 +3958,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -3404,16 +3978,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -3424,16 +3998,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -3441,19 +4015,19 @@
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -3461,16 +4035,16 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -3481,16 +4055,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
         <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -3501,16 +4075,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -3521,16 +4095,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -3541,16 +4115,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -3561,21 +4135,41 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
       </c>
       <c r="F23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="222">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -360,7 +360,7 @@
     <t>27</t>
   </si>
   <si>
-    <t>Nestoruk Lidia</t>
+    <t>Kaszak Maria</t>
   </si>
   <si>
     <t>2CB</t>
@@ -399,57 +399,129 @@
     <t>2WA|edu</t>
   </si>
   <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1FC|JA1</t>
+  </si>
+  <si>
+    <t>1S|JA1</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
     <t>Najwer Maciej</t>
   </si>
   <si>
     <t>2TFA|JA1</t>
   </si>
   <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>matura - delegowanie ZSL</t>
+  </si>
+  <si>
+    <t>1CB|JA2</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 27</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>Staliś Donata</t>
+  </si>
+  <si>
+    <t>informatyka, przeniesiona na lekcję 4</t>
+  </si>
+  <si>
+    <t>1TFB|JA1</t>
+  </si>
+  <si>
+    <t>Język angielski zawodowy</t>
+  </si>
+  <si>
+    <t>p. Filiczak, przeniesiona z lekcji 1</t>
+  </si>
+  <si>
+    <t>2FA|JA2</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>1FB|JA1</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
     <t>Informatyka</t>
   </si>
   <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>14.05.2026</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>15.05.2026</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
@@ -462,9 +534,6 @@
     <t>1FC|JA2</t>
   </si>
   <si>
-    <t>1CB|JA2</t>
-  </si>
-  <si>
     <t>1S|JA2</t>
   </si>
   <si>
@@ -498,9 +567,6 @@
     <t>10:00-12:00</t>
   </si>
   <si>
-    <t>Kaszak Maria</t>
-  </si>
-  <si>
     <t>T - współorganizowanie kształcenia uczniów</t>
   </si>
   <si>
@@ -540,6 +606,12 @@
     <t>Jęezyk polski</t>
   </si>
   <si>
+    <t xml:space="preserve"> Nikodem Gieysztor - 2CA - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>język angielski</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -606,13 +678,16 @@
     <t>Piątek-Pawłowska Bożena</t>
   </si>
   <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
     <t>parter</t>
   </si>
   <si>
     <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>14:50-14:55</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7ceaa7f1-38ec-4126-bf9b-15760bf391e8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b5ee9520-b169-4148-9a90-c1f63ce11900}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1083,8 +1158,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bdb85dd4-cd08-44cf-a54d-c9a7bfbb1365}">
-  <dimension ref="A1:I78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c35b0467-be5c-4371-84ca-704d04760114}">
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1094,7 +1169,7 @@
     <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2284,7 +2359,7 @@
         <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2498,25 +2573,25 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F49" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G49" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2530,7 +2605,7 @@
         <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
         <v>103</v>
@@ -2559,7 +2634,7 @@
         <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
         <v>103</v>
@@ -2588,7 +2663,7 @@
         <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E52" t="s">
         <v>103</v>
@@ -2611,22 +2686,22 @@
         <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="E53" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -2640,28 +2715,28 @@
         <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2669,28 +2744,28 @@
         <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" t="s">
-        <v>127</v>
-      </c>
-      <c r="F55" t="s">
-        <v>62</v>
-      </c>
       <c r="G55" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -2698,28 +2773,28 @@
         <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G56" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2727,28 +2802,28 @@
         <v>120</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
@@ -2756,28 +2831,28 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
+        <v>128</v>
+      </c>
+      <c r="E58" t="s">
+        <v>115</v>
+      </c>
+      <c r="F58" t="s">
+        <v>111</v>
+      </c>
+      <c r="G58" t="s">
         <v>129</v>
       </c>
-      <c r="E58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" t="s">
-        <v>118</v>
-      </c>
       <c r="H58" t="s">
         <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15">
@@ -2785,28 +2860,28 @@
         <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="D59" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G59" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -2814,22 +2889,22 @@
         <v>120</v>
       </c>
       <c r="B60" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="F60" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2840,80 +2915,80 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="H61" t="s">
         <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B62" t="s">
         <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G62" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H62" t="s">
         <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="G63" t="s">
         <v>118</v>
@@ -2927,22 +3002,22 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
         <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="G64" t="s">
         <v>118</v>
@@ -2956,54 +3031,54 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F65" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" t="s">
         <v>137</v>
       </c>
-      <c r="B65" t="s">
-        <v>40</v>
-      </c>
-      <c r="C65" t="s">
-        <v>88</v>
-      </c>
-      <c r="D65" t="s">
-        <v>138</v>
-      </c>
-      <c r="E65" t="s">
-        <v>43</v>
-      </c>
-      <c r="F65" t="s">
-        <v>139</v>
-      </c>
-      <c r="G65" t="s">
-        <v>65</v>
-      </c>
       <c r="H65" t="s">
         <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="F66" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G66" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
         <v>18</v>
@@ -3014,28 +3089,28 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
+        <v>139</v>
+      </c>
+      <c r="D67" t="s">
+        <v>140</v>
+      </c>
+      <c r="E67" t="s">
+        <v>115</v>
+      </c>
+      <c r="F67" t="s">
         <v>141</v>
       </c>
-      <c r="D67" t="s">
-        <v>131</v>
-      </c>
-      <c r="E67" t="s">
-        <v>127</v>
-      </c>
-      <c r="F67" t="s">
-        <v>62</v>
-      </c>
       <c r="G67" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3043,74 +3118,74 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F68" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E69" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="F69" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G69" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="H69" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
@@ -3119,68 +3194,68 @@
         <v>28</v>
       </c>
       <c r="G70" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" t="s">
+        <v>148</v>
+      </c>
+      <c r="E71" t="s">
+        <v>115</v>
+      </c>
+      <c r="F71" t="s">
+        <v>51</v>
+      </c>
+      <c r="G71" t="s">
+        <v>149</v>
+      </c>
+      <c r="H71" t="s">
         <v>142</v>
       </c>
-      <c r="D71" t="s">
-        <v>143</v>
-      </c>
-      <c r="E71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s">
-        <v>144</v>
-      </c>
-      <c r="G71" t="s">
-        <v>141</v>
-      </c>
-      <c r="H71" t="s">
-        <v>18</v>
-      </c>
       <c r="I71" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="F72" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="G72" t="s">
         <v>65</v>
       </c>
       <c r="H72" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -3188,83 +3263,83 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="D73" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F73" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G73" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="H73" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="I73" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="G74" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
       </c>
       <c r="F75" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="G75" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3275,88 +3350,900 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D76" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="F76" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G76" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="H76" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="C77" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="D77" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G77" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
+        <v>139</v>
+      </c>
+      <c r="D78" t="s">
+        <v>132</v>
+      </c>
+      <c r="E78" t="s">
+        <v>115</v>
+      </c>
+      <c r="F78" t="s">
         <v>141</v>
-      </c>
-      <c r="D78" t="s">
-        <v>147</v>
-      </c>
-      <c r="E78" t="s">
-        <v>127</v>
-      </c>
-      <c r="F78" t="s">
-        <v>62</v>
       </c>
       <c r="G78" t="s">
         <v>65</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="I78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15">
+      <c r="A79" t="s">
+        <v>138</v>
+      </c>
+      <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" t="s">
+        <v>139</v>
+      </c>
+      <c r="D79" t="s">
+        <v>154</v>
+      </c>
+      <c r="E79" t="s">
+        <v>115</v>
+      </c>
+      <c r="F79" t="s">
+        <v>51</v>
+      </c>
+      <c r="G79" t="s">
+        <v>129</v>
+      </c>
+      <c r="H79" t="s">
+        <v>142</v>
+      </c>
+      <c r="I79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15">
+      <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" t="s">
+        <v>133</v>
+      </c>
+      <c r="E80" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" t="s">
+        <v>118</v>
+      </c>
+      <c r="H80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>107</v>
+      </c>
+      <c r="D81" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" t="s">
+        <v>111</v>
+      </c>
+      <c r="G81" t="s">
+        <v>65</v>
+      </c>
+      <c r="H81" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15">
+      <c r="A82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" t="s">
+        <v>156</v>
+      </c>
+      <c r="E82" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" t="s">
+        <v>111</v>
+      </c>
+      <c r="G82" t="s">
+        <v>65</v>
+      </c>
+      <c r="H82" t="s">
+        <v>18</v>
+      </c>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15">
+      <c r="A83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" t="s">
+        <v>115</v>
+      </c>
+      <c r="F83" t="s">
+        <v>111</v>
+      </c>
+      <c r="G83" t="s">
+        <v>65</v>
+      </c>
+      <c r="H83" t="s">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15">
+      <c r="A84" t="s">
+        <v>155</v>
+      </c>
+      <c r="B84" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>157</v>
+      </c>
+      <c r="E84" t="s">
+        <v>67</v>
+      </c>
+      <c r="F84" t="s">
+        <v>158</v>
+      </c>
+      <c r="G84" t="s">
+        <v>76</v>
+      </c>
+      <c r="H84" t="s">
+        <v>18</v>
+      </c>
+      <c r="I84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15">
+      <c r="A85" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" t="s">
+        <v>143</v>
+      </c>
+      <c r="E85" t="s">
+        <v>115</v>
+      </c>
+      <c r="F85" t="s">
+        <v>111</v>
+      </c>
+      <c r="G85" t="s">
+        <v>65</v>
+      </c>
+      <c r="H85" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15">
+      <c r="A86" t="s">
+        <v>155</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" t="s">
+        <v>160</v>
+      </c>
+      <c r="G86" t="s">
+        <v>65</v>
+      </c>
+      <c r="H86" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15">
+      <c r="A87" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>40</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>161</v>
+      </c>
+      <c r="E87" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" t="s">
+        <v>158</v>
+      </c>
+      <c r="G87" t="s">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s">
+        <v>18</v>
+      </c>
+      <c r="I87" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15">
+      <c r="A88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" t="s">
+        <v>89</v>
+      </c>
+      <c r="E88" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" t="s">
+        <v>111</v>
+      </c>
+      <c r="G88" t="s">
+        <v>65</v>
+      </c>
+      <c r="H88" t="s">
+        <v>18</v>
+      </c>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15">
+      <c r="A89" t="s">
+        <v>155</v>
+      </c>
+      <c r="B89" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>162</v>
+      </c>
+      <c r="E89" t="s">
+        <v>67</v>
+      </c>
+      <c r="F89" t="s">
+        <v>158</v>
+      </c>
+      <c r="G89" t="s">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15">
+      <c r="A90" t="s">
+        <v>155</v>
+      </c>
+      <c r="B90" t="s">
+        <v>64</v>
+      </c>
+      <c r="C90" t="s">
+        <v>88</v>
+      </c>
+      <c r="D90" t="s">
+        <v>133</v>
+      </c>
+      <c r="E90" t="s">
+        <v>163</v>
+      </c>
+      <c r="F90" t="s">
+        <v>160</v>
+      </c>
+      <c r="G90" t="s">
+        <v>65</v>
+      </c>
+      <c r="H90" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15">
+      <c r="A91" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" t="s">
+        <v>135</v>
+      </c>
+      <c r="E91" t="s">
+        <v>165</v>
+      </c>
+      <c r="F91" t="s">
+        <v>62</v>
+      </c>
+      <c r="G91" t="s">
+        <v>65</v>
+      </c>
+      <c r="H91" t="s">
+        <v>18</v>
+      </c>
+      <c r="I91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15">
+      <c r="A92" t="s">
+        <v>155</v>
+      </c>
+      <c r="B92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" t="s">
+        <v>67</v>
+      </c>
+      <c r="F92" t="s">
+        <v>158</v>
+      </c>
+      <c r="G92" t="s">
+        <v>76</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15">
+      <c r="A93" t="s">
+        <v>155</v>
+      </c>
+      <c r="B93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" t="s">
+        <v>25</v>
+      </c>
+      <c r="D93" t="s">
+        <v>147</v>
+      </c>
+      <c r="E93" t="s">
+        <v>27</v>
+      </c>
+      <c r="F93" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>18</v>
+      </c>
+      <c r="I93" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15">
+      <c r="A94" t="s">
+        <v>155</v>
+      </c>
+      <c r="B94" t="s">
+        <v>74</v>
+      </c>
+      <c r="C94" t="s">
+        <v>88</v>
+      </c>
+      <c r="D94" t="s">
+        <v>133</v>
+      </c>
+      <c r="E94" t="s">
+        <v>163</v>
+      </c>
+      <c r="F94" t="s">
+        <v>160</v>
+      </c>
+      <c r="G94" t="s">
+        <v>65</v>
+      </c>
+      <c r="H94" t="s">
+        <v>18</v>
+      </c>
+      <c r="I94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15">
+      <c r="A95" t="s">
+        <v>155</v>
+      </c>
+      <c r="B95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>147</v>
+      </c>
+      <c r="E95" t="s">
+        <v>67</v>
+      </c>
+      <c r="F95" t="s">
+        <v>158</v>
+      </c>
+      <c r="G95" t="s">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15">
+      <c r="A96" t="s">
+        <v>155</v>
+      </c>
+      <c r="B96" t="s">
+        <v>74</v>
+      </c>
+      <c r="C96" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96" t="s">
+        <v>132</v>
+      </c>
+      <c r="E96" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15">
+      <c r="A97" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" t="s">
+        <v>74</v>
+      </c>
+      <c r="C97" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" t="s">
+        <v>167</v>
+      </c>
+      <c r="E97" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" t="s">
+        <v>168</v>
+      </c>
+      <c r="G97" t="s">
+        <v>164</v>
+      </c>
+      <c r="H97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15">
+      <c r="A98" t="s">
+        <v>155</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" t="s">
+        <v>88</v>
+      </c>
+      <c r="D98" t="s">
+        <v>133</v>
+      </c>
+      <c r="E98" t="s">
+        <v>163</v>
+      </c>
+      <c r="F98" t="s">
+        <v>160</v>
+      </c>
+      <c r="G98" t="s">
+        <v>65</v>
+      </c>
+      <c r="H98" t="s">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15">
+      <c r="A99" t="s">
+        <v>155</v>
+      </c>
+      <c r="B99" t="s">
+        <v>77</v>
+      </c>
+      <c r="C99" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" t="s">
+        <v>27</v>
+      </c>
+      <c r="F99" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" t="s">
+        <v>118</v>
+      </c>
+      <c r="H99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15">
+      <c r="A100" t="s">
+        <v>155</v>
+      </c>
+      <c r="B100" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100" t="s">
+        <v>134</v>
+      </c>
+      <c r="D100" t="s">
+        <v>135</v>
+      </c>
+      <c r="E100" t="s">
+        <v>136</v>
+      </c>
+      <c r="F100" t="s">
+        <v>126</v>
+      </c>
+      <c r="G100" t="s">
+        <v>137</v>
+      </c>
+      <c r="H100" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15">
+      <c r="A101" t="s">
+        <v>155</v>
+      </c>
+      <c r="B101" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
+      </c>
+      <c r="D101" t="s">
+        <v>167</v>
+      </c>
+      <c r="E101" t="s">
+        <v>27</v>
+      </c>
+      <c r="F101" t="s">
+        <v>168</v>
+      </c>
+      <c r="G101" t="s">
+        <v>164</v>
+      </c>
+      <c r="H101" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15">
+      <c r="A102" t="s">
+        <v>155</v>
+      </c>
+      <c r="B102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C102" t="s">
+        <v>164</v>
+      </c>
+      <c r="D102" t="s">
+        <v>169</v>
+      </c>
+      <c r="E102" t="s">
+        <v>165</v>
+      </c>
+      <c r="F102" t="s">
+        <v>62</v>
+      </c>
+      <c r="G102" t="s">
+        <v>63</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15">
+      <c r="A103" t="s">
+        <v>155</v>
+      </c>
+      <c r="B103" t="s">
+        <v>85</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>89</v>
+      </c>
+      <c r="E103" t="s">
+        <v>67</v>
+      </c>
+      <c r="F103" t="s">
+        <v>168</v>
+      </c>
+      <c r="G103" t="s">
+        <v>65</v>
+      </c>
+      <c r="H103" t="s">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15">
+      <c r="A104" t="s">
+        <v>155</v>
+      </c>
+      <c r="B104" t="s">
+        <v>93</v>
+      </c>
+      <c r="C104" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104" t="s">
+        <v>143</v>
+      </c>
+      <c r="E104" t="s">
+        <v>165</v>
+      </c>
+      <c r="F104" t="s">
+        <v>62</v>
+      </c>
+      <c r="G104" t="s">
+        <v>63</v>
+      </c>
+      <c r="H104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15">
+      <c r="A105" t="s">
+        <v>155</v>
+      </c>
+      <c r="B105" t="s">
+        <v>93</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>167</v>
+      </c>
+      <c r="E105" t="s">
+        <v>67</v>
+      </c>
+      <c r="F105" t="s">
+        <v>168</v>
+      </c>
+      <c r="G105" t="s">
+        <v>65</v>
+      </c>
+      <c r="H105" t="s">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15">
+      <c r="A106" t="s">
+        <v>155</v>
+      </c>
+      <c r="B106" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" t="s">
+        <v>164</v>
+      </c>
+      <c r="D106" t="s">
+        <v>170</v>
+      </c>
+      <c r="E106" t="s">
+        <v>165</v>
+      </c>
+      <c r="F106" t="s">
+        <v>62</v>
+      </c>
+      <c r="G106" t="s">
+        <v>63</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3368,18 +4255,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{972f1bbd-8d49-4d98-8c5b-73bc18370b74}">
-  <dimension ref="A1:I10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{edba52cb-cb09-4662-bfda-5e17e5fed308}">
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="17.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="105" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="9.28571428571429" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3388,16 +4275,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -3417,13 +4304,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -3446,16 +4333,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3475,19 +4362,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="F4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
@@ -3504,13 +4391,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -3533,19 +4420,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="F6" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G6" t="s">
         <v>65</v>
@@ -3562,16 +4449,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3591,16 +4478,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="E8" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3620,13 +4507,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -3646,30 +4533,59 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="G10" t="s">
         <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3681,16 +4597,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cc4d609e-a055-433c-89aa-62d0ba00b098}">
-  <dimension ref="A1:F24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1082e702-6127-442f-b382-21f41390ff6e}">
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="12.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -3698,13 +4614,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -3718,13 +4634,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -3738,16 +4654,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3758,13 +4674,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -3778,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -3798,13 +4714,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -3818,16 +4734,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -3838,16 +4754,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -3858,13 +4774,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -3878,13 +4794,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -3898,16 +4814,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="E11" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -3918,16 +4834,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -3938,16 +4854,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -3958,13 +4874,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -3978,16 +4894,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -3998,16 +4914,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E16" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -4018,16 +4934,16 @@
         <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -4035,19 +4951,19 @@
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -4055,19 +4971,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -4075,39 +4991,39 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C21" t="s">
         <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -4115,61 +5031,281 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="F24" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>205</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="255">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -399,31 +399,70 @@
     <t>2WA|edu</t>
   </si>
   <si>
+    <t>2CA</t>
+  </si>
+  <si>
     <t>1FA|JA1</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>1FC|JA1</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1S|JA1</t>
+  </si>
+  <si>
+    <t>Obsługa klientów</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Socha Dariusz [DS]</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>2TFA|JA1</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>1S|JA2+1S|JA1</t>
+  </si>
+  <si>
+    <t>lekcja przeniesiona do sali 27</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Sałdyka Karolina [Sp]</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
-    <t>1FC|JA1</t>
-  </si>
-  <si>
-    <t>1S|JA1</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>2TFA|JA1</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>4TFB</t>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>32</t>
   </si>
   <si>
     <t>Wakat1 j. niemiecki</t>
@@ -447,45 +486,84 @@
     <t>3FB</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>matura - delegowanie ZSL</t>
   </si>
   <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
     <t>1CB|JA2</t>
   </si>
   <si>
     <t>Granatowska Mariola</t>
   </si>
   <si>
+    <t>2WA</t>
+  </si>
+  <si>
     <t>1K|JA1</t>
   </si>
   <si>
-    <t>lekcja przeniesiona do sali 27</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
     <t>3TFB|JA1</t>
   </si>
   <si>
     <t>Staliś Donata</t>
   </si>
   <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
     <t>informatyka, przeniesiona na lekcję 4</t>
   </si>
   <si>
+    <t>Piątek-Pawłowska Bożena</t>
+  </si>
+  <si>
+    <t>Matura - oddelegowanie do ZSL</t>
+  </si>
+  <si>
     <t>1TFB|JA1</t>
   </si>
   <si>
+    <t>bib2</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
     <t>Język angielski zawodowy</t>
   </si>
   <si>
+    <t>3TFB|CH</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>3TFB|DZ</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
     <t>p. Filiczak, przeniesiona z lekcji 1</t>
   </si>
   <si>
+    <t>1CB</t>
+  </si>
+  <si>
     <t>2FA|JA2</t>
   </si>
   <si>
@@ -495,18 +573,21 @@
     <t>1FB|JA1</t>
   </si>
   <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>1K</t>
   </si>
   <si>
     <t>1TFB</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>1FB</t>
   </si>
   <si>
@@ -522,6 +603,12 @@
     <t>Informatyka</t>
   </si>
   <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
@@ -531,6 +618,9 @@
     <t>28</t>
   </si>
   <si>
+    <t>2B</t>
+  </si>
+  <si>
     <t>1FC|JA2</t>
   </si>
   <si>
@@ -606,12 +696,30 @@
     <t>Jęezyk polski</t>
   </si>
   <si>
+    <t>14:05-14:50</t>
+  </si>
+  <si>
+    <t>Marcel Wiśniewski - 1WA - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>15:45-16:30</t>
+  </si>
+  <si>
+    <t>08:50-09:35</t>
+  </si>
+  <si>
+    <t>08:50-10:25</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Nikodem Gieysztor - 2CA - indywidualne nauczanie</t>
   </si>
   <si>
     <t>język angielski</t>
   </si>
   <si>
+    <t>14:05-15:40</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -651,9 +759,6 @@
     <t>13:10-13:15</t>
   </si>
   <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
   </si>
   <si>
@@ -675,19 +780,13 @@
     <t>piętro_1</t>
   </si>
   <si>
-    <t>Piątek-Pawłowska Bożena</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
+    <t>14:00-14:05</t>
   </si>
   <si>
     <t>14:50-14:55</t>
   </si>
   <si>
     <t>parter</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1236,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b5ee9520-b169-4148-9a90-c1f63ce11900}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd0b6404-029b-44ec-b192-f477b1b252aa}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1158,18 +1257,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c35b0467-be5c-4371-84ca-704d04760114}">
-  <dimension ref="A1:I106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d3d71ddd-4fa6-4748-acf7-0c1d8edc8bbf}">
+  <dimension ref="A1:I149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="51.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="14.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="8" max="8" width="55.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2718,25 +2817,25 @@
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D54" t="s">
         <v>125</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F54" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
@@ -2747,25 +2846,25 @@
         <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="G55" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
@@ -2773,28 +2872,28 @@
         <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" t="s">
         <v>127</v>
       </c>
-      <c r="E56" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" t="s">
-        <v>37</v>
-      </c>
       <c r="G56" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
@@ -2805,19 +2904,19 @@
         <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="H57" t="s">
         <v>18</v>
@@ -2831,22 +2930,22 @@
         <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
         <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E58" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="G58" t="s">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="H58" t="s">
         <v>18</v>
@@ -2860,28 +2959,28 @@
         <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H59" t="s">
         <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15">
@@ -2892,19 +2991,19 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E60" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" t="s">
         <v>132</v>
       </c>
-      <c r="E60" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" t="s">
-        <v>28</v>
-      </c>
       <c r="G60" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s">
         <v>18</v>
@@ -2918,28 +3017,28 @@
         <v>120</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
         <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E61" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F61" t="s">
         <v>111</v>
       </c>
       <c r="G61" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H61" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="I61" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
@@ -2947,13 +3046,13 @@
         <v>120</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
@@ -2976,22 +3075,22 @@
         <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E63" t="s">
         <v>27</v>
       </c>
       <c r="F63" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="G63" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="H63" t="s">
         <v>18</v>
@@ -3005,28 +3104,28 @@
         <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F64" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="G64" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="H64" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15">
@@ -3034,22 +3133,22 @@
         <v>120</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F65" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
         <v>18</v>
@@ -3060,28 +3159,28 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
         <v>107</v>
       </c>
       <c r="D66" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E66" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F66" t="s">
         <v>111</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="H66" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -3089,86 +3188,86 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D67" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="E67" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F67" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H67" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D68" t="s">
         <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="H68" t="s">
         <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" t="s">
         <v>138</v>
       </c>
-      <c r="B69" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" t="s">
-        <v>107</v>
-      </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E69" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F69" t="s">
         <v>111</v>
       </c>
       <c r="G69" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="H69" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I69" t="s">
         <v>39</v>
@@ -3176,22 +3275,22 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C70" t="s">
         <v>25</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G70" t="s">
         <v>29</v>
@@ -3205,57 +3304,57 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" t="s">
         <v>138</v>
       </c>
-      <c r="B71" t="s">
-        <v>40</v>
-      </c>
-      <c r="C71" t="s">
-        <v>139</v>
-      </c>
       <c r="D71" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E71" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="F71" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F72" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H72" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -3263,141 +3362,141 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" t="s">
         <v>138</v>
       </c>
-      <c r="B73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C73" t="s">
-        <v>139</v>
-      </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E73" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="F73" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G73" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="H73" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D74" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="E74" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="F74" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="G74" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H74" t="s">
         <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F75" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G75" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C76" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="E76" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="F76" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="G76" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="F77" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="G77" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
@@ -3408,57 +3507,57 @@
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="E78" t="s">
         <v>115</v>
       </c>
       <c r="F78" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="G78" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="H78" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F79" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G79" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="H79" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
         <v>39</v>
@@ -3466,112 +3565,112 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="E80" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F80" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G80" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="H80" t="s">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="I80" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" t="s">
         <v>155</v>
       </c>
-      <c r="B81" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" t="s">
-        <v>156</v>
-      </c>
       <c r="E81" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="F81" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
         <v>115</v>
       </c>
       <c r="F82" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="G82" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="H82" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C83" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D83" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="E83" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G83" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
@@ -3582,25 +3681,25 @@
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D84" t="s">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F84" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
@@ -3611,7 +3710,7 @@
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B85" t="s">
         <v>40</v>
@@ -3620,7 +3719,7 @@
         <v>107</v>
       </c>
       <c r="D85" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="E85" t="s">
         <v>115</v>
@@ -3632,7 +3731,7 @@
         <v>65</v>
       </c>
       <c r="H85" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
@@ -3640,112 +3739,112 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
         <v>40</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="D86" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
         <v>43</v>
       </c>
       <c r="F86" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="G86" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B87" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="D87" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E87" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F87" t="s">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="G87" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="H87" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="E88" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F88" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="G88" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B89" t="s">
         <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D89" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="E89" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F89" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H89" t="s">
         <v>18</v>
@@ -3756,86 +3855,86 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D90" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E90" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="F90" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="G90" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="H90" t="s">
         <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B91" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="F91" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G91" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B92" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="F92" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
       <c r="G92" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="I92" t="s">
         <v>30</v>
@@ -3843,141 +3942,141 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
         <v>64</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="D93" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="F93" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G93" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="H93" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C94" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="E94" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F94" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="G94" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C95" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="E95" t="s">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="F95" t="s">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="G95" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E96" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F96" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C97" t="s">
-        <v>166</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="E97" t="s">
         <v>27</v>
       </c>
       <c r="F97" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="G97" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3988,112 +4087,112 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C98" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="E98" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="G98" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H98" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="D99" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="G99" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="H99" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="I99" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C100" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="E100" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F100" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="G100" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C101" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="D101" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="F101" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="G101" t="s">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4104,83 +4203,83 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B102" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C102" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E102" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F102" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G102" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B103" t="s">
         <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D103" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="E103" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F103" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="G103" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="D104" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="E104" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="F104" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="G104" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
@@ -4191,22 +4290,22 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>184</v>
       </c>
       <c r="F105" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="G105" t="s">
         <v>65</v>
@@ -4220,30 +4319,1277 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
+        <v>181</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>107</v>
+      </c>
+      <c r="D106" t="s">
+        <v>182</v>
+      </c>
+      <c r="E106" t="s">
+        <v>115</v>
+      </c>
+      <c r="F106" t="s">
+        <v>111</v>
+      </c>
+      <c r="G106" t="s">
+        <v>17</v>
+      </c>
+      <c r="H106" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15">
+      <c r="A107" t="s">
+        <v>181</v>
+      </c>
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>167</v>
+      </c>
+      <c r="D107" t="s">
+        <v>185</v>
+      </c>
+      <c r="E107" t="s">
+        <v>55</v>
+      </c>
+      <c r="F107" t="s">
+        <v>72</v>
+      </c>
+      <c r="G107" t="s">
+        <v>65</v>
+      </c>
+      <c r="H107" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15">
+      <c r="A108" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D108" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" t="s">
+        <v>184</v>
+      </c>
+      <c r="F108" t="s">
+        <v>96</v>
+      </c>
+      <c r="G108" t="s">
+        <v>65</v>
+      </c>
+      <c r="H108" t="s">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15">
+      <c r="A109" t="s">
+        <v>181</v>
+      </c>
+      <c r="B109" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D109" t="s">
+        <v>47</v>
+      </c>
+      <c r="E109" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" t="s">
+        <v>56</v>
+      </c>
+      <c r="G109" t="s">
+        <v>65</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="15">
+      <c r="A110" t="s">
+        <v>181</v>
+      </c>
+      <c r="B110" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" t="s">
+        <v>107</v>
+      </c>
+      <c r="D110" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" t="s">
+        <v>115</v>
+      </c>
+      <c r="F110" t="s">
+        <v>111</v>
+      </c>
+      <c r="G110" t="s">
+        <v>65</v>
+      </c>
+      <c r="H110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="15">
+      <c r="A111" t="s">
+        <v>181</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>179</v>
+      </c>
+      <c r="E111" t="s">
+        <v>67</v>
+      </c>
+      <c r="F111" t="s">
+        <v>127</v>
+      </c>
+      <c r="G111" t="s">
+        <v>76</v>
+      </c>
+      <c r="H111" t="s">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="15">
+      <c r="A112" t="s">
+        <v>181</v>
+      </c>
+      <c r="B112" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" t="s">
+        <v>167</v>
+      </c>
+      <c r="D112" t="s">
+        <v>185</v>
+      </c>
+      <c r="E112" t="s">
+        <v>55</v>
+      </c>
+      <c r="F112" t="s">
+        <v>72</v>
+      </c>
+      <c r="G112" t="s">
+        <v>65</v>
+      </c>
+      <c r="H112" t="s">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15">
+      <c r="A113" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" t="s">
+        <v>183</v>
+      </c>
+      <c r="D113" t="s">
+        <v>186</v>
+      </c>
+      <c r="E113" t="s">
+        <v>92</v>
+      </c>
+      <c r="F113" t="s">
+        <v>96</v>
+      </c>
+      <c r="G113" t="s">
+        <v>65</v>
+      </c>
+      <c r="H113" t="s">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="15">
+      <c r="A114" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" t="s">
+        <v>40</v>
+      </c>
+      <c r="C114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" t="s">
         <v>155</v>
       </c>
-      <c r="B106" t="s">
+      <c r="E114" t="s">
+        <v>55</v>
+      </c>
+      <c r="F114" t="s">
+        <v>56</v>
+      </c>
+      <c r="G114" t="s">
+        <v>65</v>
+      </c>
+      <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="15">
+      <c r="A115" t="s">
+        <v>181</v>
+      </c>
+      <c r="B115" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115" t="s">
+        <v>107</v>
+      </c>
+      <c r="D115" t="s">
+        <v>159</v>
+      </c>
+      <c r="E115" t="s">
+        <v>115</v>
+      </c>
+      <c r="F115" t="s">
+        <v>111</v>
+      </c>
+      <c r="G115" t="s">
+        <v>65</v>
+      </c>
+      <c r="H115" t="s">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15">
+      <c r="A116" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" t="s">
+        <v>88</v>
+      </c>
+      <c r="D116" t="s">
+        <v>187</v>
+      </c>
+      <c r="E116" t="s">
+        <v>43</v>
+      </c>
+      <c r="F116" t="s">
+        <v>132</v>
+      </c>
+      <c r="G116" t="s">
+        <v>65</v>
+      </c>
+      <c r="H116" t="s">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="15">
+      <c r="A117" t="s">
+        <v>181</v>
+      </c>
+      <c r="B117" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" t="s">
+        <v>67</v>
+      </c>
+      <c r="F117" t="s">
+        <v>127</v>
+      </c>
+      <c r="G117" t="s">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="15">
+      <c r="A118" t="s">
+        <v>181</v>
+      </c>
+      <c r="B118" t="s">
+        <v>40</v>
+      </c>
+      <c r="C118" t="s">
+        <v>167</v>
+      </c>
+      <c r="D118" t="s">
+        <v>143</v>
+      </c>
+      <c r="E118" t="s">
+        <v>55</v>
+      </c>
+      <c r="F118" t="s">
+        <v>72</v>
+      </c>
+      <c r="G118" t="s">
+        <v>65</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="15">
+      <c r="A119" t="s">
+        <v>181</v>
+      </c>
+      <c r="B119" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" t="s">
+        <v>183</v>
+      </c>
+      <c r="D119" t="s">
+        <v>186</v>
+      </c>
+      <c r="E119" t="s">
+        <v>92</v>
+      </c>
+      <c r="F119" t="s">
+        <v>96</v>
+      </c>
+      <c r="G119" t="s">
+        <v>65</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="15">
+      <c r="A120" t="s">
+        <v>181</v>
+      </c>
+      <c r="B120" t="s">
+        <v>53</v>
+      </c>
+      <c r="C120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="s">
+        <v>47</v>
+      </c>
+      <c r="E120" t="s">
+        <v>71</v>
+      </c>
+      <c r="F120" t="s">
+        <v>56</v>
+      </c>
+      <c r="G120" t="s">
+        <v>65</v>
+      </c>
+      <c r="H120" t="s">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15">
+      <c r="A121" t="s">
+        <v>181</v>
+      </c>
+      <c r="B121" t="s">
+        <v>53</v>
+      </c>
+      <c r="C121" t="s">
+        <v>107</v>
+      </c>
+      <c r="D121" t="s">
+        <v>89</v>
+      </c>
+      <c r="E121" t="s">
+        <v>115</v>
+      </c>
+      <c r="F121" t="s">
+        <v>111</v>
+      </c>
+      <c r="G121" t="s">
+        <v>65</v>
+      </c>
+      <c r="H121" t="s">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15">
+      <c r="A122" t="s">
+        <v>181</v>
+      </c>
+      <c r="B122" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" t="s">
+        <v>67</v>
+      </c>
+      <c r="F122" t="s">
+        <v>127</v>
+      </c>
+      <c r="G122" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15">
+      <c r="A123" t="s">
+        <v>181</v>
+      </c>
+      <c r="B123" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" t="s">
+        <v>167</v>
+      </c>
+      <c r="D123" t="s">
+        <v>143</v>
+      </c>
+      <c r="E123" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" t="s">
+        <v>72</v>
+      </c>
+      <c r="G123" t="s">
+        <v>65</v>
+      </c>
+      <c r="H123" t="s">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15">
+      <c r="A124" t="s">
+        <v>181</v>
+      </c>
+      <c r="B124" t="s">
+        <v>53</v>
+      </c>
+      <c r="C124" t="s">
+        <v>183</v>
+      </c>
+      <c r="D124" t="s">
+        <v>186</v>
+      </c>
+      <c r="E124" t="s">
+        <v>92</v>
+      </c>
+      <c r="F124" t="s">
+        <v>96</v>
+      </c>
+      <c r="G124" t="s">
+        <v>65</v>
+      </c>
+      <c r="H124" t="s">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15">
+      <c r="A125" t="s">
+        <v>181</v>
+      </c>
+      <c r="B125" t="s">
+        <v>64</v>
+      </c>
+      <c r="C125" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" t="s">
+        <v>187</v>
+      </c>
+      <c r="E125" t="s">
+        <v>55</v>
+      </c>
+      <c r="F125" t="s">
+        <v>56</v>
+      </c>
+      <c r="G125" t="s">
+        <v>65</v>
+      </c>
+      <c r="H125" t="s">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15">
+      <c r="A126" t="s">
+        <v>181</v>
+      </c>
+      <c r="B126" t="s">
+        <v>64</v>
+      </c>
+      <c r="C126" t="s">
+        <v>88</v>
+      </c>
+      <c r="D126" t="s">
+        <v>143</v>
+      </c>
+      <c r="E126" t="s">
+        <v>190</v>
+      </c>
+      <c r="F126" t="s">
+        <v>132</v>
+      </c>
+      <c r="G126" t="s">
+        <v>65</v>
+      </c>
+      <c r="H126" t="s">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15">
+      <c r="A127" t="s">
+        <v>181</v>
+      </c>
+      <c r="B127" t="s">
+        <v>64</v>
+      </c>
+      <c r="C127" t="s">
+        <v>191</v>
+      </c>
+      <c r="D127" t="s">
+        <v>148</v>
+      </c>
+      <c r="E127" t="s">
+        <v>192</v>
+      </c>
+      <c r="F127" t="s">
+        <v>62</v>
+      </c>
+      <c r="G127" t="s">
+        <v>65</v>
+      </c>
+      <c r="H127" t="s">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15">
+      <c r="A128" t="s">
+        <v>181</v>
+      </c>
+      <c r="B128" t="s">
+        <v>64</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>125</v>
+      </c>
+      <c r="E128" t="s">
+        <v>67</v>
+      </c>
+      <c r="F128" t="s">
+        <v>127</v>
+      </c>
+      <c r="G128" t="s">
+        <v>76</v>
+      </c>
+      <c r="H128" t="s">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="15">
+      <c r="A129" t="s">
+        <v>181</v>
+      </c>
+      <c r="B129" t="s">
+        <v>64</v>
+      </c>
+      <c r="C129" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129" t="s">
+        <v>155</v>
+      </c>
+      <c r="E129" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="15">
+      <c r="A130" t="s">
+        <v>181</v>
+      </c>
+      <c r="B130" t="s">
+        <v>64</v>
+      </c>
+      <c r="C130" t="s">
+        <v>167</v>
+      </c>
+      <c r="D130" t="s">
+        <v>193</v>
+      </c>
+      <c r="E130" t="s">
+        <v>55</v>
+      </c>
+      <c r="F130" t="s">
+        <v>72</v>
+      </c>
+      <c r="G130" t="s">
+        <v>65</v>
+      </c>
+      <c r="H130" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="15">
+      <c r="A131" t="s">
+        <v>181</v>
+      </c>
+      <c r="B131" t="s">
+        <v>64</v>
+      </c>
+      <c r="C131" t="s">
+        <v>183</v>
+      </c>
+      <c r="D131" t="s">
+        <v>186</v>
+      </c>
+      <c r="E131" t="s">
+        <v>92</v>
+      </c>
+      <c r="F131" t="s">
+        <v>96</v>
+      </c>
+      <c r="G131" t="s">
+        <v>65</v>
+      </c>
+      <c r="H131" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="15">
+      <c r="A132" t="s">
+        <v>181</v>
+      </c>
+      <c r="B132" t="s">
+        <v>74</v>
+      </c>
+      <c r="C132" t="s">
+        <v>88</v>
+      </c>
+      <c r="D132" t="s">
+        <v>143</v>
+      </c>
+      <c r="E132" t="s">
+        <v>190</v>
+      </c>
+      <c r="F132" t="s">
+        <v>132</v>
+      </c>
+      <c r="G132" t="s">
+        <v>65</v>
+      </c>
+      <c r="H132" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="15">
+      <c r="A133" t="s">
+        <v>181</v>
+      </c>
+      <c r="B133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>155</v>
+      </c>
+      <c r="E133" t="s">
+        <v>67</v>
+      </c>
+      <c r="F133" t="s">
+        <v>127</v>
+      </c>
+      <c r="G133" t="s">
+        <v>76</v>
+      </c>
+      <c r="H133" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="15">
+      <c r="A134" t="s">
+        <v>181</v>
+      </c>
+      <c r="B134" t="s">
+        <v>74</v>
+      </c>
+      <c r="C134" t="s">
+        <v>25</v>
+      </c>
+      <c r="D134" t="s">
+        <v>125</v>
+      </c>
+      <c r="E134" t="s">
+        <v>27</v>
+      </c>
+      <c r="F134" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="15">
+      <c r="A135" t="s">
+        <v>181</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135" t="s">
+        <v>167</v>
+      </c>
+      <c r="D135" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s">
+        <v>55</v>
+      </c>
+      <c r="F135" t="s">
+        <v>72</v>
+      </c>
+      <c r="G135" t="s">
+        <v>65</v>
+      </c>
+      <c r="H135" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>181</v>
+      </c>
+      <c r="B136" t="s">
+        <v>74</v>
+      </c>
+      <c r="C136" t="s">
+        <v>183</v>
+      </c>
+      <c r="D136" t="s">
+        <v>47</v>
+      </c>
+      <c r="E136" t="s">
+        <v>194</v>
+      </c>
+      <c r="F136" t="s">
+        <v>96</v>
+      </c>
+      <c r="G136" t="s">
+        <v>65</v>
+      </c>
+      <c r="H136" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>181</v>
+      </c>
+      <c r="B137" t="s">
+        <v>74</v>
+      </c>
+      <c r="C137" t="s">
+        <v>195</v>
+      </c>
+      <c r="D137" t="s">
+        <v>196</v>
+      </c>
+      <c r="E137" t="s">
+        <v>27</v>
+      </c>
+      <c r="F137" t="s">
+        <v>197</v>
+      </c>
+      <c r="G137" t="s">
+        <v>191</v>
+      </c>
+      <c r="H137" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>181</v>
+      </c>
+      <c r="B138" t="s">
+        <v>77</v>
+      </c>
+      <c r="C138" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>198</v>
+      </c>
+      <c r="E138" t="s">
+        <v>55</v>
+      </c>
+      <c r="F138" t="s">
+        <v>56</v>
+      </c>
+      <c r="G138" t="s">
+        <v>65</v>
+      </c>
+      <c r="H138" t="s">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>181</v>
+      </c>
+      <c r="B139" t="s">
+        <v>77</v>
+      </c>
+      <c r="C139" t="s">
+        <v>88</v>
+      </c>
+      <c r="D139" t="s">
+        <v>143</v>
+      </c>
+      <c r="E139" t="s">
+        <v>190</v>
+      </c>
+      <c r="F139" t="s">
+        <v>132</v>
+      </c>
+      <c r="G139" t="s">
+        <v>65</v>
+      </c>
+      <c r="H139" t="s">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>181</v>
+      </c>
+      <c r="B140" t="s">
+        <v>77</v>
+      </c>
+      <c r="C140" t="s">
+        <v>25</v>
+      </c>
+      <c r="D140" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" t="s">
+        <v>28</v>
+      </c>
+      <c r="G140" t="s">
+        <v>118</v>
+      </c>
+      <c r="H140" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>181</v>
+      </c>
+      <c r="B141" t="s">
+        <v>77</v>
+      </c>
+      <c r="C141" t="s">
+        <v>147</v>
+      </c>
+      <c r="D141" t="s">
+        <v>148</v>
+      </c>
+      <c r="E141" t="s">
+        <v>149</v>
+      </c>
+      <c r="F141" t="s">
+        <v>144</v>
+      </c>
+      <c r="G141" t="s">
+        <v>150</v>
+      </c>
+      <c r="H141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>181</v>
+      </c>
+      <c r="B142" t="s">
+        <v>77</v>
+      </c>
+      <c r="C142" t="s">
+        <v>195</v>
+      </c>
+      <c r="D142" t="s">
+        <v>196</v>
+      </c>
+      <c r="E142" t="s">
+        <v>27</v>
+      </c>
+      <c r="F142" t="s">
+        <v>197</v>
+      </c>
+      <c r="G142" t="s">
+        <v>191</v>
+      </c>
+      <c r="H142" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>181</v>
+      </c>
+      <c r="B143" t="s">
+        <v>85</v>
+      </c>
+      <c r="C143" t="s">
+        <v>41</v>
+      </c>
+      <c r="D143" t="s">
+        <v>198</v>
+      </c>
+      <c r="E143" t="s">
+        <v>55</v>
+      </c>
+      <c r="F143" t="s">
+        <v>56</v>
+      </c>
+      <c r="G143" t="s">
+        <v>65</v>
+      </c>
+      <c r="H143" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>181</v>
+      </c>
+      <c r="B144" t="s">
+        <v>85</v>
+      </c>
+      <c r="C144" t="s">
+        <v>191</v>
+      </c>
+      <c r="D144" t="s">
+        <v>199</v>
+      </c>
+      <c r="E144" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" t="s">
+        <v>62</v>
+      </c>
+      <c r="G144" t="s">
+        <v>63</v>
+      </c>
+      <c r="H144" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>181</v>
+      </c>
+      <c r="B145" t="s">
+        <v>85</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>89</v>
+      </c>
+      <c r="E145" t="s">
+        <v>67</v>
+      </c>
+      <c r="F145" t="s">
+        <v>197</v>
+      </c>
+      <c r="G145" t="s">
+        <v>65</v>
+      </c>
+      <c r="H145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>181</v>
+      </c>
+      <c r="B146" t="s">
+        <v>93</v>
+      </c>
+      <c r="C146" t="s">
+        <v>41</v>
+      </c>
+      <c r="D146" t="s">
+        <v>26</v>
+      </c>
+      <c r="E146" t="s">
+        <v>55</v>
+      </c>
+      <c r="F146" t="s">
+        <v>56</v>
+      </c>
+      <c r="G146" t="s">
+        <v>65</v>
+      </c>
+      <c r="H146" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>181</v>
+      </c>
+      <c r="B147" t="s">
+        <v>93</v>
+      </c>
+      <c r="C147" t="s">
+        <v>191</v>
+      </c>
+      <c r="D147" t="s">
+        <v>159</v>
+      </c>
+      <c r="E147" t="s">
+        <v>192</v>
+      </c>
+      <c r="F147" t="s">
+        <v>62</v>
+      </c>
+      <c r="G147" t="s">
+        <v>63</v>
+      </c>
+      <c r="H147" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>181</v>
+      </c>
+      <c r="B148" t="s">
+        <v>93</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>196</v>
+      </c>
+      <c r="E148" t="s">
+        <v>67</v>
+      </c>
+      <c r="F148" t="s">
+        <v>197</v>
+      </c>
+      <c r="G148" t="s">
+        <v>65</v>
+      </c>
+      <c r="H148" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>181</v>
+      </c>
+      <c r="B149" t="s">
         <v>99</v>
       </c>
-      <c r="C106" t="s">
-        <v>164</v>
-      </c>
-      <c r="D106" t="s">
-        <v>170</v>
-      </c>
-      <c r="E106" t="s">
-        <v>165</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="C149" t="s">
+        <v>191</v>
+      </c>
+      <c r="D149" t="s">
+        <v>200</v>
+      </c>
+      <c r="E149" t="s">
+        <v>192</v>
+      </c>
+      <c r="F149" t="s">
         <v>62</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G149" t="s">
         <v>63</v>
       </c>
-      <c r="H106" t="s">
-        <v>18</v>
-      </c>
-      <c r="I106" t="s">
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4255,8 +5601,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{edba52cb-cb09-4662-bfda-5e17e5fed308}">
-  <dimension ref="A1:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a7a94a9d-9d2a-483e-bec7-862d5a274c03}">
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4275,16 +5621,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -4304,13 +5650,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -4333,16 +5679,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4362,19 +5708,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C4" t="s">
         <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
@@ -4391,13 +5737,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -4420,19 +5766,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
         <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="G6" t="s">
         <v>65</v>
@@ -4449,16 +5795,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -4478,16 +5824,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4507,13 +5853,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -4533,28 +5879,28 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
@@ -4562,19 +5908,19 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4586,6 +5932,180 @@
         <v>18</v>
       </c>
       <c r="I11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4597,16 +6117,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1082e702-6127-442f-b382-21f41390ff6e}">
-  <dimension ref="A1:F35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e16e6be0-8b90-44da-a66d-cdb6df8cb3ea}">
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -4614,13 +6134,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -4634,13 +6154,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -4654,16 +6174,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -4674,13 +6194,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -4694,13 +6214,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -4714,13 +6234,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -4734,16 +6254,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -4754,16 +6274,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -4774,13 +6294,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -4794,13 +6314,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -4814,16 +6334,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -4834,16 +6354,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -4854,16 +6374,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E13" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -4874,13 +6394,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -4894,16 +6414,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -4914,16 +6434,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -4934,16 +6454,16 @@
         <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -4954,13 +6474,13 @@
         <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
         <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -4971,19 +6491,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -4991,39 +6511,39 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -5031,79 +6551,79 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="C22" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="F22" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
       <c r="F23" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="E24" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -5111,79 +6631,79 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="D28" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -5191,36 +6711,36 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>247</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -5231,16 +6751,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -5251,16 +6771,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C33" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -5271,16 +6791,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -5291,21 +6811,261 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>254</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D36" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" t="s">
+        <v>241</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
+        <v>254</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" t="s">
+        <v>254</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" t="s">
+        <v>235</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>251</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" t="s">
+        <v>234</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" t="s">
+        <v>251</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" t="s">
+        <v>235</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" t="s">
+        <v>234</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" t="s">
+        <v>251</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="260">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -501,13 +501,28 @@
     <t>Smirnow-Zechman Eleonora</t>
   </si>
   <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
     <t>1CB|JA2</t>
   </si>
   <si>
-    <t>Granatowska Mariola</t>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
+    <t>3TH|JA1</t>
   </si>
   <si>
     <t>2WA</t>
+  </si>
+  <si>
+    <t>1K|JA2</t>
   </si>
   <si>
     <t>1K|JA1</t>
@@ -1236,7 +1251,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd0b6404-029b-44ec-b192-f477b1b252aa}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{06cc5c9c-76c3-4cce-a868-e3c429552bc0}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1257,8 +1272,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d3d71ddd-4fa6-4748-acf7-0c1d8edc8bbf}">
-  <dimension ref="A1:I149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e9d551ec-3c92-456f-acd3-505165a4ed56}">
+  <dimension ref="A1:I153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3513,19 +3528,19 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E78" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F78" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="G78" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
@@ -3539,13 +3554,13 @@
         <v>151</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E79" t="s">
         <v>36</v>
@@ -3568,28 +3583,28 @@
         <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="F80" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G80" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
@@ -3600,25 +3615,25 @@
         <v>31</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E81" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F81" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G81" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
@@ -3626,28 +3641,28 @@
         <v>151</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E82" t="s">
         <v>115</v>
       </c>
       <c r="F82" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="G82" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -3655,19 +3670,19 @@
         <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="E83" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="G83" t="s">
         <v>17</v>
@@ -3684,28 +3699,28 @@
         <v>151</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C84" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="D84" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="E84" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="F84" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="G84" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
@@ -3713,28 +3728,28 @@
         <v>151</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E85" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="F85" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H85" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3745,25 +3760,25 @@
         <v>40</v>
       </c>
       <c r="C86" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="E86" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F86" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="G86" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="H86" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="I86" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
@@ -3771,28 +3786,28 @@
         <v>151</v>
       </c>
       <c r="B87" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C87" t="s">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="E87" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F87" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G87" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
@@ -3800,28 +3815,28 @@
         <v>151</v>
       </c>
       <c r="B88" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D88" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F88" t="s">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s">
         <v>170</v>
       </c>
-      <c r="G88" t="s">
-        <v>109</v>
-      </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
@@ -3829,28 +3844,28 @@
         <v>151</v>
       </c>
       <c r="B89" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E89" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="F89" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="I89" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
@@ -3858,28 +3873,28 @@
         <v>151</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="D90" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="E90" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="F90" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G90" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="I90" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
@@ -3890,25 +3905,25 @@
         <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F91" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G91" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H91" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I91" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
@@ -3919,25 +3934,25 @@
         <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="D92" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E92" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="G92" t="s">
-        <v>171</v>
+        <v>109</v>
       </c>
       <c r="H92" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
@@ -3945,25 +3960,25 @@
         <v>151</v>
       </c>
       <c r="B93" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="E93" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="F93" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="H93" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
         <v>30</v>
@@ -3974,28 +3989,28 @@
         <v>151</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D94" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="E94" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G94" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="H94" t="s">
         <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
@@ -4003,28 +4018,28 @@
         <v>151</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="E95" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="F95" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
@@ -4032,25 +4047,25 @@
         <v>151</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E96" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F96" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="H96" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="I96" t="s">
         <v>30</v>
@@ -4064,22 +4079,22 @@
         <v>64</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="D97" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="F97" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G97" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="H97" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I97" t="s">
         <v>30</v>
@@ -4093,25 +4108,25 @@
         <v>64</v>
       </c>
       <c r="C98" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E98" t="s">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="F98" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G98" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="H98" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
@@ -4119,28 +4134,28 @@
         <v>151</v>
       </c>
       <c r="B99" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="D99" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="E99" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="F99" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="G99" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="H99" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
@@ -4148,28 +4163,28 @@
         <v>151</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C100" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="E100" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
@@ -4177,22 +4192,22 @@
         <v>151</v>
       </c>
       <c r="B101" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C101" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="E101" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
@@ -4206,25 +4221,25 @@
         <v>151</v>
       </c>
       <c r="B102" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C102" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D102" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E102" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G102" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="H102" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="I102" t="s">
         <v>39</v>
@@ -4235,51 +4250,51 @@
         <v>151</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E103" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F103" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="G103" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="H103" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="I103" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C104" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E104" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F104" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G104" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="H104" t="s">
         <v>18</v>
@@ -4290,112 +4305,112 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="C105" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="D105" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="F105" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G105" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
         <v>115</v>
       </c>
       <c r="F106" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="G106" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="H106" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C107" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="E107" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F107" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="D108" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="E108" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="F108" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G108" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4406,22 +4421,22 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="D109" t="s">
         <v>47</v>
       </c>
       <c r="E109" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="F109" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G109" t="s">
         <v>65</v>
@@ -4435,16 +4450,16 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B110" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C110" t="s">
         <v>107</v>
       </c>
       <c r="D110" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="E110" t="s">
         <v>115</v>
@@ -4453,7 +4468,7 @@
         <v>111</v>
       </c>
       <c r="G110" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
@@ -4464,51 +4479,51 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E111" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F111" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="G111" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>47</v>
       </c>
       <c r="E112" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="F112" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G112" t="s">
         <v>65</v>
@@ -4522,22 +4537,22 @@
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B113" t="s">
         <v>31</v>
       </c>
       <c r="C113" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="D113" t="s">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="E113" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="F113" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G113" t="s">
         <v>65</v>
@@ -4551,22 +4566,22 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C114" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="E114" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="G114" t="s">
         <v>65</v>
@@ -4580,51 +4595,51 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B115" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="D115" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E115" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F115" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G115" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C116" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="D116" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E116" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F116" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="G116" t="s">
         <v>65</v>
@@ -4638,51 +4653,51 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C117" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D117" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E117" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="F117" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="G117" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B118" t="s">
         <v>40</v>
       </c>
       <c r="C118" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E118" t="s">
         <v>55</v>
       </c>
       <c r="F118" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="G118" t="s">
         <v>65</v>
@@ -4696,22 +4711,22 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B119" t="s">
         <v>40</v>
       </c>
       <c r="C119" t="s">
-        <v>183</v>
+        <v>107</v>
       </c>
       <c r="D119" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="E119" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="F119" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G119" t="s">
         <v>65</v>
@@ -4725,22 +4740,22 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B120" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C120" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D120" t="s">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="E120" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="F120" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="G120" t="s">
         <v>65</v>
@@ -4754,80 +4769,80 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B121" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C121" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="D121" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="E121" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F121" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G121" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B122" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C122" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="D122" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="E122" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F122" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="G122" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B123" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D123" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E123" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F123" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G123" t="s">
         <v>65</v>
@@ -4841,22 +4856,22 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B124" t="s">
         <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="D124" t="s">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="E124" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F124" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G124" t="s">
         <v>65</v>
@@ -4870,22 +4885,22 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B125" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C125" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D125" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="E125" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F125" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="G125" t="s">
         <v>65</v>
@@ -4899,51 +4914,51 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B126" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C126" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D126" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="E126" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="F126" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G126" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B127" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C127" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D127" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E127" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="F127" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G127" t="s">
         <v>65</v>
@@ -4957,54 +4972,54 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B128" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D128" t="s">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="E128" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="F128" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="G128" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B129" t="s">
         <v>64</v>
       </c>
       <c r="C129" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D129" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="E129" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F129" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G129" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
@@ -5015,22 +5030,22 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B130" t="s">
         <v>64</v>
       </c>
       <c r="C130" t="s">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="D130" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="E130" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="F130" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="G130" t="s">
         <v>65</v>
@@ -5044,22 +5059,22 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B131" t="s">
         <v>64</v>
       </c>
       <c r="C131" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="E131" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="F131" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="G131" t="s">
         <v>65</v>
@@ -5073,83 +5088,83 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B132" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C132" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D132" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E132" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="F132" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G132" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C133" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D133" t="s">
         <v>155</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="F133" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="G133" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B134" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="D134" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="E134" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F134" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="G134" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
@@ -5160,22 +5175,22 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B135" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C135" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D135" t="s">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="E135" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F135" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G135" t="s">
         <v>65</v>
@@ -5189,22 +5204,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B136" t="s">
         <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="D136" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="E136" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F136" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G136" t="s">
         <v>65</v>
@@ -5218,25 +5233,25 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B137" t="s">
         <v>74</v>
       </c>
       <c r="C137" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="D137" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="E137" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F137" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="G137" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5247,25 +5262,25 @@
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C138" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="E138" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F138" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5276,22 +5291,22 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C139" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="D139" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="F139" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="G139" t="s">
         <v>65</v>
@@ -5305,54 +5320,54 @@
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B140" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="D140" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="E140" t="s">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="F140" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="G140" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B141" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C141" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="D141" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="E141" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="F141" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="G141" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
@@ -5363,51 +5378,51 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B142" t="s">
         <v>77</v>
       </c>
       <c r="C142" t="s">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="D142" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E142" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="F142" t="s">
-        <v>197</v>
+        <v>56</v>
       </c>
       <c r="G142" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B143" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C143" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D143" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="E143" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="F143" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="G143" t="s">
         <v>65</v>
@@ -5421,112 +5436,112 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B144" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C144" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>199</v>
+        <v>35</v>
       </c>
       <c r="E144" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="F144" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G144" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B145" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C145" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="D145" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E145" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="F145" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="G145" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B146" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C146" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="D146" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="E146" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F146" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="G146" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B147" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C147" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="D147" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="E147" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="F147" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G147" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
@@ -5537,25 +5552,25 @@
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B148" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C148" t="s">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="D148" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E148" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="F148" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="G148" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5566,30 +5581,146 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B149" t="s">
+        <v>85</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>89</v>
+      </c>
+      <c r="E149" t="s">
+        <v>67</v>
+      </c>
+      <c r="F149" t="s">
+        <v>202</v>
+      </c>
+      <c r="G149" t="s">
+        <v>65</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>186</v>
+      </c>
+      <c r="B150" t="s">
+        <v>93</v>
+      </c>
+      <c r="C150" t="s">
+        <v>41</v>
+      </c>
+      <c r="D150" t="s">
+        <v>26</v>
+      </c>
+      <c r="E150" t="s">
+        <v>55</v>
+      </c>
+      <c r="F150" t="s">
+        <v>56</v>
+      </c>
+      <c r="G150" t="s">
+        <v>65</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>186</v>
+      </c>
+      <c r="B151" t="s">
+        <v>93</v>
+      </c>
+      <c r="C151" t="s">
+        <v>196</v>
+      </c>
+      <c r="D151" t="s">
+        <v>162</v>
+      </c>
+      <c r="E151" t="s">
+        <v>197</v>
+      </c>
+      <c r="F151" t="s">
+        <v>62</v>
+      </c>
+      <c r="G151" t="s">
+        <v>63</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>186</v>
+      </c>
+      <c r="B152" t="s">
+        <v>93</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>201</v>
+      </c>
+      <c r="E152" t="s">
+        <v>67</v>
+      </c>
+      <c r="F152" t="s">
+        <v>202</v>
+      </c>
+      <c r="G152" t="s">
+        <v>65</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>186</v>
+      </c>
+      <c r="B153" t="s">
         <v>99</v>
       </c>
-      <c r="C149" t="s">
-        <v>191</v>
-      </c>
-      <c r="D149" t="s">
-        <v>200</v>
-      </c>
-      <c r="E149" t="s">
-        <v>192</v>
-      </c>
-      <c r="F149" t="s">
+      <c r="C153" t="s">
+        <v>196</v>
+      </c>
+      <c r="D153" t="s">
+        <v>205</v>
+      </c>
+      <c r="E153" t="s">
+        <v>197</v>
+      </c>
+      <c r="F153" t="s">
         <v>62</v>
       </c>
-      <c r="G149" t="s">
+      <c r="G153" t="s">
         <v>63</v>
       </c>
-      <c r="H149" t="s">
-        <v>18</v>
-      </c>
-      <c r="I149" t="s">
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5601,7 +5732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a7a94a9d-9d2a-483e-bec7-862d5a274c03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c67ee2f7-6430-427b-9117-977fd88fee3c}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5621,16 +5752,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5650,13 +5781,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -5679,16 +5810,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -5708,19 +5839,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C4" t="s">
         <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
@@ -5737,13 +5868,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -5766,19 +5897,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
         <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F6" t="s">
         <v>218</v>
-      </c>
-      <c r="F6" t="s">
-        <v>213</v>
       </c>
       <c r="G6" t="s">
         <v>65</v>
@@ -5795,16 +5926,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -5824,16 +5955,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5853,13 +5984,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -5882,13 +6013,13 @@
         <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
         <v>55</v>
@@ -5911,13 +6042,13 @@
         <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
@@ -5940,13 +6071,13 @@
         <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
         <v>55</v>
@@ -5969,13 +6100,13 @@
         <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C13" t="s">
         <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E13" t="s">
         <v>55</v>
@@ -5998,16 +6129,16 @@
         <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
         <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F14" t="s">
         <v>146</v>
@@ -6027,13 +6158,13 @@
         <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
         <v>55</v>
@@ -6056,13 +6187,13 @@
         <v>151</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
         <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E16" t="s">
         <v>55</v>
@@ -6082,19 +6213,19 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6117,7 +6248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e16e6be0-8b90-44da-a66d-cdb6df8cb3ea}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8d1eaf53-1a21-4e9a-bb60-439868d5b975}">
   <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6134,13 +6265,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6154,13 +6285,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -6174,16 +6305,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6194,13 +6325,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -6214,13 +6345,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -6234,13 +6365,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -6254,16 +6385,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6274,16 +6405,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6294,13 +6425,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -6314,13 +6445,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -6334,16 +6465,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -6354,16 +6485,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6374,16 +6505,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6394,13 +6525,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -6414,16 +6545,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E15" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6434,16 +6565,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6454,16 +6585,16 @@
         <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6474,13 +6605,13 @@
         <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
         <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -6494,13 +6625,13 @@
         <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C19" t="s">
         <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -6514,13 +6645,13 @@
         <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C20" t="s">
         <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -6534,13 +6665,13 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E21" t="s">
         <v>52</v>
@@ -6554,16 +6685,16 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
         <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F22" t="s">
         <v>154</v>
@@ -6574,16 +6705,16 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C23" t="s">
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E23" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6594,13 +6725,13 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C24" t="s">
         <v>152</v>
       </c>
       <c r="D24" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
         <v>158</v>
@@ -6614,16 +6745,16 @@
         <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -6634,19 +6765,19 @@
         <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D26" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F26" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
@@ -6654,13 +6785,13 @@
         <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C27" t="s">
         <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s">
         <v>138</v>
@@ -6674,19 +6805,19 @@
         <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
         <v>128</v>
       </c>
       <c r="F28" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
@@ -6694,13 +6825,13 @@
         <v>151</v>
       </c>
       <c r="B29" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C29" t="s">
         <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E29" t="s">
         <v>60</v>
@@ -6714,16 +6845,16 @@
         <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
         <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E30" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F30" t="s">
         <v>154</v>
@@ -6731,16 +6862,16 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
         <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -6751,16 +6882,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -6771,16 +6902,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C33" t="s">
         <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -6791,16 +6922,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D34" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -6811,16 +6942,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
         <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -6831,16 +6962,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D36" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -6851,16 +6982,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -6871,16 +7002,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
         <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -6891,16 +7022,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B39" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -6911,16 +7042,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C40" t="s">
         <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -6931,16 +7062,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
         <v>70</v>
       </c>
       <c r="D41" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -6951,16 +7082,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C42" t="s">
         <v>68</v>
       </c>
       <c r="D42" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -6971,16 +7102,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D43" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -6991,16 +7122,16 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D44" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -7011,16 +7142,16 @@
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s">
         <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -7031,16 +7162,16 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -7051,16 +7182,16 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B47" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C47" t="s">
         <v>41</v>
       </c>
       <c r="D47" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="279">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -600,48 +600,87 @@
     <t>1K</t>
   </si>
   <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>1TFB|CH</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>1TFB|DZ</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
     <t>1TFB</t>
   </si>
   <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>3TH</t>
-  </si>
-  <si>
     <t>Zajęcia praktyczne - projektowanie i wykonywanie fryzur</t>
   </si>
   <si>
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>Technologie produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - kompetencje zawodowe</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>1FC|JA2</t>
+  </si>
+  <si>
     <t>Informatyka</t>
   </si>
   <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>Wakat2 matematyka</t>
-  </si>
-  <si>
-    <t>1S</t>
+    <t>1S|JA2</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>2B</t>
-  </si>
-  <si>
-    <t>1FC|JA2</t>
-  </si>
-  <si>
-    <t>1S|JA2</t>
-  </si>
-  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -801,7 +840,25 @@
     <t>14:50-14:55</t>
   </si>
   <si>
+    <t>Taszycka Magdalena</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
     <t>parter</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{06cc5c9c-76c3-4cce-a868-e3c429552bc0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{3e06e5f3-ff75-4e6a-a901-5777fc97ac84}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1272,8 +1329,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e9d551ec-3c92-456f-acd3-505165a4ed56}">
-  <dimension ref="A1:I153"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b22f5b59-6c4c-47a0-b8fa-03c7c81c8d53}">
+  <dimension ref="A1:I155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -4439,7 +4496,7 @@
         <v>96</v>
       </c>
       <c r="G109" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4491,19 +4548,19 @@
         <v>190</v>
       </c>
       <c r="E111" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F111" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
@@ -4526,7 +4583,7 @@
         <v>96</v>
       </c>
       <c r="G112" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
@@ -4555,7 +4612,7 @@
         <v>56</v>
       </c>
       <c r="G113" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
@@ -4584,7 +4641,7 @@
         <v>111</v>
       </c>
       <c r="G114" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H114" t="s">
         <v>18</v>
@@ -4636,19 +4693,19 @@
         <v>190</v>
       </c>
       <c r="E116" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F116" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
@@ -4671,13 +4728,13 @@
         <v>96</v>
       </c>
       <c r="G117" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
@@ -4694,19 +4751,19 @@
         <v>155</v>
       </c>
       <c r="E118" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="G118" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
@@ -4723,19 +4780,19 @@
         <v>162</v>
       </c>
       <c r="E119" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="F119" t="s">
         <v>111</v>
       </c>
       <c r="G119" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
@@ -4749,22 +4806,22 @@
         <v>88</v>
       </c>
       <c r="D120" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E120" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F120" t="s">
         <v>132</v>
       </c>
       <c r="G120" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
@@ -4775,25 +4832,25 @@
         <v>40</v>
       </c>
       <c r="C121" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D121" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E121" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="F121" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G121" t="s">
-        <v>76</v>
+        <v>195</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
@@ -4804,25 +4861,25 @@
         <v>40</v>
       </c>
       <c r="C122" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="D122" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="E122" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F122" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="G122" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H122" t="s">
         <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
@@ -4833,25 +4890,25 @@
         <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D123" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="E123" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="F123" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="G123" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
@@ -4859,28 +4916,28 @@
         <v>186</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C124" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="D124" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="E124" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F124" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G124" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
@@ -4891,25 +4948,25 @@
         <v>53</v>
       </c>
       <c r="C125" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="D125" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="E125" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F125" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="G125" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
@@ -4920,19 +4977,19 @@
         <v>53</v>
       </c>
       <c r="C126" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="D126" t="s">
-        <v>194</v>
+        <v>89</v>
       </c>
       <c r="E126" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F126" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="G126" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
@@ -4949,25 +5006,25 @@
         <v>53</v>
       </c>
       <c r="C127" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="E127" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="F127" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="G127" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
@@ -4978,25 +5035,25 @@
         <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D128" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="E128" t="s">
-        <v>92</v>
+        <v>201</v>
       </c>
       <c r="F128" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="G128" t="s">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5004,28 +5061,28 @@
         <v>186</v>
       </c>
       <c r="B129" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="D129" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E129" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="F129" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G129" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="H129" t="s">
         <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5036,25 +5093,25 @@
         <v>64</v>
       </c>
       <c r="C130" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D130" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="E130" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="F130" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="G130" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5065,19 +5122,19 @@
         <v>64</v>
       </c>
       <c r="C131" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F131" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="G131" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
@@ -5094,19 +5151,19 @@
         <v>64</v>
       </c>
       <c r="C132" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="D132" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E132" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="F132" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="G132" t="s">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5123,25 +5180,25 @@
         <v>64</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D133" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="E133" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F133" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
@@ -5152,25 +5209,25 @@
         <v>64</v>
       </c>
       <c r="C134" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="E134" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F134" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="G134" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
@@ -5181,25 +5238,25 @@
         <v>64</v>
       </c>
       <c r="C135" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D135" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="E135" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F135" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G135" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H135" t="s">
         <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
@@ -5207,28 +5264,28 @@
         <v>186</v>
       </c>
       <c r="B136" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C136" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="D136" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="E136" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
       <c r="F136" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="G136" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
@@ -5239,25 +5296,25 @@
         <v>74</v>
       </c>
       <c r="C137" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D137" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E137" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="F137" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G137" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
@@ -5268,25 +5325,25 @@
         <v>74</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D138" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="E138" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F138" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="G138" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
@@ -5297,25 +5354,25 @@
         <v>74</v>
       </c>
       <c r="C139" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E139" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="F139" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
@@ -5326,25 +5383,25 @@
         <v>74</v>
       </c>
       <c r="C140" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="F140" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G140" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
@@ -5355,25 +5412,25 @@
         <v>74</v>
       </c>
       <c r="C141" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D141" t="s">
-        <v>201</v>
+        <v>47</v>
       </c>
       <c r="E141" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="F141" t="s">
-        <v>202</v>
+        <v>96</v>
       </c>
       <c r="G141" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
@@ -5381,28 +5438,28 @@
         <v>186</v>
       </c>
       <c r="B142" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C142" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D142" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E142" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="F142" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G142" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
@@ -5413,19 +5470,19 @@
         <v>77</v>
       </c>
       <c r="C143" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="D143" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="E143" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="F143" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="G143" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
@@ -5442,25 +5499,25 @@
         <v>77</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="D144" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E144" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="F144" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="G144" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="H144" t="s">
         <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15">
@@ -5471,19 +5528,19 @@
         <v>77</v>
       </c>
       <c r="C145" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>148</v>
+        <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="F145" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="G145" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
@@ -5500,19 +5557,19 @@
         <v>77</v>
       </c>
       <c r="C146" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="D146" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="E146" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="F146" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="G146" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
@@ -5526,28 +5583,28 @@
         <v>186</v>
       </c>
       <c r="B147" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C147" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D147" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E147" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F147" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="G147" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
@@ -5558,19 +5615,19 @@
         <v>85</v>
       </c>
       <c r="C148" t="s">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="D148" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E148" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="F148" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G148" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5587,19 +5644,19 @@
         <v>85</v>
       </c>
       <c r="C149" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="D149" t="s">
-        <v>89</v>
+        <v>215</v>
       </c>
       <c r="E149" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F149" t="s">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="G149" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
@@ -5613,28 +5670,28 @@
         <v>186</v>
       </c>
       <c r="B150" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C150" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D150" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="E150" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F150" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G150" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15">
@@ -5645,16 +5702,16 @@
         <v>93</v>
       </c>
       <c r="C151" t="s">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="D151" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="E151" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="F151" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G151" t="s">
         <v>63</v>
@@ -5674,19 +5731,19 @@
         <v>93</v>
       </c>
       <c r="C152" t="s">
-        <v>68</v>
+        <v>205</v>
       </c>
       <c r="D152" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="E152" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="F152" t="s">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="G152" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
@@ -5700,27 +5757,85 @@
         <v>186</v>
       </c>
       <c r="B153" t="s">
+        <v>93</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>133</v>
+      </c>
+      <c r="E153" t="s">
+        <v>36</v>
+      </c>
+      <c r="F153" t="s">
+        <v>37</v>
+      </c>
+      <c r="G153" t="s">
+        <v>109</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>186</v>
+      </c>
+      <c r="B154" t="s">
+        <v>93</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>217</v>
+      </c>
+      <c r="E154" t="s">
+        <v>67</v>
+      </c>
+      <c r="F154" t="s">
+        <v>218</v>
+      </c>
+      <c r="G154" t="s">
+        <v>63</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>186</v>
+      </c>
+      <c r="B155" t="s">
         <v>99</v>
       </c>
-      <c r="C153" t="s">
-        <v>196</v>
-      </c>
-      <c r="D153" t="s">
+      <c r="C155" t="s">
         <v>205</v>
       </c>
-      <c r="E153" t="s">
-        <v>197</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="D155" t="s">
+        <v>217</v>
+      </c>
+      <c r="E155" t="s">
+        <v>216</v>
+      </c>
+      <c r="F155" t="s">
         <v>62</v>
       </c>
-      <c r="G153" t="s">
+      <c r="G155" t="s">
         <v>63</v>
       </c>
-      <c r="H153" t="s">
-        <v>18</v>
-      </c>
-      <c r="I153" t="s">
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5732,7 +5847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c67ee2f7-6430-427b-9117-977fd88fee3c}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d78bebf9-6807-41a8-a15c-5420f42bb5f5}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5752,16 +5867,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5781,13 +5896,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
         <v>55</v>
@@ -5810,16 +5925,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -5839,19 +5954,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
         <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F4" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
@@ -5868,13 +5983,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E5" t="s">
         <v>55</v>
@@ -5897,19 +6012,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C6" t="s">
         <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F6" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G6" t="s">
         <v>65</v>
@@ -5926,16 +6041,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E7" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -5955,16 +6070,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -5984,13 +6099,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="E9" t="s">
         <v>55</v>
@@ -6013,13 +6128,13 @@
         <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
         <v>55</v>
@@ -6042,13 +6157,13 @@
         <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
@@ -6071,13 +6186,13 @@
         <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
         <v>55</v>
@@ -6100,13 +6215,13 @@
         <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C13" t="s">
         <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
         <v>55</v>
@@ -6129,16 +6244,16 @@
         <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
         <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F14" t="s">
         <v>146</v>
@@ -6158,13 +6273,13 @@
         <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
         <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
         <v>55</v>
@@ -6187,13 +6302,13 @@
         <v>151</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="C16" t="s">
         <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="E16" t="s">
         <v>55</v>
@@ -6216,16 +6331,16 @@
         <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C17" t="s">
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="E17" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -6248,8 +6363,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8d1eaf53-1a21-4e9a-bb60-439868d5b975}">
-  <dimension ref="A1:F47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c50155dd-9a10-42e5-b4a6-78c072acaf01}">
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6265,13 +6380,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6285,13 +6400,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -6305,16 +6420,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -6325,13 +6440,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
         <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
@@ -6345,13 +6460,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -6365,13 +6480,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E6" t="s">
         <v>84</v>
@@ -6385,16 +6500,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -6405,16 +6520,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E8" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -6425,13 +6540,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E9" t="s">
         <v>52</v>
@@ -6445,13 +6560,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E10" t="s">
         <v>76</v>
@@ -6465,13 +6580,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s">
         <v>176</v>
@@ -6485,16 +6600,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E12" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6505,16 +6620,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -6525,13 +6640,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C14" t="s">
         <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -6545,16 +6660,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E15" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -6565,16 +6680,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E16" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -6585,13 +6700,13 @@
         <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C17" t="s">
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E17" t="s">
         <v>172</v>
@@ -6605,13 +6720,13 @@
         <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
         <v>107</v>
       </c>
       <c r="D18" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -6625,13 +6740,13 @@
         <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
         <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -6645,13 +6760,13 @@
         <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C20" t="s">
         <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -6665,13 +6780,13 @@
         <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E21" t="s">
         <v>52</v>
@@ -6685,16 +6800,16 @@
         <v>151</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C22" t="s">
         <v>152</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E22" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F22" t="s">
         <v>154</v>
@@ -6705,16 +6820,16 @@
         <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C23" t="s">
         <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E23" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -6725,13 +6840,13 @@
         <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s">
         <v>152</v>
       </c>
       <c r="D24" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E24" t="s">
         <v>158</v>
@@ -6745,13 +6860,13 @@
         <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E25" t="s">
         <v>169</v>
@@ -6765,13 +6880,13 @@
         <v>151</v>
       </c>
       <c r="B26" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C26" t="s">
         <v>172</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E26" t="s">
         <v>176</v>
@@ -6785,13 +6900,13 @@
         <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C27" t="s">
         <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
         <v>138</v>
@@ -6805,13 +6920,13 @@
         <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C28" t="s">
         <v>172</v>
       </c>
       <c r="D28" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="E28" t="s">
         <v>128</v>
@@ -6825,13 +6940,13 @@
         <v>151</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C29" t="s">
         <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E29" t="s">
         <v>60</v>
@@ -6845,16 +6960,16 @@
         <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C30" t="s">
         <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="E30" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F30" t="s">
         <v>154</v>
@@ -6862,16 +6977,16 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="D31" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -6885,16 +7000,16 @@
         <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -6905,16 +7020,16 @@
         <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D33" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -6925,16 +7040,16 @@
         <v>186</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C34" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -6945,16 +7060,16 @@
         <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="D35" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -6965,16 +7080,16 @@
         <v>186</v>
       </c>
       <c r="B36" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>202</v>
       </c>
       <c r="F36" t="s">
         <v>18</v>
@@ -6985,16 +7100,16 @@
         <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="D37" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -7005,16 +7120,16 @@
         <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -7025,16 +7140,16 @@
         <v>186</v>
       </c>
       <c r="B39" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -7045,16 +7160,16 @@
         <v>186</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -7065,16 +7180,16 @@
         <v>186</v>
       </c>
       <c r="B41" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>199</v>
       </c>
       <c r="F41" t="s">
         <v>18</v>
@@ -7085,16 +7200,16 @@
         <v>186</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -7105,16 +7220,16 @@
         <v>186</v>
       </c>
       <c r="B43" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="D43" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -7125,16 +7240,16 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -7145,16 +7260,16 @@
         <v>186</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C45" t="s">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -7165,16 +7280,16 @@
         <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="D46" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>278</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -7185,18 +7300,38 @@
         <v>186</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" t="s">
+        <v>252</v>
+      </c>
+      <c r="E47" t="s">
+        <v>267</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" t="s">
         <v>41</v>
       </c>
-      <c r="D47" t="s">
-        <v>256</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="D48" t="s">
+        <v>269</v>
+      </c>
+      <c r="E48" t="s">
         <v>19</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="299">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -609,6 +609,15 @@
     <t>20.05.2026</t>
   </si>
   <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
+  </si>
+  <si>
+    <t>prf2</t>
+  </si>
+  <si>
     <t>1FA</t>
   </si>
   <si>
@@ -636,6 +645,12 @@
     <t>Organizacja i technika sprzedaży</t>
   </si>
   <si>
+    <t>p. Ulanowska, j. polski za lekcję 1</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
     <t>3TFA</t>
   </si>
   <si>
@@ -648,24 +663,51 @@
     <t>1FC</t>
   </si>
   <si>
+    <t>2TFB</t>
+  </si>
+  <si>
     <t>1FC|JA1</t>
   </si>
   <si>
     <t>2CA</t>
   </si>
   <si>
-    <t>Edukacja obywatelska</t>
-  </si>
-  <si>
     <t>1S|JA1</t>
   </si>
   <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
     <t>2TFA|JA1</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
     <t>1TFA|JA2</t>
   </si>
   <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>2S|CH</t>
+  </si>
+  <si>
+    <t>sg3</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>p. Krzemińska, Projektowanie fryzur, sala 3</t>
+  </si>
+  <si>
     <t>Towar jako przedmiot handlu</t>
   </si>
   <si>
@@ -687,9 +729,6 @@
     <t>1S</t>
   </si>
   <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -705,22 +744,43 @@
     <t>1WA</t>
   </si>
   <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
     <t>1WB</t>
   </si>
   <si>
     <t>1WB|JN2</t>
   </si>
   <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
     <t>22.05.2026</t>
   </si>
   <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
     <t>1FB|JA1</t>
   </si>
   <si>
-    <t>Organizacja sprzedaży</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
+    <t>2K|CH</t>
+  </si>
+  <si>
+    <t>2K|DZ</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>1WB|JN1</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
   </si>
   <si>
     <t>Wakat2 matematyka</t>
@@ -780,6 +840,12 @@
     <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
   </si>
   <si>
+    <t>12:25-13:10</t>
+  </si>
+  <si>
+    <t>chemia</t>
+  </si>
+  <si>
     <t>08:00-08:45</t>
   </si>
   <si>
@@ -834,9 +900,6 @@
     <t>parter</t>
   </si>
   <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
   </si>
   <si>
@@ -849,13 +912,13 @@
     <t>Jarek Zbigniew</t>
   </si>
   <si>
-    <t>Jaworska Edyta</t>
-  </si>
-  <si>
     <t>Smereka Alicja</t>
   </si>
   <si>
     <t>16:30-16:35</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1368,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{dc7f51bd-bfa3-4145-a5eb-1b3bd2eba379}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{24590574-fcaa-41f1-be9a-8ddb7a3bbc60}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1326,8 +1389,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7455550a-fe04-4a81-b59a-309401409f36}">
-  <dimension ref="A1:I284"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0bd7d03d-3687-4398-b7ed-b3ec34fb293c}">
+  <dimension ref="A1:I318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5531,10 +5594,10 @@
         <v>192</v>
       </c>
       <c r="E145" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F145" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G145" t="s">
         <v>69</v>
@@ -5543,7 +5606,7 @@
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
@@ -5560,19 +5623,19 @@
         <v>193</v>
       </c>
       <c r="E146" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F146" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G146" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
@@ -5641,25 +5704,25 @@
         <v>134</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D149" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E149" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="F149" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="G149" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
@@ -5670,19 +5733,19 @@
         <v>134</v>
       </c>
       <c r="C150" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="E150" t="s">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="F150" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G150" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
@@ -5699,19 +5762,19 @@
         <v>134</v>
       </c>
       <c r="C151" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D151" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="E151" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="F151" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G151" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
@@ -5728,19 +5791,19 @@
         <v>134</v>
       </c>
       <c r="C152" t="s">
-        <v>39</v>
+        <v>169</v>
       </c>
       <c r="D152" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="E152" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="F152" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="G152" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
@@ -5757,25 +5820,25 @@
         <v>134</v>
       </c>
       <c r="C153" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="D153" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="E153" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="F153" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="G153" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15">
@@ -5789,7 +5852,7 @@
         <v>138</v>
       </c>
       <c r="D154" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E154" t="s">
         <v>140</v>
@@ -5818,7 +5881,7 @@
         <v>138</v>
       </c>
       <c r="D155" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E155" t="s">
         <v>140</v>
@@ -5847,7 +5910,7 @@
         <v>138</v>
       </c>
       <c r="D156" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E156" t="s">
         <v>140</v>
@@ -5870,28 +5933,28 @@
         <v>194</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="D157" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E157" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="F157" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G157" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
@@ -5902,25 +5965,25 @@
         <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D158" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="E158" t="s">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="F158" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="G158" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
@@ -5931,25 +5994,25 @@
         <v>12</v>
       </c>
       <c r="C159" t="s">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="D159" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="E159" t="s">
-        <v>63</v>
+        <v>196</v>
       </c>
       <c r="F159" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="G159" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
@@ -5960,19 +6023,19 @@
         <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="E160" t="s">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="F160" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
@@ -5989,25 +6052,25 @@
         <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D161" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>56</v>
+        <v>206</v>
       </c>
       <c r="F161" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="G161" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="H161" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="I161" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
@@ -6018,25 +6081,25 @@
         <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D162" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="E162" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="F162" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="G162" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
@@ -6047,22 +6110,22 @@
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="D163" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="E163" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="F163" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G163" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H163" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I163" t="s">
         <v>19</v>
@@ -6076,25 +6139,25 @@
         <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D164" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E164" t="s">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="F164" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="G164" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H164" t="s">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
@@ -6105,19 +6168,19 @@
         <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="D165" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E165" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="F165" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G165" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
@@ -6131,25 +6194,25 @@
         <v>194</v>
       </c>
       <c r="B166" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D166" t="s">
-        <v>208</v>
+        <v>72</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F166" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="G166" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H166" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I166" t="s">
         <v>19</v>
@@ -6160,25 +6223,25 @@
         <v>194</v>
       </c>
       <c r="B167" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D167" t="s">
-        <v>209</v>
+        <v>40</v>
       </c>
       <c r="E167" t="s">
         <v>210</v>
       </c>
       <c r="F167" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="G167" t="s">
         <v>120</v>
       </c>
       <c r="H167" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="I167" t="s">
         <v>19</v>
@@ -6189,28 +6252,28 @@
         <v>194</v>
       </c>
       <c r="B168" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C168" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="D168" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="E168" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="F168" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G168" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
@@ -6221,19 +6284,19 @@
         <v>45</v>
       </c>
       <c r="C169" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E169" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G169" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
@@ -6250,25 +6313,25 @@
         <v>45</v>
       </c>
       <c r="C170" t="s">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="D170" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E170" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="F170" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="G170" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
@@ -6279,25 +6342,25 @@
         <v>45</v>
       </c>
       <c r="C171" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D171" t="s">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c r="E171" t="s">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="F171" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="G171" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
@@ -6308,25 +6371,25 @@
         <v>45</v>
       </c>
       <c r="C172" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D172" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="E172" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="F172" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="G172" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
@@ -6334,28 +6397,28 @@
         <v>194</v>
       </c>
       <c r="B173" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C173" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="D173" t="s">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F173" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G173" t="s">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
@@ -6363,28 +6426,28 @@
         <v>194</v>
       </c>
       <c r="B174" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C174" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D174" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="E174" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F174" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G174" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
@@ -6392,22 +6455,22 @@
         <v>194</v>
       </c>
       <c r="B175" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C175" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="D175" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="E175" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="F175" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="G175" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H175" t="s">
         <v>18</v>
@@ -6421,28 +6484,28 @@
         <v>194</v>
       </c>
       <c r="B176" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C176" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="D176" t="s">
-        <v>177</v>
+        <v>40</v>
       </c>
       <c r="E176" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F176" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G176" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
@@ -6450,25 +6513,25 @@
         <v>194</v>
       </c>
       <c r="B177" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C177" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="D177" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="E177" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G177" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H177" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I177" t="s">
         <v>19</v>
@@ -6482,25 +6545,25 @@
         <v>70</v>
       </c>
       <c r="C178" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D178" t="s">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="E178" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F178" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15">
@@ -6511,25 +6574,25 @@
         <v>70</v>
       </c>
       <c r="C179" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="D179" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="E179" t="s">
-        <v>63</v>
+        <v>196</v>
       </c>
       <c r="F179" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="G179" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H179" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
@@ -6540,25 +6603,25 @@
         <v>70</v>
       </c>
       <c r="C180" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D180" t="s">
-        <v>46</v>
+        <v>216</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F180" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="G180" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H180" t="s">
         <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
@@ -6566,28 +6629,28 @@
         <v>194</v>
       </c>
       <c r="B181" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C181" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D181" t="s">
-        <v>213</v>
+        <v>93</v>
       </c>
       <c r="E181" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F181" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G181" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H181" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
@@ -6595,28 +6658,28 @@
         <v>194</v>
       </c>
       <c r="B182" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C182" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="D182" t="s">
-        <v>211</v>
+        <v>62</v>
       </c>
       <c r="E182" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F182" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G182" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="H182" t="s">
         <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15">
@@ -6624,28 +6687,28 @@
         <v>194</v>
       </c>
       <c r="B183" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C183" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D183" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E183" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="F183" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="G183" t="s">
-        <v>120</v>
+        <v>217</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
@@ -6653,28 +6716,28 @@
         <v>194</v>
       </c>
       <c r="B184" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C184" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="D184" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="E184" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="F184" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="G184" t="s">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="H184" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I184" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="15">
@@ -6682,28 +6745,28 @@
         <v>194</v>
       </c>
       <c r="B185" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C185" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D185" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F185" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G185" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
@@ -6711,28 +6774,28 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C186" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D186" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="E186" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="F186" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G186" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H186" t="s">
         <v>32</v>
       </c>
       <c r="I186" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
@@ -6740,22 +6803,22 @@
         <v>194</v>
       </c>
       <c r="B187" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C187" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D187" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E187" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F187" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="G187" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="H187" t="s">
         <v>18</v>
@@ -6772,25 +6835,25 @@
         <v>92</v>
       </c>
       <c r="C188" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D188" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="E188" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F188" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="G188" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H188" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I188" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="15">
@@ -6798,28 +6861,28 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C189" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D189" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="E189" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F189" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="G189" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H189" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I189" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15">
@@ -6827,28 +6890,28 @@
         <v>194</v>
       </c>
       <c r="B190" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C190" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="D190" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="E190" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F190" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="G190" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H190" t="s">
         <v>18</v>
       </c>
       <c r="I190" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15">
@@ -6856,28 +6919,28 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C191" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="E191" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F191" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="H191" t="s">
         <v>18</v>
       </c>
       <c r="I191" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15">
@@ -6885,28 +6948,28 @@
         <v>194</v>
       </c>
       <c r="B192" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C192" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D192" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="E192" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F192" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G192" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="H192" t="s">
         <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15">
@@ -6914,28 +6977,28 @@
         <v>194</v>
       </c>
       <c r="B193" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C193" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="D193" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="E193" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F193" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G193" t="s">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H193" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15">
@@ -6943,28 +7006,28 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C194" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="D194" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="E194" t="s">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="F194" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G194" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H194" t="s">
         <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
@@ -6972,28 +7035,28 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C195" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="D195" t="s">
-        <v>195</v>
+        <v>151</v>
       </c>
       <c r="E195" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F195" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="G195" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H195" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I195" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="15">
@@ -7001,28 +7064,28 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C196" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="E196" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F196" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G196" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="H196" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I196" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15">
@@ -7030,28 +7093,28 @@
         <v>194</v>
       </c>
       <c r="B197" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C197" t="s">
         <v>91</v>
       </c>
       <c r="D197" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="E197" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F197" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
       <c r="G197" t="s">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="H197" t="s">
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
@@ -7059,170 +7122,170 @@
         <v>194</v>
       </c>
       <c r="B198" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="C198" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D198" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E198" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F198" t="s">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="G198" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="H198" t="s">
         <v>18</v>
       </c>
       <c r="I198" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B199" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C199" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D199" t="s">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="E199" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F199" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="G199" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H199" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I199" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B200" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C200" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D200" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E200" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="F200" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="G200" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H200" t="s">
         <v>18</v>
       </c>
       <c r="I200" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B201" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C201" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D201" t="s">
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="F201" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="G201" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H201" t="s">
         <v>18</v>
       </c>
       <c r="I201" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="15">
       <c r="A202" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B202" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C202" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D202" t="s">
-        <v>220</v>
+        <v>25</v>
       </c>
       <c r="E202" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F202" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="G202" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="H202" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I202" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="15">
       <c r="A203" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C203" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="D203" t="s">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="E203" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F203" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="G203" t="s">
-        <v>221</v>
+        <v>120</v>
       </c>
       <c r="H203" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="I203" t="s">
         <v>19</v>
@@ -7230,28 +7293,28 @@
     </row>
     <row r="204" spans="1:9" ht="15">
       <c r="A204" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C204" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="D204" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E204" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F204" t="s">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="G204" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H204" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I204" t="s">
         <v>19</v>
@@ -7259,115 +7322,115 @@
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B205" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C205" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="D205" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="E205" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F205" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="G205" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H205" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I205" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C206" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="D206" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E206" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="F206" t="s">
-        <v>103</v>
+        <v>197</v>
       </c>
       <c r="G206" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H206" t="s">
         <v>18</v>
       </c>
       <c r="I206" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B207" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C207" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D207" t="s">
-        <v>220</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
       <c r="F207" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="G207" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H207" t="s">
         <v>18</v>
       </c>
       <c r="I207" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B208" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C208" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D208" t="s">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="E208" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="F208" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G208" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H208" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I208" t="s">
         <v>19</v>
@@ -7375,25 +7438,25 @@
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B209" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C209" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="D209" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E209" t="s">
         <v>77</v>
       </c>
       <c r="F209" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="G209" t="s">
-        <v>221</v>
+        <v>126</v>
       </c>
       <c r="H209" t="s">
         <v>18</v>
@@ -7404,112 +7467,112 @@
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B210" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C210" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D210" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E210" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F210" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="G210" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H210" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="I210" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B211" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C211" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D211" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E211" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="F211" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="G211" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H211" t="s">
         <v>18</v>
       </c>
       <c r="I211" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B212" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C212" t="s">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="D212" t="s">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="E212" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="F212" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="G212" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="H212" t="s">
         <v>18</v>
       </c>
       <c r="I212" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B213" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C213" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="D213" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="E213" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F213" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="G213" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H213" t="s">
         <v>18</v>
@@ -7520,25 +7583,25 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B214" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C214" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D214" t="s">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="E214" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="F214" t="s">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="G214" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H214" t="s">
         <v>18</v>
@@ -7549,28 +7612,28 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B215" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C215" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="D215" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="F215" t="s">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="G215" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H215" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I215" t="s">
         <v>19</v>
@@ -7578,16 +7641,16 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B216" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C216" t="s">
         <v>96</v>
       </c>
       <c r="D216" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="E216" t="s">
         <v>73</v>
@@ -7596,7 +7659,7 @@
         <v>95</v>
       </c>
       <c r="G216" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H216" t="s">
         <v>80</v>
@@ -7607,28 +7670,28 @@
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B217" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C217" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="D217" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E217" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F217" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G217" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H217" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I217" t="s">
         <v>19</v>
@@ -7636,112 +7699,112 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B218" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C218" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D218" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E218" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="F218" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="G218" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H218" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I218" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B219" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C219" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D219" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="E219" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F219" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G219" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H219" t="s">
         <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B220" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C220" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D220" t="s">
-        <v>55</v>
+        <v>236</v>
       </c>
       <c r="E220" t="s">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="F220" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G220" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H220" t="s">
         <v>18</v>
       </c>
       <c r="I220" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B221" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C221" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D221" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="E221" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="F221" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="G221" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H221" t="s">
         <v>18</v>
@@ -7752,28 +7815,28 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B222" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C222" t="s">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="D222" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="E222" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="F222" t="s">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="G222" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H222" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I222" t="s">
         <v>19</v>
@@ -7781,16 +7844,16 @@
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B223" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C223" t="s">
         <v>96</v>
       </c>
       <c r="D223" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
       <c r="E223" t="s">
         <v>73</v>
@@ -7799,7 +7862,7 @@
         <v>95</v>
       </c>
       <c r="G223" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H223" t="s">
         <v>80</v>
@@ -7810,25 +7873,25 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B224" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C224" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="D224" t="s">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="E224" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="F224" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="G224" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H224" t="s">
         <v>18</v>
@@ -7839,28 +7902,28 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B225" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C225" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D225" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="E225" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F225" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="G225" t="s">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="H225" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I225" t="s">
         <v>19</v>
@@ -7868,45 +7931,45 @@
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B226" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C226" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D226" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="E226" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F226" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="G226" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H226" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I226" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B227" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C227" t="s">
         <v>20</v>
       </c>
       <c r="D227" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E227" t="s">
         <v>22</v>
@@ -7915,7 +7978,7 @@
         <v>23</v>
       </c>
       <c r="G227" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H227" t="s">
         <v>18</v>
@@ -7926,10 +7989,10 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B228" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C228" t="s">
         <v>166</v>
@@ -7944,7 +8007,7 @@
         <v>103</v>
       </c>
       <c r="G228" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H228" t="s">
         <v>18</v>
@@ -7955,54 +8018,54 @@
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C229" t="s">
         <v>33</v>
       </c>
       <c r="D229" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
       <c r="E229" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F229" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G229" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H229" t="s">
         <v>18</v>
       </c>
       <c r="I229" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B230" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C230" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="D230" t="s">
-        <v>55</v>
+        <v>234</v>
       </c>
       <c r="E230" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="F230" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="G230" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H230" t="s">
         <v>18</v>
@@ -8013,57 +8076,57 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B231" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C231" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="D231" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="E231" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F231" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="G231" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H231" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="I231" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="C232" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D232" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="F232" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G232" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H232" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I232" t="s">
         <v>19</v>
@@ -8071,28 +8134,28 @@
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C233" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D233" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E233" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F233" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="G233" t="s">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="H233" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I233" t="s">
         <v>19</v>
@@ -8100,54 +8163,54 @@
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C234" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="D234" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E234" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F234" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="G234" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="H234" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I234" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B235" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C235" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="D235" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="E235" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="F235" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G235" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H235" t="s">
         <v>18</v>
@@ -8158,86 +8221,86 @@
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B236" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C236" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D236" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="E236" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="F236" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G236" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H236" t="s">
         <v>18</v>
       </c>
       <c r="I236" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B237" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C237" t="s">
         <v>169</v>
       </c>
       <c r="D237" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="E237" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="F237" t="s">
         <v>89</v>
       </c>
       <c r="G237" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H237" t="s">
         <v>18</v>
       </c>
       <c r="I237" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B238" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C238" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="D238" t="s">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="E238" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="F238" t="s">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="G238" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H238" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I238" t="s">
         <v>19</v>
@@ -8245,86 +8308,86 @@
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B239" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C239" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="D239" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="E239" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F239" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G239" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H239" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I239" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B240" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="C240" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="D240" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E240" t="s">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="F240" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="G240" t="s">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="H240" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I240" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B241" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="C241" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D241" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="E241" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F241" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G241" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H241" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I241" t="s">
         <v>19</v>
@@ -8332,112 +8395,112 @@
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B242" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C242" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D242" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E242" t="s">
-        <v>214</v>
+        <v>51</v>
       </c>
       <c r="F242" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="G242" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H242" t="s">
         <v>18</v>
       </c>
       <c r="I242" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B243" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C243" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D243" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F243" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G243" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H243" t="s">
         <v>80</v>
       </c>
       <c r="I243" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B244" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C244" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D244" t="s">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="E244" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F244" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G244" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H244" t="s">
         <v>18</v>
       </c>
       <c r="I244" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B245" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C245" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D245" t="s">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="E245" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F245" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="G245" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="H245" t="s">
         <v>18</v>
@@ -8448,141 +8511,141 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B246" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C246" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="D246" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="E246" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F246" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G246" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H246" t="s">
         <v>18</v>
       </c>
       <c r="I246" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B247" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="C247" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="D247" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="E247" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F247" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G247" t="s">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="H247" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I247" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B248" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="C248" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D248" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="E248" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F248" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G248" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H248" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I248" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B249" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="C249" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D249" t="s">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="E249" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="F249" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G249" t="s">
-        <v>120</v>
+        <v>217</v>
       </c>
       <c r="H249" t="s">
         <v>18</v>
       </c>
       <c r="I249" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B250" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C250" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D250" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E250" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F250" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G250" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H250" t="s">
         <v>18</v>
@@ -8593,83 +8656,83 @@
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B251" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C251" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="D251" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="E251" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F251" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="G251" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="H251" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I251" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
+        <v>232</v>
+      </c>
+      <c r="B252" t="s">
+        <v>98</v>
+      </c>
+      <c r="C252" t="s">
+        <v>13</v>
+      </c>
+      <c r="D252" t="s">
         <v>229</v>
       </c>
-      <c r="B252" t="s">
-        <v>45</v>
-      </c>
-      <c r="C252" t="s">
-        <v>20</v>
-      </c>
-      <c r="D252" t="s">
-        <v>202</v>
-      </c>
       <c r="E252" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F252" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G252" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H252" t="s">
         <v>18</v>
       </c>
       <c r="I252" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B253" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C253" t="s">
         <v>166</v>
       </c>
       <c r="D253" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="E253" t="s">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="F253" t="s">
         <v>103</v>
       </c>
       <c r="G253" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H253" t="s">
         <v>18</v>
@@ -8680,141 +8743,141 @@
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B254" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C254" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D254" t="s">
-        <v>215</v>
+        <v>14</v>
       </c>
       <c r="E254" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F254" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="G254" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="H254" t="s">
         <v>18</v>
       </c>
       <c r="I254" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B255" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="C255" t="s">
         <v>169</v>
       </c>
       <c r="D255" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E255" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F255" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G255" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H255" t="s">
         <v>18</v>
       </c>
       <c r="I255" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B256" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C256" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D256" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="E256" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="F256" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G256" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H256" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I256" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B257" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C257" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="D257" t="s">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="E257" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="F257" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G257" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H257" t="s">
         <v>18</v>
       </c>
       <c r="I257" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B258" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C258" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="D258" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="E258" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F258" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="G258" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H258" t="s">
         <v>18</v>
@@ -8825,170 +8888,170 @@
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B259" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C259" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="D259" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="E259" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F259" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G259" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H259" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I259" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B260" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C260" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D260" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E260" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="F260" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G260" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H260" t="s">
         <v>18</v>
       </c>
       <c r="I260" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B261" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C261" t="s">
         <v>166</v>
       </c>
       <c r="D261" t="s">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="E261" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F261" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G261" t="s">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="H261" t="s">
         <v>18</v>
       </c>
       <c r="I261" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B262" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C262" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D262" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="E262" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="F262" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G262" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="H262" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I262" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B263" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C263" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="D263" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E263" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F263" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="G263" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H263" t="s">
         <v>18</v>
       </c>
       <c r="I263" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B264" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C264" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="D264" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="E264" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="F264" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="G264" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H264" t="s">
         <v>18</v>
@@ -8999,25 +9062,25 @@
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B265" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C265" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D265" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="E265" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F265" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G265" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H265" t="s">
         <v>18</v>
@@ -9028,112 +9091,112 @@
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B266" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C266" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D266" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="E266" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F266" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G266" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H266" t="s">
         <v>18</v>
       </c>
       <c r="I266" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B267" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C267" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D267" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E267" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F267" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="G267" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H267" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I267" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B268" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C268" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D268" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="E268" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F268" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G268" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="H268" t="s">
         <v>18</v>
       </c>
       <c r="I268" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B269" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C269" t="s">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="D269" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="E269" t="s">
-        <v>232</v>
+        <v>51</v>
       </c>
       <c r="F269" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G269" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H269" t="s">
         <v>18</v>
@@ -9144,25 +9207,25 @@
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B270" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C270" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="D270" t="s">
-        <v>14</v>
+        <v>247</v>
       </c>
       <c r="E270" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="F270" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G270" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H270" t="s">
         <v>18</v>
@@ -9173,25 +9236,25 @@
     </row>
     <row r="271" spans="1:9" ht="15">
       <c r="A271" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B271" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="C271" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="D271" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="E271" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F271" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G271" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H271" t="s">
         <v>18</v>
@@ -9202,25 +9265,25 @@
     </row>
     <row r="272" spans="1:9" ht="15">
       <c r="A272" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B272" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="C272" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="D272" t="s">
         <v>209</v>
       </c>
       <c r="E272" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F272" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G272" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H272" t="s">
         <v>18</v>
@@ -9231,54 +9294,54 @@
     </row>
     <row r="273" spans="1:9" ht="15">
       <c r="A273" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B273" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="C273" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="D273" t="s">
-        <v>55</v>
+        <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F273" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G273" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H273" t="s">
         <v>18</v>
       </c>
       <c r="I273" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="15">
       <c r="A274" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B274" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="C274" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D274" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="E274" t="s">
-        <v>232</v>
+        <v>22</v>
       </c>
       <c r="F274" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="G274" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H274" t="s">
         <v>18</v>
@@ -9289,112 +9352,112 @@
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B275" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="C275" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="D275" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E275" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F275" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G275" t="s">
-        <v>234</v>
+        <v>37</v>
       </c>
       <c r="H275" t="s">
         <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
+        <v>245</v>
+      </c>
+      <c r="B276" t="s">
+        <v>45</v>
+      </c>
+      <c r="C276" t="s">
+        <v>85</v>
+      </c>
+      <c r="D276" t="s">
         <v>229</v>
       </c>
-      <c r="B276" t="s">
-        <v>123</v>
-      </c>
-      <c r="C276" t="s">
-        <v>166</v>
-      </c>
-      <c r="D276" t="s">
-        <v>182</v>
-      </c>
       <c r="E276" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="F276" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G276" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H276" t="s">
         <v>18</v>
       </c>
       <c r="I276" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B277" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="C277" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="D277" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="E277" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F277" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G277" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H277" t="s">
         <v>18</v>
       </c>
       <c r="I277" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B278" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="C278" t="s">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="D278" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="E278" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="F278" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="H278" t="s">
         <v>18</v>
@@ -9405,25 +9468,25 @@
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B279" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="C279" t="s">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="D279" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="E279" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F279" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G279" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H279" t="s">
         <v>18</v>
@@ -9434,147 +9497,1133 @@
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B280" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="C280" t="s">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="D280" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="E280" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F280" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G280" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B281" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C281" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="D281" t="s">
-        <v>182</v>
+        <v>236</v>
       </c>
       <c r="E281" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
       <c r="F281" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G281" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H281" t="s">
         <v>18</v>
       </c>
       <c r="I281" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B282" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C282" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D282" t="s">
-        <v>94</v>
+        <v>234</v>
       </c>
       <c r="E282" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="F282" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G282" t="s">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="H282" t="s">
         <v>18</v>
       </c>
       <c r="I282" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B283" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C283" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D283" t="s">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="E283" t="s">
-        <v>232</v>
+        <v>63</v>
       </c>
       <c r="F283" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G283" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="H283" t="s">
         <v>18</v>
       </c>
       <c r="I283" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B284" t="s">
+        <v>70</v>
+      </c>
+      <c r="C284" t="s">
+        <v>169</v>
+      </c>
+      <c r="D284" t="s">
+        <v>25</v>
+      </c>
+      <c r="E284" t="s">
+        <v>60</v>
+      </c>
+      <c r="F284" t="s">
+        <v>61</v>
+      </c>
+      <c r="G284" t="s">
+        <v>37</v>
+      </c>
+      <c r="H284" t="s">
+        <v>18</v>
+      </c>
+      <c r="I284" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="15">
+      <c r="A285" t="s">
+        <v>245</v>
+      </c>
+      <c r="B285" t="s">
+        <v>92</v>
+      </c>
+      <c r="C285" t="s">
+        <v>246</v>
+      </c>
+      <c r="D285" t="s">
+        <v>55</v>
+      </c>
+      <c r="E285" t="s">
+        <v>129</v>
+      </c>
+      <c r="F285" t="s">
+        <v>78</v>
+      </c>
+      <c r="G285" t="s">
+        <v>17</v>
+      </c>
+      <c r="H285" t="s">
+        <v>18</v>
+      </c>
+      <c r="I285" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="15">
+      <c r="A286" t="s">
+        <v>245</v>
+      </c>
+      <c r="B286" t="s">
+        <v>92</v>
+      </c>
+      <c r="C286" t="s">
+        <v>13</v>
+      </c>
+      <c r="D286" t="s">
+        <v>182</v>
+      </c>
+      <c r="E286" t="s">
+        <v>88</v>
+      </c>
+      <c r="F286" t="s">
+        <v>68</v>
+      </c>
+      <c r="G286" t="s">
+        <v>90</v>
+      </c>
+      <c r="H286" t="s">
+        <v>18</v>
+      </c>
+      <c r="I286" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="15">
+      <c r="A287" t="s">
+        <v>245</v>
+      </c>
+      <c r="B287" t="s">
+        <v>92</v>
+      </c>
+      <c r="C287" t="s">
+        <v>20</v>
+      </c>
+      <c r="D287" t="s">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>60</v>
+      </c>
+      <c r="F287" t="s">
+        <v>61</v>
+      </c>
+      <c r="G287" t="s">
+        <v>37</v>
+      </c>
+      <c r="H287" t="s">
+        <v>18</v>
+      </c>
+      <c r="I287" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="15">
+      <c r="A288" t="s">
+        <v>245</v>
+      </c>
+      <c r="B288" t="s">
+        <v>92</v>
+      </c>
+      <c r="C288" t="s">
+        <v>166</v>
+      </c>
+      <c r="D288" t="s">
+        <v>14</v>
+      </c>
+      <c r="E288" t="s">
+        <v>102</v>
+      </c>
+      <c r="F288" t="s">
+        <v>103</v>
+      </c>
+      <c r="G288" t="s">
+        <v>126</v>
+      </c>
+      <c r="H288" t="s">
+        <v>18</v>
+      </c>
+      <c r="I288" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="15">
+      <c r="A289" t="s">
+        <v>245</v>
+      </c>
+      <c r="B289" t="s">
+        <v>92</v>
+      </c>
+      <c r="C289" t="s">
+        <v>85</v>
+      </c>
+      <c r="D289" t="s">
+        <v>128</v>
+      </c>
+      <c r="E289" t="s">
+        <v>63</v>
+      </c>
+      <c r="F289" t="s">
+        <v>95</v>
+      </c>
+      <c r="G289" t="s">
+        <v>66</v>
+      </c>
+      <c r="H289" t="s">
+        <v>18</v>
+      </c>
+      <c r="I289" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="15">
+      <c r="A290" t="s">
+        <v>245</v>
+      </c>
+      <c r="B290" t="s">
+        <v>92</v>
+      </c>
+      <c r="C290" t="s">
+        <v>169</v>
+      </c>
+      <c r="D290" t="s">
+        <v>25</v>
+      </c>
+      <c r="E290" t="s">
+        <v>73</v>
+      </c>
+      <c r="F290" t="s">
+        <v>89</v>
+      </c>
+      <c r="G290" t="s">
+        <v>106</v>
+      </c>
+      <c r="H290" t="s">
+        <v>18</v>
+      </c>
+      <c r="I290" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="15">
+      <c r="A291" t="s">
+        <v>245</v>
+      </c>
+      <c r="B291" t="s">
+        <v>92</v>
+      </c>
+      <c r="C291" t="s">
+        <v>108</v>
+      </c>
+      <c r="D291" t="s">
+        <v>234</v>
+      </c>
+      <c r="E291" t="s">
+        <v>250</v>
+      </c>
+      <c r="F291" t="s">
+        <v>27</v>
+      </c>
+      <c r="G291" t="s">
+        <v>24</v>
+      </c>
+      <c r="H291" t="s">
+        <v>18</v>
+      </c>
+      <c r="I291" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="15">
+      <c r="A292" t="s">
+        <v>245</v>
+      </c>
+      <c r="B292" t="s">
+        <v>98</v>
+      </c>
+      <c r="C292" t="s">
+        <v>246</v>
+      </c>
+      <c r="D292" t="s">
+        <v>213</v>
+      </c>
+      <c r="E292" t="s">
+        <v>129</v>
+      </c>
+      <c r="F292" t="s">
+        <v>48</v>
+      </c>
+      <c r="G292" t="s">
+        <v>49</v>
+      </c>
+      <c r="H292" t="s">
+        <v>18</v>
+      </c>
+      <c r="I292" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="15">
+      <c r="A293" t="s">
+        <v>245</v>
+      </c>
+      <c r="B293" t="s">
+        <v>98</v>
+      </c>
+      <c r="C293" t="s">
+        <v>13</v>
+      </c>
+      <c r="D293" t="s">
+        <v>165</v>
+      </c>
+      <c r="E293" t="s">
+        <v>15</v>
+      </c>
+      <c r="F293" t="s">
+        <v>16</v>
+      </c>
+      <c r="G293" t="s">
+        <v>82</v>
+      </c>
+      <c r="H293" t="s">
+        <v>18</v>
+      </c>
+      <c r="I293" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="15">
+      <c r="A294" t="s">
+        <v>245</v>
+      </c>
+      <c r="B294" t="s">
+        <v>98</v>
+      </c>
+      <c r="C294" t="s">
+        <v>166</v>
+      </c>
+      <c r="D294" t="s">
+        <v>14</v>
+      </c>
+      <c r="E294" t="s">
+        <v>102</v>
+      </c>
+      <c r="F294" t="s">
+        <v>103</v>
+      </c>
+      <c r="G294" t="s">
+        <v>126</v>
+      </c>
+      <c r="H294" t="s">
+        <v>18</v>
+      </c>
+      <c r="I294" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="15">
+      <c r="A295" t="s">
+        <v>245</v>
+      </c>
+      <c r="B295" t="s">
+        <v>98</v>
+      </c>
+      <c r="C295" t="s">
+        <v>85</v>
+      </c>
+      <c r="D295" t="s">
+        <v>215</v>
+      </c>
+      <c r="E295" t="s">
+        <v>63</v>
+      </c>
+      <c r="F295" t="s">
+        <v>95</v>
+      </c>
+      <c r="G295" t="s">
+        <v>66</v>
+      </c>
+      <c r="H295" t="s">
+        <v>18</v>
+      </c>
+      <c r="I295" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="15">
+      <c r="A296" t="s">
+        <v>245</v>
+      </c>
+      <c r="B296" t="s">
+        <v>98</v>
+      </c>
+      <c r="C296" t="s">
+        <v>33</v>
+      </c>
+      <c r="D296" t="s">
+        <v>212</v>
+      </c>
+      <c r="E296" t="s">
+        <v>60</v>
+      </c>
+      <c r="F296" t="s">
+        <v>61</v>
+      </c>
+      <c r="G296" t="s">
+        <v>37</v>
+      </c>
+      <c r="H296" t="s">
+        <v>18</v>
+      </c>
+      <c r="I296" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="15">
+      <c r="A297" t="s">
+        <v>245</v>
+      </c>
+      <c r="B297" t="s">
+        <v>98</v>
+      </c>
+      <c r="C297" t="s">
+        <v>169</v>
+      </c>
+      <c r="D297" t="s">
+        <v>177</v>
+      </c>
+      <c r="E297" t="s">
+        <v>73</v>
+      </c>
+      <c r="F297" t="s">
+        <v>89</v>
+      </c>
+      <c r="G297" t="s">
+        <v>106</v>
+      </c>
+      <c r="H297" t="s">
+        <v>18</v>
+      </c>
+      <c r="I297" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" ht="15">
+      <c r="A298" t="s">
+        <v>245</v>
+      </c>
+      <c r="B298" t="s">
+        <v>98</v>
+      </c>
+      <c r="C298" t="s">
+        <v>108</v>
+      </c>
+      <c r="D298" t="s">
+        <v>251</v>
+      </c>
+      <c r="E298" t="s">
+        <v>252</v>
+      </c>
+      <c r="F298" t="s">
+        <v>105</v>
+      </c>
+      <c r="G298" t="s">
+        <v>220</v>
+      </c>
+      <c r="H298" t="s">
+        <v>18</v>
+      </c>
+      <c r="I298" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" ht="15">
+      <c r="A299" t="s">
+        <v>245</v>
+      </c>
+      <c r="B299" t="s">
+        <v>98</v>
+      </c>
+      <c r="C299" t="s">
+        <v>108</v>
+      </c>
+      <c r="D299" t="s">
+        <v>243</v>
+      </c>
+      <c r="E299" t="s">
+        <v>252</v>
+      </c>
+      <c r="F299" t="s">
+        <v>105</v>
+      </c>
+      <c r="G299" t="s">
+        <v>220</v>
+      </c>
+      <c r="H299" t="s">
+        <v>18</v>
+      </c>
+      <c r="I299" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="15">
+      <c r="A300" t="s">
+        <v>245</v>
+      </c>
+      <c r="B300" t="s">
+        <v>114</v>
+      </c>
+      <c r="C300" t="s">
+        <v>246</v>
+      </c>
+      <c r="D300" t="s">
+        <v>213</v>
+      </c>
+      <c r="E300" t="s">
+        <v>129</v>
+      </c>
+      <c r="F300" t="s">
+        <v>48</v>
+      </c>
+      <c r="G300" t="s">
+        <v>49</v>
+      </c>
+      <c r="H300" t="s">
+        <v>18</v>
+      </c>
+      <c r="I300" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="15">
+      <c r="A301" t="s">
+        <v>245</v>
+      </c>
+      <c r="B301" t="s">
+        <v>114</v>
+      </c>
+      <c r="C301" t="s">
+        <v>13</v>
+      </c>
+      <c r="D301" t="s">
+        <v>179</v>
+      </c>
+      <c r="E301" t="s">
+        <v>63</v>
+      </c>
+      <c r="F301" t="s">
+        <v>16</v>
+      </c>
+      <c r="G301" t="s">
+        <v>65</v>
+      </c>
+      <c r="H301" t="s">
+        <v>18</v>
+      </c>
+      <c r="I301" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" ht="15">
+      <c r="A302" t="s">
+        <v>245</v>
+      </c>
+      <c r="B302" t="s">
+        <v>114</v>
+      </c>
+      <c r="C302" t="s">
+        <v>166</v>
+      </c>
+      <c r="D302" t="s">
+        <v>14</v>
+      </c>
+      <c r="E302" t="s">
+        <v>102</v>
+      </c>
+      <c r="F302" t="s">
+        <v>103</v>
+      </c>
+      <c r="G302" t="s">
+        <v>126</v>
+      </c>
+      <c r="H302" t="s">
+        <v>18</v>
+      </c>
+      <c r="I302" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="15">
+      <c r="A303" t="s">
+        <v>245</v>
+      </c>
+      <c r="B303" t="s">
+        <v>114</v>
+      </c>
+      <c r="C303" t="s">
+        <v>85</v>
+      </c>
+      <c r="D303" t="s">
+        <v>212</v>
+      </c>
+      <c r="E303" t="s">
+        <v>63</v>
+      </c>
+      <c r="F303" t="s">
+        <v>95</v>
+      </c>
+      <c r="G303" t="s">
+        <v>66</v>
+      </c>
+      <c r="H303" t="s">
+        <v>18</v>
+      </c>
+      <c r="I303" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" ht="15">
+      <c r="A304" t="s">
+        <v>245</v>
+      </c>
+      <c r="B304" t="s">
+        <v>114</v>
+      </c>
+      <c r="C304" t="s">
+        <v>33</v>
+      </c>
+      <c r="D304" t="s">
+        <v>215</v>
+      </c>
+      <c r="E304" t="s">
+        <v>73</v>
+      </c>
+      <c r="F304" t="s">
+        <v>89</v>
+      </c>
+      <c r="G304" t="s">
+        <v>106</v>
+      </c>
+      <c r="H304" t="s">
+        <v>18</v>
+      </c>
+      <c r="I304" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" ht="15">
+      <c r="A305" t="s">
+        <v>245</v>
+      </c>
+      <c r="B305" t="s">
+        <v>114</v>
+      </c>
+      <c r="C305" t="s">
+        <v>169</v>
+      </c>
+      <c r="D305" t="s">
+        <v>55</v>
+      </c>
+      <c r="E305" t="s">
+        <v>129</v>
+      </c>
+      <c r="F305" t="s">
+        <v>78</v>
+      </c>
+      <c r="G305" t="s">
+        <v>130</v>
+      </c>
+      <c r="H305" t="s">
+        <v>18</v>
+      </c>
+      <c r="I305" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="15">
+      <c r="A306" t="s">
+        <v>245</v>
+      </c>
+      <c r="B306" t="s">
+        <v>114</v>
+      </c>
+      <c r="C306" t="s">
+        <v>108</v>
+      </c>
+      <c r="D306" t="s">
+        <v>242</v>
+      </c>
+      <c r="E306" t="s">
+        <v>73</v>
+      </c>
+      <c r="F306" t="s">
+        <v>74</v>
+      </c>
+      <c r="G306" t="s">
+        <v>71</v>
+      </c>
+      <c r="H306" t="s">
+        <v>18</v>
+      </c>
+      <c r="I306" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" ht="15">
+      <c r="A307" t="s">
+        <v>245</v>
+      </c>
+      <c r="B307" t="s">
+        <v>114</v>
+      </c>
+      <c r="C307" t="s">
+        <v>253</v>
+      </c>
+      <c r="D307" t="s">
+        <v>234</v>
+      </c>
+      <c r="E307" t="s">
+        <v>56</v>
+      </c>
+      <c r="F307" t="s">
+        <v>64</v>
+      </c>
+      <c r="G307" t="s">
+        <v>254</v>
+      </c>
+      <c r="H307" t="s">
+        <v>18</v>
+      </c>
+      <c r="I307" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="15">
+      <c r="A308" t="s">
+        <v>245</v>
+      </c>
+      <c r="B308" t="s">
+        <v>123</v>
+      </c>
+      <c r="C308" t="s">
+        <v>246</v>
+      </c>
+      <c r="D308" t="s">
+        <v>209</v>
+      </c>
+      <c r="E308" t="s">
+        <v>129</v>
+      </c>
+      <c r="F308" t="s">
+        <v>36</v>
+      </c>
+      <c r="G308" t="s">
+        <v>126</v>
+      </c>
+      <c r="H308" t="s">
+        <v>18</v>
+      </c>
+      <c r="I308" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="15">
+      <c r="A309" t="s">
+        <v>245</v>
+      </c>
+      <c r="B309" t="s">
+        <v>123</v>
+      </c>
+      <c r="C309" t="s">
+        <v>166</v>
+      </c>
+      <c r="D309" t="s">
+        <v>182</v>
+      </c>
+      <c r="E309" t="s">
+        <v>15</v>
+      </c>
+      <c r="F309" t="s">
+        <v>89</v>
+      </c>
+      <c r="G309" t="s">
+        <v>244</v>
+      </c>
+      <c r="H309" t="s">
+        <v>18</v>
+      </c>
+      <c r="I309" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="15">
+      <c r="A310" t="s">
+        <v>245</v>
+      </c>
+      <c r="B310" t="s">
+        <v>123</v>
+      </c>
+      <c r="C310" t="s">
+        <v>33</v>
+      </c>
+      <c r="D310" t="s">
+        <v>55</v>
+      </c>
+      <c r="E310" t="s">
+        <v>56</v>
+      </c>
+      <c r="F310" t="s">
+        <v>81</v>
+      </c>
+      <c r="G310" t="s">
+        <v>58</v>
+      </c>
+      <c r="H310" t="s">
+        <v>18</v>
+      </c>
+      <c r="I310" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="15">
+      <c r="A311" t="s">
+        <v>245</v>
+      </c>
+      <c r="B311" t="s">
+        <v>123</v>
+      </c>
+      <c r="C311" t="s">
+        <v>108</v>
+      </c>
+      <c r="D311" t="s">
+        <v>179</v>
+      </c>
+      <c r="E311" t="s">
+        <v>51</v>
+      </c>
+      <c r="F311" t="s">
+        <v>107</v>
+      </c>
+      <c r="G311" t="s">
+        <v>66</v>
+      </c>
+      <c r="H311" t="s">
+        <v>18</v>
+      </c>
+      <c r="I311" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" ht="15">
+      <c r="A312" t="s">
+        <v>245</v>
+      </c>
+      <c r="B312" t="s">
+        <v>123</v>
+      </c>
+      <c r="C312" t="s">
+        <v>230</v>
+      </c>
+      <c r="D312" t="s">
+        <v>231</v>
+      </c>
+      <c r="E312" t="s">
+        <v>67</v>
+      </c>
+      <c r="F312" t="s">
+        <v>68</v>
+      </c>
+      <c r="G312" t="s">
+        <v>69</v>
+      </c>
+      <c r="H312" t="s">
+        <v>18</v>
+      </c>
+      <c r="I312" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="15">
+      <c r="A313" t="s">
+        <v>245</v>
+      </c>
+      <c r="B313" t="s">
+        <v>123</v>
+      </c>
+      <c r="C313" t="s">
+        <v>253</v>
+      </c>
+      <c r="D313" t="s">
+        <v>234</v>
+      </c>
+      <c r="E313" t="s">
+        <v>56</v>
+      </c>
+      <c r="F313" t="s">
+        <v>64</v>
+      </c>
+      <c r="G313" t="s">
+        <v>254</v>
+      </c>
+      <c r="H313" t="s">
+        <v>18</v>
+      </c>
+      <c r="I313" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" ht="15">
+      <c r="A314" t="s">
+        <v>245</v>
+      </c>
+      <c r="B314" t="s">
+        <v>131</v>
+      </c>
+      <c r="C314" t="s">
+        <v>246</v>
+      </c>
+      <c r="D314" t="s">
+        <v>209</v>
+      </c>
+      <c r="E314" t="s">
+        <v>129</v>
+      </c>
+      <c r="F314" t="s">
+        <v>36</v>
+      </c>
+      <c r="G314" t="s">
+        <v>126</v>
+      </c>
+      <c r="H314" t="s">
+        <v>18</v>
+      </c>
+      <c r="I314" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="15">
+      <c r="A315" t="s">
+        <v>245</v>
+      </c>
+      <c r="B315" t="s">
+        <v>131</v>
+      </c>
+      <c r="C315" t="s">
+        <v>166</v>
+      </c>
+      <c r="D315" t="s">
+        <v>182</v>
+      </c>
+      <c r="E315" t="s">
+        <v>15</v>
+      </c>
+      <c r="F315" t="s">
+        <v>89</v>
+      </c>
+      <c r="G315" t="s">
+        <v>244</v>
+      </c>
+      <c r="H315" t="s">
+        <v>18</v>
+      </c>
+      <c r="I315" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" ht="15">
+      <c r="A316" t="s">
+        <v>245</v>
+      </c>
+      <c r="B316" t="s">
+        <v>131</v>
+      </c>
+      <c r="C316" t="s">
+        <v>85</v>
+      </c>
+      <c r="D316" t="s">
+        <v>94</v>
+      </c>
+      <c r="E316" t="s">
+        <v>63</v>
+      </c>
+      <c r="F316" t="s">
+        <v>64</v>
+      </c>
+      <c r="G316" t="s">
+        <v>66</v>
+      </c>
+      <c r="H316" t="s">
+        <v>18</v>
+      </c>
+      <c r="I316" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="15">
+      <c r="A317" t="s">
+        <v>245</v>
+      </c>
+      <c r="B317" t="s">
+        <v>131</v>
+      </c>
+      <c r="C317" t="s">
+        <v>108</v>
+      </c>
+      <c r="D317" t="s">
+        <v>34</v>
+      </c>
+      <c r="E317" t="s">
+        <v>60</v>
+      </c>
+      <c r="F317" t="s">
+        <v>61</v>
+      </c>
+      <c r="G317" t="s">
+        <v>109</v>
+      </c>
+      <c r="H317" t="s">
+        <v>18</v>
+      </c>
+      <c r="I317" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="15">
+      <c r="A318" t="s">
+        <v>245</v>
+      </c>
+      <c r="B318" t="s">
         <v>191</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C318" t="s">
         <v>85</v>
       </c>
-      <c r="D284" t="s">
-        <v>220</v>
-      </c>
-      <c r="E284" t="s">
+      <c r="D318" t="s">
+        <v>234</v>
+      </c>
+      <c r="E318" t="s">
         <v>63</v>
       </c>
-      <c r="F284" t="s">
+      <c r="F318" t="s">
         <v>64</v>
       </c>
-      <c r="G284" t="s">
-        <v>120</v>
-      </c>
-      <c r="H284" t="s">
-        <v>18</v>
-      </c>
-      <c r="I284" t="s">
-        <v>19</v>
+      <c r="G318" t="s">
+        <v>66</v>
+      </c>
+      <c r="H318" t="s">
+        <v>18</v>
+      </c>
+      <c r="I318" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -9585,8 +10634,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c7cd7d39-2484-43f1-90d0-0e67dee91f46}">
-  <dimension ref="A1:I8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b4fcc0ae-9d1a-469b-9be5-961b0865458a}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -9605,16 +10654,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -9634,16 +10683,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -9663,13 +10712,13 @@
         <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C3" t="s">
         <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
         <v>73</v>
@@ -9692,16 +10741,16 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E4" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -9721,13 +10770,13 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -9750,16 +10799,16 @@
         <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -9779,13 +10828,13 @@
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -9805,19 +10854,19 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>273</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -9826,9 +10875,67 @@
         <v>120</v>
       </c>
       <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15">
+      <c r="A9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" t="s">
         <v>181</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15">
+      <c r="A10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -9840,8 +10947,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{ad97df8f-eca8-4a88-868e-5b46354c5b5c}">
-  <dimension ref="A1:F75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{65f72751-3406-420f-84ff-c5838d2826a9}">
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -9857,13 +10964,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -9877,13 +10984,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -9897,13 +11004,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -9917,13 +11024,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -9937,13 +11044,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -9957,13 +11064,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="E6" t="s">
         <v>69</v>
@@ -9977,13 +11084,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="E7" t="s">
         <v>112</v>
@@ -9997,13 +11104,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E8" t="s">
         <v>189</v>
@@ -10017,13 +11124,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E9" t="s">
         <v>90</v>
@@ -10037,13 +11144,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -10057,13 +11164,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E11" t="s">
         <v>148</v>
@@ -10077,13 +11184,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -10097,13 +11204,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -10117,13 +11224,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -10137,13 +11244,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -10157,13 +11264,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E16" t="s">
         <v>183</v>
@@ -10177,16 +11284,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E17" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -10197,16 +11304,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E18" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
@@ -10217,13 +11324,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -10237,16 +11344,16 @@
         <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C20" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E20" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
@@ -10257,16 +11364,16 @@
         <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C21" t="s">
         <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E21" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -10277,16 +11384,16 @@
         <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C22" t="s">
         <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E22" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -10297,13 +11404,13 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
@@ -10317,16 +11424,16 @@
         <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C24" t="s">
         <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E24" t="s">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -10337,13 +11444,13 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E25" t="s">
         <v>75</v>
@@ -10357,13 +11464,13 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
         <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -10377,13 +11484,13 @@
         <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C27" t="s">
         <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -10397,13 +11504,13 @@
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
         <v>189</v>
@@ -10417,13 +11524,13 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E29" t="s">
         <v>96</v>
@@ -10437,13 +11544,13 @@
         <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="E30" t="s">
         <v>158</v>
@@ -10457,16 +11564,16 @@
         <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="D31" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -10477,16 +11584,16 @@
         <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -10497,16 +11604,16 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E33" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -10517,16 +11624,16 @@
         <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
         <v>18</v>
@@ -10537,19 +11644,19 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="E35" t="s">
-        <v>276</v>
+        <v>178</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
@@ -10557,19 +11664,19 @@
         <v>133</v>
       </c>
       <c r="B36" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
@@ -10577,19 +11684,19 @@
         <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
@@ -10597,16 +11704,16 @@
         <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E38" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -10617,16 +11724,16 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -10637,19 +11744,19 @@
         <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E40" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
@@ -10657,36 +11764,36 @@
         <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E41" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="D42" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -10697,16 +11804,16 @@
         <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -10717,16 +11824,16 @@
         <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -10737,19 +11844,19 @@
         <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
@@ -10757,16 +11864,16 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -10777,19 +11884,19 @@
         <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C47" t="s">
-        <v>183</v>
+        <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
@@ -10797,19 +11904,19 @@
         <v>194</v>
       </c>
       <c r="B48" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
@@ -10817,13 +11924,13 @@
         <v>194</v>
       </c>
       <c r="B49" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -10837,16 +11944,16 @@
         <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -10857,16 +11964,16 @@
         <v>194</v>
       </c>
       <c r="B51" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="C51" t="s">
         <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="F51" t="s">
         <v>32</v>
@@ -10877,16 +11984,16 @@
         <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="F52" t="s">
         <v>18</v>
@@ -10894,19 +12001,19 @@
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -10914,119 +12021,119 @@
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="F56" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F57" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B59" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F59" t="s">
         <v>18</v>
@@ -11034,19 +12141,19 @@
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
         <v>18</v>
@@ -11054,59 +12161,59 @@
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B61" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B63" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -11114,19 +12221,19 @@
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B64" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -11134,39 +12241,39 @@
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B65" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F65" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B66" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="C66" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F66" t="s">
         <v>18</v>
@@ -11174,19 +12281,19 @@
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="D67" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -11194,19 +12301,19 @@
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="C68" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -11214,19 +12321,19 @@
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="D69" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
@@ -11234,19 +12341,19 @@
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D70" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
@@ -11254,19 +12361,19 @@
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B71" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -11274,19 +12381,19 @@
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E72" t="s">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -11294,36 +12401,36 @@
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B73" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="D73" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>244</v>
       </c>
       <c r="F73" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
@@ -11334,21 +12441,281 @@
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C75" t="s">
+        <v>169</v>
+      </c>
+      <c r="D75" t="s">
+        <v>291</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15">
+      <c r="A76" t="s">
+        <v>245</v>
+      </c>
+      <c r="B76" t="s">
+        <v>281</v>
+      </c>
+      <c r="C76" t="s">
+        <v>246</v>
+      </c>
+      <c r="D76" t="s">
+        <v>278</v>
+      </c>
+      <c r="E76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15">
+      <c r="A77" t="s">
+        <v>245</v>
+      </c>
+      <c r="B77" t="s">
+        <v>281</v>
+      </c>
+      <c r="C77" t="s">
+        <v>85</v>
+      </c>
+      <c r="D77" t="s">
+        <v>291</v>
+      </c>
+      <c r="E77" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15">
+      <c r="A78" t="s">
+        <v>245</v>
+      </c>
+      <c r="B78" t="s">
+        <v>282</v>
+      </c>
+      <c r="C78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78" t="s">
+        <v>291</v>
+      </c>
+      <c r="E78" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15">
+      <c r="A79" t="s">
+        <v>245</v>
+      </c>
+      <c r="B79" t="s">
+        <v>285</v>
+      </c>
+      <c r="C79" t="s">
+        <v>246</v>
+      </c>
+      <c r="D79" t="s">
+        <v>284</v>
+      </c>
+      <c r="E79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15">
+      <c r="A80" t="s">
+        <v>245</v>
+      </c>
+      <c r="B80" t="s">
+        <v>285</v>
+      </c>
+      <c r="C80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D80" t="s">
+        <v>286</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15">
+      <c r="A81" t="s">
+        <v>245</v>
+      </c>
+      <c r="B81" t="s">
+        <v>288</v>
+      </c>
+      <c r="C81" t="s">
+        <v>246</v>
+      </c>
+      <c r="D81" t="s">
+        <v>278</v>
+      </c>
+      <c r="E81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15">
+      <c r="A82" t="s">
+        <v>245</v>
+      </c>
+      <c r="B82" t="s">
+        <v>288</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>283</v>
+      </c>
+      <c r="E82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15">
+      <c r="A83" t="s">
+        <v>245</v>
+      </c>
+      <c r="B83" t="s">
+        <v>288</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83" t="s">
+        <v>286</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15">
+      <c r="A84" t="s">
+        <v>245</v>
+      </c>
+      <c r="B84" t="s">
+        <v>289</v>
+      </c>
+      <c r="C84" t="s">
+        <v>85</v>
+      </c>
+      <c r="D84" t="s">
+        <v>291</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15">
+      <c r="A85" t="s">
+        <v>245</v>
+      </c>
+      <c r="B85" t="s">
+        <v>289</v>
+      </c>
+      <c r="C85" t="s">
+        <v>169</v>
+      </c>
+      <c r="D85" t="s">
+        <v>286</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15">
+      <c r="A86" t="s">
+        <v>245</v>
+      </c>
+      <c r="B86" t="s">
+        <v>290</v>
+      </c>
+      <c r="C86" t="s">
         <v>108</v>
       </c>
-      <c r="D75" t="s">
-        <v>269</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="D86" t="s">
+        <v>291</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15">
+      <c r="A87" t="s">
+        <v>245</v>
+      </c>
+      <c r="B87" t="s">
+        <v>292</v>
+      </c>
+      <c r="C87" t="s">
+        <v>246</v>
+      </c>
+      <c r="D87" t="s">
+        <v>286</v>
+      </c>
+      <c r="E87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15">
+      <c r="A88" t="s">
+        <v>245</v>
+      </c>
+      <c r="B88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D88" t="s">
+        <v>291</v>
+      </c>
+      <c r="E88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="307">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -672,6 +672,15 @@
     <t>2CA</t>
   </si>
   <si>
+    <t>2TH+4TH</t>
+  </si>
+  <si>
+    <t>Złączenie grup</t>
+  </si>
+  <si>
+    <t>zaplanowano zastępstwo z nauczycielem Nowak Damiana [DW]</t>
+  </si>
+  <si>
     <t>1S|JA1</t>
   </si>
   <si>
@@ -723,18 +732,30 @@
     <t>21.05.2026</t>
   </si>
   <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>1WA|DZ</t>
   </si>
   <si>
     <t>1S</t>
   </si>
   <si>
+    <t>1WB</t>
+  </si>
+  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
     <t>1CB|JA2</t>
   </si>
   <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
     <t>1K|JA2</t>
   </si>
   <si>
@@ -744,15 +765,9 @@
     <t>1WA</t>
   </si>
   <si>
-    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
-  </si>
-  <si>
     <t>Bokuniewicz Sylwia</t>
   </si>
   <si>
-    <t>1WB</t>
-  </si>
-  <si>
     <t>1WB|JN2</t>
   </si>
   <si>
@@ -789,6 +804,12 @@
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
+    <t>sg2</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -844,6 +865,9 @@
   </si>
   <si>
     <t>chemia</t>
+  </si>
+  <si>
+    <t>07:10-07:55</t>
   </si>
   <si>
     <t>08:00-08:45</t>
@@ -1368,7 +1392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{24590574-fcaa-41f1-be9a-8ddb7a3bbc60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{34caae0a-0567-4bb1-bbd4-a9fbbdaa8b8f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1389,8 +1413,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0bd7d03d-3687-4398-b7ed-b3ec34fb293c}">
-  <dimension ref="A1:I318"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{af2b73b2-1b5a-4313-ae87-d1a2c083fe46}">
+  <dimension ref="A1:I335"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1400,7 +1424,7 @@
     <col min="5" max="5" width="54.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="8" max="8" width="56.7142857142857" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6380,7 +6404,7 @@
         <v>118</v>
       </c>
       <c r="F172" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G172" t="s">
         <v>82</v>
@@ -6403,22 +6427,22 @@
         <v>166</v>
       </c>
       <c r="D173" t="s">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="E173" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F173" t="s">
         <v>57</v>
       </c>
       <c r="G173" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
@@ -6499,13 +6523,13 @@
         <v>61</v>
       </c>
       <c r="G176" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="H176" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="I176" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
@@ -6606,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="D180" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E180" t="s">
         <v>22</v>
@@ -6702,7 +6726,7 @@
         <v>161</v>
       </c>
       <c r="G183" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
@@ -6722,16 +6746,16 @@
         <v>28</v>
       </c>
       <c r="D184" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E184" t="s">
         <v>77</v>
       </c>
       <c r="F184" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G184" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H184" t="s">
         <v>32</v>
@@ -6783,7 +6807,7 @@
         <v>25</v>
       </c>
       <c r="E186" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F186" t="s">
         <v>27</v>
@@ -6838,7 +6862,7 @@
         <v>75</v>
       </c>
       <c r="D188" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E188" t="s">
         <v>15</v>
@@ -6925,7 +6949,7 @@
         <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E191" t="s">
         <v>22</v>
@@ -7108,7 +7132,7 @@
         <v>200</v>
       </c>
       <c r="G197" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H197" t="s">
         <v>18</v>
@@ -7125,16 +7149,16 @@
         <v>98</v>
       </c>
       <c r="C198" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D198" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E198" t="s">
         <v>77</v>
       </c>
       <c r="F198" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G198" t="s">
         <v>126</v>
@@ -7218,7 +7242,7 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F201" t="s">
         <v>107</v>
@@ -7285,7 +7309,7 @@
         <v>120</v>
       </c>
       <c r="H203" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I203" t="s">
         <v>19</v>
@@ -7299,16 +7323,16 @@
         <v>114</v>
       </c>
       <c r="C204" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D204" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E204" t="s">
         <v>77</v>
       </c>
       <c r="F204" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G204" t="s">
         <v>126</v>
@@ -7392,7 +7416,7 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F207" t="s">
         <v>146</v>
@@ -7444,16 +7468,16 @@
         <v>123</v>
       </c>
       <c r="C209" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D209" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E209" t="s">
         <v>77</v>
       </c>
       <c r="F209" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G209" t="s">
         <v>126</v>
@@ -7476,7 +7500,7 @@
         <v>71</v>
       </c>
       <c r="D210" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E210" t="s">
         <v>35</v>
@@ -7508,7 +7532,7 @@
         <v>182</v>
       </c>
       <c r="E211" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F211" t="s">
         <v>107</v>
@@ -7531,10 +7555,10 @@
         <v>131</v>
       </c>
       <c r="C212" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D212" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E212" t="s">
         <v>67</v>
@@ -7554,22 +7578,22 @@
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B213" t="s">
         <v>134</v>
       </c>
       <c r="C213" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="D213" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="E213" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F213" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="G213" t="s">
         <v>17</v>
@@ -7583,22 +7607,22 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B214" t="s">
         <v>134</v>
       </c>
       <c r="C214" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D214" t="s">
-        <v>154</v>
+        <v>238</v>
       </c>
       <c r="E214" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F214" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G214" t="s">
         <v>17</v>
@@ -7612,22 +7636,22 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B215" t="s">
         <v>134</v>
       </c>
       <c r="C215" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D215" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="E215" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="F215" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="G215" t="s">
         <v>17</v>
@@ -7641,28 +7665,28 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B216" t="s">
         <v>134</v>
       </c>
       <c r="C216" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="D216" t="s">
-        <v>234</v>
+        <v>14</v>
       </c>
       <c r="E216" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="F216" t="s">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="G216" t="s">
         <v>17</v>
       </c>
       <c r="H216" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I216" t="s">
         <v>19</v>
@@ -7670,28 +7694,28 @@
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C217" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="D217" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E217" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F217" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="G217" t="s">
         <v>17</v>
       </c>
       <c r="H217" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I217" t="s">
         <v>19</v>
@@ -7699,77 +7723,77 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
       </c>
       <c r="C218" t="s">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="D218" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E218" t="s">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="F218" t="s">
-        <v>107</v>
+        <v>237</v>
       </c>
       <c r="G218" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="H218" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I218" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B219" t="s">
         <v>12</v>
       </c>
       <c r="C219" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D219" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="E219" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F219" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G219" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H219" t="s">
         <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B220" t="s">
         <v>12</v>
       </c>
       <c r="C220" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="D220" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E220" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F220" t="s">
         <v>107</v>
@@ -7778,94 +7802,94 @@
         <v>108</v>
       </c>
       <c r="H220" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I220" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B221" t="s">
         <v>12</v>
       </c>
       <c r="C221" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D221" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="E221" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F221" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G221" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H221" t="s">
         <v>18</v>
       </c>
       <c r="I221" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B222" t="s">
         <v>12</v>
       </c>
       <c r="C222" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D222" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E222" t="s">
-        <v>41</v>
+        <v>229</v>
       </c>
       <c r="F222" t="s">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="G222" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="H222" t="s">
         <v>18</v>
       </c>
       <c r="I222" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B223" t="s">
         <v>12</v>
       </c>
       <c r="C223" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="D223" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="E223" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F223" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G223" t="s">
         <v>17</v>
       </c>
       <c r="H223" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I223" t="s">
         <v>19</v>
@@ -7873,22 +7897,22 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B224" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C224" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="D224" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E224" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F224" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="G224" t="s">
         <v>17</v>
@@ -7902,22 +7926,22 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B225" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C225" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D225" t="s">
-        <v>237</v>
+        <v>14</v>
       </c>
       <c r="E225" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="F225" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="G225" t="s">
         <v>17</v>
@@ -7931,25 +7955,25 @@
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B226" t="s">
         <v>45</v>
       </c>
       <c r="C226" t="s">
-        <v>13</v>
+        <v>236</v>
       </c>
       <c r="D226" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E226" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="F226" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G226" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H226" t="s">
         <v>18</v>
@@ -7960,22 +7984,22 @@
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B227" t="s">
         <v>45</v>
       </c>
       <c r="C227" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D227" t="s">
         <v>238</v>
       </c>
       <c r="E227" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F227" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G227" t="s">
         <v>17</v>
@@ -7989,28 +8013,28 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B228" t="s">
         <v>45</v>
       </c>
       <c r="C228" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="D228" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="E228" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="F228" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G228" t="s">
         <v>17</v>
       </c>
       <c r="H228" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I228" t="s">
         <v>19</v>
@@ -8018,51 +8042,51 @@
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B229" t="s">
         <v>45</v>
       </c>
       <c r="C229" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D229" t="s">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="E229" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F229" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="G229" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="H229" t="s">
         <v>18</v>
       </c>
       <c r="I229" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B230" t="s">
         <v>45</v>
       </c>
       <c r="C230" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D230" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="E230" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="F230" t="s">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="G230" t="s">
         <v>17</v>
@@ -8076,86 +8100,86 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B231" t="s">
         <v>45</v>
       </c>
       <c r="C231" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D231" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E231" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F231" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G231" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H231" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I231" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B232" t="s">
         <v>45</v>
       </c>
       <c r="C232" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D232" t="s">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="E232" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F232" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G232" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H232" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I232" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B233" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C233" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D233" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E233" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="F233" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G233" t="s">
         <v>17</v>
       </c>
       <c r="H233" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I233" t="s">
         <v>19</v>
@@ -8163,28 +8187,28 @@
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B234" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C234" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="D234" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="E234" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F234" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G234" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="H234" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I234" t="s">
         <v>44</v>
@@ -8192,28 +8216,28 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C235" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D235" t="s">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="F235" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="G235" t="s">
         <v>17</v>
       </c>
       <c r="H235" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I235" t="s">
         <v>19</v>
@@ -8221,231 +8245,231 @@
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B236" t="s">
         <v>70</v>
       </c>
       <c r="C236" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="D236" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="E236" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="F236" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="G236" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="H236" t="s">
         <v>18</v>
       </c>
       <c r="I236" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B237" t="s">
         <v>70</v>
       </c>
       <c r="C237" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="D237" t="s">
-        <v>55</v>
+        <v>244</v>
       </c>
       <c r="E237" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="F237" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="G237" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H237" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I237" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B238" t="s">
         <v>70</v>
       </c>
       <c r="C238" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D238" t="s">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="E238" t="s">
-        <v>199</v>
+        <v>51</v>
       </c>
       <c r="F238" t="s">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="G238" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H238" t="s">
         <v>18</v>
       </c>
       <c r="I238" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B239" t="s">
         <v>70</v>
       </c>
       <c r="C239" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="D239" t="s">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="E239" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F239" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G239" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H239" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I239" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B240" t="s">
         <v>70</v>
       </c>
       <c r="C240" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="D240" t="s">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="E240" t="s">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="F240" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G240" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H240" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I240" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B241" t="s">
         <v>70</v>
       </c>
       <c r="C241" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="D241" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="E241" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="F241" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G241" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H241" t="s">
         <v>18</v>
       </c>
       <c r="I241" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B242" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C242" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="D242" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E242" t="s">
-        <v>51</v>
+        <v>199</v>
       </c>
       <c r="F242" t="s">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="G242" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="H242" t="s">
         <v>18</v>
       </c>
       <c r="I242" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B243" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C243" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="D243" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="E243" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="F243" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G243" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="H243" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="I243" t="s">
         <v>44</v>
@@ -8453,51 +8477,51 @@
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B244" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C244" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D244" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="E244" t="s">
-        <v>60</v>
+        <v>243</v>
       </c>
       <c r="F244" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G244" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H244" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I244" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B245" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C245" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="D245" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="E245" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F245" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G245" t="s">
         <v>17</v>
@@ -8511,25 +8535,25 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B246" t="s">
         <v>92</v>
       </c>
       <c r="C246" t="s">
-        <v>33</v>
+        <v>236</v>
       </c>
       <c r="D246" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="E246" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F246" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="G246" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="H246" t="s">
         <v>18</v>
@@ -8540,54 +8564,54 @@
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B247" t="s">
         <v>92</v>
       </c>
       <c r="C247" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D247" t="s">
-        <v>55</v>
+        <v>239</v>
       </c>
       <c r="E247" t="s">
         <v>51</v>
       </c>
       <c r="F247" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G247" t="s">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="H247" t="s">
         <v>18</v>
       </c>
       <c r="I247" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B248" t="s">
         <v>92</v>
       </c>
       <c r="C248" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D248" t="s">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="E248" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F248" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G248" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="H248" t="s">
         <v>80</v>
@@ -8598,54 +8622,54 @@
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B249" t="s">
         <v>92</v>
       </c>
       <c r="C249" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D249" t="s">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="E249" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="F249" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G249" t="s">
-        <v>217</v>
+        <v>37</v>
       </c>
       <c r="H249" t="s">
         <v>18</v>
       </c>
       <c r="I249" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B250" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C250" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D250" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="E250" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F250" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="G250" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="H250" t="s">
         <v>18</v>
@@ -8656,112 +8680,112 @@
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B251" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C251" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="D251" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E251" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F251" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G251" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="H251" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I251" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B252" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C252" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D252" t="s">
-        <v>229</v>
+        <v>55</v>
       </c>
       <c r="E252" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F252" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G252" t="s">
-        <v>66</v>
+        <v>247</v>
       </c>
       <c r="H252" t="s">
         <v>18</v>
       </c>
       <c r="I252" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B253" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C253" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="D253" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="E253" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="F253" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G253" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H253" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I253" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B254" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C254" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="D254" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="E254" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="F254" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G254" t="s">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="H254" t="s">
         <v>18</v>
@@ -8772,16 +8796,16 @@
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B255" t="s">
         <v>98</v>
       </c>
       <c r="C255" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="D255" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="E255" t="s">
         <v>15</v>
@@ -8796,62 +8820,62 @@
         <v>18</v>
       </c>
       <c r="I255" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B256" t="s">
         <v>98</v>
       </c>
       <c r="C256" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="D256" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="E256" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F256" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="G256" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="H256" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I256" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B257" t="s">
         <v>98</v>
       </c>
       <c r="C257" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D257" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E257" t="s">
         <v>51</v>
       </c>
       <c r="F257" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="H257" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I257" t="s">
         <v>44</v>
@@ -8859,83 +8883,83 @@
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
+        <v>235</v>
+      </c>
+      <c r="B258" t="s">
+        <v>98</v>
+      </c>
+      <c r="C258" t="s">
+        <v>13</v>
+      </c>
+      <c r="D258" t="s">
         <v>232</v>
       </c>
-      <c r="B258" t="s">
-        <v>114</v>
-      </c>
-      <c r="C258" t="s">
-        <v>148</v>
-      </c>
-      <c r="D258" t="s">
-        <v>243</v>
-      </c>
       <c r="E258" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F258" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="G258" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="H258" t="s">
         <v>18</v>
       </c>
       <c r="I258" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B259" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C259" t="s">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="D259" t="s">
-        <v>222</v>
+        <v>132</v>
       </c>
       <c r="E259" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F259" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="G259" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H259" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I259" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B260" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C260" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D260" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E260" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F260" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="G260" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H260" t="s">
         <v>18</v>
@@ -8946,25 +8970,25 @@
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B261" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C261" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D261" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="E261" t="s">
         <v>15</v>
       </c>
       <c r="F261" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="G261" t="s">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="H261" t="s">
         <v>18</v>
@@ -8975,10 +8999,10 @@
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B262" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C262" t="s">
         <v>96</v>
@@ -8987,42 +9011,42 @@
         <v>150</v>
       </c>
       <c r="E262" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="F262" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G262" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H262" t="s">
         <v>80</v>
       </c>
       <c r="I262" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B263" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C263" t="s">
         <v>91</v>
       </c>
       <c r="D263" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E263" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="F263" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G263" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="H263" t="s">
         <v>18</v>
@@ -9033,16 +9057,16 @@
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B264" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C264" t="s">
         <v>148</v>
       </c>
       <c r="D264" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E264" t="s">
         <v>77</v>
@@ -9062,54 +9086,54 @@
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B265" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C265" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="D265" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E265" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F265" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G265" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="H265" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I265" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B266" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C266" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D266" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="E266" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F266" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="G266" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H266" t="s">
         <v>18</v>
@@ -9120,28 +9144,28 @@
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B267" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C267" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="D267" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
       <c r="E267" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="F267" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G267" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="H267" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I267" t="s">
         <v>44</v>
@@ -9149,28 +9173,28 @@
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B268" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C268" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D268" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E268" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="F268" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G268" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H268" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I268" t="s">
         <v>44</v>
@@ -9178,54 +9202,54 @@
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B269" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C269" t="s">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="D269" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="E269" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="F269" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G269" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H269" t="s">
         <v>18</v>
       </c>
       <c r="I269" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B270" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C270" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="D270" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E270" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F270" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="G270" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="H270" t="s">
         <v>18</v>
@@ -9236,25 +9260,25 @@
     </row>
     <row r="271" spans="1:9" ht="15">
       <c r="A271" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B271" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="C271" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D271" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="E271" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F271" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G271" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="H271" t="s">
         <v>18</v>
@@ -9265,57 +9289,57 @@
     </row>
     <row r="272" spans="1:9" ht="15">
       <c r="A272" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B272" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="C272" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D272" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="E272" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F272" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G272" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="H272" t="s">
         <v>18</v>
       </c>
       <c r="I272" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="15">
       <c r="A273" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B273" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="C273" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D273" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="E273" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
       </c>
       <c r="G273" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H273" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I273" t="s">
         <v>44</v>
@@ -9323,109 +9347,109 @@
     </row>
     <row r="274" spans="1:9" ht="15">
       <c r="A274" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B274" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D274" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="E274" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F274" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G274" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H274" t="s">
         <v>18</v>
       </c>
       <c r="I274" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B275" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C275" t="s">
-        <v>166</v>
+        <v>251</v>
       </c>
       <c r="D275" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E275" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F275" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G275" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H275" t="s">
         <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B276" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="C276" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="D276" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E276" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F276" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G276" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H276" t="s">
         <v>18</v>
       </c>
       <c r="I276" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B277" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C277" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D277" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="E277" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="F277" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G277" t="s">
         <v>17</v>
@@ -9439,22 +9463,22 @@
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B278" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C278" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="D278" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="E278" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F278" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G278" t="s">
         <v>17</v>
@@ -9468,25 +9492,25 @@
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B279" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C279" t="s">
         <v>13</v>
       </c>
       <c r="D279" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="E279" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F279" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G279" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H279" t="s">
         <v>18</v>
@@ -9497,83 +9521,83 @@
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B280" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C280" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D280" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="E280" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F280" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G280" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B281" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C281" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="D281" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E281" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="F281" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="G281" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="H281" t="s">
         <v>18</v>
       </c>
       <c r="I281" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B282" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C282" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="D282" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E282" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F282" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G282" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="H282" t="s">
         <v>18</v>
@@ -9584,54 +9608,54 @@
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B283" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C283" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="D283" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="E283" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F283" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G283" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H283" t="s">
         <v>18</v>
       </c>
       <c r="I283" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B284" t="s">
         <v>70</v>
       </c>
       <c r="C284" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="D284" t="s">
-        <v>25</v>
+        <v>241</v>
       </c>
       <c r="E284" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="F284" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G284" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="H284" t="s">
         <v>18</v>
@@ -9642,13 +9666,13 @@
     </row>
     <row r="285" spans="1:9" ht="15">
       <c r="A285" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B285" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C285" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D285" t="s">
         <v>55</v>
@@ -9671,25 +9695,25 @@
     </row>
     <row r="286" spans="1:9" ht="15">
       <c r="A286" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B286" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C286" t="s">
         <v>13</v>
       </c>
       <c r="D286" t="s">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="E286" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F286" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G286" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H286" t="s">
         <v>18</v>
@@ -9700,25 +9724,25 @@
     </row>
     <row r="287" spans="1:9" ht="15">
       <c r="A287" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B287" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C287" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D287" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="E287" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F287" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G287" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="H287" t="s">
         <v>18</v>
@@ -9729,54 +9753,54 @@
     </row>
     <row r="288" spans="1:9" ht="15">
       <c r="A288" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B288" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C288" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="D288" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="E288" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F288" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="G288" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="H288" t="s">
         <v>18</v>
       </c>
       <c r="I288" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="289" spans="1:9" ht="15">
       <c r="A289" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B289" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C289" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D289" t="s">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="E289" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="F289" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G289" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="H289" t="s">
         <v>18</v>
@@ -9787,25 +9811,25 @@
     </row>
     <row r="290" spans="1:9" ht="15">
       <c r="A290" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B290" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C290" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D290" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="E290" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F290" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G290" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="H290" t="s">
         <v>18</v>
@@ -9816,199 +9840,199 @@
     </row>
     <row r="291" spans="1:9" ht="15">
       <c r="A291" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B291" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C291" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D291" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="E291" t="s">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="F291" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="G291" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H291" t="s">
         <v>18</v>
       </c>
       <c r="I291" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="15">
       <c r="A292" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B292" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C292" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="D292" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="E292" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F292" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="G292" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="H292" t="s">
         <v>18</v>
       </c>
       <c r="I292" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15">
       <c r="A293" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B293" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C293" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="D293" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="E293" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="F293" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G293" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="H293" t="s">
         <v>18</v>
       </c>
       <c r="I293" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="15">
       <c r="A294" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B294" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C294" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D294" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="E294" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F294" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="G294" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="H294" t="s">
         <v>18</v>
       </c>
       <c r="I294" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="15">
       <c r="A295" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B295" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C295" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="D295" t="s">
-        <v>215</v>
+        <v>94</v>
       </c>
       <c r="E295" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F295" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G295" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H295" t="s">
         <v>18</v>
       </c>
       <c r="I295" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="15">
       <c r="A296" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B296" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C296" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D296" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F296" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="G296" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="H296" t="s">
         <v>18</v>
       </c>
       <c r="I296" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297" spans="1:9" ht="15">
       <c r="A297" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B297" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C297" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D297" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E297" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F297" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G297" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="H297" t="s">
         <v>18</v>
@@ -10019,25 +10043,25 @@
     </row>
     <row r="298" spans="1:9" ht="15">
       <c r="A298" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B298" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C298" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D298" t="s">
-        <v>251</v>
+        <v>25</v>
       </c>
       <c r="E298" t="s">
-        <v>252</v>
+        <v>73</v>
       </c>
       <c r="F298" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="G298" t="s">
-        <v>220</v>
+        <v>106</v>
       </c>
       <c r="H298" t="s">
         <v>18</v>
@@ -10048,83 +10072,83 @@
     </row>
     <row r="299" spans="1:9" ht="15">
       <c r="A299" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B299" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C299" t="s">
         <v>108</v>
       </c>
       <c r="D299" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E299" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F299" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="G299" t="s">
-        <v>220</v>
+        <v>24</v>
       </c>
       <c r="H299" t="s">
         <v>18</v>
       </c>
       <c r="I299" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15">
       <c r="A300" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B300" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C300" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="D300" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="E300" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F300" t="s">
-        <v>48</v>
+        <v>228</v>
       </c>
       <c r="G300" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="H300" t="s">
         <v>18</v>
       </c>
       <c r="I300" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="15">
       <c r="A301" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B301" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C301" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="D301" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="E301" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="F301" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G301" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H301" t="s">
         <v>18</v>
@@ -10135,83 +10159,83 @@
     </row>
     <row r="302" spans="1:9" ht="15">
       <c r="A302" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B302" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C302" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D302" t="s">
-        <v>14</v>
+        <v>165</v>
       </c>
       <c r="E302" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="F302" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G302" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="H302" t="s">
         <v>18</v>
       </c>
       <c r="I302" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="15">
       <c r="A303" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B303" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C303" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D303" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="E303" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="F303" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G303" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H303" t="s">
         <v>18</v>
       </c>
       <c r="I303" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="15">
       <c r="A304" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B304" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C304" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D304" t="s">
         <v>215</v>
       </c>
       <c r="E304" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F304" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G304" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="H304" t="s">
         <v>18</v>
@@ -10222,54 +10246,54 @@
     </row>
     <row r="305" spans="1:9" ht="15">
       <c r="A305" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B305" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C305" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D305" t="s">
-        <v>55</v>
+        <v>212</v>
       </c>
       <c r="E305" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="F305" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G305" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="H305" t="s">
         <v>18</v>
       </c>
       <c r="I305" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="15">
       <c r="A306" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B306" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C306" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D306" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="E306" t="s">
         <v>73</v>
       </c>
       <c r="F306" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G306" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="H306" t="s">
         <v>18</v>
@@ -10280,25 +10304,25 @@
     </row>
     <row r="307" spans="1:9" ht="15">
       <c r="A307" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B307" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C307" t="s">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="D307" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="E307" t="s">
-        <v>56</v>
+        <v>257</v>
       </c>
       <c r="F307" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="G307" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="H307" t="s">
         <v>18</v>
@@ -10309,83 +10333,83 @@
     </row>
     <row r="308" spans="1:9" ht="15">
       <c r="A308" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B308" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C308" t="s">
-        <v>246</v>
+        <v>108</v>
       </c>
       <c r="D308" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="E308" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="F308" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="G308" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="H308" t="s">
         <v>18</v>
       </c>
       <c r="I308" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="15">
       <c r="A309" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B309" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C309" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="D309" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E309" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F309" t="s">
-        <v>89</v>
+        <v>237</v>
       </c>
       <c r="G309" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="H309" t="s">
         <v>18</v>
       </c>
       <c r="I309" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15">
       <c r="A310" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B310" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C310" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="D310" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="E310" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="F310" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G310" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H310" t="s">
         <v>18</v>
@@ -10396,25 +10420,25 @@
     </row>
     <row r="311" spans="1:9" ht="15">
       <c r="A311" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B311" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C311" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="D311" t="s">
         <v>179</v>
       </c>
       <c r="E311" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F311" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="G311" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H311" t="s">
         <v>18</v>
@@ -10425,54 +10449,54 @@
     </row>
     <row r="312" spans="1:9" ht="15">
       <c r="A312" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B312" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C312" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="D312" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
       <c r="E312" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="F312" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="G312" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="H312" t="s">
         <v>18</v>
       </c>
       <c r="I312" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="15">
       <c r="A313" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B313" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C313" t="s">
-        <v>253</v>
+        <v>85</v>
       </c>
       <c r="D313" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="E313" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F313" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="G313" t="s">
-        <v>254</v>
+        <v>66</v>
       </c>
       <c r="H313" t="s">
         <v>18</v>
@@ -10483,54 +10507,54 @@
     </row>
     <row r="314" spans="1:9" ht="15">
       <c r="A314" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B314" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C314" t="s">
-        <v>246</v>
+        <v>33</v>
       </c>
       <c r="D314" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E314" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F314" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="G314" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H314" t="s">
         <v>18</v>
       </c>
       <c r="I314" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="15">
       <c r="A315" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B315" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C315" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D315" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="E315" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="F315" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G315" t="s">
-        <v>244</v>
+        <v>130</v>
       </c>
       <c r="H315" t="s">
         <v>18</v>
@@ -10541,25 +10565,25 @@
     </row>
     <row r="316" spans="1:9" ht="15">
       <c r="A316" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B316" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C316" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D316" t="s">
-        <v>94</v>
+        <v>240</v>
       </c>
       <c r="E316" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F316" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G316" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H316" t="s">
         <v>18</v>
@@ -10570,60 +10594,553 @@
     </row>
     <row r="317" spans="1:9" ht="15">
       <c r="A317" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B317" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C317" t="s">
-        <v>108</v>
+        <v>258</v>
       </c>
       <c r="D317" t="s">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="E317" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F317" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G317" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="H317" t="s">
         <v>18</v>
       </c>
       <c r="I317" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15">
       <c r="A318" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B318" t="s">
+        <v>123</v>
+      </c>
+      <c r="C318" t="s">
+        <v>236</v>
+      </c>
+      <c r="D318" t="s">
+        <v>240</v>
+      </c>
+      <c r="E318" t="s">
+        <v>56</v>
+      </c>
+      <c r="F318" t="s">
+        <v>237</v>
+      </c>
+      <c r="G318" t="s">
+        <v>126</v>
+      </c>
+      <c r="H318" t="s">
+        <v>18</v>
+      </c>
+      <c r="I318" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="15">
+      <c r="A319" t="s">
+        <v>250</v>
+      </c>
+      <c r="B319" t="s">
+        <v>123</v>
+      </c>
+      <c r="C319" t="s">
+        <v>226</v>
+      </c>
+      <c r="D319" t="s">
+        <v>173</v>
+      </c>
+      <c r="E319" t="s">
+        <v>77</v>
+      </c>
+      <c r="F319" t="s">
+        <v>260</v>
+      </c>
+      <c r="G319" t="s">
+        <v>126</v>
+      </c>
+      <c r="H319" t="s">
+        <v>18</v>
+      </c>
+      <c r="I319" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="15">
+      <c r="A320" t="s">
+        <v>250</v>
+      </c>
+      <c r="B320" t="s">
+        <v>123</v>
+      </c>
+      <c r="C320" t="s">
+        <v>251</v>
+      </c>
+      <c r="D320" t="s">
+        <v>209</v>
+      </c>
+      <c r="E320" t="s">
+        <v>129</v>
+      </c>
+      <c r="F320" t="s">
+        <v>36</v>
+      </c>
+      <c r="G320" t="s">
+        <v>126</v>
+      </c>
+      <c r="H320" t="s">
+        <v>18</v>
+      </c>
+      <c r="I320" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="15">
+      <c r="A321" t="s">
+        <v>250</v>
+      </c>
+      <c r="B321" t="s">
+        <v>123</v>
+      </c>
+      <c r="C321" t="s">
+        <v>166</v>
+      </c>
+      <c r="D321" t="s">
+        <v>182</v>
+      </c>
+      <c r="E321" t="s">
+        <v>15</v>
+      </c>
+      <c r="F321" t="s">
+        <v>89</v>
+      </c>
+      <c r="G321" t="s">
+        <v>249</v>
+      </c>
+      <c r="H321" t="s">
+        <v>18</v>
+      </c>
+      <c r="I321" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="15">
+      <c r="A322" t="s">
+        <v>250</v>
+      </c>
+      <c r="B322" t="s">
+        <v>123</v>
+      </c>
+      <c r="C322" t="s">
+        <v>33</v>
+      </c>
+      <c r="D322" t="s">
+        <v>55</v>
+      </c>
+      <c r="E322" t="s">
+        <v>56</v>
+      </c>
+      <c r="F322" t="s">
+        <v>81</v>
+      </c>
+      <c r="G322" t="s">
+        <v>58</v>
+      </c>
+      <c r="H322" t="s">
+        <v>18</v>
+      </c>
+      <c r="I322" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="15">
+      <c r="A323" t="s">
+        <v>250</v>
+      </c>
+      <c r="B323" t="s">
+        <v>123</v>
+      </c>
+      <c r="C323" t="s">
+        <v>108</v>
+      </c>
+      <c r="D323" t="s">
+        <v>179</v>
+      </c>
+      <c r="E323" t="s">
+        <v>51</v>
+      </c>
+      <c r="F323" t="s">
+        <v>107</v>
+      </c>
+      <c r="G323" t="s">
+        <v>66</v>
+      </c>
+      <c r="H323" t="s">
+        <v>18</v>
+      </c>
+      <c r="I323" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="15">
+      <c r="A324" t="s">
+        <v>250</v>
+      </c>
+      <c r="B324" t="s">
+        <v>123</v>
+      </c>
+      <c r="C324" t="s">
+        <v>233</v>
+      </c>
+      <c r="D324" t="s">
+        <v>234</v>
+      </c>
+      <c r="E324" t="s">
+        <v>67</v>
+      </c>
+      <c r="F324" t="s">
+        <v>68</v>
+      </c>
+      <c r="G324" t="s">
+        <v>69</v>
+      </c>
+      <c r="H324" t="s">
+        <v>18</v>
+      </c>
+      <c r="I324" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="15">
+      <c r="A325" t="s">
+        <v>250</v>
+      </c>
+      <c r="B325" t="s">
+        <v>123</v>
+      </c>
+      <c r="C325" t="s">
+        <v>258</v>
+      </c>
+      <c r="D325" t="s">
+        <v>239</v>
+      </c>
+      <c r="E325" t="s">
+        <v>56</v>
+      </c>
+      <c r="F325" t="s">
+        <v>64</v>
+      </c>
+      <c r="G325" t="s">
+        <v>259</v>
+      </c>
+      <c r="H325" t="s">
+        <v>18</v>
+      </c>
+      <c r="I325" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="15">
+      <c r="A326" t="s">
+        <v>250</v>
+      </c>
+      <c r="B326" t="s">
+        <v>131</v>
+      </c>
+      <c r="C326" t="s">
+        <v>236</v>
+      </c>
+      <c r="D326" t="s">
+        <v>179</v>
+      </c>
+      <c r="E326" t="s">
+        <v>56</v>
+      </c>
+      <c r="F326" t="s">
+        <v>237</v>
+      </c>
+      <c r="G326" t="s">
+        <v>126</v>
+      </c>
+      <c r="H326" t="s">
+        <v>18</v>
+      </c>
+      <c r="I326" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="15">
+      <c r="A327" t="s">
+        <v>250</v>
+      </c>
+      <c r="B327" t="s">
+        <v>131</v>
+      </c>
+      <c r="C327" t="s">
+        <v>226</v>
+      </c>
+      <c r="D327" t="s">
+        <v>173</v>
+      </c>
+      <c r="E327" t="s">
+        <v>77</v>
+      </c>
+      <c r="F327" t="s">
+        <v>260</v>
+      </c>
+      <c r="G327" t="s">
+        <v>126</v>
+      </c>
+      <c r="H327" t="s">
+        <v>18</v>
+      </c>
+      <c r="I327" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="15">
+      <c r="A328" t="s">
+        <v>250</v>
+      </c>
+      <c r="B328" t="s">
+        <v>131</v>
+      </c>
+      <c r="C328" t="s">
+        <v>251</v>
+      </c>
+      <c r="D328" t="s">
+        <v>209</v>
+      </c>
+      <c r="E328" t="s">
+        <v>129</v>
+      </c>
+      <c r="F328" t="s">
+        <v>36</v>
+      </c>
+      <c r="G328" t="s">
+        <v>126</v>
+      </c>
+      <c r="H328" t="s">
+        <v>18</v>
+      </c>
+      <c r="I328" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="15">
+      <c r="A329" t="s">
+        <v>250</v>
+      </c>
+      <c r="B329" t="s">
+        <v>131</v>
+      </c>
+      <c r="C329" t="s">
+        <v>166</v>
+      </c>
+      <c r="D329" t="s">
+        <v>182</v>
+      </c>
+      <c r="E329" t="s">
+        <v>15</v>
+      </c>
+      <c r="F329" t="s">
+        <v>89</v>
+      </c>
+      <c r="G329" t="s">
+        <v>249</v>
+      </c>
+      <c r="H329" t="s">
+        <v>18</v>
+      </c>
+      <c r="I329" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="15">
+      <c r="A330" t="s">
+        <v>250</v>
+      </c>
+      <c r="B330" t="s">
+        <v>131</v>
+      </c>
+      <c r="C330" t="s">
+        <v>85</v>
+      </c>
+      <c r="D330" t="s">
+        <v>94</v>
+      </c>
+      <c r="E330" t="s">
+        <v>63</v>
+      </c>
+      <c r="F330" t="s">
+        <v>64</v>
+      </c>
+      <c r="G330" t="s">
+        <v>66</v>
+      </c>
+      <c r="H330" t="s">
+        <v>18</v>
+      </c>
+      <c r="I330" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="15">
+      <c r="A331" t="s">
+        <v>250</v>
+      </c>
+      <c r="B331" t="s">
+        <v>131</v>
+      </c>
+      <c r="C331" t="s">
+        <v>108</v>
+      </c>
+      <c r="D331" t="s">
+        <v>34</v>
+      </c>
+      <c r="E331" t="s">
+        <v>60</v>
+      </c>
+      <c r="F331" t="s">
+        <v>61</v>
+      </c>
+      <c r="G331" t="s">
+        <v>109</v>
+      </c>
+      <c r="H331" t="s">
+        <v>18</v>
+      </c>
+      <c r="I331" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="15">
+      <c r="A332" t="s">
+        <v>250</v>
+      </c>
+      <c r="B332" t="s">
         <v>191</v>
       </c>
-      <c r="C318" t="s">
+      <c r="C332" t="s">
+        <v>236</v>
+      </c>
+      <c r="D332" t="s">
+        <v>213</v>
+      </c>
+      <c r="E332" t="s">
+        <v>56</v>
+      </c>
+      <c r="F332" t="s">
+        <v>237</v>
+      </c>
+      <c r="G332" t="s">
+        <v>126</v>
+      </c>
+      <c r="H332" t="s">
+        <v>18</v>
+      </c>
+      <c r="I332" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="15">
+      <c r="A333" t="s">
+        <v>250</v>
+      </c>
+      <c r="B333" t="s">
+        <v>191</v>
+      </c>
+      <c r="C333" t="s">
+        <v>226</v>
+      </c>
+      <c r="D333" t="s">
+        <v>173</v>
+      </c>
+      <c r="E333" t="s">
+        <v>77</v>
+      </c>
+      <c r="F333" t="s">
+        <v>260</v>
+      </c>
+      <c r="G333" t="s">
+        <v>126</v>
+      </c>
+      <c r="H333" t="s">
+        <v>18</v>
+      </c>
+      <c r="I333" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="15">
+      <c r="A334" t="s">
+        <v>250</v>
+      </c>
+      <c r="B334" t="s">
+        <v>191</v>
+      </c>
+      <c r="C334" t="s">
         <v>85</v>
       </c>
-      <c r="D318" t="s">
-        <v>234</v>
-      </c>
-      <c r="E318" t="s">
+      <c r="D334" t="s">
+        <v>239</v>
+      </c>
+      <c r="E334" t="s">
         <v>63</v>
       </c>
-      <c r="F318" t="s">
+      <c r="F334" t="s">
         <v>64</v>
       </c>
-      <c r="G318" t="s">
+      <c r="G334" t="s">
         <v>66</v>
       </c>
-      <c r="H318" t="s">
-        <v>18</v>
-      </c>
-      <c r="I318" t="s">
-        <v>44</v>
+      <c r="H334" t="s">
+        <v>18</v>
+      </c>
+      <c r="I334" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" ht="15">
+      <c r="A335" t="s">
+        <v>250</v>
+      </c>
+      <c r="B335" t="s">
+        <v>261</v>
+      </c>
+      <c r="C335" t="s">
+        <v>236</v>
+      </c>
+      <c r="D335" t="s">
+        <v>182</v>
+      </c>
+      <c r="E335" t="s">
+        <v>56</v>
+      </c>
+      <c r="F335" t="s">
+        <v>237</v>
+      </c>
+      <c r="G335" t="s">
+        <v>126</v>
+      </c>
+      <c r="H335" t="s">
+        <v>18</v>
+      </c>
+      <c r="I335" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -10634,8 +11151,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b4fcc0ae-9d1a-469b-9be5-961b0865458a}">
-  <dimension ref="A1:I10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{976a95ae-a43f-4221-a1f0-79a513ca89d0}">
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -10654,16 +11171,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -10683,16 +11200,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -10712,13 +11229,13 @@
         <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
         <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
         <v>73</v>
@@ -10741,16 +11258,16 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -10770,13 +11287,13 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -10799,16 +11316,16 @@
         <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -10828,13 +11345,13 @@
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -10857,16 +11374,16 @@
         <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E8" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -10883,19 +11400,19 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="D9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -10904,7 +11421,7 @@
         <v>120</v>
       </c>
       <c r="H9" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -10912,19 +11429,19 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -10933,9 +11450,38 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10947,8 +11493,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{65f72751-3406-420f-84ff-c5838d2826a9}">
-  <dimension ref="A1:F88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ece62f9-e85e-489e-8e4c-18eb3b29e383}">
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -10964,13 +11510,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -10984,13 +11530,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -11004,13 +11550,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -11024,13 +11570,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -11044,13 +11590,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -11064,13 +11610,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E6" t="s">
         <v>69</v>
@@ -11084,13 +11630,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E7" t="s">
         <v>112</v>
@@ -11104,13 +11650,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E8" t="s">
         <v>189</v>
@@ -11124,13 +11670,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E9" t="s">
         <v>90</v>
@@ -11144,13 +11690,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -11164,13 +11710,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E11" t="s">
         <v>148</v>
@@ -11184,13 +11730,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -11204,13 +11750,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -11224,13 +11770,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -11244,13 +11790,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -11264,13 +11810,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E16" t="s">
         <v>183</v>
@@ -11284,16 +11830,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E17" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -11304,16 +11850,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E18" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
@@ -11324,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -11344,16 +11890,16 @@
         <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E20" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
@@ -11364,16 +11910,16 @@
         <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C21" t="s">
         <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E21" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -11384,16 +11930,16 @@
         <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C22" t="s">
         <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E22" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -11404,13 +11950,13 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
@@ -11424,13 +11970,13 @@
         <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
         <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E24" t="s">
         <v>195</v>
@@ -11444,13 +11990,13 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E25" t="s">
         <v>75</v>
@@ -11464,13 +12010,13 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C26" t="s">
         <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -11484,13 +12030,13 @@
         <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C27" t="s">
         <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -11504,13 +12050,13 @@
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E28" t="s">
         <v>189</v>
@@ -11524,13 +12070,13 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s">
         <v>96</v>
@@ -11544,13 +12090,13 @@
         <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
         <v>158</v>
@@ -11564,13 +12110,13 @@
         <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C31" t="s">
         <v>162</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E31" t="s">
         <v>130</v>
@@ -11584,13 +12130,13 @@
         <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
         <v>65</v>
@@ -11604,13 +12150,13 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C33" t="s">
         <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E33" t="s">
         <v>96</v>
@@ -11624,13 +12170,13 @@
         <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C34" t="s">
         <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E34" t="s">
         <v>189</v>
@@ -11644,13 +12190,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C35" t="s">
         <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E35" t="s">
         <v>178</v>
@@ -11664,16 +12210,16 @@
         <v>133</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E36" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F36" t="s">
         <v>80</v>
@@ -11684,13 +12230,13 @@
         <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C37" t="s">
         <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
         <v>100</v>
@@ -11704,13 +12250,13 @@
         <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E38" t="s">
         <v>54</v>
@@ -11724,13 +12270,13 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C39" t="s">
         <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
         <v>90</v>
@@ -11744,13 +12290,13 @@
         <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C40" t="s">
         <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E40" t="s">
         <v>130</v>
@@ -11764,16 +12310,16 @@
         <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C41" t="s">
         <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E41" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F41" t="s">
         <v>80</v>
@@ -11784,16 +12330,16 @@
         <v>133</v>
       </c>
       <c r="B42" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C42" t="s">
         <v>183</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E42" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -11804,13 +12350,13 @@
         <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C43" t="s">
         <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E43" t="s">
         <v>130</v>
@@ -11824,16 +12370,16 @@
         <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E44" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -11844,16 +12390,16 @@
         <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C45" t="s">
         <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E45" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -11864,13 +12410,13 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C46" t="s">
         <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E46" t="s">
         <v>69</v>
@@ -11884,13 +12430,13 @@
         <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C47" t="s">
         <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E47" t="s">
         <v>135</v>
@@ -11904,13 +12450,13 @@
         <v>194</v>
       </c>
       <c r="B48" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C48" t="s">
         <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E48" t="s">
         <v>24</v>
@@ -11924,13 +12470,13 @@
         <v>194</v>
       </c>
       <c r="B49" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -11944,13 +12490,13 @@
         <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C50" t="s">
         <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E50" t="s">
         <v>190</v>
@@ -11964,16 +12510,16 @@
         <v>194</v>
       </c>
       <c r="B51" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C51" t="s">
         <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E51" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F51" t="s">
         <v>32</v>
@@ -11984,13 +12530,13 @@
         <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C52" t="s">
         <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E52" t="s">
         <v>130</v>
@@ -12004,13 +12550,13 @@
         <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E53" t="s">
         <v>108</v>
@@ -12024,13 +12570,13 @@
         <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C54" t="s">
         <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E54" t="s">
         <v>148</v>
@@ -12044,13 +12590,13 @@
         <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C55" t="s">
         <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E55" t="s">
         <v>96</v>
@@ -12064,13 +12610,13 @@
         <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C56" t="s">
         <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E56" t="s">
         <v>69</v>
@@ -12081,19 +12627,19 @@
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="D57" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E57" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -12101,59 +12647,59 @@
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
         <v>291</v>
       </c>
       <c r="E58" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B59" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="F59" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F60" t="s">
         <v>18</v>
@@ -12161,39 +12707,39 @@
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E61" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F61" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E62" t="s">
-        <v>246</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
         <v>80</v>
@@ -12201,39 +12747,39 @@
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E63" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B64" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="D64" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E64" t="s">
-        <v>28</v>
+        <v>158</v>
       </c>
       <c r="F64" t="s">
         <v>18</v>
@@ -12241,19 +12787,19 @@
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
         <v>291</v>
       </c>
       <c r="E65" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
         <v>18</v>
@@ -12261,19 +12807,19 @@
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B66" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="E66" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F66" t="s">
         <v>18</v>
@@ -12281,19 +12827,19 @@
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B67" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C67" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E67" t="s">
-        <v>217</v>
+        <v>28</v>
       </c>
       <c r="F67" t="s">
         <v>18</v>
@@ -12301,19 +12847,19 @@
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B68" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="D68" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -12321,19 +12867,19 @@
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C69" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
@@ -12341,19 +12887,19 @@
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E70" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
         <v>18</v>
@@ -12361,19 +12907,19 @@
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E71" t="s">
-        <v>294</v>
+        <v>90</v>
       </c>
       <c r="F71" t="s">
         <v>18</v>
@@ -12381,19 +12927,19 @@
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B72" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E72" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -12401,59 +12947,59 @@
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
         <v>291</v>
       </c>
       <c r="E73" t="s">
-        <v>244</v>
+        <v>306</v>
       </c>
       <c r="F73" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F74" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C75" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
         <v>291</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -12461,19 +13007,19 @@
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B76" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F76" t="s">
         <v>18</v>
@@ -12481,19 +13027,19 @@
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>251</v>
       </c>
       <c r="D77" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="F77" t="s">
         <v>18</v>
@@ -12501,19 +13047,19 @@
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C78" t="s">
         <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
         <v>18</v>
@@ -12521,19 +13067,19 @@
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B79" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
         <v>18</v>
@@ -12541,19 +13087,19 @@
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B80" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>251</v>
       </c>
       <c r="D80" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F80" t="s">
         <v>18</v>
@@ -12561,19 +13107,19 @@
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C81" t="s">
-        <v>246</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
@@ -12581,19 +13127,19 @@
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B82" t="s">
+        <v>296</v>
+      </c>
+      <c r="C82" t="s">
+        <v>236</v>
+      </c>
+      <c r="D82" t="s">
         <v>288</v>
       </c>
-      <c r="C82" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" t="s">
-        <v>283</v>
-      </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>304</v>
       </c>
       <c r="F82" t="s">
         <v>18</v>
@@ -12601,19 +13147,19 @@
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B83" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>251</v>
       </c>
       <c r="D83" t="s">
         <v>286</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
         <v>18</v>
@@ -12621,19 +13167,19 @@
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B84" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
         <v>291</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -12641,19 +13187,19 @@
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B85" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C85" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
         <v>18</v>
@@ -12661,19 +13207,19 @@
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -12681,19 +13227,19 @@
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B87" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C87" t="s">
-        <v>246</v>
+        <v>169</v>
       </c>
       <c r="D87" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F87" t="s">
         <v>18</v>
@@ -12701,21 +13247,81 @@
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B88" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C88" t="s">
         <v>108</v>
       </c>
       <c r="D88" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="F88" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15">
+      <c r="A89" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" t="s">
+        <v>300</v>
+      </c>
+      <c r="C89" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" t="s">
+        <v>294</v>
+      </c>
+      <c r="E89" t="s">
+        <v>249</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15">
+      <c r="A90" t="s">
+        <v>250</v>
+      </c>
+      <c r="B90" t="s">
+        <v>300</v>
+      </c>
+      <c r="C90" t="s">
+        <v>108</v>
+      </c>
+      <c r="D90" t="s">
+        <v>299</v>
+      </c>
+      <c r="E90" t="s">
+        <v>303</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15">
+      <c r="A91" t="s">
+        <v>250</v>
+      </c>
+      <c r="B91" t="s">
+        <v>305</v>
+      </c>
+      <c r="C91" t="s">
+        <v>226</v>
+      </c>
+      <c r="D91" t="s">
+        <v>286</v>
+      </c>
+      <c r="E91" t="s">
+        <v>302</v>
+      </c>
+      <c r="F91" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="313">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -765,6 +765,9 @@
     <t>1WA</t>
   </si>
   <si>
+    <t>kin</t>
+  </si>
+  <si>
     <t>Bokuniewicz Sylwia</t>
   </si>
   <si>
@@ -789,6 +792,9 @@
     <t>2K|DZ</t>
   </si>
   <si>
+    <t>p. Biczysko, za lekcję 10</t>
+  </si>
+  <si>
     <t>Doradztwo zawodowe</t>
   </si>
   <si>
@@ -873,7 +879,19 @@
     <t>08:00-08:45</t>
   </si>
   <si>
+    <t xml:space="preserve"> Nikodem Gieysztor - 2CA - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>lekcja odwołana</t>
+  </si>
+  <si>
     <t>Julia Falenta - 4TFB - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>08:50-09:40</t>
+  </si>
+  <si>
+    <t>Marcel Wiśniewski - 1WA - indywidualne nauczanie</t>
   </si>
   <si>
     <t>Miejsce dyżuru</t>
@@ -1392,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{34caae0a-0567-4bb1-bbd4-a9fbbdaa8b8f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{163b631a-49de-4771-be67-006349543ed4}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1413,8 +1431,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{af2b73b2-1b5a-4313-ae87-d1a2c083fe46}">
-  <dimension ref="A1:I335"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f73ef7ce-6bdc-48db-84c7-95fe8f82498b}">
+  <dimension ref="A1:I340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -8550,7 +8568,7 @@
         <v>51</v>
       </c>
       <c r="F246" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G246" t="s">
         <v>28</v>
@@ -8657,25 +8675,25 @@
         <v>92</v>
       </c>
       <c r="C250" t="s">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="D250" t="s">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="E250" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="F250" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="G250" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H250" t="s">
         <v>18</v>
       </c>
       <c r="I250" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="15">
@@ -8686,25 +8704,25 @@
         <v>92</v>
       </c>
       <c r="C251" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D251" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="E251" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="F251" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G251" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="H251" t="s">
         <v>18</v>
       </c>
       <c r="I251" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15">
@@ -8715,19 +8733,19 @@
         <v>92</v>
       </c>
       <c r="C252" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D252" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E252" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F252" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G252" t="s">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="H252" t="s">
         <v>18</v>
@@ -8744,25 +8762,25 @@
         <v>92</v>
       </c>
       <c r="C253" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="D253" t="s">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="E253" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="F253" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G253" t="s">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="H253" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I253" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="254" spans="1:9" ht="15">
@@ -8773,22 +8791,22 @@
         <v>92</v>
       </c>
       <c r="C254" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D254" t="s">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E254" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="F254" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="H254" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I254" t="s">
         <v>44</v>
@@ -8799,28 +8817,28 @@
         <v>235</v>
       </c>
       <c r="B255" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C255" t="s">
-        <v>236</v>
+        <v>91</v>
       </c>
       <c r="D255" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="E255" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="F255" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="G255" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="H255" t="s">
         <v>18</v>
       </c>
       <c r="I255" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15">
@@ -8831,25 +8849,25 @@
         <v>98</v>
       </c>
       <c r="C256" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="D256" t="s">
-        <v>248</v>
+        <v>179</v>
       </c>
       <c r="E256" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F256" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="G256" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="H256" t="s">
         <v>18</v>
       </c>
       <c r="I256" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15">
@@ -8860,25 +8878,25 @@
         <v>98</v>
       </c>
       <c r="C257" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="D257" t="s">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="E257" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="F257" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G257" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="H257" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I257" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="15">
@@ -8889,22 +8907,22 @@
         <v>98</v>
       </c>
       <c r="C258" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="D258" t="s">
-        <v>232</v>
+        <v>55</v>
       </c>
       <c r="E258" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F258" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
       <c r="G258" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="H258" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I258" t="s">
         <v>44</v>
@@ -8918,25 +8936,25 @@
         <v>98</v>
       </c>
       <c r="C259" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="E259" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="F259" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G259" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H259" t="s">
         <v>18</v>
       </c>
       <c r="I259" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="15">
@@ -8947,25 +8965,25 @@
         <v>98</v>
       </c>
       <c r="C260" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D260" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="E260" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="F260" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="G260" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H260" t="s">
         <v>18</v>
       </c>
       <c r="I260" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:9" ht="15">
@@ -8976,19 +8994,19 @@
         <v>98</v>
       </c>
       <c r="C261" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D261" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="E261" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F261" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G261" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="H261" t="s">
         <v>18</v>
@@ -9005,25 +9023,25 @@
         <v>98</v>
       </c>
       <c r="C262" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="D262" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="E262" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F262" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G262" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="H262" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I262" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15">
@@ -9034,25 +9052,25 @@
         <v>98</v>
       </c>
       <c r="C263" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D263" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="E263" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F263" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G263" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="H263" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I263" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15">
@@ -9060,28 +9078,28 @@
         <v>235</v>
       </c>
       <c r="B264" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C264" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="D264" t="s">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="E264" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="F264" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="G264" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="H264" t="s">
         <v>18</v>
       </c>
       <c r="I264" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="15">
@@ -9092,25 +9110,25 @@
         <v>114</v>
       </c>
       <c r="C265" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="D265" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="E265" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F265" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="G265" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="H265" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I265" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="15">
@@ -9121,25 +9139,25 @@
         <v>114</v>
       </c>
       <c r="C266" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="D266" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="E266" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F266" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G266" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H266" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I266" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
@@ -9150,19 +9168,19 @@
         <v>114</v>
       </c>
       <c r="C267" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D267" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
       <c r="E267" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F267" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="G267" t="s">
-        <v>249</v>
+        <v>66</v>
       </c>
       <c r="H267" t="s">
         <v>18</v>
@@ -9179,22 +9197,22 @@
         <v>114</v>
       </c>
       <c r="C268" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="D268" t="s">
-        <v>150</v>
+        <v>239</v>
       </c>
       <c r="E268" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="F268" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G268" t="s">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c r="H268" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I268" t="s">
         <v>44</v>
@@ -9208,22 +9226,22 @@
         <v>114</v>
       </c>
       <c r="C269" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D269" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="E269" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="F269" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G269" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="H269" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I269" t="s">
         <v>44</v>
@@ -9234,28 +9252,28 @@
         <v>235</v>
       </c>
       <c r="B270" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C270" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="D270" t="s">
-        <v>248</v>
+        <v>55</v>
       </c>
       <c r="E270" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F270" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="G270" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="H270" t="s">
         <v>18</v>
       </c>
       <c r="I270" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="15">
@@ -9266,16 +9284,16 @@
         <v>123</v>
       </c>
       <c r="C271" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D271" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="E271" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="F271" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G271" t="s">
         <v>126</v>
@@ -9295,25 +9313,25 @@
         <v>123</v>
       </c>
       <c r="C272" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D272" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="E272" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="F272" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="G272" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="H272" t="s">
         <v>18</v>
       </c>
       <c r="I272" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="15">
@@ -9324,22 +9342,22 @@
         <v>123</v>
       </c>
       <c r="C273" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="D273" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E273" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F273" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="G273" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H273" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="I273" t="s">
         <v>44</v>
@@ -9350,25 +9368,25 @@
         <v>235</v>
       </c>
       <c r="B274" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C274" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D274" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="E274" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F274" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="G274" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H274" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="I274" t="s">
         <v>44</v>
@@ -9376,51 +9394,51 @@
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B275" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C275" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="D275" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="E275" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F275" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="G275" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="H275" t="s">
         <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B276" t="s">
         <v>134</v>
       </c>
       <c r="C276" t="s">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="D276" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="E276" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F276" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G276" t="s">
         <v>17</v>
@@ -9434,16 +9452,16 @@
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B277" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="C277" t="s">
         <v>20</v>
       </c>
       <c r="D277" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E277" t="s">
         <v>22</v>
@@ -9463,22 +9481,22 @@
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B278" t="s">
         <v>12</v>
       </c>
       <c r="C278" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D278" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E278" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="F278" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G278" t="s">
         <v>17</v>
@@ -9492,196 +9510,196 @@
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B279" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C279" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D279" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="E279" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F279" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G279" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="H279" t="s">
         <v>18</v>
       </c>
       <c r="I279" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B280" t="s">
         <v>45</v>
       </c>
       <c r="C280" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D280" t="s">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="E280" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F280" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G280" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B281" t="s">
         <v>45</v>
       </c>
       <c r="C281" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="D281" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="E281" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="F281" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G281" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H281" t="s">
         <v>18</v>
       </c>
       <c r="I281" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B282" t="s">
         <v>45</v>
       </c>
       <c r="C282" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D282" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E282" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F282" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G282" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="H282" t="s">
         <v>18</v>
       </c>
       <c r="I282" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B283" t="s">
         <v>45</v>
       </c>
       <c r="C283" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="D283" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="E283" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F283" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G283" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="H283" t="s">
         <v>18</v>
       </c>
       <c r="I283" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B284" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C284" t="s">
-        <v>226</v>
+        <v>85</v>
       </c>
       <c r="D284" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E284" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="F284" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="G284" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H284" t="s">
         <v>18</v>
       </c>
       <c r="I284" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="285" spans="1:9" ht="15">
       <c r="A285" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B285" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C285" t="s">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="D285" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="E285" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F285" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G285" t="s">
         <v>17</v>
@@ -9695,83 +9713,83 @@
     </row>
     <row r="286" spans="1:9" ht="15">
       <c r="A286" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B286" t="s">
         <v>70</v>
       </c>
       <c r="C286" t="s">
-        <v>13</v>
+        <v>226</v>
       </c>
       <c r="D286" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E286" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="F286" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="G286" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H286" t="s">
         <v>18</v>
       </c>
       <c r="I286" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="287" spans="1:9" ht="15">
       <c r="A287" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B287" t="s">
         <v>70</v>
       </c>
       <c r="C287" t="s">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="D287" t="s">
-        <v>254</v>
+        <v>55</v>
       </c>
       <c r="E287" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="F287" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G287" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H287" t="s">
         <v>18</v>
       </c>
       <c r="I287" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" spans="1:9" ht="15">
       <c r="A288" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B288" t="s">
         <v>70</v>
       </c>
       <c r="C288" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D288" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E288" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="F288" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="G288" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H288" t="s">
         <v>18</v>
@@ -9782,54 +9800,54 @@
     </row>
     <row r="289" spans="1:9" ht="15">
       <c r="A289" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B289" t="s">
         <v>70</v>
       </c>
       <c r="C289" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D289" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="E289" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="F289" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G289" t="s">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="H289" t="s">
         <v>18</v>
       </c>
       <c r="I289" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="15">
       <c r="A290" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B290" t="s">
         <v>70</v>
       </c>
       <c r="C290" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="D290" t="s">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="E290" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="F290" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="G290" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H290" t="s">
         <v>18</v>
@@ -9840,141 +9858,141 @@
     </row>
     <row r="291" spans="1:9" ht="15">
       <c r="A291" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B291" t="s">
         <v>70</v>
       </c>
       <c r="C291" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D291" t="s">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="E291" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F291" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G291" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
       <c r="H291" t="s">
         <v>18</v>
       </c>
       <c r="I291" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="15">
       <c r="A292" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B292" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C292" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
       <c r="D292" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E292" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F292" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="G292" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="H292" t="s">
         <v>18</v>
       </c>
       <c r="I292" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15">
       <c r="A293" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B293" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C293" t="s">
-        <v>251</v>
+        <v>85</v>
       </c>
       <c r="D293" t="s">
-        <v>55</v>
+        <v>172</v>
       </c>
       <c r="E293" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="F293" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G293" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="H293" t="s">
         <v>18</v>
       </c>
       <c r="I293" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="15">
       <c r="A294" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B294" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C294" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D294" t="s">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="E294" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F294" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G294" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="H294" t="s">
         <v>18</v>
       </c>
       <c r="I294" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="15">
       <c r="A295" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B295" t="s">
         <v>92</v>
       </c>
       <c r="C295" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="D295" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="E295" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F295" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="G295" t="s">
-        <v>37</v>
+        <v>155</v>
       </c>
       <c r="H295" t="s">
         <v>18</v>
@@ -9985,25 +10003,25 @@
     </row>
     <row r="296" spans="1:9" ht="15">
       <c r="A296" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B296" t="s">
         <v>92</v>
       </c>
       <c r="C296" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="D296" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="E296" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F296" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="G296" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="H296" t="s">
         <v>18</v>
@@ -10014,141 +10032,141 @@
     </row>
     <row r="297" spans="1:9" ht="15">
       <c r="A297" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B297" t="s">
         <v>92</v>
       </c>
       <c r="C297" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D297" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="E297" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="F297" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="G297" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="H297" t="s">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="I297" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="15">
       <c r="A298" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B298" t="s">
         <v>92</v>
       </c>
       <c r="C298" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="D298" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="E298" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F298" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G298" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="H298" t="s">
         <v>18</v>
       </c>
       <c r="I298" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="299" spans="1:9" ht="15">
       <c r="A299" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B299" t="s">
         <v>92</v>
       </c>
       <c r="C299" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="D299" t="s">
-        <v>239</v>
+        <v>14</v>
       </c>
       <c r="E299" t="s">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="F299" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="G299" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="H299" t="s">
         <v>18</v>
       </c>
       <c r="I299" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15">
       <c r="A300" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B300" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C300" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
       <c r="D300" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E300" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F300" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
       <c r="G300" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="H300" t="s">
         <v>18</v>
       </c>
       <c r="I300" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="15">
       <c r="A301" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B301" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C301" t="s">
-        <v>251</v>
+        <v>85</v>
       </c>
       <c r="D301" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
       <c r="E301" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="F301" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="G301" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="H301" t="s">
         <v>18</v>
@@ -10159,25 +10177,25 @@
     </row>
     <row r="302" spans="1:9" ht="15">
       <c r="A302" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B302" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C302" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D302" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E302" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F302" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G302" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H302" t="s">
         <v>18</v>
@@ -10188,112 +10206,112 @@
     </row>
     <row r="303" spans="1:9" ht="15">
       <c r="A303" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B303" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C303" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="D303" t="s">
-        <v>14</v>
+        <v>239</v>
       </c>
       <c r="E303" t="s">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="F303" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="G303" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="H303" t="s">
         <v>18</v>
       </c>
       <c r="I303" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="15">
       <c r="A304" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B304" t="s">
         <v>98</v>
       </c>
       <c r="C304" t="s">
-        <v>85</v>
+        <v>226</v>
       </c>
       <c r="D304" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="E304" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F304" t="s">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="G304" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="H304" t="s">
         <v>18</v>
       </c>
       <c r="I304" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="305" spans="1:9" ht="15">
       <c r="A305" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B305" t="s">
         <v>98</v>
       </c>
       <c r="C305" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="D305" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E305" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="F305" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G305" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H305" t="s">
         <v>18</v>
       </c>
       <c r="I305" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="15">
       <c r="A306" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B306" t="s">
         <v>98</v>
       </c>
       <c r="C306" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="D306" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E306" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F306" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="G306" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H306" t="s">
         <v>18</v>
@@ -10304,141 +10322,141 @@
     </row>
     <row r="307" spans="1:9" ht="15">
       <c r="A307" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B307" t="s">
         <v>98</v>
       </c>
       <c r="C307" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="D307" t="s">
-        <v>256</v>
+        <v>14</v>
       </c>
       <c r="E307" t="s">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="F307" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G307" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="H307" t="s">
         <v>18</v>
       </c>
       <c r="I307" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="15">
       <c r="A308" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B308" t="s">
         <v>98</v>
       </c>
       <c r="C308" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="D308" t="s">
-        <v>248</v>
+        <v>55</v>
       </c>
       <c r="E308" t="s">
-        <v>257</v>
+        <v>22</v>
       </c>
       <c r="F308" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="G308" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="H308" t="s">
         <v>18</v>
       </c>
       <c r="I308" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="15">
       <c r="A309" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B309" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C309" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="D309" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="E309" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F309" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="G309" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="H309" t="s">
         <v>18</v>
       </c>
       <c r="I309" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15">
       <c r="A310" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B310" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C310" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="D310" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E310" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="F310" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G310" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H310" t="s">
         <v>18</v>
       </c>
       <c r="I310" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="311" spans="1:9" ht="15">
       <c r="A311" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B311" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C311" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D311" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E311" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F311" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="G311" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="H311" t="s">
         <v>18</v>
@@ -10449,112 +10467,112 @@
     </row>
     <row r="312" spans="1:9" ht="15">
       <c r="A312" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B312" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C312" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="D312" t="s">
-        <v>14</v>
+        <v>258</v>
       </c>
       <c r="E312" t="s">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="F312" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G312" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="H312" t="s">
         <v>18</v>
       </c>
       <c r="I312" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="15">
       <c r="A313" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B313" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C313" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D313" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="E313" t="s">
-        <v>63</v>
+        <v>259</v>
       </c>
       <c r="F313" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G313" t="s">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="H313" t="s">
         <v>18</v>
       </c>
       <c r="I313" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="314" spans="1:9" ht="15">
       <c r="A314" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B314" t="s">
         <v>114</v>
       </c>
       <c r="C314" t="s">
-        <v>33</v>
+        <v>236</v>
       </c>
       <c r="D314" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="E314" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F314" t="s">
-        <v>89</v>
+        <v>237</v>
       </c>
       <c r="G314" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="H314" t="s">
         <v>18</v>
       </c>
       <c r="I314" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="15">
       <c r="A315" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B315" t="s">
         <v>114</v>
       </c>
       <c r="C315" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="D315" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
       <c r="E315" t="s">
         <v>129</v>
       </c>
       <c r="F315" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="G315" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="H315" t="s">
         <v>18</v>
@@ -10565,25 +10583,25 @@
     </row>
     <row r="316" spans="1:9" ht="15">
       <c r="A316" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B316" t="s">
         <v>114</v>
       </c>
       <c r="C316" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="D316" t="s">
-        <v>240</v>
+        <v>179</v>
       </c>
       <c r="E316" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F316" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="G316" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H316" t="s">
         <v>18</v>
@@ -10594,141 +10612,141 @@
     </row>
     <row r="317" spans="1:9" ht="15">
       <c r="A317" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B317" t="s">
         <v>114</v>
       </c>
       <c r="C317" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="D317" t="s">
-        <v>239</v>
+        <v>14</v>
       </c>
       <c r="E317" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="F317" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="G317" t="s">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="H317" t="s">
         <v>18</v>
       </c>
       <c r="I317" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15">
       <c r="A318" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B318" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C318" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="D318" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="E318" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F318" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="G318" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="H318" t="s">
         <v>18</v>
       </c>
       <c r="I318" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="15">
       <c r="A319" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B319" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C319" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
       <c r="D319" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="E319" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F319" t="s">
-        <v>260</v>
+        <v>89</v>
       </c>
       <c r="G319" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="H319" t="s">
         <v>18</v>
       </c>
       <c r="I319" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="320" spans="1:9" ht="15">
       <c r="A320" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B320" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C320" t="s">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="D320" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="E320" t="s">
         <v>129</v>
       </c>
       <c r="F320" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="G320" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H320" t="s">
         <v>18</v>
       </c>
       <c r="I320" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="15">
       <c r="A321" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B321" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C321" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="D321" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="E321" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F321" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="G321" t="s">
-        <v>249</v>
+        <v>71</v>
       </c>
       <c r="H321" t="s">
         <v>18</v>
@@ -10739,25 +10757,25 @@
     </row>
     <row r="322" spans="1:9" ht="15">
       <c r="A322" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B322" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C322" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="D322" t="s">
-        <v>55</v>
+        <v>239</v>
       </c>
       <c r="E322" t="s">
         <v>56</v>
       </c>
       <c r="F322" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G322" t="s">
-        <v>58</v>
+        <v>261</v>
       </c>
       <c r="H322" t="s">
         <v>18</v>
@@ -10768,109 +10786,109 @@
     </row>
     <row r="323" spans="1:9" ht="15">
       <c r="A323" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B323" t="s">
         <v>123</v>
       </c>
       <c r="C323" t="s">
-        <v>108</v>
+        <v>236</v>
       </c>
       <c r="D323" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="E323" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F323" t="s">
-        <v>107</v>
+        <v>237</v>
       </c>
       <c r="G323" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H323" t="s">
         <v>18</v>
       </c>
       <c r="I323" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="15">
       <c r="A324" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B324" t="s">
         <v>123</v>
       </c>
       <c r="C324" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D324" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="E324" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F324" t="s">
-        <v>68</v>
+        <v>262</v>
       </c>
       <c r="G324" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="H324" t="s">
         <v>18</v>
       </c>
       <c r="I324" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="325" spans="1:9" ht="15">
       <c r="A325" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B325" t="s">
         <v>123</v>
       </c>
       <c r="C325" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D325" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="E325" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="F325" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G325" t="s">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="H325" t="s">
         <v>18</v>
       </c>
       <c r="I325" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="15">
       <c r="A326" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B326" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C326" t="s">
-        <v>236</v>
+        <v>166</v>
       </c>
       <c r="D326" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E326" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="F326" t="s">
-        <v>237</v>
+        <v>103</v>
       </c>
       <c r="G326" t="s">
         <v>126</v>
@@ -10884,83 +10902,83 @@
     </row>
     <row r="327" spans="1:9" ht="15">
       <c r="A327" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B327" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C327" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
       <c r="D327" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="E327" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F327" t="s">
-        <v>260</v>
+        <v>81</v>
       </c>
       <c r="G327" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="H327" t="s">
         <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="328" spans="1:9" ht="15">
       <c r="A328" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B328" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C328" t="s">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="D328" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="E328" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="F328" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="G328" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="H328" t="s">
         <v>18</v>
       </c>
       <c r="I328" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="329" spans="1:9" ht="15">
       <c r="A329" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B329" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C329" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="D329" t="s">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="E329" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F329" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="G329" t="s">
-        <v>249</v>
+        <v>69</v>
       </c>
       <c r="H329" t="s">
         <v>18</v>
@@ -10971,25 +10989,25 @@
     </row>
     <row r="330" spans="1:9" ht="15">
       <c r="A330" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B330" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C330" t="s">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="D330" t="s">
-        <v>94</v>
+        <v>239</v>
       </c>
       <c r="E330" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F330" t="s">
         <v>64</v>
       </c>
       <c r="G330" t="s">
-        <v>66</v>
+        <v>261</v>
       </c>
       <c r="H330" t="s">
         <v>18</v>
@@ -11000,51 +11018,51 @@
     </row>
     <row r="331" spans="1:9" ht="15">
       <c r="A331" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B331" t="s">
         <v>131</v>
       </c>
       <c r="C331" t="s">
-        <v>108</v>
+        <v>236</v>
       </c>
       <c r="D331" t="s">
-        <v>34</v>
+        <v>179</v>
       </c>
       <c r="E331" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F331" t="s">
-        <v>61</v>
+        <v>237</v>
       </c>
       <c r="G331" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H331" t="s">
         <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="332" spans="1:9" ht="15">
       <c r="A332" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B332" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="C332" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D332" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="E332" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F332" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="G332" t="s">
         <v>126</v>
@@ -11058,22 +11076,22 @@
     </row>
     <row r="333" spans="1:9" ht="15">
       <c r="A333" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B333" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="C333" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="D333" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="E333" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="F333" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="G333" t="s">
         <v>126</v>
@@ -11087,59 +11105,204 @@
     </row>
     <row r="334" spans="1:9" ht="15">
       <c r="A334" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B334" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="C334" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D334" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="E334" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="F334" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="G334" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H334" t="s">
         <v>18</v>
       </c>
       <c r="I334" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="335" spans="1:9" ht="15">
       <c r="A335" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B335" t="s">
-        <v>261</v>
+        <v>131</v>
       </c>
       <c r="C335" t="s">
+        <v>85</v>
+      </c>
+      <c r="D335" t="s">
+        <v>94</v>
+      </c>
+      <c r="E335" t="s">
+        <v>63</v>
+      </c>
+      <c r="F335" t="s">
+        <v>64</v>
+      </c>
+      <c r="G335" t="s">
+        <v>66</v>
+      </c>
+      <c r="H335" t="s">
+        <v>18</v>
+      </c>
+      <c r="I335" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="15">
+      <c r="A336" t="s">
+        <v>251</v>
+      </c>
+      <c r="B336" t="s">
+        <v>131</v>
+      </c>
+      <c r="C336" t="s">
+        <v>108</v>
+      </c>
+      <c r="D336" t="s">
+        <v>34</v>
+      </c>
+      <c r="E336" t="s">
+        <v>60</v>
+      </c>
+      <c r="F336" t="s">
+        <v>61</v>
+      </c>
+      <c r="G336" t="s">
+        <v>109</v>
+      </c>
+      <c r="H336" t="s">
+        <v>18</v>
+      </c>
+      <c r="I336" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" ht="15">
+      <c r="A337" t="s">
+        <v>251</v>
+      </c>
+      <c r="B337" t="s">
+        <v>191</v>
+      </c>
+      <c r="C337" t="s">
         <v>236</v>
       </c>
-      <c r="D335" t="s">
+      <c r="D337" t="s">
+        <v>213</v>
+      </c>
+      <c r="E337" t="s">
+        <v>56</v>
+      </c>
+      <c r="F337" t="s">
+        <v>237</v>
+      </c>
+      <c r="G337" t="s">
+        <v>126</v>
+      </c>
+      <c r="H337" t="s">
+        <v>18</v>
+      </c>
+      <c r="I337" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" ht="15">
+      <c r="A338" t="s">
+        <v>251</v>
+      </c>
+      <c r="B338" t="s">
+        <v>191</v>
+      </c>
+      <c r="C338" t="s">
+        <v>226</v>
+      </c>
+      <c r="D338" t="s">
+        <v>173</v>
+      </c>
+      <c r="E338" t="s">
+        <v>77</v>
+      </c>
+      <c r="F338" t="s">
+        <v>262</v>
+      </c>
+      <c r="G338" t="s">
+        <v>126</v>
+      </c>
+      <c r="H338" t="s">
+        <v>18</v>
+      </c>
+      <c r="I338" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" ht="15">
+      <c r="A339" t="s">
+        <v>251</v>
+      </c>
+      <c r="B339" t="s">
+        <v>191</v>
+      </c>
+      <c r="C339" t="s">
+        <v>85</v>
+      </c>
+      <c r="D339" t="s">
+        <v>239</v>
+      </c>
+      <c r="E339" t="s">
+        <v>63</v>
+      </c>
+      <c r="F339" t="s">
+        <v>64</v>
+      </c>
+      <c r="G339" t="s">
+        <v>66</v>
+      </c>
+      <c r="H339" t="s">
+        <v>18</v>
+      </c>
+      <c r="I339" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" ht="15">
+      <c r="A340" t="s">
+        <v>251</v>
+      </c>
+      <c r="B340" t="s">
+        <v>263</v>
+      </c>
+      <c r="C340" t="s">
+        <v>236</v>
+      </c>
+      <c r="D340" t="s">
         <v>182</v>
       </c>
-      <c r="E335" t="s">
+      <c r="E340" t="s">
         <v>56</v>
       </c>
-      <c r="F335" t="s">
+      <c r="F340" t="s">
         <v>237</v>
       </c>
-      <c r="G335" t="s">
+      <c r="G340" t="s">
         <v>126</v>
       </c>
-      <c r="H335" t="s">
-        <v>18</v>
-      </c>
-      <c r="I335" t="s">
+      <c r="H340" t="s">
+        <v>18</v>
+      </c>
+      <c r="I340" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11151,8 +11314,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{976a95ae-a43f-4221-a1f0-79a513ca89d0}">
-  <dimension ref="A1:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cddca9e2-298d-40c7-bc37-df63020dc154}">
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -11161,7 +11324,7 @@
     <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="14.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="15.5714285714286" customWidth="1"/>
     <col min="8" max="8" width="12.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
@@ -11171,16 +11334,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -11200,16 +11363,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -11229,13 +11392,13 @@
         <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
         <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
         <v>73</v>
@@ -11258,16 +11421,16 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -11287,13 +11450,13 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -11316,16 +11479,16 @@
         <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -11345,13 +11508,13 @@
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -11374,16 +11537,16 @@
         <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -11403,13 +11566,13 @@
         <v>235</v>
       </c>
       <c r="B9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C9" t="s">
         <v>236</v>
       </c>
       <c r="D9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
@@ -11432,25 +11595,25 @@
         <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>120</v>
+        <v>286</v>
       </c>
       <c r="H10" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
@@ -11461,16 +11624,16 @@
         <v>235</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -11479,9 +11642,67 @@
         <v>120</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>120</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11493,8 +11714,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ece62f9-e85e-489e-8e4c-18eb3b29e383}">
-  <dimension ref="A1:F91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6a8d15a8-b74c-474a-9d00-7e7f8bfb83ae}">
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -11510,13 +11731,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -11530,13 +11751,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -11550,13 +11771,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -11570,13 +11791,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -11590,13 +11811,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -11610,13 +11831,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C6" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
         <v>69</v>
@@ -11630,13 +11851,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s">
         <v>112</v>
@@ -11650,13 +11871,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E8" t="s">
         <v>189</v>
@@ -11670,13 +11891,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
         <v>90</v>
@@ -11690,13 +11911,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -11710,13 +11931,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E11" t="s">
         <v>148</v>
@@ -11730,13 +11951,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -11750,13 +11971,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -11770,13 +11991,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -11790,13 +12011,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -11810,13 +12031,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E16" t="s">
         <v>183</v>
@@ -11830,16 +12051,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -11850,16 +12071,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
@@ -11870,13 +12091,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -11890,16 +12111,16 @@
         <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C20" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E20" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
@@ -11910,16 +12131,16 @@
         <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C21" t="s">
         <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E21" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -11930,16 +12151,16 @@
         <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
         <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E22" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -11950,13 +12171,13 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
@@ -11970,13 +12191,13 @@
         <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C24" t="s">
         <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E24" t="s">
         <v>195</v>
@@ -11990,13 +12211,13 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E25" t="s">
         <v>75</v>
@@ -12010,13 +12231,13 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C26" t="s">
         <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -12030,13 +12251,13 @@
         <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C27" t="s">
         <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -12050,13 +12271,13 @@
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E28" t="s">
         <v>189</v>
@@ -12070,13 +12291,13 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E29" t="s">
         <v>96</v>
@@ -12090,13 +12311,13 @@
         <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E30" t="s">
         <v>158</v>
@@ -12110,13 +12331,13 @@
         <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
         <v>162</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E31" t="s">
         <v>130</v>
@@ -12130,13 +12351,13 @@
         <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E32" t="s">
         <v>65</v>
@@ -12150,13 +12371,13 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C33" t="s">
         <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E33" t="s">
         <v>96</v>
@@ -12170,13 +12391,13 @@
         <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C34" t="s">
         <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E34" t="s">
         <v>189</v>
@@ -12190,13 +12411,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C35" t="s">
         <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E35" t="s">
         <v>178</v>
@@ -12210,16 +12431,16 @@
         <v>133</v>
       </c>
       <c r="B36" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E36" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F36" t="s">
         <v>80</v>
@@ -12230,13 +12451,13 @@
         <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C37" t="s">
         <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E37" t="s">
         <v>100</v>
@@ -12250,13 +12471,13 @@
         <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E38" t="s">
         <v>54</v>
@@ -12270,13 +12491,13 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C39" t="s">
         <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E39" t="s">
         <v>90</v>
@@ -12290,13 +12511,13 @@
         <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s">
         <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E40" t="s">
         <v>130</v>
@@ -12310,16 +12531,16 @@
         <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C41" t="s">
         <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F41" t="s">
         <v>80</v>
@@ -12330,16 +12551,16 @@
         <v>133</v>
       </c>
       <c r="B42" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C42" t="s">
         <v>183</v>
       </c>
       <c r="D42" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E42" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -12350,13 +12571,13 @@
         <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C43" t="s">
         <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E43" t="s">
         <v>130</v>
@@ -12370,16 +12591,16 @@
         <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -12390,16 +12611,16 @@
         <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C45" t="s">
         <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -12410,13 +12631,13 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C46" t="s">
         <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E46" t="s">
         <v>69</v>
@@ -12430,13 +12651,13 @@
         <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C47" t="s">
         <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E47" t="s">
         <v>135</v>
@@ -12450,13 +12671,13 @@
         <v>194</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C48" t="s">
         <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E48" t="s">
         <v>24</v>
@@ -12470,13 +12691,13 @@
         <v>194</v>
       </c>
       <c r="B49" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -12490,13 +12711,13 @@
         <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C50" t="s">
         <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E50" t="s">
         <v>190</v>
@@ -12510,16 +12731,16 @@
         <v>194</v>
       </c>
       <c r="B51" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C51" t="s">
         <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E51" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F51" t="s">
         <v>32</v>
@@ -12530,13 +12751,13 @@
         <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C52" t="s">
         <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E52" t="s">
         <v>130</v>
@@ -12550,13 +12771,13 @@
         <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E53" t="s">
         <v>108</v>
@@ -12570,13 +12791,13 @@
         <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C54" t="s">
         <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E54" t="s">
         <v>148</v>
@@ -12590,13 +12811,13 @@
         <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C55" t="s">
         <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E55" t="s">
         <v>96</v>
@@ -12610,13 +12831,13 @@
         <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C56" t="s">
         <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E56" t="s">
         <v>69</v>
@@ -12630,13 +12851,13 @@
         <v>235</v>
       </c>
       <c r="B57" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C57" t="s">
         <v>236</v>
       </c>
       <c r="D57" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E57" t="s">
         <v>69</v>
@@ -12650,13 +12871,13 @@
         <v>235</v>
       </c>
       <c r="B58" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C58" t="s">
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -12670,16 +12891,16 @@
         <v>235</v>
       </c>
       <c r="B59" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C59" t="s">
         <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E59" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F59" t="s">
         <v>80</v>
@@ -12690,13 +12911,13 @@
         <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E60" t="s">
         <v>66</v>
@@ -12710,13 +12931,13 @@
         <v>235</v>
       </c>
       <c r="B61" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C61" t="s">
         <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E61" t="s">
         <v>53</v>
@@ -12730,13 +12951,13 @@
         <v>235</v>
       </c>
       <c r="B62" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C62" t="s">
         <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E62" t="s">
         <v>144</v>
@@ -12750,16 +12971,16 @@
         <v>235</v>
       </c>
       <c r="B63" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s">
         <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E63" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F63" t="s">
         <v>80</v>
@@ -12770,13 +12991,13 @@
         <v>235</v>
       </c>
       <c r="B64" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C64" t="s">
         <v>110</v>
       </c>
       <c r="D64" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E64" t="s">
         <v>158</v>
@@ -12790,13 +13011,13 @@
         <v>235</v>
       </c>
       <c r="B65" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -12810,13 +13031,13 @@
         <v>235</v>
       </c>
       <c r="B66" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C66" t="s">
         <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E66" t="s">
         <v>54</v>
@@ -12830,13 +13051,13 @@
         <v>235</v>
       </c>
       <c r="B67" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C67" t="s">
         <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -12850,13 +13071,13 @@
         <v>235</v>
       </c>
       <c r="B68" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C68" t="s">
         <v>110</v>
       </c>
       <c r="D68" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E68" t="s">
         <v>220</v>
@@ -12870,13 +13091,13 @@
         <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E69" t="s">
         <v>53</v>
@@ -12890,13 +13111,13 @@
         <v>235</v>
       </c>
       <c r="B70" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C70" t="s">
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E70" t="s">
         <v>49</v>
@@ -12910,13 +13131,13 @@
         <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C71" t="s">
         <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E71" t="s">
         <v>90</v>
@@ -12930,16 +13151,16 @@
         <v>235</v>
       </c>
       <c r="B72" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C72" t="s">
         <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E72" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -12950,16 +13171,16 @@
         <v>235</v>
       </c>
       <c r="B73" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E73" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -12970,16 +13191,16 @@
         <v>235</v>
       </c>
       <c r="B74" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C74" t="s">
         <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F74" t="s">
         <v>80</v>
@@ -12987,19 +13208,19 @@
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B75" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C75" t="s">
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E75" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -13007,16 +13228,16 @@
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C76" t="s">
         <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E76" t="s">
         <v>24</v>
@@ -13027,16 +13248,16 @@
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D77" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E77" t="s">
         <v>130</v>
@@ -13047,16 +13268,16 @@
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C78" t="s">
         <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E78" t="s">
         <v>178</v>
@@ -13067,16 +13288,16 @@
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C79" t="s">
         <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E79" t="s">
         <v>178</v>
@@ -13087,16 +13308,16 @@
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D80" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E80" t="s">
         <v>155</v>
@@ -13107,19 +13328,19 @@
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D81" t="s">
         <v>294</v>
       </c>
       <c r="E81" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F81" t="s">
         <v>18</v>
@@ -13127,19 +13348,19 @@
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B82" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C82" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E82" t="s">
-        <v>304</v>
+        <v>66</v>
       </c>
       <c r="F82" t="s">
         <v>18</v>
@@ -13147,19 +13368,19 @@
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B83" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C83" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="D83" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E83" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="F83" t="s">
         <v>18</v>
@@ -13167,19 +13388,19 @@
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" t="s">
+        <v>251</v>
+      </c>
+      <c r="B84" t="s">
+        <v>302</v>
+      </c>
+      <c r="C84" t="s">
+        <v>252</v>
+      </c>
+      <c r="D84" t="s">
+        <v>292</v>
+      </c>
+      <c r="E84" t="s">
         <v>250</v>
-      </c>
-      <c r="B84" t="s">
-        <v>296</v>
-      </c>
-      <c r="C84" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" t="s">
-        <v>291</v>
-      </c>
-      <c r="E84" t="s">
-        <v>303</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -13187,19 +13408,19 @@
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B85" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C85" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E85" t="s">
-        <v>106</v>
+        <v>309</v>
       </c>
       <c r="F85" t="s">
         <v>18</v>
@@ -13207,19 +13428,19 @@
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B86" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C86" t="s">
         <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="F86" t="s">
         <v>18</v>
@@ -13227,19 +13448,19 @@
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C87" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E87" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
         <v>18</v>
@@ -13247,19 +13468,19 @@
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B88" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D88" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E88" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="F88" t="s">
         <v>18</v>
@@ -13267,19 +13488,19 @@
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B89" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C89" t="s">
-        <v>251</v>
+        <v>108</v>
       </c>
       <c r="D89" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E89" t="s">
-        <v>249</v>
+        <v>130</v>
       </c>
       <c r="F89" t="s">
         <v>18</v>
@@ -13287,19 +13508,19 @@
     </row>
     <row r="90" spans="1:6" ht="15">
       <c r="A90" t="s">
+        <v>251</v>
+      </c>
+      <c r="B90" t="s">
+        <v>306</v>
+      </c>
+      <c r="C90" t="s">
+        <v>252</v>
+      </c>
+      <c r="D90" t="s">
+        <v>300</v>
+      </c>
+      <c r="E90" t="s">
         <v>250</v>
-      </c>
-      <c r="B90" t="s">
-        <v>300</v>
-      </c>
-      <c r="C90" t="s">
-        <v>108</v>
-      </c>
-      <c r="D90" t="s">
-        <v>299</v>
-      </c>
-      <c r="E90" t="s">
-        <v>303</v>
       </c>
       <c r="F90" t="s">
         <v>18</v>
@@ -13307,21 +13528,41 @@
     </row>
     <row r="91" spans="1:6" ht="15">
       <c r="A91" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s">
+        <v>306</v>
+      </c>
+      <c r="C91" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" t="s">
         <v>305</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" t="s">
+        <v>309</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15">
+      <c r="A92" t="s">
+        <v>251</v>
+      </c>
+      <c r="B92" t="s">
+        <v>311</v>
+      </c>
+      <c r="C92" t="s">
         <v>226</v>
       </c>
-      <c r="D91" t="s">
-        <v>286</v>
-      </c>
-      <c r="E91" t="s">
-        <v>302</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="D92" t="s">
+        <v>292</v>
+      </c>
+      <c r="E92" t="s">
+        <v>308</v>
+      </c>
+      <c r="F92" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3731" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="314">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>p. Nowak, historia za piątek 22.05.2026</t>
   </si>
   <si>
     <t>Projektowanie fryzur</t>
@@ -1410,7 +1413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{163b631a-49de-4771-be67-006349543ed4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{256b28b1-bc9d-4f30-8c35-63697d54083d}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1431,8 +1434,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f73ef7ce-6bdc-48db-84c7-95fe8f82498b}">
-  <dimension ref="A1:I340"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{dda4a915-1038-4675-a052-0e408e819058}">
+  <dimension ref="A1:I341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6796,19 +6799,19 @@
         <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F185" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G185" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="H185" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="I185" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
@@ -6825,7 +6828,7 @@
         <v>25</v>
       </c>
       <c r="E186" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F186" t="s">
         <v>27</v>
@@ -6880,7 +6883,7 @@
         <v>75</v>
       </c>
       <c r="D188" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E188" t="s">
         <v>15</v>
@@ -7167,16 +7170,16 @@
         <v>98</v>
       </c>
       <c r="C198" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D198" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E198" t="s">
         <v>77</v>
       </c>
       <c r="F198" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G198" t="s">
         <v>126</v>
@@ -7260,7 +7263,7 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F201" t="s">
         <v>107</v>
@@ -7327,7 +7330,7 @@
         <v>120</v>
       </c>
       <c r="H203" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I203" t="s">
         <v>19</v>
@@ -7341,16 +7344,16 @@
         <v>114</v>
       </c>
       <c r="C204" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D204" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E204" t="s">
         <v>77</v>
       </c>
       <c r="F204" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G204" t="s">
         <v>126</v>
@@ -7434,7 +7437,7 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F207" t="s">
         <v>146</v>
@@ -7486,16 +7489,16 @@
         <v>123</v>
       </c>
       <c r="C209" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D209" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E209" t="s">
         <v>77</v>
       </c>
       <c r="F209" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G209" t="s">
         <v>126</v>
@@ -7518,7 +7521,7 @@
         <v>71</v>
       </c>
       <c r="D210" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E210" t="s">
         <v>35</v>
@@ -7550,7 +7553,7 @@
         <v>182</v>
       </c>
       <c r="E211" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F211" t="s">
         <v>107</v>
@@ -7573,10 +7576,10 @@
         <v>131</v>
       </c>
       <c r="C212" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D212" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E212" t="s">
         <v>67</v>
@@ -7596,13 +7599,13 @@
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B213" t="s">
         <v>134</v>
       </c>
       <c r="C213" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D213" t="s">
         <v>160</v>
@@ -7611,7 +7614,7 @@
         <v>56</v>
       </c>
       <c r="F213" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G213" t="s">
         <v>17</v>
@@ -7625,7 +7628,7 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B214" t="s">
         <v>134</v>
@@ -7634,7 +7637,7 @@
         <v>148</v>
       </c>
       <c r="D214" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E214" t="s">
         <v>77</v>
@@ -7654,7 +7657,7 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B215" t="s">
         <v>134</v>
@@ -7683,7 +7686,7 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B216" t="s">
         <v>134</v>
@@ -7712,7 +7715,7 @@
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B217" t="s">
         <v>134</v>
@@ -7721,7 +7724,7 @@
         <v>96</v>
       </c>
       <c r="D217" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E217" t="s">
         <v>73</v>
@@ -7741,22 +7744,22 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
       </c>
       <c r="C218" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D218" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E218" t="s">
         <v>56</v>
       </c>
       <c r="F218" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G218" t="s">
         <v>17</v>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B219" t="s">
         <v>12</v>
@@ -7779,7 +7782,7 @@
         <v>148</v>
       </c>
       <c r="D219" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E219" t="s">
         <v>77</v>
@@ -7799,7 +7802,7 @@
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B220" t="s">
         <v>12</v>
@@ -7808,10 +7811,10 @@
         <v>75</v>
       </c>
       <c r="D220" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E220" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F220" t="s">
         <v>107</v>
@@ -7828,7 +7831,7 @@
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B221" t="s">
         <v>12</v>
@@ -7857,7 +7860,7 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B222" t="s">
         <v>12</v>
@@ -7866,10 +7869,10 @@
         <v>20</v>
       </c>
       <c r="D222" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E222" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F222" t="s">
         <v>107</v>
@@ -7886,7 +7889,7 @@
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B223" t="s">
         <v>12</v>
@@ -7915,7 +7918,7 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B224" t="s">
         <v>12</v>
@@ -7924,7 +7927,7 @@
         <v>39</v>
       </c>
       <c r="D224" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E224" t="s">
         <v>41</v>
@@ -7944,7 +7947,7 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B225" t="s">
         <v>12</v>
@@ -7973,19 +7976,19 @@
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B226" t="s">
         <v>45</v>
       </c>
       <c r="C226" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D226" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E226" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F226" t="s">
         <v>48</v>
@@ -8002,7 +8005,7 @@
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B227" t="s">
         <v>45</v>
@@ -8011,7 +8014,7 @@
         <v>148</v>
       </c>
       <c r="D227" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E227" t="s">
         <v>77</v>
@@ -8031,7 +8034,7 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B228" t="s">
         <v>45</v>
@@ -8040,7 +8043,7 @@
         <v>75</v>
       </c>
       <c r="D228" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E228" t="s">
         <v>22</v>
@@ -8060,7 +8063,7 @@
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B229" t="s">
         <v>45</v>
@@ -8089,7 +8092,7 @@
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B230" t="s">
         <v>45</v>
@@ -8098,7 +8101,7 @@
         <v>20</v>
       </c>
       <c r="D230" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E230" t="s">
         <v>22</v>
@@ -8118,7 +8121,7 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B231" t="s">
         <v>45</v>
@@ -8147,7 +8150,7 @@
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B232" t="s">
         <v>45</v>
@@ -8176,7 +8179,7 @@
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B233" t="s">
         <v>45</v>
@@ -8185,7 +8188,7 @@
         <v>39</v>
       </c>
       <c r="D233" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E233" t="s">
         <v>199</v>
@@ -8205,7 +8208,7 @@
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B234" t="s">
         <v>45</v>
@@ -8234,7 +8237,7 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B235" t="s">
         <v>45</v>
@@ -8263,13 +8266,13 @@
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B236" t="s">
         <v>70</v>
       </c>
       <c r="C236" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D236" t="s">
         <v>87</v>
@@ -8292,7 +8295,7 @@
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B237" t="s">
         <v>70</v>
@@ -8301,7 +8304,7 @@
         <v>75</v>
       </c>
       <c r="D237" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E237" t="s">
         <v>22</v>
@@ -8321,7 +8324,7 @@
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B238" t="s">
         <v>70</v>
@@ -8350,7 +8353,7 @@
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B239" t="s">
         <v>70</v>
@@ -8359,7 +8362,7 @@
         <v>20</v>
       </c>
       <c r="D239" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E239" t="s">
         <v>22</v>
@@ -8379,7 +8382,7 @@
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B240" t="s">
         <v>70</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B241" t="s">
         <v>70</v>
@@ -8437,7 +8440,7 @@
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B242" t="s">
         <v>70</v>
@@ -8446,7 +8449,7 @@
         <v>39</v>
       </c>
       <c r="D242" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E242" t="s">
         <v>199</v>
@@ -8466,7 +8469,7 @@
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B243" t="s">
         <v>70</v>
@@ -8495,7 +8498,7 @@
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B244" t="s">
         <v>70</v>
@@ -8504,10 +8507,10 @@
         <v>96</v>
       </c>
       <c r="D244" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E244" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F244" t="s">
         <v>89</v>
@@ -8524,7 +8527,7 @@
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B245" t="s">
         <v>70</v>
@@ -8553,13 +8556,13 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B246" t="s">
         <v>92</v>
       </c>
       <c r="C246" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D246" t="s">
         <v>40</v>
@@ -8568,7 +8571,7 @@
         <v>51</v>
       </c>
       <c r="F246" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G246" t="s">
         <v>28</v>
@@ -8582,7 +8585,7 @@
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B247" t="s">
         <v>92</v>
@@ -8591,7 +8594,7 @@
         <v>148</v>
       </c>
       <c r="D247" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E247" t="s">
         <v>51</v>
@@ -8611,7 +8614,7 @@
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B248" t="s">
         <v>92</v>
@@ -8640,7 +8643,7 @@
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B249" t="s">
         <v>92</v>
@@ -8669,7 +8672,7 @@
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B250" t="s">
         <v>92</v>
@@ -8678,13 +8681,13 @@
         <v>82</v>
       </c>
       <c r="D250" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E250" t="s">
         <v>51</v>
       </c>
       <c r="F250" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G250" t="s">
         <v>28</v>
@@ -8698,7 +8701,7 @@
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B251" t="s">
         <v>92</v>
@@ -8727,7 +8730,7 @@
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B252" t="s">
         <v>92</v>
@@ -8756,7 +8759,7 @@
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B253" t="s">
         <v>92</v>
@@ -8774,7 +8777,7 @@
         <v>89</v>
       </c>
       <c r="G253" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H253" t="s">
         <v>18</v>
@@ -8785,7 +8788,7 @@
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B254" t="s">
         <v>92</v>
@@ -8794,13 +8797,13 @@
         <v>96</v>
       </c>
       <c r="D254" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E254" t="s">
         <v>51</v>
       </c>
       <c r="F254" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G254" t="s">
         <v>28</v>
@@ -8814,7 +8817,7 @@
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B255" t="s">
         <v>92</v>
@@ -8843,13 +8846,13 @@
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B256" t="s">
         <v>98</v>
       </c>
       <c r="C256" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D256" t="s">
         <v>179</v>
@@ -8872,7 +8875,7 @@
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B257" t="s">
         <v>98</v>
@@ -8881,7 +8884,7 @@
         <v>148</v>
       </c>
       <c r="D257" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E257" t="s">
         <v>77</v>
@@ -8901,7 +8904,7 @@
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B258" t="s">
         <v>98</v>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B259" t="s">
         <v>98</v>
@@ -8939,7 +8942,7 @@
         <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E259" t="s">
         <v>63</v>
@@ -8959,7 +8962,7 @@
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B260" t="s">
         <v>98</v>
@@ -8988,7 +8991,7 @@
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B261" t="s">
         <v>98</v>
@@ -9017,7 +9020,7 @@
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B262" t="s">
         <v>98</v>
@@ -9046,7 +9049,7 @@
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B263" t="s">
         <v>98</v>
@@ -9075,7 +9078,7 @@
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B264" t="s">
         <v>98</v>
@@ -9104,7 +9107,7 @@
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B265" t="s">
         <v>114</v>
@@ -9113,7 +9116,7 @@
         <v>148</v>
       </c>
       <c r="D265" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E265" t="s">
         <v>77</v>
@@ -9133,7 +9136,7 @@
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B266" t="s">
         <v>114</v>
@@ -9142,7 +9145,7 @@
         <v>75</v>
       </c>
       <c r="D266" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E266" t="s">
         <v>60</v>
@@ -9162,7 +9165,7 @@
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B267" t="s">
         <v>114</v>
@@ -9191,7 +9194,7 @@
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B268" t="s">
         <v>114</v>
@@ -9200,7 +9203,7 @@
         <v>166</v>
       </c>
       <c r="D268" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E268" t="s">
         <v>15</v>
@@ -9209,7 +9212,7 @@
         <v>78</v>
       </c>
       <c r="G268" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H268" t="s">
         <v>18</v>
@@ -9220,7 +9223,7 @@
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B269" t="s">
         <v>114</v>
@@ -9249,7 +9252,7 @@
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B270" t="s">
         <v>114</v>
@@ -9278,7 +9281,7 @@
     </row>
     <row r="271" spans="1:9" ht="15">
       <c r="A271" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B271" t="s">
         <v>123</v>
@@ -9287,7 +9290,7 @@
         <v>148</v>
       </c>
       <c r="D271" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E271" t="s">
         <v>77</v>
@@ -9307,7 +9310,7 @@
     </row>
     <row r="272" spans="1:9" ht="15">
       <c r="A272" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B272" t="s">
         <v>123</v>
@@ -9336,7 +9339,7 @@
     </row>
     <row r="273" spans="1:9" ht="15">
       <c r="A273" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B273" t="s">
         <v>123</v>
@@ -9365,7 +9368,7 @@
     </row>
     <row r="274" spans="1:9" ht="15">
       <c r="A274" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B274" t="s">
         <v>123</v>
@@ -9394,7 +9397,7 @@
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B275" t="s">
         <v>131</v>
@@ -9423,13 +9426,13 @@
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B276" t="s">
         <v>134</v>
       </c>
       <c r="C276" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D276" t="s">
         <v>209</v>
@@ -9452,7 +9455,7 @@
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B277" t="s">
         <v>134</v>
@@ -9461,7 +9464,7 @@
         <v>20</v>
       </c>
       <c r="D277" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E277" t="s">
         <v>22</v>
@@ -9481,7 +9484,7 @@
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B278" t="s">
         <v>12</v>
@@ -9490,7 +9493,7 @@
         <v>20</v>
       </c>
       <c r="D278" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E278" t="s">
         <v>22</v>
@@ -9510,7 +9513,7 @@
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B279" t="s">
         <v>12</v>
@@ -9539,7 +9542,7 @@
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B280" t="s">
         <v>45</v>
@@ -9554,7 +9557,7 @@
         <v>15</v>
       </c>
       <c r="F280" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G280" t="s">
         <v>82</v>
@@ -9568,7 +9571,7 @@
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B281" t="s">
         <v>45</v>
@@ -9597,7 +9600,7 @@
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B282" t="s">
         <v>45</v>
@@ -9606,7 +9609,7 @@
         <v>166</v>
       </c>
       <c r="D282" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E282" t="s">
         <v>60</v>
@@ -9626,7 +9629,7 @@
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B283" t="s">
         <v>45</v>
@@ -9641,7 +9644,7 @@
         <v>15</v>
       </c>
       <c r="F283" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G283" t="s">
         <v>82</v>
@@ -9655,7 +9658,7 @@
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B284" t="s">
         <v>45</v>
@@ -9664,7 +9667,7 @@
         <v>85</v>
       </c>
       <c r="D284" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E284" t="s">
         <v>63</v>
@@ -9684,7 +9687,7 @@
     </row>
     <row r="285" spans="1:9" ht="15">
       <c r="A285" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B285" t="s">
         <v>45</v>
@@ -9713,22 +9716,22 @@
     </row>
     <row r="286" spans="1:9" ht="15">
       <c r="A286" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B286" t="s">
         <v>70</v>
       </c>
       <c r="C286" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D286" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E286" t="s">
         <v>118</v>
       </c>
       <c r="F286" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G286" t="s">
         <v>82</v>
@@ -9742,13 +9745,13 @@
     </row>
     <row r="287" spans="1:9" ht="15">
       <c r="A287" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B287" t="s">
         <v>70</v>
       </c>
       <c r="C287" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D287" t="s">
         <v>55</v>
@@ -9771,7 +9774,7 @@
     </row>
     <row r="288" spans="1:9" ht="15">
       <c r="A288" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B288" t="s">
         <v>70</v>
@@ -9780,7 +9783,7 @@
         <v>13</v>
       </c>
       <c r="D288" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E288" t="s">
         <v>77</v>
@@ -9800,7 +9803,7 @@
     </row>
     <row r="289" spans="1:9" ht="15">
       <c r="A289" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B289" t="s">
         <v>70</v>
@@ -9809,7 +9812,7 @@
         <v>13</v>
       </c>
       <c r="D289" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E289" t="s">
         <v>77</v>
@@ -9829,7 +9832,7 @@
     </row>
     <row r="290" spans="1:9" ht="15">
       <c r="A290" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B290" t="s">
         <v>70</v>
@@ -9838,13 +9841,13 @@
         <v>20</v>
       </c>
       <c r="D290" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E290" t="s">
         <v>118</v>
       </c>
       <c r="F290" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G290" t="s">
         <v>82</v>
@@ -9858,7 +9861,7 @@
     </row>
     <row r="291" spans="1:9" ht="15">
       <c r="A291" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B291" t="s">
         <v>70</v>
@@ -9867,7 +9870,7 @@
         <v>166</v>
       </c>
       <c r="D291" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E291" t="s">
         <v>15</v>
@@ -9876,7 +9879,7 @@
         <v>78</v>
       </c>
       <c r="G291" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H291" t="s">
         <v>18</v>
@@ -9887,7 +9890,7 @@
     </row>
     <row r="292" spans="1:9" ht="15">
       <c r="A292" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B292" t="s">
         <v>70</v>
@@ -9916,7 +9919,7 @@
     </row>
     <row r="293" spans="1:9" ht="15">
       <c r="A293" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B293" t="s">
         <v>70</v>
@@ -9945,7 +9948,7 @@
     </row>
     <row r="294" spans="1:9" ht="15">
       <c r="A294" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B294" t="s">
         <v>70</v>
@@ -9974,22 +9977,22 @@
     </row>
     <row r="295" spans="1:9" ht="15">
       <c r="A295" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B295" t="s">
         <v>92</v>
       </c>
       <c r="C295" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D295" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E295" t="s">
         <v>77</v>
       </c>
       <c r="F295" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G295" t="s">
         <v>155</v>
@@ -10003,13 +10006,13 @@
     </row>
     <row r="296" spans="1:9" ht="15">
       <c r="A296" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B296" t="s">
         <v>92</v>
       </c>
       <c r="C296" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D296" t="s">
         <v>55</v>
@@ -10032,7 +10035,7 @@
     </row>
     <row r="297" spans="1:9" ht="15">
       <c r="A297" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B297" t="s">
         <v>92</v>
@@ -10053,7 +10056,7 @@
         <v>120</v>
       </c>
       <c r="H297" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I297" t="s">
         <v>19</v>
@@ -10061,7 +10064,7 @@
     </row>
     <row r="298" spans="1:9" ht="15">
       <c r="A298" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B298" t="s">
         <v>92</v>
@@ -10090,7 +10093,7 @@
     </row>
     <row r="299" spans="1:9" ht="15">
       <c r="A299" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B299" t="s">
         <v>92</v>
@@ -10119,7 +10122,7 @@
     </row>
     <row r="300" spans="1:9" ht="15">
       <c r="A300" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B300" t="s">
         <v>92</v>
@@ -10134,7 +10137,7 @@
         <v>15</v>
       </c>
       <c r="F300" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G300" t="s">
         <v>82</v>
@@ -10148,7 +10151,7 @@
     </row>
     <row r="301" spans="1:9" ht="15">
       <c r="A301" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B301" t="s">
         <v>92</v>
@@ -10177,7 +10180,7 @@
     </row>
     <row r="302" spans="1:9" ht="15">
       <c r="A302" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B302" t="s">
         <v>92</v>
@@ -10206,7 +10209,7 @@
     </row>
     <row r="303" spans="1:9" ht="15">
       <c r="A303" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B303" t="s">
         <v>92</v>
@@ -10215,10 +10218,10 @@
         <v>108</v>
       </c>
       <c r="D303" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E303" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F303" t="s">
         <v>27</v>
@@ -10235,22 +10238,22 @@
     </row>
     <row r="304" spans="1:9" ht="15">
       <c r="A304" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B304" t="s">
         <v>98</v>
       </c>
       <c r="C304" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D304" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E304" t="s">
         <v>77</v>
       </c>
       <c r="F304" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G304" t="s">
         <v>155</v>
@@ -10264,13 +10267,13 @@
     </row>
     <row r="305" spans="1:9" ht="15">
       <c r="A305" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B305" t="s">
         <v>98</v>
       </c>
       <c r="C305" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D305" t="s">
         <v>213</v>
@@ -10293,7 +10296,7 @@
     </row>
     <row r="306" spans="1:9" ht="15">
       <c r="A306" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B306" t="s">
         <v>98</v>
@@ -10308,7 +10311,7 @@
         <v>15</v>
       </c>
       <c r="F306" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G306" t="s">
         <v>82</v>
@@ -10322,7 +10325,7 @@
     </row>
     <row r="307" spans="1:9" ht="15">
       <c r="A307" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B307" t="s">
         <v>98</v>
@@ -10351,7 +10354,7 @@
     </row>
     <row r="308" spans="1:9" ht="15">
       <c r="A308" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B308" t="s">
         <v>98</v>
@@ -10380,7 +10383,7 @@
     </row>
     <row r="309" spans="1:9" ht="15">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B309" t="s">
         <v>98</v>
@@ -10398,18 +10401,18 @@
         <v>95</v>
       </c>
       <c r="G309" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H309" t="s">
         <v>18</v>
       </c>
       <c r="I309" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15">
       <c r="A310" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B310" t="s">
         <v>98</v>
@@ -10421,24 +10424,24 @@
         <v>212</v>
       </c>
       <c r="E310" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F310" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G310" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H310" t="s">
         <v>18</v>
       </c>
       <c r="I310" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="311" spans="1:9" ht="15">
       <c r="A311" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B311" t="s">
         <v>98</v>
@@ -10467,7 +10470,7 @@
     </row>
     <row r="312" spans="1:9" ht="15">
       <c r="A312" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B312" t="s">
         <v>98</v>
@@ -10476,10 +10479,10 @@
         <v>108</v>
       </c>
       <c r="D312" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E312" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F312" t="s">
         <v>105</v>
@@ -10496,7 +10499,7 @@
     </row>
     <row r="313" spans="1:9" ht="15">
       <c r="A313" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B313" t="s">
         <v>98</v>
@@ -10505,10 +10508,10 @@
         <v>108</v>
       </c>
       <c r="D313" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E313" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F313" t="s">
         <v>105</v>
@@ -10525,13 +10528,13 @@
     </row>
     <row r="314" spans="1:9" ht="15">
       <c r="A314" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B314" t="s">
         <v>114</v>
       </c>
       <c r="C314" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D314" t="s">
         <v>177</v>
@@ -10540,7 +10543,7 @@
         <v>56</v>
       </c>
       <c r="F314" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G314" t="s">
         <v>126</v>
@@ -10554,13 +10557,13 @@
     </row>
     <row r="315" spans="1:9" ht="15">
       <c r="A315" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B315" t="s">
         <v>114</v>
       </c>
       <c r="C315" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D315" t="s">
         <v>213</v>
@@ -10583,7 +10586,7 @@
     </row>
     <row r="316" spans="1:9" ht="15">
       <c r="A316" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B316" t="s">
         <v>114</v>
@@ -10592,16 +10595,16 @@
         <v>13</v>
       </c>
       <c r="D316" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="E316" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F316" t="s">
         <v>16</v>
       </c>
       <c r="G316" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="H316" t="s">
         <v>18</v>
@@ -10612,83 +10615,83 @@
     </row>
     <row r="317" spans="1:9" ht="15">
       <c r="A317" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B317" t="s">
         <v>114</v>
       </c>
       <c r="C317" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="D317" t="s">
-        <v>14</v>
+        <v>245</v>
       </c>
       <c r="E317" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="F317" t="s">
-        <v>103</v>
+        <v>16</v>
       </c>
       <c r="G317" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="H317" t="s">
         <v>18</v>
       </c>
       <c r="I317" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15">
       <c r="A318" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B318" t="s">
         <v>114</v>
       </c>
       <c r="C318" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D318" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="E318" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="F318" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G318" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H318" t="s">
         <v>18</v>
       </c>
       <c r="I318" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="15">
       <c r="A319" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B319" t="s">
         <v>114</v>
       </c>
       <c r="C319" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D319" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E319" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F319" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G319" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="H319" t="s">
         <v>18</v>
@@ -10699,54 +10702,54 @@
     </row>
     <row r="320" spans="1:9" ht="15">
       <c r="A320" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B320" t="s">
         <v>114</v>
       </c>
       <c r="C320" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="D320" t="s">
-        <v>55</v>
+        <v>215</v>
       </c>
       <c r="E320" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F320" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G320" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H320" t="s">
         <v>18</v>
       </c>
       <c r="I320" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="15">
       <c r="A321" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B321" t="s">
         <v>114</v>
       </c>
       <c r="C321" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="D321" t="s">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="E321" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="F321" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G321" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="H321" t="s">
         <v>18</v>
@@ -10757,25 +10760,25 @@
     </row>
     <row r="322" spans="1:9" ht="15">
       <c r="A322" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B322" t="s">
         <v>114</v>
       </c>
       <c r="C322" t="s">
-        <v>260</v>
+        <v>108</v>
       </c>
       <c r="D322" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E322" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F322" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G322" t="s">
-        <v>261</v>
+        <v>71</v>
       </c>
       <c r="H322" t="s">
         <v>18</v>
@@ -10786,13 +10789,13 @@
     </row>
     <row r="323" spans="1:9" ht="15">
       <c r="A323" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B323" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C323" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D323" t="s">
         <v>240</v>
@@ -10801,36 +10804,36 @@
         <v>56</v>
       </c>
       <c r="F323" t="s">
-        <v>237</v>
+        <v>64</v>
       </c>
       <c r="G323" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
       <c r="H323" t="s">
         <v>18</v>
       </c>
       <c r="I323" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="15">
       <c r="A324" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B324" t="s">
         <v>123</v>
       </c>
       <c r="C324" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D324" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="E324" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F324" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="G324" t="s">
         <v>126</v>
@@ -10844,22 +10847,22 @@
     </row>
     <row r="325" spans="1:9" ht="15">
       <c r="A325" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B325" t="s">
         <v>123</v>
       </c>
       <c r="C325" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D325" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="E325" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F325" t="s">
-        <v>36</v>
+        <v>263</v>
       </c>
       <c r="G325" t="s">
         <v>126</v>
@@ -10873,22 +10876,22 @@
     </row>
     <row r="326" spans="1:9" ht="15">
       <c r="A326" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B326" t="s">
         <v>123</v>
       </c>
       <c r="C326" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="D326" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E326" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="F326" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="G326" t="s">
         <v>126</v>
@@ -10902,54 +10905,54 @@
     </row>
     <row r="327" spans="1:9" ht="15">
       <c r="A327" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B327" t="s">
         <v>123</v>
       </c>
       <c r="C327" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="D327" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E327" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="F327" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G327" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="H327" t="s">
         <v>18</v>
       </c>
       <c r="I327" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="328" spans="1:9" ht="15">
       <c r="A328" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B328" t="s">
         <v>123</v>
       </c>
       <c r="C328" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="D328" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="E328" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F328" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="G328" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H328" t="s">
         <v>18</v>
@@ -10960,25 +10963,25 @@
     </row>
     <row r="329" spans="1:9" ht="15">
       <c r="A329" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B329" t="s">
         <v>123</v>
       </c>
       <c r="C329" t="s">
-        <v>233</v>
+        <v>108</v>
       </c>
       <c r="D329" t="s">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="E329" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F329" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G329" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H329" t="s">
         <v>18</v>
@@ -10989,25 +10992,25 @@
     </row>
     <row r="330" spans="1:9" ht="15">
       <c r="A330" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B330" t="s">
         <v>123</v>
       </c>
       <c r="C330" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="D330" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E330" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F330" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G330" t="s">
-        <v>261</v>
+        <v>69</v>
       </c>
       <c r="H330" t="s">
         <v>18</v>
@@ -11018,51 +11021,51 @@
     </row>
     <row r="331" spans="1:9" ht="15">
       <c r="A331" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B331" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C331" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D331" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="E331" t="s">
         <v>56</v>
       </c>
       <c r="F331" t="s">
-        <v>237</v>
+        <v>64</v>
       </c>
       <c r="G331" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
       <c r="H331" t="s">
         <v>18</v>
       </c>
       <c r="I331" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="332" spans="1:9" ht="15">
       <c r="A332" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B332" t="s">
         <v>131</v>
       </c>
       <c r="C332" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D332" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E332" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F332" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="G332" t="s">
         <v>126</v>
@@ -11076,22 +11079,22 @@
     </row>
     <row r="333" spans="1:9" ht="15">
       <c r="A333" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B333" t="s">
         <v>131</v>
       </c>
       <c r="C333" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="D333" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="E333" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="F333" t="s">
-        <v>36</v>
+        <v>263</v>
       </c>
       <c r="G333" t="s">
         <v>126</v>
@@ -11105,22 +11108,22 @@
     </row>
     <row r="334" spans="1:9" ht="15">
       <c r="A334" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B334" t="s">
         <v>131</v>
       </c>
       <c r="C334" t="s">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="D334" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E334" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="F334" t="s">
-        <v>103</v>
+        <v>36</v>
       </c>
       <c r="G334" t="s">
         <v>126</v>
@@ -11134,109 +11137,109 @@
     </row>
     <row r="335" spans="1:9" ht="15">
       <c r="A335" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B335" t="s">
         <v>131</v>
       </c>
       <c r="C335" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D335" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="E335" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="F335" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="G335" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H335" t="s">
         <v>18</v>
       </c>
       <c r="I335" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="336" spans="1:9" ht="15">
       <c r="A336" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B336" t="s">
         <v>131</v>
       </c>
       <c r="C336" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D336" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="E336" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F336" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G336" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="H336" t="s">
         <v>18</v>
       </c>
       <c r="I336" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="15">
       <c r="A337" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B337" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="C337" t="s">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="D337" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="E337" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F337" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="G337" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H337" t="s">
         <v>18</v>
       </c>
       <c r="I337" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="338" spans="1:9" ht="15">
       <c r="A338" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B338" t="s">
         <v>191</v>
       </c>
       <c r="C338" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D338" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="E338" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F338" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="G338" t="s">
         <v>126</v>
@@ -11250,59 +11253,88 @@
     </row>
     <row r="339" spans="1:9" ht="15">
       <c r="A339" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B339" t="s">
         <v>191</v>
       </c>
       <c r="C339" t="s">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="D339" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="E339" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="F339" t="s">
-        <v>64</v>
+        <v>263</v>
       </c>
       <c r="G339" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="H339" t="s">
         <v>18</v>
       </c>
       <c r="I339" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="340" spans="1:9" ht="15">
       <c r="A340" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B340" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="C340" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="D340" t="s">
+        <v>240</v>
+      </c>
+      <c r="E340" t="s">
+        <v>63</v>
+      </c>
+      <c r="F340" t="s">
+        <v>64</v>
+      </c>
+      <c r="G340" t="s">
+        <v>66</v>
+      </c>
+      <c r="H340" t="s">
+        <v>18</v>
+      </c>
+      <c r="I340" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" ht="15">
+      <c r="A341" t="s">
+        <v>252</v>
+      </c>
+      <c r="B341" t="s">
+        <v>264</v>
+      </c>
+      <c r="C341" t="s">
+        <v>237</v>
+      </c>
+      <c r="D341" t="s">
         <v>182</v>
       </c>
-      <c r="E340" t="s">
+      <c r="E341" t="s">
         <v>56</v>
       </c>
-      <c r="F340" t="s">
-        <v>237</v>
-      </c>
-      <c r="G340" t="s">
+      <c r="F341" t="s">
+        <v>238</v>
+      </c>
+      <c r="G341" t="s">
         <v>126</v>
       </c>
-      <c r="H340" t="s">
-        <v>18</v>
-      </c>
-      <c r="I340" t="s">
+      <c r="H341" t="s">
+        <v>18</v>
+      </c>
+      <c r="I341" t="s">
         <v>19</v>
       </c>
     </row>
@@ -11314,7 +11346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cddca9e2-298d-40c7-bc37-df63020dc154}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d4be3991-a5f4-44db-b0a5-c5375b71d691}">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11334,16 +11366,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -11363,16 +11395,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -11392,13 +11424,13 @@
         <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C3" t="s">
         <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
         <v>73</v>
@@ -11421,16 +11453,16 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
         <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -11450,13 +11482,13 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
@@ -11479,16 +11511,16 @@
         <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -11508,13 +11540,13 @@
         <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -11537,16 +11569,16 @@
         <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -11563,16 +11595,16 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
@@ -11592,16 +11624,16 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -11610,7 +11642,7 @@
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -11621,16 +11653,16 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C11" t="s">
         <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
@@ -11650,19 +11682,19 @@
     </row>
     <row r="12" spans="1:9" ht="15">
       <c r="A12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -11679,16 +11711,16 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E13" t="s">
         <v>35</v>
@@ -11697,7 +11729,7 @@
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
@@ -11714,7 +11746,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6a8d15a8-b74c-474a-9d00-7e7f8bfb83ae}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6981ffda-c82f-4c7e-94ae-f4a212e76c27}">
   <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11731,13 +11763,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -11751,13 +11783,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -11771,13 +11803,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -11791,13 +11823,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C4" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -11811,13 +11843,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
         <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -11831,13 +11863,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C6" t="s">
         <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E6" t="s">
         <v>69</v>
@@ -11851,13 +11883,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C7" t="s">
         <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E7" t="s">
         <v>112</v>
@@ -11871,13 +11903,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E8" t="s">
         <v>189</v>
@@ -11891,13 +11923,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E9" t="s">
         <v>90</v>
@@ -11911,13 +11943,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E10" t="s">
         <v>90</v>
@@ -11931,13 +11963,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E11" t="s">
         <v>148</v>
@@ -11951,13 +11983,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
         <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -11971,13 +12003,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E13" t="s">
         <v>69</v>
@@ -11991,13 +12023,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
@@ -12011,13 +12043,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -12031,13 +12063,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E16" t="s">
         <v>183</v>
@@ -12051,16 +12083,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -12071,16 +12103,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E18" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
@@ -12091,13 +12123,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" t="s">
         <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -12111,16 +12143,16 @@
         <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F20" t="s">
         <v>32</v>
@@ -12131,16 +12163,16 @@
         <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s">
         <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -12151,16 +12183,16 @@
         <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C22" t="s">
         <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -12171,13 +12203,13 @@
         <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E23" t="s">
         <v>75</v>
@@ -12191,13 +12223,13 @@
         <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
         <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E24" t="s">
         <v>195</v>
@@ -12211,13 +12243,13 @@
         <v>133</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E25" t="s">
         <v>75</v>
@@ -12231,13 +12263,13 @@
         <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C26" t="s">
         <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -12251,13 +12283,13 @@
         <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C27" t="s">
         <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
         <v>130</v>
@@ -12271,13 +12303,13 @@
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E28" t="s">
         <v>189</v>
@@ -12291,13 +12323,13 @@
         <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E29" t="s">
         <v>96</v>
@@ -12311,13 +12343,13 @@
         <v>133</v>
       </c>
       <c r="B30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E30" t="s">
         <v>158</v>
@@ -12331,13 +12363,13 @@
         <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C31" t="s">
         <v>162</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E31" t="s">
         <v>130</v>
@@ -12351,13 +12383,13 @@
         <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E32" t="s">
         <v>65</v>
@@ -12371,13 +12403,13 @@
         <v>133</v>
       </c>
       <c r="B33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C33" t="s">
         <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E33" t="s">
         <v>96</v>
@@ -12391,13 +12423,13 @@
         <v>133</v>
       </c>
       <c r="B34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
         <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E34" t="s">
         <v>189</v>
@@ -12411,13 +12443,13 @@
         <v>133</v>
       </c>
       <c r="B35" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" t="s">
         <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E35" t="s">
         <v>178</v>
@@ -12431,16 +12463,16 @@
         <v>133</v>
       </c>
       <c r="B36" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E36" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F36" t="s">
         <v>80</v>
@@ -12451,13 +12483,13 @@
         <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C37" t="s">
         <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E37" t="s">
         <v>100</v>
@@ -12471,13 +12503,13 @@
         <v>133</v>
       </c>
       <c r="B38" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E38" t="s">
         <v>54</v>
@@ -12491,13 +12523,13 @@
         <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C39" t="s">
         <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E39" t="s">
         <v>90</v>
@@ -12511,13 +12543,13 @@
         <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C40" t="s">
         <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E40" t="s">
         <v>130</v>
@@ -12531,16 +12563,16 @@
         <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C41" t="s">
         <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E41" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F41" t="s">
         <v>80</v>
@@ -12551,16 +12583,16 @@
         <v>133</v>
       </c>
       <c r="B42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C42" t="s">
         <v>183</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E42" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -12571,13 +12603,13 @@
         <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C43" t="s">
         <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E43" t="s">
         <v>130</v>
@@ -12591,16 +12623,16 @@
         <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F44" t="s">
         <v>18</v>
@@ -12611,16 +12643,16 @@
         <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C45" t="s">
         <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -12631,13 +12663,13 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C46" t="s">
         <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E46" t="s">
         <v>69</v>
@@ -12651,13 +12683,13 @@
         <v>194</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C47" t="s">
         <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s">
         <v>135</v>
@@ -12671,13 +12703,13 @@
         <v>194</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C48" t="s">
         <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E48" t="s">
         <v>24</v>
@@ -12691,13 +12723,13 @@
         <v>194</v>
       </c>
       <c r="B49" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -12711,13 +12743,13 @@
         <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C50" t="s">
         <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E50" t="s">
         <v>190</v>
@@ -12731,16 +12763,16 @@
         <v>194</v>
       </c>
       <c r="B51" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C51" t="s">
         <v>66</v>
       </c>
       <c r="D51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E51" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F51" t="s">
         <v>32</v>
@@ -12751,13 +12783,13 @@
         <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C52" t="s">
         <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E52" t="s">
         <v>130</v>
@@ -12771,13 +12803,13 @@
         <v>194</v>
       </c>
       <c r="B53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E53" t="s">
         <v>108</v>
@@ -12791,13 +12823,13 @@
         <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" t="s">
         <v>85</v>
       </c>
       <c r="D54" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E54" t="s">
         <v>148</v>
@@ -12811,13 +12843,13 @@
         <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C55" t="s">
         <v>66</v>
       </c>
       <c r="D55" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E55" t="s">
         <v>96</v>
@@ -12831,13 +12863,13 @@
         <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C56" t="s">
         <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E56" t="s">
         <v>69</v>
@@ -12848,16 +12880,16 @@
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B57" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E57" t="s">
         <v>69</v>
@@ -12868,16 +12900,16 @@
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B58" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C58" t="s">
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -12888,19 +12920,19 @@
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C59" t="s">
         <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E59" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F59" t="s">
         <v>80</v>
@@ -12908,16 +12940,16 @@
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E60" t="s">
         <v>66</v>
@@ -12928,16 +12960,16 @@
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C61" t="s">
         <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E61" t="s">
         <v>53</v>
@@ -12948,16 +12980,16 @@
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C62" t="s">
         <v>75</v>
       </c>
       <c r="D62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E62" t="s">
         <v>144</v>
@@ -12968,19 +13000,19 @@
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C63" t="s">
         <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E63" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F63" t="s">
         <v>80</v>
@@ -12988,16 +13020,16 @@
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C64" t="s">
         <v>110</v>
       </c>
       <c r="D64" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E64" t="s">
         <v>158</v>
@@ -13008,16 +13040,16 @@
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -13028,16 +13060,16 @@
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
         <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E66" t="s">
         <v>54</v>
@@ -13048,16 +13080,16 @@
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C67" t="s">
         <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -13068,16 +13100,16 @@
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C68" t="s">
         <v>110</v>
       </c>
       <c r="D68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E68" t="s">
         <v>220</v>
@@ -13088,16 +13120,16 @@
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E69" t="s">
         <v>53</v>
@@ -13108,16 +13140,16 @@
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C70" t="s">
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E70" t="s">
         <v>49</v>
@@ -13128,16 +13160,16 @@
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C71" t="s">
         <v>91</v>
       </c>
       <c r="D71" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E71" t="s">
         <v>90</v>
@@ -13148,19 +13180,19 @@
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C72" t="s">
         <v>148</v>
       </c>
       <c r="D72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -13168,19 +13200,19 @@
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E73" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F73" t="s">
         <v>18</v>
@@ -13188,19 +13220,19 @@
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C74" t="s">
         <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F74" t="s">
         <v>80</v>
@@ -13208,19 +13240,19 @@
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C75" t="s">
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E75" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F75" t="s">
         <v>18</v>
@@ -13228,16 +13260,16 @@
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C76" t="s">
         <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E76" t="s">
         <v>24</v>
@@ -13248,16 +13280,16 @@
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D77" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E77" t="s">
         <v>130</v>
@@ -13268,16 +13300,16 @@
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C78" t="s">
         <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E78" t="s">
         <v>178</v>
@@ -13288,16 +13320,16 @@
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C79" t="s">
         <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E79" t="s">
         <v>178</v>
@@ -13308,16 +13340,16 @@
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s">
+        <v>300</v>
+      </c>
+      <c r="C80" t="s">
+        <v>253</v>
+      </c>
+      <c r="D80" t="s">
         <v>299</v>
-      </c>
-      <c r="C80" t="s">
-        <v>252</v>
-      </c>
-      <c r="D80" t="s">
-        <v>298</v>
       </c>
       <c r="E80" t="s">
         <v>155</v>
@@ -13328,16 +13360,16 @@
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C81" t="s">
         <v>65</v>
       </c>
       <c r="D81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E81" t="s">
         <v>71</v>
@@ -13348,16 +13380,16 @@
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C82" t="s">
         <v>85</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E82" t="s">
         <v>66</v>
@@ -13368,19 +13400,19 @@
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B83" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D83" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E83" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F83" t="s">
         <v>18</v>
@@ -13388,19 +13420,19 @@
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" t="s">
+        <v>252</v>
+      </c>
+      <c r="B84" t="s">
+        <v>303</v>
+      </c>
+      <c r="C84" t="s">
+        <v>253</v>
+      </c>
+      <c r="D84" t="s">
+        <v>293</v>
+      </c>
+      <c r="E84" t="s">
         <v>251</v>
-      </c>
-      <c r="B84" t="s">
-        <v>302</v>
-      </c>
-      <c r="C84" t="s">
-        <v>252</v>
-      </c>
-      <c r="D84" t="s">
-        <v>292</v>
-      </c>
-      <c r="E84" t="s">
-        <v>250</v>
       </c>
       <c r="F84" t="s">
         <v>18</v>
@@ -13408,19 +13440,19 @@
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E85" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F85" t="s">
         <v>18</v>
@@ -13428,16 +13460,16 @@
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B86" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C86" t="s">
         <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E86" t="s">
         <v>106</v>
@@ -13448,16 +13480,16 @@
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B87" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C87" t="s">
         <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E87" t="s">
         <v>178</v>
@@ -13468,16 +13500,16 @@
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C88" t="s">
         <v>169</v>
       </c>
       <c r="D88" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E88" t="s">
         <v>66</v>
@@ -13488,16 +13520,16 @@
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B89" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C89" t="s">
         <v>108</v>
       </c>
       <c r="D89" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E89" t="s">
         <v>130</v>
@@ -13508,19 +13540,19 @@
     </row>
     <row r="90" spans="1:6" ht="15">
       <c r="A90" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" t="s">
+        <v>307</v>
+      </c>
+      <c r="C90" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" t="s">
+        <v>301</v>
+      </c>
+      <c r="E90" t="s">
         <v>251</v>
-      </c>
-      <c r="B90" t="s">
-        <v>306</v>
-      </c>
-      <c r="C90" t="s">
-        <v>252</v>
-      </c>
-      <c r="D90" t="s">
-        <v>300</v>
-      </c>
-      <c r="E90" t="s">
-        <v>250</v>
       </c>
       <c r="F90" t="s">
         <v>18</v>
@@ -13528,19 +13560,19 @@
     </row>
     <row r="91" spans="1:6" ht="15">
       <c r="A91" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B91" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C91" t="s">
         <v>108</v>
       </c>
       <c r="D91" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E91" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F91" t="s">
         <v>18</v>
@@ -13548,19 +13580,19 @@
     </row>
     <row r="92" spans="1:6" ht="15">
       <c r="A92" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B92" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C92" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E92" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F92" t="s">
         <v>18</v>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="236">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 25.05.2026 (pon.) - 31.05.2026 (niedz.)</t>
+    <t>Okres: 25.05.2026 (pon.) - 30.05.2026 (sob.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -84,6 +84,27 @@
     <t>-</t>
   </si>
   <si>
+    <t>Vacat DoradztwoZawodowe</t>
+  </si>
+  <si>
+    <t>3WA</t>
+  </si>
+  <si>
+    <t>Doradztwo zawodowe</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krzemińska Beata</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Dodatkowo płatne</t>
+  </si>
+  <si>
     <t>2, 08:50-09:35</t>
   </si>
   <si>
@@ -99,9 +120,6 @@
     <t>26</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Nowak Magdalena</t>
   </si>
   <si>
@@ -117,9 +135,6 @@
     <t>Kopij Marcin</t>
   </si>
   <si>
-    <t>Dodatkowo płatne</t>
-  </si>
-  <si>
     <t>2TFB|JA2</t>
   </si>
   <si>
@@ -273,9 +288,6 @@
     <t>6, 12:25-13:10</t>
   </si>
   <si>
-    <t>3WA</t>
-  </si>
-  <si>
     <t>Matematyka</t>
   </si>
   <si>
@@ -351,6 +363,9 @@
     <t>2WB</t>
   </si>
   <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
     <t>Techniki fryzjerskie</t>
   </si>
   <si>
@@ -381,12 +396,33 @@
     <t>26.05.2026</t>
   </si>
   <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
     <t>3FB</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>Zastępstwo</t>
   </si>
   <si>
@@ -447,6 +483,18 @@
     <t>1TFA|JA2</t>
   </si>
   <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
     <t>Okienko dla uczniów</t>
   </si>
   <si>
@@ -495,6 +543,18 @@
     <t>3TFB|JA1</t>
   </si>
   <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
     <t>28.05.2026</t>
   </si>
   <si>
@@ -525,15 +585,21 @@
     <t>1CB|JA1</t>
   </si>
   <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
     <t>2FB|CH</t>
   </si>
   <si>
     <t>sg2</t>
   </si>
   <si>
-    <t>1S</t>
-  </si>
-  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -627,16 +693,10 @@
     <t>boisko - dziedziniec wejściowy/boisko</t>
   </si>
   <si>
-    <t>Krzemińska Beata</t>
-  </si>
-  <si>
     <t>11:20-11:25</t>
   </si>
   <si>
     <t>piętro_1</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
   </si>
   <si>
     <t>12:10-12:25</t>
@@ -1119,7 +1179,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1f6c0c5f-19f7-4d56-876b-384b1b3ed909}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cf7a4a76-a128-4091-8c6c-8c178302766a}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1140,13 +1200,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{6dcefaaa-1f50-4cff-be58-b66781091808}">
-  <dimension ref="A1:I135"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a8c5c3e6-2f6a-4f1c-97b9-d3c1e60357ed}">
+  <dimension ref="A1:I149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="25.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
@@ -1218,28 +1278,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
       <c r="H3" t="s">
         <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -1247,28 +1307,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1276,28 +1336,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
@@ -1305,28 +1365,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
@@ -1334,28 +1394,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
@@ -1363,28 +1423,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
         <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1392,28 +1452,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1421,28 +1481,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H10" t="s">
         <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1450,28 +1510,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
         <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1479,19 +1539,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
         <v>60</v>
@@ -1500,7 +1560,7 @@
         <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1508,28 +1568,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1537,13 +1597,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>63</v>
@@ -1555,10 +1615,10 @@
         <v>65</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1566,28 +1626,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1595,28 +1655,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1624,28 +1684,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
         <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1653,28 +1713,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1682,28 +1742,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
         <v>51</v>
       </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" t="s">
-        <v>76</v>
-      </c>
       <c r="H19" t="s">
         <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1711,28 +1771,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="D20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" t="s">
-        <v>78</v>
-      </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1740,28 +1800,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1769,28 +1829,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
         <v>43</v>
       </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>55</v>
-      </c>
       <c r="H22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1798,28 +1858,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
         <v>69</v>
       </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" t="s">
-        <v>75</v>
-      </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
         <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1827,28 +1887,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s">
         <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1856,28 +1916,28 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="H25" t="s">
         <v>25</v>
       </c>
       <c r="I25" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1885,28 +1945,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
         <v>77</v>
       </c>
-      <c r="E26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" t="s">
-        <v>72</v>
-      </c>
       <c r="H26" t="s">
         <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1914,28 +1974,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
         <v>82</v>
       </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>43</v>
-      </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
         <v>25</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1943,28 +2003,28 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I28" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -1972,28 +2032,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -2001,28 +2061,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H30" t="s">
         <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2030,28 +2090,28 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s">
         <v>25</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
@@ -2059,28 +2119,28 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="H32" t="s">
         <v>25</v>
       </c>
       <c r="I32" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -2088,28 +2148,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="G33" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s">
         <v>25</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2117,28 +2177,28 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
         <v>25</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2146,28 +2206,28 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="H35" t="s">
         <v>25</v>
       </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2175,28 +2235,28 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G36" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H36" t="s">
         <v>25</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2204,28 +2264,28 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H37" t="s">
         <v>25</v>
       </c>
       <c r="I37" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2233,28 +2293,28 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
         <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2262,28 +2322,28 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H39" t="s">
         <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2291,28 +2351,28 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s">
         <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2320,28 +2380,28 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="F41" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="H41" t="s">
         <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15">
@@ -2349,28 +2409,28 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s">
         <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2378,28 +2438,28 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="H43" t="s">
         <v>25</v>
       </c>
       <c r="I43" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2407,28 +2467,28 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" t="s">
         <v>101</v>
       </c>
-      <c r="C44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
       <c r="G44" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H44" t="s">
         <v>25</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
@@ -2436,28 +2496,28 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="F45" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G45" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="H45" t="s">
         <v>25</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
@@ -2465,28 +2525,28 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s">
         <v>25</v>
       </c>
       <c r="I46" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2494,28 +2554,28 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="F47" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="H47" t="s">
         <v>25</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2523,28 +2583,28 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" t="s">
+        <v>117</v>
+      </c>
+      <c r="E48" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" t="s">
         <v>111</v>
       </c>
-      <c r="C48" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" t="s">
-        <v>41</v>
-      </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s">
         <v>25</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
@@ -2552,28 +2612,28 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" t="s">
         <v>114</v>
       </c>
-      <c r="C49" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" t="s">
-        <v>84</v>
-      </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="G49" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s">
         <v>25</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2584,48 +2644,48 @@
         <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="H50" t="s">
         <v>25</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F51" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s">
         <v>25</v>
@@ -2636,25 +2696,25 @@
     </row>
     <row r="52" spans="1:9" ht="15">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
         <v>122</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
@@ -2665,103 +2725,103 @@
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="F53" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G53" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H53" t="s">
         <v>25</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="E54" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F54" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G54" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H54" t="s">
         <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="F55" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G55" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H55" t="s">
         <v>25</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
         <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E56" t="s">
         <v>126</v>
@@ -2770,36 +2830,36 @@
         <v>127</v>
       </c>
       <c r="G56" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H56" t="s">
         <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F57" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G57" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H57" t="s">
         <v>25</v>
@@ -2810,25 +2870,25 @@
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H58" t="s">
         <v>25</v>
@@ -2839,25 +2899,25 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G59" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H59" t="s">
         <v>25</v>
@@ -2868,25 +2928,25 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="F60" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G60" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H60" t="s">
         <v>25</v>
@@ -2897,25 +2957,25 @@
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E61" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="F61" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G61" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H61" t="s">
         <v>25</v>
@@ -2926,25 +2986,25 @@
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F62" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G62" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H62" t="s">
         <v>25</v>
@@ -2955,25 +3015,25 @@
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E63" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="F63" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G63" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H63" t="s">
         <v>25</v>
@@ -2984,25 +3044,25 @@
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G64" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H64" t="s">
         <v>25</v>
@@ -3013,25 +3073,25 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="F65" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G65" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H65" t="s">
         <v>25</v>
@@ -3042,25 +3102,25 @@
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E66" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G66" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H66" t="s">
         <v>25</v>
@@ -3071,25 +3131,25 @@
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="E67" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F67" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G67" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H67" t="s">
         <v>25</v>
@@ -3100,25 +3160,25 @@
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F68" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G68" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H68" t="s">
         <v>25</v>
@@ -3129,25 +3189,25 @@
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G69" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H69" t="s">
         <v>25</v>
@@ -3158,25 +3218,25 @@
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E70" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G70" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H70" t="s">
         <v>25</v>
@@ -3187,25 +3247,25 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E71" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F71" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G71" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="H71" t="s">
         <v>25</v>
@@ -3216,25 +3276,25 @@
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" t="s">
         <v>135</v>
       </c>
-      <c r="E72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" t="s">
-        <v>123</v>
-      </c>
       <c r="G72" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H72" t="s">
         <v>25</v>
@@ -3245,25 +3305,25 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
+      </c>
+      <c r="C73" t="s">
         <v>136</v>
       </c>
-      <c r="B73" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>137</v>
-      </c>
       <c r="D73" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" t="s">
         <v>138</v>
-      </c>
-      <c r="E73" t="s">
-        <v>58</v>
       </c>
       <c r="F73" t="s">
         <v>139</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="H73" t="s">
         <v>25</v>
@@ -3274,28 +3334,28 @@
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G74" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
@@ -3303,25 +3363,25 @@
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E75" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F75" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G75" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H75" t="s">
         <v>25</v>
@@ -3332,25 +3392,25 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="F76" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="G76" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H76" t="s">
         <v>25</v>
@@ -3361,57 +3421,57 @@
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F77" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G77" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s">
         <v>25</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="D78" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G78" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3419,25 +3479,25 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="D79" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E79" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="F79" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G79" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
         <v>25</v>
@@ -3448,28 +3508,28 @@
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E80" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
@@ -3477,141 +3537,141 @@
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B81" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D81" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E81" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F81" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G81" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H81" t="s">
         <v>25</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" t="s">
+        <v>154</v>
+      </c>
+      <c r="E82" t="s">
+        <v>126</v>
+      </c>
+      <c r="F82" t="s">
+        <v>127</v>
+      </c>
+      <c r="G82" t="s">
+        <v>128</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" t="s">
         <v>26</v>
-      </c>
-      <c r="D82" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82" t="s">
-        <v>84</v>
-      </c>
-      <c r="F82" t="s">
-        <v>120</v>
-      </c>
-      <c r="G82" t="s">
-        <v>121</v>
-      </c>
-      <c r="H82" t="s">
-        <v>25</v>
-      </c>
-      <c r="I82" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="D83" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G83" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H83" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E84" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="F84" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G84" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H84" t="s">
         <v>25</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E85" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="F85" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="G85" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H85" t="s">
         <v>25</v>
@@ -3622,25 +3682,25 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F86" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="G86" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H86" t="s">
         <v>25</v>
@@ -3651,57 +3711,57 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B87" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D87" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F87" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G87" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="H87" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B88" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>39</v>
+        <v>159</v>
       </c>
       <c r="E88" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
@@ -3709,25 +3769,25 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D89" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E89" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F89" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G89" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H89" t="s">
         <v>25</v>
@@ -3738,25 +3798,25 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B90" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="D90" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="E90" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="G90" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H90" t="s">
         <v>25</v>
@@ -3767,57 +3827,57 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E91" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F91" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="G91" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H91" t="s">
         <v>25</v>
       </c>
       <c r="I91" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="E92" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F92" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G92" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
@@ -3825,28 +3885,28 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="E93" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H93" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
@@ -3854,25 +3914,25 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D94" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E94" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F94" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G94" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H94" t="s">
         <v>25</v>
@@ -3883,25 +3943,25 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C95" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="D95" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E95" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="F95" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="G95" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H95" t="s">
         <v>25</v>
@@ -3912,25 +3972,25 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D96" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F96" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G96" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H96" t="s">
         <v>25</v>
@@ -3941,16 +4001,16 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C97" t="s">
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="E97" t="s">
         <v>15</v>
@@ -3959,7 +4019,7 @@
         <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -3970,28 +4030,28 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D98" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="E98" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G98" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H98" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
@@ -3999,25 +4059,25 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B99" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C99" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D99" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F99" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G99" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="H99" t="s">
         <v>25</v>
@@ -4028,25 +4088,25 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B100" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C100" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="D100" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="E100" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="F100" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="G100" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H100" t="s">
         <v>25</v>
@@ -4057,57 +4117,57 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D101" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E101" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="G101" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C102" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E102" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G102" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
@@ -4115,25 +4175,25 @@
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C103" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="D103" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="E103" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F103" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G103" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H103" t="s">
         <v>25</v>
@@ -4144,25 +4204,25 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C104" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="D104" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="E104" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="F104" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G104" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="H104" t="s">
         <v>25</v>
@@ -4173,25 +4233,25 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C105" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="D105" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E105" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F105" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G105" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H105" t="s">
         <v>25</v>
@@ -4202,25 +4262,25 @@
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C106" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D106" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F106" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G106" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H106" t="s">
         <v>25</v>
@@ -4231,28 +4291,28 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B107" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E107" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="F107" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="G107" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H107" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
@@ -4260,28 +4320,28 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B108" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C108" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D108" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="E108" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F108" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G108" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H108" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
@@ -4289,54 +4349,54 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" t="s">
+        <v>94</v>
+      </c>
+      <c r="C109" t="s">
+        <v>149</v>
+      </c>
+      <c r="D109" t="s">
+        <v>166</v>
+      </c>
+      <c r="E109" t="s">
+        <v>63</v>
+      </c>
+      <c r="F109" t="s">
+        <v>151</v>
+      </c>
+      <c r="G109" t="s">
         <v>157</v>
       </c>
-      <c r="B109" t="s">
-        <v>82</v>
-      </c>
-      <c r="C109" t="s">
-        <v>26</v>
-      </c>
-      <c r="D109" t="s">
-        <v>22</v>
-      </c>
-      <c r="E109" t="s">
-        <v>84</v>
-      </c>
-      <c r="F109" t="s">
-        <v>120</v>
-      </c>
-      <c r="G109" t="s">
-        <v>142</v>
-      </c>
       <c r="H109" t="s">
         <v>25</v>
       </c>
       <c r="I109" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C110" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="D110" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E110" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="F110" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="G110" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H110" t="s">
         <v>25</v>
@@ -4347,28 +4407,28 @@
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B111" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C111" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="E111" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F111" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G111" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H111" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
         <v>19</v>
@@ -4376,54 +4436,54 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C112" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D112" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E112" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="F112" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="G112" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H112" t="s">
         <v>25</v>
       </c>
       <c r="I112" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D113" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="E113" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="F113" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G113" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H113" t="s">
         <v>25</v>
@@ -4434,25 +4494,25 @@
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="D114" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E114" t="s">
-        <v>161</v>
+        <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="G114" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H114" t="s">
         <v>25</v>
@@ -4463,54 +4523,54 @@
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="D115" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E115" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="F115" t="s">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="G115" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="H115" t="s">
         <v>25</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C116" t="s">
+        <v>32</v>
+      </c>
+      <c r="D116" t="s">
         <v>160</v>
       </c>
-      <c r="D116" t="s">
-        <v>164</v>
-      </c>
       <c r="E116" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="F116" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="G116" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H116" t="s">
         <v>25</v>
@@ -4521,25 +4581,25 @@
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B117" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C117" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="D117" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F117" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G117" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H117" t="s">
         <v>25</v>
@@ -4550,25 +4610,25 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B118" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" t="s">
+        <v>32</v>
+      </c>
+      <c r="D118" t="s">
         <v>48</v>
       </c>
-      <c r="C118" t="s">
-        <v>56</v>
-      </c>
-      <c r="D118" t="s">
-        <v>129</v>
-      </c>
       <c r="E118" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F118" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="G118" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H118" t="s">
         <v>25</v>
@@ -4579,25 +4639,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C119" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="D119" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="E119" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="F119" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="G119" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H119" t="s">
         <v>25</v>
@@ -4608,54 +4668,54 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B120" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C120" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="D120" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="E120" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F120" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="G120" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="H120" t="s">
         <v>25</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C121" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D121" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="E121" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="F121" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="G121" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H121" t="s">
         <v>25</v>
@@ -4666,25 +4726,25 @@
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B122" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C122" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="D122" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="E122" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="F122" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="G122" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H122" t="s">
         <v>25</v>
@@ -4695,54 +4755,54 @@
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B123" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="C123" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E123" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F123" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="G123" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="H123" t="s">
         <v>25</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B124" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="D124" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="E124" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="F124" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="G124" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H124" t="s">
         <v>25</v>
@@ -4753,25 +4813,25 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B125" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C125" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="D125" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E125" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="F125" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="G125" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
@@ -4782,25 +4842,25 @@
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B126" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="D126" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E126" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="F126" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="G126" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H126" t="s">
         <v>25</v>
@@ -4811,25 +4871,25 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="E127" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="F127" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="G127" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H127" t="s">
         <v>25</v>
@@ -4840,25 +4900,25 @@
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C128" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="D128" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="E128" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F128" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G128" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H128" t="s">
         <v>25</v>
@@ -4869,25 +4929,25 @@
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="D129" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="E129" t="s">
         <v>102</v>
       </c>
       <c r="F129" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H129" t="s">
         <v>25</v>
@@ -4898,25 +4958,25 @@
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B130" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="D130" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E130" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="F130" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G130" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H130" t="s">
         <v>25</v>
@@ -4927,54 +4987,54 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B131" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C131" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="D131" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="E131" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F131" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G131" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H131" t="s">
         <v>25</v>
       </c>
       <c r="I131" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="D132" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="E132" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="F132" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="G132" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H132" t="s">
         <v>25</v>
@@ -4985,25 +5045,25 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C133" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="D133" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="F133" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="G133" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H133" t="s">
         <v>25</v>
@@ -5014,25 +5074,25 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B134" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D134" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="E134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F134" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G134" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H134" t="s">
         <v>25</v>
@@ -5043,30 +5103,436 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B135" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D135" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E135" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F135" t="s">
+        <v>84</v>
+      </c>
+      <c r="G135" t="s">
+        <v>133</v>
+      </c>
+      <c r="H135" t="s">
+        <v>25</v>
+      </c>
+      <c r="I135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="15">
+      <c r="A136" t="s">
+        <v>179</v>
+      </c>
+      <c r="B136" t="s">
+        <v>87</v>
+      </c>
+      <c r="C136" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" t="s">
+        <v>160</v>
+      </c>
+      <c r="E136" t="s">
+        <v>88</v>
+      </c>
+      <c r="F136" t="s">
+        <v>127</v>
+      </c>
+      <c r="G136" t="s">
+        <v>133</v>
+      </c>
+      <c r="H136" t="s">
+        <v>25</v>
+      </c>
+      <c r="I136" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="15">
+      <c r="A137" t="s">
+        <v>179</v>
+      </c>
+      <c r="B137" t="s">
+        <v>87</v>
+      </c>
+      <c r="C137" t="s">
+        <v>180</v>
+      </c>
+      <c r="D137" t="s">
+        <v>184</v>
+      </c>
+      <c r="E137" t="s">
+        <v>185</v>
+      </c>
+      <c r="F137" t="s">
+        <v>182</v>
+      </c>
+      <c r="G137" t="s">
+        <v>133</v>
+      </c>
+      <c r="H137" t="s">
+        <v>25</v>
+      </c>
+      <c r="I137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="15">
+      <c r="A138" t="s">
+        <v>179</v>
+      </c>
+      <c r="B138" t="s">
+        <v>94</v>
+      </c>
+      <c r="C138" t="s">
+        <v>61</v>
+      </c>
+      <c r="D138" t="s">
+        <v>160</v>
+      </c>
+      <c r="E138" t="s">
+        <v>102</v>
+      </c>
+      <c r="F138" t="s">
+        <v>84</v>
+      </c>
+      <c r="G138" t="s">
+        <v>133</v>
+      </c>
+      <c r="H138" t="s">
+        <v>25</v>
+      </c>
+      <c r="I138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="15">
+      <c r="A139" t="s">
+        <v>179</v>
+      </c>
+      <c r="B139" t="s">
+        <v>94</v>
+      </c>
+      <c r="C139" t="s">
+        <v>32</v>
+      </c>
+      <c r="D139" t="s">
+        <v>164</v>
+      </c>
+      <c r="E139" t="s">
+        <v>88</v>
+      </c>
+      <c r="F139" t="s">
+        <v>127</v>
+      </c>
+      <c r="G139" t="s">
+        <v>133</v>
+      </c>
+      <c r="H139" t="s">
+        <v>25</v>
+      </c>
+      <c r="I139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="15">
+      <c r="A140" t="s">
+        <v>179</v>
+      </c>
+      <c r="B140" t="s">
+        <v>94</v>
+      </c>
+      <c r="C140" t="s">
+        <v>180</v>
+      </c>
+      <c r="D140" t="s">
         <v>97</v>
       </c>
-      <c r="G135" t="s">
-        <v>121</v>
-      </c>
-      <c r="H135" t="s">
-        <v>25</v>
-      </c>
-      <c r="I135" t="s">
+      <c r="E140" t="s">
+        <v>106</v>
+      </c>
+      <c r="F140" t="s">
+        <v>182</v>
+      </c>
+      <c r="G140" t="s">
+        <v>133</v>
+      </c>
+      <c r="H140" t="s">
+        <v>25</v>
+      </c>
+      <c r="I140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="15">
+      <c r="A141" t="s">
+        <v>179</v>
+      </c>
+      <c r="B141" t="s">
+        <v>94</v>
+      </c>
+      <c r="C141" t="s">
+        <v>187</v>
+      </c>
+      <c r="D141" t="s">
+        <v>188</v>
+      </c>
+      <c r="E141" t="s">
+        <v>88</v>
+      </c>
+      <c r="F141" t="s">
+        <v>101</v>
+      </c>
+      <c r="G141" t="s">
+        <v>189</v>
+      </c>
+      <c r="H141" t="s">
+        <v>25</v>
+      </c>
+      <c r="I141" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="15">
+      <c r="A142" t="s">
+        <v>179</v>
+      </c>
+      <c r="B142" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" t="s">
+        <v>167</v>
+      </c>
+      <c r="D142" t="s">
+        <v>190</v>
+      </c>
+      <c r="E142" t="s">
+        <v>63</v>
+      </c>
+      <c r="F142" t="s">
+        <v>191</v>
+      </c>
+      <c r="G142" t="s">
+        <v>133</v>
+      </c>
+      <c r="H142" t="s">
+        <v>25</v>
+      </c>
+      <c r="I142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="15">
+      <c r="A143" t="s">
+        <v>179</v>
+      </c>
+      <c r="B143" t="s">
+        <v>105</v>
+      </c>
+      <c r="C143" t="s">
+        <v>32</v>
+      </c>
+      <c r="D143" t="s">
+        <v>67</v>
+      </c>
+      <c r="E143" t="s">
+        <v>88</v>
+      </c>
+      <c r="F143" t="s">
+        <v>127</v>
+      </c>
+      <c r="G143" t="s">
+        <v>158</v>
+      </c>
+      <c r="H143" t="s">
+        <v>25</v>
+      </c>
+      <c r="I143" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="15">
+      <c r="A144" t="s">
+        <v>179</v>
+      </c>
+      <c r="B144" t="s">
+        <v>105</v>
+      </c>
+      <c r="C144" t="s">
+        <v>173</v>
+      </c>
+      <c r="D144" t="s">
+        <v>174</v>
+      </c>
+      <c r="E144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F144" t="s">
+        <v>175</v>
+      </c>
+      <c r="G144" t="s">
+        <v>176</v>
+      </c>
+      <c r="H144" t="s">
+        <v>25</v>
+      </c>
+      <c r="I144" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="15">
+      <c r="A145" t="s">
+        <v>179</v>
+      </c>
+      <c r="B145" t="s">
+        <v>105</v>
+      </c>
+      <c r="C145" t="s">
+        <v>187</v>
+      </c>
+      <c r="D145" t="s">
+        <v>188</v>
+      </c>
+      <c r="E145" t="s">
+        <v>88</v>
+      </c>
+      <c r="F145" t="s">
+        <v>101</v>
+      </c>
+      <c r="G145" t="s">
+        <v>189</v>
+      </c>
+      <c r="H145" t="s">
+        <v>25</v>
+      </c>
+      <c r="I145" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="15">
+      <c r="A146" t="s">
+        <v>179</v>
+      </c>
+      <c r="B146" t="s">
+        <v>116</v>
+      </c>
+      <c r="C146" t="s">
+        <v>167</v>
+      </c>
+      <c r="D146" t="s">
+        <v>190</v>
+      </c>
+      <c r="E146" t="s">
+        <v>63</v>
+      </c>
+      <c r="F146" t="s">
+        <v>191</v>
+      </c>
+      <c r="G146" t="s">
+        <v>133</v>
+      </c>
+      <c r="H146" t="s">
+        <v>25</v>
+      </c>
+      <c r="I146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="15">
+      <c r="A147" t="s">
+        <v>179</v>
+      </c>
+      <c r="B147" t="s">
+        <v>116</v>
+      </c>
+      <c r="C147" t="s">
+        <v>61</v>
+      </c>
+      <c r="D147" t="s">
+        <v>118</v>
+      </c>
+      <c r="E147" t="s">
+        <v>102</v>
+      </c>
+      <c r="F147" t="s">
+        <v>101</v>
+      </c>
+      <c r="G147" t="s">
+        <v>133</v>
+      </c>
+      <c r="H147" t="s">
+        <v>25</v>
+      </c>
+      <c r="I147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="15">
+      <c r="A148" t="s">
+        <v>179</v>
+      </c>
+      <c r="B148" t="s">
+        <v>119</v>
+      </c>
+      <c r="C148" t="s">
+        <v>167</v>
+      </c>
+      <c r="D148" t="s">
+        <v>190</v>
+      </c>
+      <c r="E148" t="s">
+        <v>63</v>
+      </c>
+      <c r="F148" t="s">
+        <v>191</v>
+      </c>
+      <c r="G148" t="s">
+        <v>133</v>
+      </c>
+      <c r="H148" t="s">
+        <v>25</v>
+      </c>
+      <c r="I148" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="15">
+      <c r="A149" t="s">
+        <v>179</v>
+      </c>
+      <c r="B149" t="s">
+        <v>119</v>
+      </c>
+      <c r="C149" t="s">
+        <v>61</v>
+      </c>
+      <c r="D149" t="s">
+        <v>188</v>
+      </c>
+      <c r="E149" t="s">
+        <v>102</v>
+      </c>
+      <c r="F149" t="s">
+        <v>101</v>
+      </c>
+      <c r="G149" t="s">
+        <v>133</v>
+      </c>
+      <c r="H149" t="s">
+        <v>25</v>
+      </c>
+      <c r="I149" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5078,7 +5544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c6b3584a-d390-4510-93a7-05e662ddb121}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d0e2ec0c-24ac-41a9-acc9-a97e99f872a6}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5098,16 +5564,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5127,22 +5593,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
         <v>25</v>
@@ -5156,22 +5622,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -5185,22 +5651,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -5211,25 +5677,25 @@
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -5240,25 +5706,25 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="F6" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -5269,25 +5735,25 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -5298,25 +5764,25 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -5327,25 +5793,25 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -5356,25 +5822,25 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -5391,7 +5857,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{69ac7726-b955-47e2-a250-de1b6460c1bb}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2351e571-ed08-40f5-8b6b-2b2dd1bc113f}">
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5408,13 +5874,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5428,16 +5894,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
         <v>25</v>
@@ -5448,16 +5914,16 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -5468,16 +5934,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
@@ -5488,16 +5954,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
         <v>25</v>
@@ -5508,16 +5974,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>201</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -5528,16 +5994,16 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -5548,16 +6014,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -5568,16 +6034,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E9" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -5588,16 +6054,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -5608,16 +6074,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -5628,16 +6094,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -5648,16 +6114,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -5668,16 +6134,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -5688,16 +6154,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -5708,16 +6174,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -5728,16 +6194,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E17" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -5748,13 +6214,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -5765,16 +6231,16 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -5785,16 +6251,16 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -5805,16 +6271,16 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -5825,16 +6291,16 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D22" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -5845,16 +6311,16 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -5865,16 +6331,16 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -5885,16 +6351,16 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -5905,16 +6371,16 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -5925,16 +6391,16 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -5945,16 +6411,16 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -5965,16 +6431,16 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -5985,16 +6451,16 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -6005,16 +6471,16 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -6025,16 +6491,16 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -6045,16 +6511,16 @@
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -6065,16 +6531,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -6085,16 +6551,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -6105,16 +6571,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -6125,16 +6591,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -6145,16 +6611,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D38" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -6165,16 +6631,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -6185,16 +6651,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D40" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -6205,16 +6671,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B41" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D41" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -6225,16 +6691,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -6245,16 +6711,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D43" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -6265,16 +6731,16 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="264">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
   <si>
-    <t>Okres: 25.05.2026 (pon.) - 30.05.2026 (sob.)</t>
+    <t>Okres: 25.05.2026 (pon.) - 31.05.2026 (niedz.)</t>
   </si>
   <si>
     <t>Dzień</t>
@@ -63,6 +63,27 @@
     <t>1, 08:00-08:45</t>
   </si>
   <si>
+    <t>Kopij Marcin</t>
+  </si>
+  <si>
+    <t>2FA</t>
+  </si>
+  <si>
+    <t>Zajęcia biblioteczne</t>
+  </si>
+  <si>
+    <t>bib</t>
+  </si>
+  <si>
+    <t>Nowak Damiana</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Bezpłatne</t>
+  </si>
+  <si>
     <t>Taszycka Magdalena</t>
   </si>
   <si>
@@ -99,9 +120,6 @@
     <t>Krzemińska Beata</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Dodatkowo płatne</t>
   </si>
   <si>
@@ -126,441 +144,489 @@
     <t>1CA</t>
   </si>
   <si>
+    <t>2TFB|JA2</t>
+  </si>
+  <si>
+    <t>3, 09:40-10:25</t>
+  </si>
+  <si>
+    <t>Czukiewska Bożena</t>
+  </si>
+  <si>
+    <t>1TH|JA2</t>
+  </si>
+  <si>
+    <t>Pracownia sprzedaży</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Kosin Anna</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - barber</t>
+  </si>
+  <si>
+    <t>prF3</t>
+  </si>
+  <si>
+    <t>Sobczak Anna</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>4, 10:35-11:20</t>
+  </si>
+  <si>
+    <t>Granatowska Mariola</t>
+  </si>
+  <si>
+    <t>1CA|JA2</t>
+  </si>
+  <si>
+    <t>Język angielski</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Karczmarz Aleksandra</t>
+  </si>
+  <si>
+    <t>3FA</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Kończyńska Małgorzata</t>
+  </si>
+  <si>
+    <t>Mucha Anna</t>
+  </si>
+  <si>
+    <t>3CA|CH</t>
+  </si>
+  <si>
+    <t>Wychowanie fizyczne</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Rejno Julita</t>
+  </si>
+  <si>
+    <t>3CA|DZ</t>
+  </si>
+  <si>
+    <t>2TFA</t>
+  </si>
+  <si>
+    <t>Biznes i zarządzanie</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Socha Dariusz</t>
+  </si>
+  <si>
+    <t>Zaleska Magdalena</t>
+  </si>
+  <si>
+    <t>Zajęcia z wychowawcą</t>
+  </si>
+  <si>
+    <t>5, 11:25-12:10</t>
+  </si>
+  <si>
+    <t>Bujanowska Iwona</t>
+  </si>
+  <si>
+    <t>1TFB</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Najwer Maciej</t>
+  </si>
+  <si>
+    <t>Małecka Barbara</t>
+  </si>
+  <si>
+    <t>2TFB</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Wojciechowski Łukasz</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>Język polski</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Ulanowska Magdalena</t>
+  </si>
+  <si>
+    <t>1TH|JA1</t>
+  </si>
+  <si>
+    <t>6, 12:25-13:10</t>
+  </si>
+  <si>
+    <t>Matematyka</t>
+  </si>
+  <si>
+    <t>Uczniowie zwolnieni do domu</t>
+  </si>
+  <si>
+    <t>3S</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Smirnow-Zechman Eleonora</t>
+  </si>
+  <si>
+    <t>3TFA|JA2</t>
+  </si>
+  <si>
+    <t>7, 13:15-14:00</t>
+  </si>
+  <si>
+    <t>3K|JA2</t>
+  </si>
+  <si>
+    <t>3CA</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Derezińska Katarzyna</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - E-commerce</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Biologia</t>
+  </si>
+  <si>
+    <t>Sałdyka Karolina</t>
+  </si>
+  <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
+    <t>8, 14:05-14:50</t>
+  </si>
+  <si>
+    <t>Technika w produkcji gastronomicznej</t>
+  </si>
+  <si>
+    <t>1TH</t>
+  </si>
+  <si>
+    <t>Filipek Anna</t>
+  </si>
+  <si>
+    <t>Towaroznawstwo</t>
+  </si>
+  <si>
+    <t>2WB</t>
+  </si>
+  <si>
+    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
+  </si>
+  <si>
+    <t>Techniki fryzjerskie</t>
+  </si>
+  <si>
+    <t>Jastrzębska-Majtyka Agnieszka</t>
+  </si>
+  <si>
+    <t>9, 14:55-15:40</t>
+  </si>
+  <si>
+    <t>3TH|JA1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>2FC</t>
+  </si>
+  <si>
+    <t>10, 15:45-16:30</t>
+  </si>
+  <si>
+    <t>3TH</t>
+  </si>
+  <si>
+    <t>11, 16:35-17:20</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>26.05.2026</t>
+  </si>
+  <si>
+    <t>Wakat3 edukacja zdrow.</t>
+  </si>
+  <si>
+    <t>3CA|edu</t>
+  </si>
+  <si>
+    <t>Edukacja zdrowotna</t>
+  </si>
+  <si>
+    <t>Mocarski Arkadiusz</t>
+  </si>
+  <si>
+    <t>3FA|edu</t>
+  </si>
+  <si>
+    <t>3M|edu</t>
+  </si>
+  <si>
+    <t>3TFA|edu</t>
+  </si>
+  <si>
+    <t>3FB|DZ</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Antoszewska Joanna</t>
+  </si>
+  <si>
+    <t>3FB|CH</t>
+  </si>
+  <si>
+    <t>1TFA|JA1</t>
+  </si>
+  <si>
     <t>Historia</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Kopij Marcin</t>
-  </si>
-  <si>
-    <t>2TFB|JA2</t>
-  </si>
-  <si>
-    <t>3, 09:40-10:25</t>
-  </si>
-  <si>
-    <t>Czukiewska Bożena</t>
-  </si>
-  <si>
-    <t>1TH|JA2</t>
-  </si>
-  <si>
-    <t>Pracownia sprzedaży</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Kosin Anna</t>
-  </si>
-  <si>
-    <t>2FA</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
-    <t>prF3</t>
-  </si>
-  <si>
-    <t>Sobczak Anna</t>
-  </si>
-  <si>
-    <t>2S</t>
-  </si>
-  <si>
-    <t>Zajęcia biblioteczne</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>Nowak Damiana</t>
-  </si>
-  <si>
-    <t>Bezpłatne</t>
-  </si>
-  <si>
-    <t>4, 10:35-11:20</t>
-  </si>
-  <si>
-    <t>Granatowska Mariola</t>
-  </si>
-  <si>
-    <t>1CA|JA2</t>
-  </si>
-  <si>
-    <t>Język angielski</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Karczmarz Aleksandra</t>
-  </si>
-  <si>
-    <t>3FA</t>
-  </si>
-  <si>
-    <t>Kończyńska Małgorzata</t>
-  </si>
-  <si>
-    <t>Mucha Anna</t>
-  </si>
-  <si>
-    <t>3CA|CH</t>
-  </si>
-  <si>
-    <t>Wychowanie fizyczne</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Rejno Julita</t>
-  </si>
-  <si>
-    <t>3CA|DZ</t>
-  </si>
-  <si>
-    <t>2TFA</t>
-  </si>
-  <si>
-    <t>Biznes i zarządzanie</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Socha Dariusz</t>
-  </si>
-  <si>
-    <t>Zaleska Magdalena</t>
-  </si>
-  <si>
-    <t>Zajęcia z wychowawcą</t>
-  </si>
-  <si>
-    <t>5, 11:25-12:10</t>
-  </si>
-  <si>
-    <t>Bujanowska Iwona</t>
-  </si>
-  <si>
-    <t>1TFB</t>
-  </si>
-  <si>
-    <t>kin</t>
-  </si>
-  <si>
-    <t>Najwer Maciej</t>
-  </si>
-  <si>
-    <t>Małecka Barbara</t>
-  </si>
-  <si>
-    <t>2TFB</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Wojciechowski Łukasz</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>Język polski</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Ulanowska Magdalena</t>
-  </si>
-  <si>
-    <t>1TH|JA1</t>
-  </si>
-  <si>
-    <t>6, 12:25-13:10</t>
-  </si>
-  <si>
-    <t>Matematyka</t>
-  </si>
-  <si>
-    <t>Uczniowie zwolnieni do domu</t>
-  </si>
-  <si>
-    <t>3S</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Smirnow-Zechman Eleonora</t>
-  </si>
-  <si>
-    <t>3TFA|JA2</t>
-  </si>
-  <si>
-    <t>7, 13:15-14:00</t>
-  </si>
-  <si>
-    <t>3K|JA2</t>
-  </si>
-  <si>
-    <t>3CA</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>Derezińska Katarzyna</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - E-commerce</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Biologia</t>
-  </si>
-  <si>
-    <t>Sałdyka Karolina</t>
-  </si>
-  <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
-    <t>8, 14:05-14:50</t>
-  </si>
-  <si>
-    <t>Technika w produkcji gastronomicznej</t>
-  </si>
-  <si>
-    <t>1TH</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Filipek Anna</t>
-  </si>
-  <si>
-    <t>Towaroznawstwo</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>2WB</t>
-  </si>
-  <si>
-    <t>Rozwój zainteresowań i kreatywności - obsługa klienta</t>
-  </si>
-  <si>
-    <t>Techniki fryzjerskie</t>
-  </si>
-  <si>
-    <t>Jastrzębska-Majtyka Agnieszka</t>
-  </si>
-  <si>
-    <t>9, 14:55-15:40</t>
-  </si>
-  <si>
-    <t>3TH|JA1</t>
-  </si>
-  <si>
-    <t>2FC</t>
-  </si>
-  <si>
-    <t>10, 15:45-16:30</t>
-  </si>
-  <si>
-    <t>3TH</t>
-  </si>
-  <si>
-    <t>11, 16:35-17:20</t>
-  </si>
-  <si>
-    <t>3M</t>
-  </si>
-  <si>
-    <t>26.05.2026</t>
-  </si>
-  <si>
-    <t>Wakat3 edukacja zdrow.</t>
-  </si>
-  <si>
-    <t>3CA|edu</t>
-  </si>
-  <si>
-    <t>Edukacja zdrowotna</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>Mocarski Arkadiusz</t>
-  </si>
-  <si>
-    <t>3FA|edu</t>
-  </si>
-  <si>
-    <t>3M|edu</t>
-  </si>
-  <si>
-    <t>3TFA|edu</t>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Zastępstwo</t>
+  </si>
+  <si>
+    <t>p. Granatowska, j. angielski z poniedziałku 25 maja</t>
+  </si>
+  <si>
+    <t>p. Marzec, technika przeniesiona na lekcję 3</t>
+  </si>
+  <si>
+    <t>Edukacja obywatelska</t>
+  </si>
+  <si>
+    <t>3TFA|JA1</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Biezmienow Małgorzata</t>
+  </si>
+  <si>
+    <t>Misiąg Anna</t>
+  </si>
+  <si>
+    <t>2WA|JN1</t>
+  </si>
+  <si>
+    <t>Język niemiecki</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>2CB</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1FB</t>
+  </si>
+  <si>
+    <t>4TH|CH</t>
+  </si>
+  <si>
+    <t>Nestoruk Lidia</t>
+  </si>
+  <si>
+    <t>4TH|DZ</t>
+  </si>
+  <si>
+    <t>1CA|JA1</t>
+  </si>
+  <si>
+    <t>1TFA</t>
+  </si>
+  <si>
+    <t>p. Mikołajczak, podstawy fryzjerstwa za lekcję 7</t>
+  </si>
+  <si>
+    <t>3M|JN2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Mikołajczak Sylwia</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Fiodorów Małgorzata</t>
+  </si>
+  <si>
+    <t>3FA|reln</t>
+  </si>
+  <si>
+    <t>3FA|relu</t>
+  </si>
+  <si>
+    <t>Fizyka</t>
+  </si>
+  <si>
+    <t>Biczysko Wojciech</t>
+  </si>
+  <si>
+    <t>Jarek Zbigniew</t>
+  </si>
+  <si>
+    <t>1WB|JN2</t>
+  </si>
+  <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>p. Kopij, edukacja obywatelska za lekcję 10</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>1S|DZ</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>Okienko dla uczniów</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>2TFA|JA2</t>
+  </si>
+  <si>
+    <t>2CA|CH</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>2S|CH</t>
+  </si>
+  <si>
+    <t>sg3</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
+  </si>
+  <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
   </si>
   <si>
     <t>3FB</t>
   </si>
   <si>
-    <t>Zastępstwo</t>
-  </si>
-  <si>
-    <t>1TFA|JA1</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Misiąg Anna</t>
-  </si>
-  <si>
-    <t>2WA|JN1</t>
-  </si>
-  <si>
-    <t>Język niemiecki</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>2CB</t>
-  </si>
-  <si>
-    <t>1FB</t>
-  </si>
-  <si>
-    <t>3M|JN2</t>
-  </si>
-  <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>1WB|JN2</t>
-  </si>
-  <si>
-    <t>Edukacja dla bezpieczeństwa</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>27.05.2026</t>
-  </si>
-  <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>1S|DZ</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>1FA|JA2</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1WA|JN1</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>2TFA|JA2</t>
-  </si>
-  <si>
-    <t>2CA|CH</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>2S|CH</t>
-  </si>
-  <si>
-    <t>sg3</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
-  </si>
-  <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Fiodorów Małgorzata</t>
-  </si>
-  <si>
-    <t>28.05.2026</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
     <t>29.05.2026</t>
   </si>
   <si>
@@ -657,6 +723,12 @@
     <t>12:25-17:00</t>
   </si>
   <si>
+    <t>07:10-07:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
+  </si>
+  <si>
     <t>13:00-14:05</t>
   </si>
   <si>
@@ -726,10 +798,22 @@
     <t>17:20-17:25</t>
   </si>
   <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
+    <t>Marzec Renata</t>
+  </si>
+  <si>
+    <t>15:40-15:45</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>16:30-16:35</t>
+  </si>
+  <si>
     <t>07:55-08:00</t>
-  </si>
-  <si>
-    <t>16:30-16:35</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cf7a4a76-a128-4091-8c6c-8c178302766a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{88abd0e4-537f-4f59-8793-f962a58d8f9c}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1200,8 +1284,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a8c5c3e6-2f6a-4f1c-97b9-d3c1e60357ed}">
-  <dimension ref="A1:I149"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b3dfd00b-d52e-41e8-9ecf-04a236d73347}">
+  <dimension ref="A1:I175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1307,28 +1391,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -1336,25 +1420,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1365,13 +1449,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -1394,22 +1478,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -1423,28 +1507,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>46</v>
       </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
@@ -1452,28 +1536,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
@@ -1481,28 +1565,28 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15">
@@ -1510,28 +1594,28 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
@@ -1539,28 +1623,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
         <v>53</v>
       </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15">
@@ -1568,28 +1652,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
@@ -1597,28 +1681,28 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
         <v>61</v>
       </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
       <c r="E14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
         <v>63</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>64</v>
       </c>
-      <c r="G14" t="s">
-        <v>65</v>
-      </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
@@ -1626,28 +1710,28 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
@@ -1655,28 +1739,28 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
@@ -1684,28 +1768,28 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1713,28 +1797,28 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1742,28 +1826,28 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15">
@@ -1771,28 +1855,28 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1800,28 +1884,28 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
@@ -1829,28 +1913,28 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
@@ -1858,28 +1942,28 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
         <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1887,28 +1971,28 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
@@ -1916,25 +2000,25 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" t="s">
-        <v>41</v>
-      </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -1945,28 +2029,28 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
@@ -1974,28 +2058,28 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s">
         <v>76</v>
       </c>
-      <c r="G27" t="s">
-        <v>77</v>
-      </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -2003,28 +2087,28 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
@@ -2032,28 +2116,28 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
         <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15">
@@ -2061,28 +2145,28 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>25</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15">
@@ -2090,25 +2174,25 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
@@ -2119,25 +2203,25 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
@@ -2148,28 +2232,28 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="H33" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15">
@@ -2177,28 +2261,28 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
         <v>94</v>
       </c>
-      <c r="C34" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2206,28 +2290,28 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15">
@@ -2235,28 +2319,28 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15">
@@ -2264,28 +2348,28 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G37" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="H37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15">
@@ -2293,28 +2377,28 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H38" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15">
@@ -2322,28 +2406,28 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15">
@@ -2351,28 +2435,28 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" t="s">
         <v>105</v>
       </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" t="s">
-        <v>72</v>
-      </c>
       <c r="F40" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="G40" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="H40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15">
@@ -2380,25 +2464,25 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="E41" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -2409,28 +2493,28 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="H42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15">
@@ -2438,28 +2522,28 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15">
@@ -2467,28 +2551,28 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
         <v>102</v>
       </c>
-      <c r="F44" t="s">
-        <v>101</v>
-      </c>
-      <c r="G44" t="s">
-        <v>103</v>
-      </c>
       <c r="H44" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15">
@@ -2496,28 +2580,28 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H45" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15">
@@ -2525,28 +2609,28 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" t="s">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s">
         <v>88</v>
       </c>
-      <c r="F46" t="s">
-        <v>80</v>
-      </c>
-      <c r="G46" t="s">
-        <v>89</v>
-      </c>
       <c r="H46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15">
@@ -2554,28 +2638,28 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G47" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H47" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15">
@@ -2583,28 +2667,28 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" t="s">
         <v>54</v>
       </c>
-      <c r="D48" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" t="s">
-        <v>56</v>
-      </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15">
@@ -2612,28 +2696,28 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
         <v>116</v>
       </c>
-      <c r="C49" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" t="s">
-        <v>118</v>
-      </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F49" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15">
@@ -2641,28 +2725,28 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E50" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15">
@@ -2670,28 +2754,28 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s">
         <v>88</v>
       </c>
-      <c r="F51" t="s">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s">
-        <v>89</v>
-      </c>
       <c r="H51" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15">
@@ -2699,199 +2783,199 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" t="s">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s">
         <v>88</v>
       </c>
-      <c r="F52" t="s">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s">
-        <v>89</v>
-      </c>
       <c r="H52" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" t="s">
         <v>124</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53" t="s">
         <v>125</v>
       </c>
-      <c r="E53" t="s">
-        <v>126</v>
-      </c>
-      <c r="F53" t="s">
-        <v>127</v>
-      </c>
-      <c r="G53" t="s">
-        <v>128</v>
-      </c>
       <c r="H53" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54" t="s">
         <v>124</v>
       </c>
-      <c r="D54" t="s">
-        <v>129</v>
-      </c>
-      <c r="E54" t="s">
-        <v>126</v>
-      </c>
       <c r="F54" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="G54" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15">
       <c r="A55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" t="s">
+        <v>127</v>
+      </c>
+      <c r="E55" t="s">
         <v>124</v>
       </c>
-      <c r="D55" t="s">
-        <v>130</v>
-      </c>
-      <c r="E55" t="s">
-        <v>126</v>
-      </c>
       <c r="F55" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="G55" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H55" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" t="s">
         <v>124</v>
       </c>
-      <c r="D56" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" t="s">
-        <v>126</v>
-      </c>
       <c r="F56" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="G56" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G57" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H57" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="G58" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H58" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
@@ -2899,28 +2983,28 @@
     </row>
     <row r="59" spans="1:9" ht="15">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="H59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
@@ -2928,144 +3012,144 @@
     </row>
     <row r="60" spans="1:9" ht="15">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F60" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G60" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H60" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15">
       <c r="A61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="F61" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G61" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H61" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F62" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F63" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="H63" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D64" t="s">
+        <v>140</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" t="s">
         <v>141</v>
       </c>
-      <c r="E64" t="s">
-        <v>34</v>
-      </c>
-      <c r="F64" t="s">
-        <v>135</v>
-      </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
         <v>19</v>
@@ -3073,173 +3157,173 @@
     </row>
     <row r="65" spans="1:9" ht="15">
       <c r="A65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="F65" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G65" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H65" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15">
       <c r="A66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="D66" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="F66" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G66" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C67" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="F67" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G67" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="H67" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F68" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G68" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="E69" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F69" t="s">
-        <v>135</v>
+        <v>37</v>
       </c>
       <c r="G69" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="E70" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="G70" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -3247,57 +3331,57 @@
     </row>
     <row r="71" spans="1:9" ht="15">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="D71" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
+        <v>145</v>
+      </c>
+      <c r="F71" t="s">
+        <v>146</v>
+      </c>
+      <c r="G71" t="s">
         <v>88</v>
       </c>
-      <c r="F71" t="s">
-        <v>127</v>
-      </c>
-      <c r="G71" t="s">
-        <v>133</v>
-      </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F72" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="G72" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="H72" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
@@ -3305,86 +3389,86 @@
     </row>
     <row r="73" spans="1:9" ht="15">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="E73" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="F73" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="G73" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B74" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="D74" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F74" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="G74" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="D75" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -3392,86 +3476,86 @@
     </row>
     <row r="76" spans="1:9" ht="15">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="F76" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="G76" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="H76" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" t="s">
+        <v>74</v>
+      </c>
+      <c r="E77" t="s">
+        <v>111</v>
+      </c>
+      <c r="F77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G77" t="s">
+        <v>112</v>
+      </c>
+      <c r="H77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
         <v>32</v>
-      </c>
-      <c r="D77" t="s">
-        <v>29</v>
-      </c>
-      <c r="E77" t="s">
-        <v>88</v>
-      </c>
-      <c r="F77" t="s">
-        <v>127</v>
-      </c>
-      <c r="G77" t="s">
-        <v>89</v>
-      </c>
-      <c r="H77" t="s">
-        <v>25</v>
-      </c>
-      <c r="I77" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B78" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="D78" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F78" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
@@ -3479,115 +3563,115 @@
     </row>
     <row r="79" spans="1:9" ht="15">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C79" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="F79" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="G79" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H79" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15">
       <c r="A80" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="G80" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
       <c r="A81" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D81" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F81" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="G81" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="H81" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15">
       <c r="A82" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="D82" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E82" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="F82" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="G82" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
         <v>26</v>
@@ -3595,86 +3679,86 @@
     </row>
     <row r="83" spans="1:9" ht="15">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="D83" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E83" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>127</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="D84" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="E84" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="F84" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D85" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E85" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="F85" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G85" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H85" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
@@ -3682,57 +3766,57 @@
     </row>
     <row r="86" spans="1:9" ht="15">
       <c r="A86" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C86" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F86" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="G86" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C87" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D87" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="E87" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F87" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G87" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H87" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="I87" t="s">
         <v>26</v>
@@ -3740,405 +3824,405 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="D88" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="D89" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E89" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F89" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="G89" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="H89" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="E90" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="G90" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H90" t="s">
         <v>25</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D91" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="E91" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F91" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="G91" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H91" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92" t="s">
+        <v>175</v>
+      </c>
+      <c r="E92" t="s">
+        <v>124</v>
+      </c>
+      <c r="F92" t="s">
+        <v>58</v>
+      </c>
+      <c r="G92" t="s">
+        <v>125</v>
+      </c>
+      <c r="H92" t="s">
+        <v>18</v>
+      </c>
+      <c r="I92" t="s">
         <v>32</v>
-      </c>
-      <c r="D92" t="s">
-        <v>140</v>
-      </c>
-      <c r="E92" t="s">
-        <v>88</v>
-      </c>
-      <c r="F92" t="s">
-        <v>127</v>
-      </c>
-      <c r="G92" t="s">
-        <v>133</v>
-      </c>
-      <c r="H92" t="s">
-        <v>25</v>
-      </c>
-      <c r="I92" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D93" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="F93" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G93" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H93" t="s">
         <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="D94" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E94" t="s">
-        <v>34</v>
+        <v>124</v>
       </c>
       <c r="F94" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G94" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B95" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="E95" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F95" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H95" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B96" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="D96" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E96" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="G96" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H96" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B97" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D97" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="E97" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G97" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B98" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C98" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D98" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="F98" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G98" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="H98" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B99" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C99" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E99" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F99" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="G99" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H99" t="s">
         <v>25</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D100" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="E100" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F100" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="G100" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B101" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" t="s">
         <v>73</v>
       </c>
-      <c r="C101" t="s">
-        <v>32</v>
-      </c>
       <c r="D101" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="E101" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F101" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I101" t="s">
         <v>26</v>
@@ -4146,405 +4230,405 @@
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B102" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="E102" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F102" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="G102" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C103" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="E103" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="F103" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G103" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H103" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B104" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" t="s">
+        <v>38</v>
+      </c>
+      <c r="D104" t="s">
+        <v>147</v>
+      </c>
+      <c r="E104" t="s">
         <v>87</v>
       </c>
-      <c r="C104" t="s">
-        <v>149</v>
-      </c>
-      <c r="D104" t="s">
-        <v>166</v>
-      </c>
-      <c r="E104" t="s">
-        <v>63</v>
-      </c>
       <c r="F104" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="G104" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H104" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C105" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F105" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H105" t="s">
         <v>25</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B106" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C106" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D106" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E106" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F106" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G106" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H106" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B107" t="s">
+        <v>51</v>
+      </c>
+      <c r="C107" t="s">
+        <v>73</v>
+      </c>
+      <c r="D107" t="s">
+        <v>185</v>
+      </c>
+      <c r="E107" t="s">
         <v>87</v>
       </c>
-      <c r="C107" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" t="s">
-        <v>40</v>
-      </c>
-      <c r="E107" t="s">
-        <v>15</v>
-      </c>
       <c r="F107" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H107" t="s">
         <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B108" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C108" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D108" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="E108" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="F108" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="G108" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H108" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B109" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C109" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E109" t="s">
+        <v>101</v>
+      </c>
+      <c r="F109" t="s">
         <v>63</v>
       </c>
-      <c r="F109" t="s">
-        <v>151</v>
-      </c>
       <c r="G109" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="H109" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C110" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="D110" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E110" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F110" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="G110" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H110" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D111" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E111" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G111" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H111" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B112" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D112" t="s">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="F112" t="s">
         <v>135</v>
       </c>
       <c r="G112" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H112" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C113" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="D113" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="E113" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F113" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H113" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B114" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C114" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="E114" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F114" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="G114" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="C115" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="D115" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="F115" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="G115" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="H115" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
         <v>26</v>
@@ -4552,144 +4636,144 @@
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C116" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D116" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="E116" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F116" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="G116" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H116" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C117" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="E117" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="F117" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G117" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="H117" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="E118" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="F118" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="G118" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H118" t="s">
         <v>25</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B119" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D119" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E119" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="F119" t="s">
         <v>135</v>
       </c>
       <c r="G119" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H119" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B120" t="s">
+        <v>86</v>
+      </c>
+      <c r="C120" t="s">
+        <v>73</v>
+      </c>
+      <c r="D120" t="s">
+        <v>167</v>
+      </c>
+      <c r="E120" t="s">
         <v>87</v>
       </c>
-      <c r="C120" t="s">
-        <v>32</v>
-      </c>
-      <c r="D120" t="s">
-        <v>29</v>
-      </c>
-      <c r="E120" t="s">
-        <v>88</v>
-      </c>
       <c r="F120" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="G120" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H120" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
         <v>26</v>
@@ -4697,86 +4781,86 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B121" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C121" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="D121" t="s">
+        <v>189</v>
+      </c>
+      <c r="E121" t="s">
+        <v>62</v>
+      </c>
+      <c r="F121" t="s">
+        <v>172</v>
+      </c>
+      <c r="G121" t="s">
         <v>178</v>
       </c>
-      <c r="E121" t="s">
-        <v>34</v>
-      </c>
-      <c r="F121" t="s">
-        <v>135</v>
-      </c>
-      <c r="G121" t="s">
-        <v>133</v>
-      </c>
       <c r="H121" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B122" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C122" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="D122" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="E122" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F122" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="G122" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B123" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="D123" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E123" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F123" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="G123" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H123" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I123" t="s">
         <v>26</v>
@@ -4784,521 +4868,521 @@
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="C124" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="E124" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="F124" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="G124" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H124" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C125" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="E125" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F125" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="G125" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C126" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D126" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E126" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F126" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="G126" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H126" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="C127" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="D127" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E127" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="F127" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="G127" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H127" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B128" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C128" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D128" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E128" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G128" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H128" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B129" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C129" t="s">
-        <v>61</v>
+        <v>190</v>
       </c>
       <c r="D129" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="E129" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="G129" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H129" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B130" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C130" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="D130" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="E130" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="F130" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="G130" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H130" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B131" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C131" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E131" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F131" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="G131" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H131" t="s">
         <v>25</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B132" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C132" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D132" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="E132" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F132" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="G132" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H132" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B133" t="s">
+        <v>104</v>
+      </c>
+      <c r="C133" t="s">
         <v>73</v>
       </c>
-      <c r="C133" t="s">
-        <v>180</v>
-      </c>
       <c r="D133" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="E133" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="F133" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H133" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B134" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C134" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D134" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F134" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="G134" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H134" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B135" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C135" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="E135" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="F135" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="G135" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H135" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B136" t="s">
+        <v>113</v>
+      </c>
+      <c r="C136" t="s">
+        <v>73</v>
+      </c>
+      <c r="D136" t="s">
+        <v>96</v>
+      </c>
+      <c r="E136" t="s">
         <v>87</v>
       </c>
-      <c r="C136" t="s">
-        <v>32</v>
-      </c>
-      <c r="D136" t="s">
-        <v>160</v>
-      </c>
-      <c r="E136" t="s">
-        <v>88</v>
-      </c>
       <c r="F136" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="G136" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H136" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B137" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C137" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D137" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="E137" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="F137" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G137" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="H137" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B138" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="C138" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D138" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="E138" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F138" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="G138" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H138" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B139" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D139" t="s">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F139" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G139" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H139" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B140" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C140" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="D140" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="E140" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="F140" t="s">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="G140" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H140" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B141" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C141" t="s">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="D141" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="E141" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F141" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="G141" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="H141" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I141" t="s">
         <v>26</v>
@@ -5306,57 +5390,57 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
+        <v>199</v>
+      </c>
+      <c r="B142" t="s">
+        <v>86</v>
+      </c>
+      <c r="C142" t="s">
+        <v>38</v>
+      </c>
+      <c r="D142" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" t="s">
+        <v>87</v>
+      </c>
+      <c r="F142" t="s">
+        <v>58</v>
+      </c>
+      <c r="G142" t="s">
         <v>179</v>
       </c>
-      <c r="B142" t="s">
-        <v>105</v>
-      </c>
-      <c r="C142" t="s">
-        <v>167</v>
-      </c>
-      <c r="D142" t="s">
-        <v>190</v>
-      </c>
-      <c r="E142" t="s">
-        <v>63</v>
-      </c>
-      <c r="F142" t="s">
-        <v>191</v>
-      </c>
-      <c r="G142" t="s">
-        <v>133</v>
-      </c>
       <c r="H142" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B143" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C143" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D143" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
       <c r="E143" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="F143" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G143" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="H143" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I143" t="s">
         <v>26</v>
@@ -5364,28 +5448,28 @@
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B144" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C144" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="D144" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="E144" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F144" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="G144" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="H144" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
         <v>26</v>
@@ -5393,147 +5477,901 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
+        <v>199</v>
+      </c>
+      <c r="B145" t="s">
+        <v>113</v>
+      </c>
+      <c r="C145" t="s">
+        <v>38</v>
+      </c>
+      <c r="D145" t="s">
+        <v>184</v>
+      </c>
+      <c r="E145" t="s">
+        <v>87</v>
+      </c>
+      <c r="F145" t="s">
+        <v>58</v>
+      </c>
+      <c r="G145" t="s">
         <v>179</v>
       </c>
-      <c r="B145" t="s">
-        <v>105</v>
-      </c>
-      <c r="C145" t="s">
-        <v>187</v>
-      </c>
-      <c r="D145" t="s">
-        <v>188</v>
-      </c>
-      <c r="E145" t="s">
-        <v>88</v>
-      </c>
-      <c r="F145" t="s">
-        <v>101</v>
-      </c>
-      <c r="G145" t="s">
-        <v>189</v>
-      </c>
       <c r="H145" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B146" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="E146" t="s">
-        <v>63</v>
+        <v>203</v>
       </c>
       <c r="F146" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="G146" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H146" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="C147" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="D147" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E147" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="F147" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="G147" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H147" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B148" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="C148" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="D148" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="E148" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="F148" t="s">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="G148" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H148" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
+        <v>201</v>
+      </c>
+      <c r="B149" t="s">
+        <v>41</v>
+      </c>
+      <c r="C149" t="s">
+        <v>60</v>
+      </c>
+      <c r="D149" t="s">
+        <v>205</v>
+      </c>
+      <c r="E149" t="s">
+        <v>101</v>
+      </c>
+      <c r="F149" t="s">
+        <v>83</v>
+      </c>
+      <c r="G149" t="s">
+        <v>136</v>
+      </c>
+      <c r="H149" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="15">
+      <c r="A150" t="s">
+        <v>201</v>
+      </c>
+      <c r="B150" t="s">
+        <v>41</v>
+      </c>
+      <c r="C150" t="s">
+        <v>202</v>
+      </c>
+      <c r="D150" t="s">
+        <v>206</v>
+      </c>
+      <c r="E150" t="s">
+        <v>207</v>
+      </c>
+      <c r="F150" t="s">
+        <v>204</v>
+      </c>
+      <c r="G150" t="s">
+        <v>136</v>
+      </c>
+      <c r="H150" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="15">
+      <c r="A151" t="s">
+        <v>201</v>
+      </c>
+      <c r="B151" t="s">
+        <v>51</v>
+      </c>
+      <c r="C151" t="s">
+        <v>190</v>
+      </c>
+      <c r="D151" t="s">
+        <v>208</v>
+      </c>
+      <c r="E151" t="s">
+        <v>62</v>
+      </c>
+      <c r="F151" t="s">
+        <v>192</v>
+      </c>
+      <c r="G151" t="s">
+        <v>136</v>
+      </c>
+      <c r="H151" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="15">
+      <c r="A152" t="s">
+        <v>201</v>
+      </c>
+      <c r="B152" t="s">
+        <v>51</v>
+      </c>
+      <c r="C152" t="s">
+        <v>77</v>
+      </c>
+      <c r="D152" t="s">
+        <v>186</v>
+      </c>
+      <c r="E152" t="s">
+        <v>101</v>
+      </c>
+      <c r="F152" t="s">
+        <v>100</v>
+      </c>
+      <c r="G152" t="s">
+        <v>136</v>
+      </c>
+      <c r="H152" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="15">
+      <c r="A153" t="s">
+        <v>201</v>
+      </c>
+      <c r="B153" t="s">
+        <v>51</v>
+      </c>
+      <c r="C153" t="s">
+        <v>60</v>
+      </c>
+      <c r="D153" t="s">
+        <v>149</v>
+      </c>
+      <c r="E153" t="s">
+        <v>101</v>
+      </c>
+      <c r="F153" t="s">
+        <v>83</v>
+      </c>
+      <c r="G153" t="s">
+        <v>136</v>
+      </c>
+      <c r="H153" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="15">
+      <c r="A154" t="s">
+        <v>201</v>
+      </c>
+      <c r="B154" t="s">
+        <v>51</v>
+      </c>
+      <c r="C154" t="s">
+        <v>202</v>
+      </c>
+      <c r="D154" t="s">
+        <v>206</v>
+      </c>
+      <c r="E154" t="s">
+        <v>207</v>
+      </c>
+      <c r="F154" t="s">
+        <v>204</v>
+      </c>
+      <c r="G154" t="s">
+        <v>136</v>
+      </c>
+      <c r="H154" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="15">
+      <c r="A155" t="s">
+        <v>201</v>
+      </c>
+      <c r="B155" t="s">
+        <v>72</v>
+      </c>
+      <c r="C155" t="s">
+        <v>190</v>
+      </c>
+      <c r="D155" t="s">
+        <v>208</v>
+      </c>
+      <c r="E155" t="s">
+        <v>62</v>
+      </c>
+      <c r="F155" t="s">
+        <v>192</v>
+      </c>
+      <c r="G155" t="s">
+        <v>136</v>
+      </c>
+      <c r="H155" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="15">
+      <c r="A156" t="s">
+        <v>201</v>
+      </c>
+      <c r="B156" t="s">
+        <v>72</v>
+      </c>
+      <c r="C156" t="s">
+        <v>77</v>
+      </c>
+      <c r="D156" t="s">
+        <v>186</v>
+      </c>
+      <c r="E156" t="s">
+        <v>101</v>
+      </c>
+      <c r="F156" t="s">
+        <v>100</v>
+      </c>
+      <c r="G156" t="s">
+        <v>136</v>
+      </c>
+      <c r="H156" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="15">
+      <c r="A157" t="s">
+        <v>201</v>
+      </c>
+      <c r="B157" t="s">
+        <v>72</v>
+      </c>
+      <c r="C157" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" t="s">
+        <v>118</v>
+      </c>
+      <c r="E157" t="s">
+        <v>101</v>
+      </c>
+      <c r="F157" t="s">
+        <v>83</v>
+      </c>
+      <c r="G157" t="s">
+        <v>136</v>
+      </c>
+      <c r="H157" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="15">
+      <c r="A158" t="s">
+        <v>201</v>
+      </c>
+      <c r="B158" t="s">
+        <v>72</v>
+      </c>
+      <c r="C158" t="s">
+        <v>202</v>
+      </c>
+      <c r="D158" t="s">
+        <v>206</v>
+      </c>
+      <c r="E158" t="s">
+        <v>207</v>
+      </c>
+      <c r="F158" t="s">
+        <v>204</v>
+      </c>
+      <c r="G158" t="s">
+        <v>136</v>
+      </c>
+      <c r="H158" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="15">
+      <c r="A159" t="s">
+        <v>201</v>
+      </c>
+      <c r="B159" t="s">
+        <v>86</v>
+      </c>
+      <c r="C159" t="s">
+        <v>190</v>
+      </c>
+      <c r="D159" t="s">
+        <v>208</v>
+      </c>
+      <c r="E159" t="s">
+        <v>62</v>
+      </c>
+      <c r="F159" t="s">
+        <v>192</v>
+      </c>
+      <c r="G159" t="s">
+        <v>136</v>
+      </c>
+      <c r="H159" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="15">
+      <c r="A160" t="s">
+        <v>201</v>
+      </c>
+      <c r="B160" t="s">
+        <v>86</v>
+      </c>
+      <c r="C160" t="s">
+        <v>77</v>
+      </c>
+      <c r="D160" t="s">
+        <v>66</v>
+      </c>
+      <c r="E160" t="s">
+        <v>101</v>
+      </c>
+      <c r="F160" t="s">
+        <v>100</v>
+      </c>
+      <c r="G160" t="s">
+        <v>136</v>
+      </c>
+      <c r="H160" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="15">
+      <c r="A161" t="s">
+        <v>201</v>
+      </c>
+      <c r="B161" t="s">
+        <v>86</v>
+      </c>
+      <c r="C161" t="s">
+        <v>60</v>
+      </c>
+      <c r="D161" t="s">
+        <v>187</v>
+      </c>
+      <c r="E161" t="s">
+        <v>101</v>
+      </c>
+      <c r="F161" t="s">
+        <v>83</v>
+      </c>
+      <c r="G161" t="s">
+        <v>136</v>
+      </c>
+      <c r="H161" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="15">
+      <c r="A162" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" t="s">
+        <v>86</v>
+      </c>
+      <c r="C162" t="s">
+        <v>38</v>
+      </c>
+      <c r="D162" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162" t="s">
+        <v>87</v>
+      </c>
+      <c r="F162" t="s">
+        <v>58</v>
+      </c>
+      <c r="G162" t="s">
+        <v>136</v>
+      </c>
+      <c r="H162" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="15">
+      <c r="A163" t="s">
+        <v>201</v>
+      </c>
+      <c r="B163" t="s">
+        <v>86</v>
+      </c>
+      <c r="C163" t="s">
+        <v>202</v>
+      </c>
+      <c r="D163" t="s">
+        <v>206</v>
+      </c>
+      <c r="E163" t="s">
+        <v>207</v>
+      </c>
+      <c r="F163" t="s">
+        <v>204</v>
+      </c>
+      <c r="G163" t="s">
+        <v>136</v>
+      </c>
+      <c r="H163" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="15">
+      <c r="A164" t="s">
+        <v>201</v>
+      </c>
+      <c r="B164" t="s">
+        <v>93</v>
+      </c>
+      <c r="C164" t="s">
+        <v>60</v>
+      </c>
+      <c r="D164" t="s">
+        <v>181</v>
+      </c>
+      <c r="E164" t="s">
+        <v>101</v>
+      </c>
+      <c r="F164" t="s">
+        <v>83</v>
+      </c>
+      <c r="G164" t="s">
+        <v>136</v>
+      </c>
+      <c r="H164" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="15">
+      <c r="A165" t="s">
+        <v>201</v>
+      </c>
+      <c r="B165" t="s">
+        <v>93</v>
+      </c>
+      <c r="C165" t="s">
+        <v>38</v>
+      </c>
+      <c r="D165" t="s">
+        <v>187</v>
+      </c>
+      <c r="E165" t="s">
+        <v>87</v>
+      </c>
+      <c r="F165" t="s">
+        <v>58</v>
+      </c>
+      <c r="G165" t="s">
+        <v>136</v>
+      </c>
+      <c r="H165" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="15">
+      <c r="A166" t="s">
+        <v>201</v>
+      </c>
+      <c r="B166" t="s">
+        <v>93</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
+      </c>
+      <c r="D166" t="s">
+        <v>96</v>
+      </c>
+      <c r="E166" t="s">
+        <v>105</v>
+      </c>
+      <c r="F166" t="s">
+        <v>204</v>
+      </c>
+      <c r="G166" t="s">
+        <v>136</v>
+      </c>
+      <c r="H166" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="15">
+      <c r="A167" t="s">
+        <v>201</v>
+      </c>
+      <c r="B167" t="s">
+        <v>93</v>
+      </c>
+      <c r="C167" t="s">
+        <v>209</v>
+      </c>
+      <c r="D167" t="s">
+        <v>210</v>
+      </c>
+      <c r="E167" t="s">
+        <v>87</v>
+      </c>
+      <c r="F167" t="s">
+        <v>100</v>
+      </c>
+      <c r="G167" t="s">
+        <v>211</v>
+      </c>
+      <c r="H167" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="15">
+      <c r="A168" t="s">
+        <v>201</v>
+      </c>
+      <c r="B168" t="s">
+        <v>104</v>
+      </c>
+      <c r="C168" t="s">
+        <v>190</v>
+      </c>
+      <c r="D168" t="s">
+        <v>212</v>
+      </c>
+      <c r="E168" t="s">
+        <v>62</v>
+      </c>
+      <c r="F168" t="s">
+        <v>213</v>
+      </c>
+      <c r="G168" t="s">
+        <v>136</v>
+      </c>
+      <c r="H168" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="15">
+      <c r="A169" t="s">
+        <v>201</v>
+      </c>
+      <c r="B169" t="s">
+        <v>104</v>
+      </c>
+      <c r="C169" t="s">
+        <v>38</v>
+      </c>
+      <c r="D169" t="s">
+        <v>66</v>
+      </c>
+      <c r="E169" t="s">
+        <v>87</v>
+      </c>
+      <c r="F169" t="s">
+        <v>58</v>
+      </c>
+      <c r="G169" t="s">
         <v>179</v>
       </c>
-      <c r="B149" t="s">
-        <v>119</v>
-      </c>
-      <c r="C149" t="s">
-        <v>61</v>
-      </c>
-      <c r="D149" t="s">
-        <v>188</v>
-      </c>
-      <c r="E149" t="s">
-        <v>102</v>
-      </c>
-      <c r="F149" t="s">
+      <c r="H169" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="15">
+      <c r="A170" t="s">
+        <v>201</v>
+      </c>
+      <c r="B170" t="s">
+        <v>104</v>
+      </c>
+      <c r="C170" t="s">
+        <v>197</v>
+      </c>
+      <c r="D170" t="s">
+        <v>198</v>
+      </c>
+      <c r="E170" t="s">
+        <v>145</v>
+      </c>
+      <c r="F170" t="s">
+        <v>159</v>
+      </c>
+      <c r="G170" t="s">
+        <v>160</v>
+      </c>
+      <c r="H170" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="15">
+      <c r="A171" t="s">
+        <v>201</v>
+      </c>
+      <c r="B171" t="s">
+        <v>104</v>
+      </c>
+      <c r="C171" t="s">
+        <v>209</v>
+      </c>
+      <c r="D171" t="s">
+        <v>210</v>
+      </c>
+      <c r="E171" t="s">
+        <v>87</v>
+      </c>
+      <c r="F171" t="s">
+        <v>100</v>
+      </c>
+      <c r="G171" t="s">
+        <v>211</v>
+      </c>
+      <c r="H171" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="15">
+      <c r="A172" t="s">
+        <v>201</v>
+      </c>
+      <c r="B172" t="s">
+        <v>113</v>
+      </c>
+      <c r="C172" t="s">
+        <v>190</v>
+      </c>
+      <c r="D172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E172" t="s">
+        <v>62</v>
+      </c>
+      <c r="F172" t="s">
+        <v>213</v>
+      </c>
+      <c r="G172" t="s">
+        <v>136</v>
+      </c>
+      <c r="H172" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="15">
+      <c r="A173" t="s">
+        <v>201</v>
+      </c>
+      <c r="B173" t="s">
+        <v>113</v>
+      </c>
+      <c r="C173" t="s">
+        <v>60</v>
+      </c>
+      <c r="D173" t="s">
+        <v>116</v>
+      </c>
+      <c r="E173" t="s">
         <v>101</v>
       </c>
-      <c r="G149" t="s">
-        <v>133</v>
-      </c>
-      <c r="H149" t="s">
-        <v>25</v>
-      </c>
-      <c r="I149" t="s">
-        <v>19</v>
+      <c r="F173" t="s">
+        <v>100</v>
+      </c>
+      <c r="G173" t="s">
+        <v>136</v>
+      </c>
+      <c r="H173" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="15">
+      <c r="A174" t="s">
+        <v>201</v>
+      </c>
+      <c r="B174" t="s">
+        <v>117</v>
+      </c>
+      <c r="C174" t="s">
+        <v>190</v>
+      </c>
+      <c r="D174" t="s">
+        <v>212</v>
+      </c>
+      <c r="E174" t="s">
+        <v>62</v>
+      </c>
+      <c r="F174" t="s">
+        <v>213</v>
+      </c>
+      <c r="G174" t="s">
+        <v>136</v>
+      </c>
+      <c r="H174" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="15">
+      <c r="A175" t="s">
+        <v>201</v>
+      </c>
+      <c r="B175" t="s">
+        <v>117</v>
+      </c>
+      <c r="C175" t="s">
+        <v>60</v>
+      </c>
+      <c r="D175" t="s">
+        <v>210</v>
+      </c>
+      <c r="E175" t="s">
+        <v>101</v>
+      </c>
+      <c r="F175" t="s">
+        <v>100</v>
+      </c>
+      <c r="G175" t="s">
+        <v>136</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -5544,14 +6382,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{d0e2ec0c-24ac-41a9-acc9-a97e99f872a6}">
-  <dimension ref="A1:I10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00cc960f-ee24-44cd-8580-d47f83727a66}">
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="18.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="45.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="24.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
@@ -5564,16 +6402,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -5593,28 +6431,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15">
@@ -5622,28 +6460,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -5651,202 +6489,231 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="E4" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D5" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="F5" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>201</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="E9" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" t="s">
-        <v>133</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="D10" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="E10" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="F10" t="s">
-        <v>202</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15">
+      <c r="A11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -5857,8 +6724,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2351e571-ed08-40f5-8b6b-2b2dd1bc113f}">
-  <dimension ref="A1:F44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0b02628f-28a3-41d1-b08e-c42ecf42add2}">
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -5874,13 +6741,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -5894,19 +6761,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
@@ -5914,19 +6781,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
@@ -5934,19 +6801,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -5954,19 +6821,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
@@ -5974,19 +6841,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
@@ -5994,19 +6861,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
@@ -6014,19 +6881,19 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
@@ -6034,19 +6901,19 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
@@ -6054,19 +6921,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
@@ -6074,19 +6941,19 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15">
@@ -6094,19 +6961,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
@@ -6114,19 +6981,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
@@ -6134,19 +7001,19 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
@@ -6154,19 +7021,19 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
@@ -6174,19 +7041,19 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
@@ -6194,19 +7061,19 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
@@ -6214,176 +7081,176 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="D26" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -6391,79 +7258,79 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="D29" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="F29" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -6471,79 +7338,79 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
         <v>25</v>
@@ -6551,139 +7418,139 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C41" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
         <v>25</v>
@@ -6691,62 +7558,322 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="D42" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B45" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="s">
+        <v>256</v>
+      </c>
+      <c r="E45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" t="s">
+        <v>253</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" t="s">
+        <v>241</v>
+      </c>
+      <c r="C47" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" t="s">
+        <v>242</v>
+      </c>
+      <c r="E47" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" t="s">
+        <v>201</v>
+      </c>
+      <c r="B49" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>256</v>
+      </c>
+      <c r="E50" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" t="s">
+        <v>202</v>
+      </c>
+      <c r="D51" t="s">
+        <v>243</v>
+      </c>
+      <c r="E51" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" t="s">
+        <v>201</v>
+      </c>
+      <c r="B52" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" t="s">
+        <v>242</v>
+      </c>
+      <c r="E52" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15">
+      <c r="A53" t="s">
+        <v>201</v>
+      </c>
+      <c r="B53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" t="s">
+        <v>201</v>
+      </c>
+      <c r="B54" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" t="s">
+        <v>202</v>
+      </c>
+      <c r="D54" t="s">
+        <v>251</v>
+      </c>
+      <c r="E54" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" t="s">
+        <v>250</v>
+      </c>
+      <c r="C55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" t="s">
+        <v>248</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15">
+      <c r="A56" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" t="s">
+        <v>256</v>
+      </c>
+      <c r="E56" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15">
+      <c r="A57" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C57" t="s">
+        <v>190</v>
+      </c>
+      <c r="D57" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="280">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -519,285 +519,336 @@
     <t>Biczysko Wojciech</t>
   </si>
   <si>
+    <t>2FB</t>
+  </si>
+  <si>
+    <t>p. Kopij, edukacja obywatelska za lekcję 10</t>
+  </si>
+  <si>
+    <t>27.05.2026</t>
+  </si>
+  <si>
+    <t>Cieśla Marcin</t>
+  </si>
+  <si>
+    <t>1S|DZ</t>
+  </si>
+  <si>
+    <t>sg4</t>
+  </si>
+  <si>
+    <t>Skarupa Agnieszka</t>
+  </si>
+  <si>
+    <t>4TH</t>
+  </si>
+  <si>
+    <t>1TFA|JA2</t>
+  </si>
+  <si>
+    <t>2CA|edu</t>
+  </si>
+  <si>
+    <t>2FC|edu</t>
+  </si>
+  <si>
+    <t>2S|edu</t>
+  </si>
+  <si>
+    <t>2WA|edu</t>
+  </si>
+  <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>Obsługa klienta</t>
+  </si>
+  <si>
+    <t>p. Kopij, edukacja obywatelska za czwartek 28 maja 2026</t>
+  </si>
+  <si>
+    <t>1FA|JA2</t>
+  </si>
+  <si>
+    <t>1FC</t>
+  </si>
+  <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>p. Piątek- Pawłowska, j. polski przeniesiony na lekcję 3, sala 18</t>
+  </si>
+  <si>
+    <t>1WA|JN1</t>
+  </si>
+  <si>
+    <t>4TFB</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur</t>
+  </si>
+  <si>
+    <t>Leńczowska Iwona</t>
+  </si>
+  <si>
+    <t>Marketing w działalności handlowej</t>
+  </si>
+  <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>2CA</t>
+  </si>
+  <si>
+    <t>3TH|JA2</t>
+  </si>
+  <si>
+    <t>2TFA|JA2</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>2CA|CH</t>
+  </si>
+  <si>
+    <t>Wójcik Kamil</t>
+  </si>
+  <si>
+    <t>Pietrycha Małgorzata</t>
+  </si>
+  <si>
+    <t>p. Krzemińska, techniki za lekcję 1</t>
+  </si>
+  <si>
+    <t>Dalach Sławomir</t>
+  </si>
+  <si>
+    <t>2S|CH</t>
+  </si>
+  <si>
+    <t>sg3</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
+  </si>
+  <si>
+    <t>2WA</t>
+  </si>
+  <si>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>Wakat1 j. niemiecki</t>
+  </si>
+  <si>
+    <t>1WA|JN2</t>
+  </si>
+  <si>
+    <t>28.05.2026</t>
+  </si>
+  <si>
+    <t>p. Hudziec, chemia za lekcję 7</t>
+  </si>
+  <si>
+    <t>3FB</t>
+  </si>
+  <si>
+    <t>29.05.2026</t>
+  </si>
+  <si>
+    <t>Świerzewicz Katarzyna</t>
+  </si>
+  <si>
+    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>1CB|reln</t>
+  </si>
+  <si>
+    <t>1CB|relu</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>Technologia gastronomiczna z towaroznawstwem</t>
+  </si>
+  <si>
+    <t>1CB|JA1</t>
+  </si>
+  <si>
+    <t>Kruk Marcin</t>
+  </si>
+  <si>
+    <t>1FC|JA2</t>
+  </si>
+  <si>
+    <t>Edukacja dla bezpieczeństwa</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>1FC|JA1</t>
+  </si>
+  <si>
+    <t>Technika w produkcji cukierniczej</t>
+  </si>
+  <si>
+    <t>Wakat2 matematyka</t>
+  </si>
+  <si>
+    <t>1S</t>
+  </si>
+  <si>
+    <t>Młynarczyk Paweł</t>
+  </si>
+  <si>
+    <t>2FB|CH</t>
+  </si>
+  <si>
+    <t>Godzina</t>
+  </si>
+  <si>
+    <t>Nauczyciel</t>
+  </si>
+  <si>
+    <t>Dziennik zajęć innych</t>
+  </si>
+  <si>
+    <t>Opis zajęć</t>
+  </si>
+  <si>
+    <t>08:50-10:20</t>
+  </si>
+  <si>
+    <t>Krystian Pietrowski - 3M - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>09:00-15:00</t>
+  </si>
+  <si>
+    <t>Bokuniewicz Sylwia</t>
+  </si>
+  <si>
+    <t>dziennik psychologa - Sylwia Bokuniewicz</t>
+  </si>
+  <si>
+    <t>dyżur psychologa</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>14:05-14:45</t>
+  </si>
+  <si>
+    <t>Julia Falenta - 4TFB - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>chemia</t>
+  </si>
+  <si>
+    <t>11:00-11:25</t>
+  </si>
+  <si>
+    <t>11:25-12:25</t>
+  </si>
+  <si>
+    <t>MP_2WA – zajęcia resocjalizacyjne</t>
+  </si>
+  <si>
+    <t>zajęcia resocjalizacyjne</t>
+  </si>
+  <si>
+    <t>12:25-17:00</t>
+  </si>
+  <si>
+    <t>07:10-07:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
+  </si>
+  <si>
+    <t>13:00-14:05</t>
+  </si>
+  <si>
+    <t>14:05-15:05</t>
+  </si>
+  <si>
+    <t>NP_1S – zajęcia socjoterapeutyczne</t>
+  </si>
+  <si>
+    <t>zajęcia socjoterapeutyczne</t>
+  </si>
+  <si>
+    <t>15:05-16:00</t>
+  </si>
+  <si>
+    <t>Miejsce dyżuru</t>
+  </si>
+  <si>
+    <t>08:45-08:50</t>
+  </si>
+  <si>
+    <t>piętro_2</t>
+  </si>
+  <si>
+    <t>piętro_3</t>
+  </si>
+  <si>
+    <t>09:35-09:40</t>
+  </si>
+  <si>
+    <t>10:25-10:35</t>
+  </si>
+  <si>
+    <t>boisko - dziedziniec wejściowy/boisko</t>
+  </si>
+  <si>
+    <t>11:20-11:25</t>
+  </si>
+  <si>
+    <t>piętro_1</t>
+  </si>
+  <si>
+    <t>12:10-12:25</t>
+  </si>
+  <si>
+    <t>13:10-13:15</t>
+  </si>
+  <si>
+    <t>bramka wejściowa</t>
+  </si>
+  <si>
+    <t>14:00-14:05</t>
+  </si>
+  <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>14:50-14:55</t>
+  </si>
+  <si>
+    <t>parter</t>
+  </si>
+  <si>
+    <t>17:20-17:25</t>
+  </si>
+  <si>
     <t>Jarek Zbigniew</t>
   </si>
   <si>
-    <t>1WB|JN2</t>
-  </si>
-  <si>
-    <t>2FB</t>
-  </si>
-  <si>
-    <t>p. Kopij, edukacja obywatelska za lekcję 10</t>
-  </si>
-  <si>
-    <t>27.05.2026</t>
-  </si>
-  <si>
-    <t>Cieśla Marcin</t>
-  </si>
-  <si>
-    <t>1S|DZ</t>
-  </si>
-  <si>
-    <t>sg4</t>
-  </si>
-  <si>
-    <t>1TFA|JA2</t>
-  </si>
-  <si>
-    <t>2CA|edu</t>
-  </si>
-  <si>
-    <t>2FC|edu</t>
-  </si>
-  <si>
-    <t>2S|edu</t>
-  </si>
-  <si>
-    <t>2WA|edu</t>
-  </si>
-  <si>
-    <t>Okienko dla uczniów</t>
-  </si>
-  <si>
-    <t>Filusz Marzena</t>
-  </si>
-  <si>
-    <t>1FA|JA2</t>
-  </si>
-  <si>
-    <t>1FC</t>
-  </si>
-  <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>1WA|JN1</t>
-  </si>
-  <si>
-    <t>4TFB</t>
-  </si>
-  <si>
-    <t>4TH</t>
-  </si>
-  <si>
-    <t>3TFA</t>
-  </si>
-  <si>
-    <t>2CA</t>
-  </si>
-  <si>
-    <t>2TFA|JA2</t>
-  </si>
-  <si>
-    <t>2CA|CH</t>
-  </si>
-  <si>
-    <t>Dalach Sławomir</t>
-  </si>
-  <si>
-    <t>2S|CH</t>
-  </si>
-  <si>
-    <t>sg3</t>
-  </si>
-  <si>
-    <t>3TFB</t>
-  </si>
-  <si>
-    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
-  </si>
-  <si>
-    <t>2WA</t>
-  </si>
-  <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
-    <t>Wakat1 j. niemiecki</t>
-  </si>
-  <si>
-    <t>1WA|JN2</t>
-  </si>
-  <si>
-    <t>28.05.2026</t>
-  </si>
-  <si>
-    <t>3FB</t>
-  </si>
-  <si>
-    <t>29.05.2026</t>
-  </si>
-  <si>
-    <t>Świerzewicz Katarzyna</t>
-  </si>
-  <si>
-    <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1CB</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>Technologia gastronomiczna z towaroznawstwem</t>
-  </si>
-  <si>
-    <t>1CB|JA1</t>
-  </si>
-  <si>
-    <t>Wakat2 matematyka</t>
-  </si>
-  <si>
-    <t>1S</t>
-  </si>
-  <si>
-    <t>Młynarczyk Paweł</t>
-  </si>
-  <si>
-    <t>2FB|CH</t>
-  </si>
-  <si>
-    <t>sg2</t>
-  </si>
-  <si>
-    <t>Godzina</t>
-  </si>
-  <si>
-    <t>Nauczyciel</t>
-  </si>
-  <si>
-    <t>Dziennik zajęć innych</t>
-  </si>
-  <si>
-    <t>Opis zajęć</t>
-  </si>
-  <si>
-    <t>08:50-10:20</t>
-  </si>
-  <si>
-    <t>Krystian Pietrowski - 3M - indywidualne nauczanie</t>
-  </si>
-  <si>
-    <t>09:00-15:00</t>
-  </si>
-  <si>
-    <t>Bokuniewicz Sylwia</t>
-  </si>
-  <si>
-    <t>dziennik psychologa - Sylwia Bokuniewicz</t>
-  </si>
-  <si>
-    <t>dyżur psychologa</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>14:05-14:45</t>
-  </si>
-  <si>
-    <t>Julia Falenta - 4TFB - indywidualne nauczanie</t>
-  </si>
-  <si>
-    <t>chemia</t>
-  </si>
-  <si>
-    <t>11:00-11:25</t>
-  </si>
-  <si>
-    <t>11:25-12:25</t>
-  </si>
-  <si>
-    <t>MP_2WA – zajęcia resocjalizacyjne</t>
-  </si>
-  <si>
-    <t>zajęcia resocjalizacyjne</t>
-  </si>
-  <si>
-    <t>12:25-17:00</t>
-  </si>
-  <si>
-    <t>07:10-07:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kornelia Gałązka -  klasa 4TFB - indywidualne nauczanie </t>
-  </si>
-  <si>
-    <t>13:00-14:05</t>
-  </si>
-  <si>
-    <t>14:05-15:05</t>
-  </si>
-  <si>
-    <t>NP_1S – zajęcia socjoterapeutyczne</t>
-  </si>
-  <si>
-    <t>zajęcia socjoterapeutyczne</t>
-  </si>
-  <si>
-    <t>15:05-16:00</t>
-  </si>
-  <si>
-    <t>Miejsce dyżuru</t>
-  </si>
-  <si>
-    <t>08:45-08:50</t>
-  </si>
-  <si>
-    <t>piętro_2</t>
-  </si>
-  <si>
-    <t>piętro_3</t>
-  </si>
-  <si>
-    <t>09:35-09:40</t>
-  </si>
-  <si>
-    <t>10:25-10:35</t>
-  </si>
-  <si>
-    <t>boisko - dziedziniec wejściowy/boisko</t>
-  </si>
-  <si>
-    <t>11:20-11:25</t>
-  </si>
-  <si>
-    <t>piętro_1</t>
-  </si>
-  <si>
-    <t>12:10-12:25</t>
-  </si>
-  <si>
-    <t>13:10-13:15</t>
-  </si>
-  <si>
-    <t>bramka wejściowa</t>
-  </si>
-  <si>
-    <t>Leńczowska Iwona</t>
-  </si>
-  <si>
-    <t>14:00-14:05</t>
-  </si>
-  <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
-    <t>14:50-14:55</t>
-  </si>
-  <si>
-    <t>parter</t>
-  </si>
-  <si>
-    <t>17:20-17:25</t>
-  </si>
-  <si>
     <t>Jaworska Edyta</t>
   </si>
   <si>
@@ -805,9 +856,6 @@
   </si>
   <si>
     <t>15:40-15:45</t>
-  </si>
-  <si>
-    <t>Kruk Marcin</t>
   </si>
   <si>
     <t>16:30-16:35</t>
@@ -1263,7 +1311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{88abd0e4-537f-4f59-8793-f962a58d8f9c}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cb10051d-bf4d-4863-9db9-038ba902a32d}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1284,8 +1332,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{b3dfd00b-d52e-41e8-9ecf-04a236d73347}">
-  <dimension ref="A1:I175"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7c7c1aca-f1b4-473f-8866-25922a6bc57b}">
+  <dimension ref="A1:I181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1295,7 +1343,7 @@
     <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="8" max="8" width="56.1428571428571" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3743,25 +3791,25 @@
         <v>113</v>
       </c>
       <c r="C85" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="D85" t="s">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="F85" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="G85" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3772,22 +3820,22 @@
         <v>113</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="E86" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="F86" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G86" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="H86" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="I86" t="s">
         <v>26</v>
@@ -3795,28 +3843,28 @@
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D87" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="F87" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="G87" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H87" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="I87" t="s">
         <v>26</v>
@@ -3824,25 +3872,25 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="E88" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F88" t="s">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="G88" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
@@ -3853,22 +3901,22 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E89" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F89" t="s">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="G89" t="s">
         <v>24</v>
@@ -3882,7 +3930,7 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -3900,7 +3948,7 @@
         <v>23</v>
       </c>
       <c r="G90" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H90" t="s">
         <v>25</v>
@@ -3911,7 +3959,7 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
@@ -3940,7 +3988,7 @@
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
@@ -3969,7 +4017,7 @@
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
@@ -3998,7 +4046,7 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
@@ -4027,7 +4075,7 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B95" t="s">
         <v>33</v>
@@ -4039,42 +4087,42 @@
         <v>118</v>
       </c>
       <c r="E95" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F95" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G95" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B96" t="s">
         <v>33</v>
       </c>
       <c r="C96" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D96" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E96" t="s">
         <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G96" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
@@ -4085,7 +4133,7 @@
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B97" t="s">
         <v>33</v>
@@ -4103,7 +4151,7 @@
         <v>100</v>
       </c>
       <c r="G97" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
@@ -4114,7 +4162,7 @@
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B98" t="s">
         <v>33</v>
@@ -4132,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="G98" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
@@ -4143,28 +4191,28 @@
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B99" t="s">
         <v>33</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="D99" t="s">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="E99" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G99" t="s">
         <v>136</v>
       </c>
       <c r="H99" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="I99" t="s">
         <v>26</v>
@@ -4172,28 +4220,28 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B100" t="s">
         <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D100" t="s">
         <v>181</v>
       </c>
       <c r="E100" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="G100" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I100" t="s">
         <v>26</v>
@@ -4201,83 +4249,83 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B101" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D101" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="E101" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
         <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B102" t="s">
         <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="D102" t="s">
-        <v>171</v>
+        <v>118</v>
       </c>
       <c r="E102" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F102" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="G102" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="H102" t="s">
         <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B103" t="s">
         <v>41</v>
       </c>
       <c r="C103" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E103" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F103" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="G103" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
@@ -4288,28 +4336,28 @@
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B104" t="s">
         <v>41</v>
       </c>
       <c r="C104" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D104" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F104" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="G104" t="s">
         <v>136</v>
       </c>
       <c r="H104" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="I104" t="s">
         <v>26</v>
@@ -4317,86 +4365,86 @@
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B105" t="s">
         <v>41</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D105" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E105" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G105" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H105" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B106" t="s">
         <v>41</v>
       </c>
       <c r="C106" t="s">
-        <v>70</v>
+        <v>171</v>
       </c>
       <c r="D106" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="E106" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="F106" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="G106" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C107" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="D107" t="s">
         <v>185</v>
       </c>
       <c r="E107" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F107" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="G107" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H107" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I107" t="s">
         <v>26</v>
@@ -4404,286 +4452,286 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B108" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C108" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D108" t="s">
         <v>186</v>
       </c>
       <c r="E108" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="F108" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="G108" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B109" t="s">
         <v>51</v>
       </c>
       <c r="C109" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D109" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E109" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="F109" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G109" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B110" t="s">
         <v>51</v>
       </c>
       <c r="C110" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D110" t="s">
+        <v>190</v>
+      </c>
+      <c r="E110" t="s">
         <v>187</v>
       </c>
-      <c r="E110" t="s">
-        <v>87</v>
-      </c>
       <c r="F110" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="G110" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
         <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
         <v>51</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D111" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E111" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F111" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="G111" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="H111" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B112" t="s">
         <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="E112" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="F112" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G112" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="D113" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E113" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="F113" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="G113" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E114" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="F114" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="G114" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="H114" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I114" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B115" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C115" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D115" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F115" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="G115" t="s">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B116" t="s">
         <v>72</v>
       </c>
       <c r="C116" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D116" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E116" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="F116" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B117" t="s">
         <v>72</v>
       </c>
       <c r="C117" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="D117" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E117" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F117" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="G117" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="H117" t="s">
         <v>18</v>
@@ -4694,202 +4742,202 @@
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B118" t="s">
         <v>72</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D118" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="E118" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F118" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="G118" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H118" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B119" t="s">
         <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D119" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E119" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="F119" t="s">
         <v>135</v>
       </c>
       <c r="G119" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B120" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C120" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D120" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="E120" t="s">
         <v>87</v>
       </c>
       <c r="F120" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G120" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B121" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C121" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D121" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E121" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
       <c r="G121" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C122" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="E122" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F122" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="G122" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="H122" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I122" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C123" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D123" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="E123" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F123" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G123" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B124" t="s">
         <v>86</v>
       </c>
       <c r="C124" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="E124" t="s">
         <v>87</v>
       </c>
       <c r="F124" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s">
         <v>136</v>
       </c>
       <c r="H124" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="I124" t="s">
         <v>26</v>
@@ -4897,57 +4945,57 @@
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B125" t="s">
         <v>86</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="D125" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="E125" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>23</v>
+        <v>170</v>
       </c>
       <c r="G125" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="H125" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B126" t="s">
         <v>86</v>
       </c>
       <c r="C126" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="D126" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="F126" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="G126" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H126" t="s">
-        <v>194</v>
+        <v>18</v>
       </c>
       <c r="I126" t="s">
         <v>26</v>
@@ -4955,115 +5003,115 @@
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B127" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C127" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D127" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F127" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G127" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H127" t="s">
         <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B128" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C128" t="s">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="D128" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E128" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F128" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="G128" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B129" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C129" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="E129" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F129" t="s">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="G129" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="H129" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I129" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B130" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C130" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D130" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="E130" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="F130" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G130" t="s">
         <v>136</v>
       </c>
       <c r="H130" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="I130" t="s">
         <v>26</v>
@@ -5071,28 +5119,28 @@
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B131" t="s">
         <v>93</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E131" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F131" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="G131" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H131" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I131" t="s">
         <v>26</v>
@@ -5100,54 +5148,54 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B132" t="s">
         <v>93</v>
       </c>
       <c r="C132" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D132" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="E132" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="F132" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G132" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C133" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="D133" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="E133" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F133" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="G133" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
@@ -5158,57 +5206,57 @@
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B134" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C134" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="D134" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="E134" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F134" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="G134" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H134" t="s">
         <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B135" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C135" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="E135" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="F135" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I135" t="s">
         <v>26</v>
@@ -5216,25 +5264,25 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B136" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C136" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D136" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="E136" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="F136" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="G136" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H136" t="s">
         <v>18</v>
@@ -5245,54 +5293,54 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B137" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C137" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="D137" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="E137" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="F137" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="G137" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
+        <v>167</v>
+      </c>
+      <c r="B138" t="s">
+        <v>104</v>
+      </c>
+      <c r="C138" t="s">
         <v>199</v>
       </c>
-      <c r="B138" t="s">
-        <v>41</v>
-      </c>
-      <c r="C138" t="s">
-        <v>38</v>
-      </c>
       <c r="D138" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="E138" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F138" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="G138" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H138" t="s">
         <v>18</v>
@@ -5303,54 +5351,54 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B139" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C139" t="s">
         <v>70</v>
       </c>
       <c r="D139" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="E139" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="F139" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="G139" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s">
         <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B140" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C140" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D140" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="E140" t="s">
         <v>87</v>
       </c>
       <c r="F140" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
@@ -5361,115 +5409,115 @@
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B141" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C141" t="s">
-        <v>70</v>
+        <v>206</v>
       </c>
       <c r="D141" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E141" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F141" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="G141" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B142" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C142" t="s">
         <v>38</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="E142" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F142" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G142" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="H142" t="s">
         <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B143" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="C143" t="s">
         <v>70</v>
       </c>
       <c r="D143" t="s">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="E143" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="F143" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G143" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B144" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C144" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E144" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="F144" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G144" t="s">
         <v>136</v>
       </c>
       <c r="H144" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="I144" t="s">
         <v>26</v>
@@ -5477,25 +5525,25 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B145" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C145" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D145" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="E145" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F145" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G145" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
@@ -5506,141 +5554,141 @@
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="C146" t="s">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="D146" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="E146" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="F146" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="G146" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B147" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C147" t="s">
-        <v>202</v>
+        <v>70</v>
       </c>
       <c r="D147" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E147" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c r="G147" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B148" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C148" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D148" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="E148" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="F148" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="G148" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
       </c>
       <c r="I148" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B149" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="C149" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="E149" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F149" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G149" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="H149" t="s">
         <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B150" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D150" t="s">
-        <v>206</v>
+        <v>96</v>
       </c>
       <c r="E150" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F150" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G150" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H150" t="s">
         <v>18</v>
@@ -5651,25 +5699,25 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B151" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C151" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D151" t="s">
-        <v>208</v>
+        <v>96</v>
       </c>
       <c r="E151" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="F151" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G151" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H151" t="s">
         <v>18</v>
@@ -5680,45 +5728,45 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B152" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C152" t="s">
         <v>77</v>
       </c>
       <c r="D152" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="E152" t="s">
         <v>101</v>
       </c>
       <c r="F152" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G152" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="H152" t="s">
         <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B153" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C153" t="s">
         <v>60</v>
       </c>
       <c r="D153" t="s">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="E153" t="s">
         <v>101</v>
@@ -5727,7 +5775,7 @@
         <v>83</v>
       </c>
       <c r="G153" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H153" t="s">
         <v>18</v>
@@ -5738,257 +5786,257 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B154" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C154" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="D154" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E154" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="F154" t="s">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c r="G154" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="H154" t="s">
         <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B155" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C155" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D155" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="F155" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G155" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B156" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C156" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="D156" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="E156" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="G156" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B157" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C157" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D157" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="E157" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="G157" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="H157" t="s">
         <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B158" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C158" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="D158" t="s">
-        <v>206</v>
+        <v>149</v>
       </c>
       <c r="E158" t="s">
-        <v>207</v>
+        <v>36</v>
       </c>
       <c r="F158" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="G158" t="s">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B159" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="C159" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D159" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E159" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="F159" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G159" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C160" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="D160" t="s">
-        <v>66</v>
+        <v>220</v>
       </c>
       <c r="E160" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F160" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="G160" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B161" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C161" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D161" t="s">
+        <v>190</v>
+      </c>
+      <c r="E161" t="s">
         <v>187</v>
       </c>
-      <c r="E161" t="s">
-        <v>101</v>
-      </c>
       <c r="F161" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="G161" t="s">
-        <v>136</v>
+        <v>31</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B162" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D162" t="s">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="E162" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F162" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G162" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
@@ -5999,199 +6047,199 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B163" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C163" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D163" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E163" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F163" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G163" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B164" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C164" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="D164" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="E164" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F164" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="G164" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B165" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C165" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D165" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="E165" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F165" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G165" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="H165" t="s">
         <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B166" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C166" t="s">
-        <v>202</v>
+        <v>60</v>
       </c>
       <c r="D166" t="s">
-        <v>96</v>
+        <v>191</v>
       </c>
       <c r="E166" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="F166" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="G166" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B167" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C167" t="s">
-        <v>209</v>
+        <v>38</v>
       </c>
       <c r="D167" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E167" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="F167" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G167" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="H167" t="s">
         <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B168" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C168" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="D168" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E168" t="s">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="F168" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="G168" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="H168" t="s">
         <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B169" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C169" t="s">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="D169" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
       <c r="E169" t="s">
-        <v>87</v>
+        <v>219</v>
       </c>
       <c r="F169" t="s">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="G169" t="s">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="H169" t="s">
         <v>18</v>
@@ -6202,25 +6250,25 @@
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B170" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C170" t="s">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="D170" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="E170" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="F170" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="G170" t="s">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
@@ -6231,25 +6279,25 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B171" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C171" t="s">
-        <v>209</v>
+        <v>38</v>
       </c>
       <c r="D171" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="E171" t="s">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="F171" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G171" t="s">
-        <v>211</v>
+        <v>59</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
@@ -6260,25 +6308,25 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B172" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C172" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="D172" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="E172" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="F172" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G172" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H172" t="s">
         <v>18</v>
@@ -6289,89 +6337,263 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B173" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C173" t="s">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="D173" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="E173" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F173" t="s">
         <v>100</v>
       </c>
       <c r="G173" t="s">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="H173" t="s">
         <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B174" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C174" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D174" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E174" t="s">
         <v>62</v>
       </c>
       <c r="F174" t="s">
-        <v>213</v>
+        <v>18</v>
       </c>
       <c r="G174" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B175" t="s">
+        <v>104</v>
+      </c>
+      <c r="C175" t="s">
+        <v>38</v>
+      </c>
+      <c r="D175" t="s">
+        <v>66</v>
+      </c>
+      <c r="E175" t="s">
+        <v>87</v>
+      </c>
+      <c r="F175" t="s">
+        <v>58</v>
+      </c>
+      <c r="G175" t="s">
+        <v>178</v>
+      </c>
+      <c r="H175" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="15">
+      <c r="A176" t="s">
+        <v>211</v>
+      </c>
+      <c r="B176" t="s">
+        <v>104</v>
+      </c>
+      <c r="C176" t="s">
+        <v>206</v>
+      </c>
+      <c r="D176" t="s">
+        <v>207</v>
+      </c>
+      <c r="E176" t="s">
+        <v>145</v>
+      </c>
+      <c r="F176" t="s">
+        <v>159</v>
+      </c>
+      <c r="G176" t="s">
+        <v>160</v>
+      </c>
+      <c r="H176" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="15">
+      <c r="A177" t="s">
+        <v>211</v>
+      </c>
+      <c r="B177" t="s">
+        <v>104</v>
+      </c>
+      <c r="C177" t="s">
+        <v>227</v>
+      </c>
+      <c r="D177" t="s">
+        <v>228</v>
+      </c>
+      <c r="E177" t="s">
+        <v>87</v>
+      </c>
+      <c r="F177" t="s">
+        <v>100</v>
+      </c>
+      <c r="G177" t="s">
+        <v>229</v>
+      </c>
+      <c r="H177" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="15">
+      <c r="A178" t="s">
+        <v>211</v>
+      </c>
+      <c r="B178" t="s">
+        <v>113</v>
+      </c>
+      <c r="C178" t="s">
+        <v>199</v>
+      </c>
+      <c r="D178" t="s">
+        <v>230</v>
+      </c>
+      <c r="E178" t="s">
+        <v>62</v>
+      </c>
+      <c r="F178" t="s">
+        <v>18</v>
+      </c>
+      <c r="G178" t="s">
+        <v>197</v>
+      </c>
+      <c r="H178" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="15">
+      <c r="A179" t="s">
+        <v>211</v>
+      </c>
+      <c r="B179" t="s">
+        <v>113</v>
+      </c>
+      <c r="C179" t="s">
+        <v>60</v>
+      </c>
+      <c r="D179" t="s">
+        <v>116</v>
+      </c>
+      <c r="E179" t="s">
+        <v>101</v>
+      </c>
+      <c r="F179" t="s">
+        <v>100</v>
+      </c>
+      <c r="G179" t="s">
+        <v>102</v>
+      </c>
+      <c r="H179" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="15">
+      <c r="A180" t="s">
+        <v>211</v>
+      </c>
+      <c r="B180" t="s">
         <v>117</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C180" t="s">
+        <v>199</v>
+      </c>
+      <c r="D180" t="s">
+        <v>230</v>
+      </c>
+      <c r="E180" t="s">
+        <v>62</v>
+      </c>
+      <c r="F180" t="s">
+        <v>18</v>
+      </c>
+      <c r="G180" t="s">
+        <v>197</v>
+      </c>
+      <c r="H180" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="15">
+      <c r="A181" t="s">
+        <v>211</v>
+      </c>
+      <c r="B181" t="s">
+        <v>117</v>
+      </c>
+      <c r="C181" t="s">
         <v>60</v>
       </c>
-      <c r="D175" t="s">
-        <v>210</v>
-      </c>
-      <c r="E175" t="s">
+      <c r="D181" t="s">
+        <v>228</v>
+      </c>
+      <c r="E181" t="s">
         <v>101</v>
       </c>
-      <c r="F175" t="s">
+      <c r="F181" t="s">
         <v>100</v>
       </c>
-      <c r="G175" t="s">
-        <v>136</v>
-      </c>
-      <c r="H175" t="s">
-        <v>18</v>
-      </c>
-      <c r="I175" t="s">
-        <v>26</v>
+      <c r="G181" t="s">
+        <v>102</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -6382,7 +6604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{00cc960f-ee24-44cd-8580-d47f83727a66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{99993fb3-164c-4a0f-b3f8-aac9cd3736ec}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6402,16 +6624,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6431,13 +6653,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -6460,19 +6682,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G3" t="s">
         <v>136</v>
@@ -6489,16 +6711,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="E4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6518,19 +6740,19 @@
         <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C5" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G5" t="s">
         <v>136</v>
@@ -6547,19 +6769,19 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G6" t="s">
         <v>136</v>
@@ -6576,19 +6798,19 @@
         <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C7" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G7" t="s">
         <v>136</v>
@@ -6602,16 +6824,16 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -6631,22 +6853,22 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="E9" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F9" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G9" t="s">
         <v>136</v>
@@ -6660,19 +6882,19 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="E10" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6689,22 +6911,22 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" t="s">
         <v>239</v>
       </c>
-      <c r="C11" t="s">
-        <v>221</v>
-      </c>
-      <c r="D11" t="s">
-        <v>222</v>
-      </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="G11" t="s">
         <v>136</v>
@@ -6724,7 +6946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0b02628f-28a3-41d1-b08e-c42ecf42add2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{de62a0cd-f96a-4c06-9e53-196ffa59af86}">
   <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6741,13 +6963,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6761,13 +6983,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
@@ -6781,13 +7003,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C3" t="s">
         <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
         <v>76</v>
@@ -6801,13 +7023,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -6821,13 +7043,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E5" t="s">
         <v>46</v>
@@ -6841,13 +7063,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C6" t="s">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -6861,13 +7083,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E7" t="s">
         <v>102</v>
@@ -6881,13 +7103,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E8" t="s">
         <v>143</v>
@@ -6901,13 +7123,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E9" t="s">
         <v>160</v>
@@ -6921,13 +7143,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
@@ -6941,13 +7163,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -6961,16 +7183,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E12" t="s">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -6981,13 +7203,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -7001,13 +7223,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
         <v>46</v>
@@ -7021,16 +7243,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -7041,16 +7263,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7061,13 +7283,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
         <v>112</v>
@@ -7081,13 +7303,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -7101,16 +7323,16 @@
         <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7121,16 +7343,16 @@
         <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C20" t="s">
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7141,16 +7363,16 @@
         <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C21" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="D21" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E21" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -7161,13 +7383,13 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C22" t="s">
         <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -7181,13 +7403,13 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C23" t="s">
         <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E23" t="s">
         <v>56</v>
@@ -7201,13 +7423,13 @@
         <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E24" t="s">
         <v>52</v>
@@ -7221,13 +7443,13 @@
         <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="D25" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E25" t="s">
         <v>164</v>
@@ -7241,13 +7463,13 @@
         <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D26" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E26" t="s">
         <v>102</v>
@@ -7261,13 +7483,13 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E27" t="s">
         <v>56</v>
@@ -7281,13 +7503,13 @@
         <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C28" t="s">
         <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
         <v>158</v>
@@ -7301,13 +7523,13 @@
         <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>274</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E29" t="s">
         <v>164</v>
@@ -7321,13 +7543,13 @@
         <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C30" t="s">
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E30" t="s">
         <v>98</v>
@@ -7341,13 +7563,13 @@
         <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C31" t="s">
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
@@ -7361,16 +7583,16 @@
         <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E32" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7381,13 +7603,13 @@
         <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -7398,16 +7620,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E34" t="s">
         <v>26</v>
@@ -7418,16 +7640,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
@@ -7438,16 +7660,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
         <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
         <v>26</v>
@@ -7458,16 +7680,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C37" t="s">
         <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -7478,16 +7700,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C38" t="s">
         <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -7498,16 +7720,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C39" t="s">
         <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E39" t="s">
         <v>26</v>
@@ -7518,16 +7740,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C40" t="s">
         <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E40" t="s">
         <v>26</v>
@@ -7538,16 +7760,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E41" t="s">
         <v>26</v>
@@ -7558,16 +7780,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D42" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E42" t="s">
         <v>26</v>
@@ -7578,16 +7800,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C43" t="s">
         <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -7598,16 +7820,16 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
         <v>26</v>
@@ -7618,16 +7840,16 @@
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C45" t="s">
         <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
@@ -7638,16 +7860,16 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B46" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C46" t="s">
         <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
@@ -7658,16 +7880,16 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B47" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C47" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E47" t="s">
         <v>26</v>
@@ -7678,16 +7900,16 @@
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B48" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
         <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E48" t="s">
         <v>26</v>
@@ -7698,16 +7920,16 @@
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D49" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E49" t="s">
         <v>26</v>
@@ -7718,16 +7940,16 @@
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C50" t="s">
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s">
         <v>26</v>
@@ -7738,16 +7960,16 @@
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D51" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
@@ -7758,16 +7980,16 @@
     </row>
     <row r="52" spans="1:6" ht="15">
       <c r="A52" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C52" t="s">
         <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E52" t="s">
         <v>26</v>
@@ -7778,16 +8000,16 @@
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B53" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C53" t="s">
         <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E53" t="s">
         <v>26</v>
@@ -7798,16 +8020,16 @@
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B54" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C54" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D54" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
@@ -7818,16 +8040,16 @@
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C55" t="s">
         <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E55" t="s">
         <v>26</v>
@@ -7838,16 +8060,16 @@
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C56" t="s">
         <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
         <v>26</v>
@@ -7858,16 +8080,16 @@
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B57" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C57" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D57" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="E57" t="s">
         <v>26</v>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="306">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -474,6 +474,18 @@
     <t>1FB</t>
   </si>
   <si>
+    <t>Filusz Marzena</t>
+  </si>
+  <si>
+    <t>3TFB</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>p. Biczysko, fizyka</t>
+  </si>
+  <si>
     <t>4TH|CH</t>
   </si>
   <si>
@@ -486,6 +498,12 @@
     <t>1CA|JA1</t>
   </si>
   <si>
+    <t>3TFA</t>
+  </si>
+  <si>
+    <t>bib2</t>
+  </si>
+  <si>
     <t>1TFA</t>
   </si>
   <si>
@@ -501,9 +519,6 @@
     <t>Mikołajczak Sylwia</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>Fiodorów Małgorzata</t>
   </si>
   <si>
@@ -558,7 +573,7 @@
     <t>2WA|edu</t>
   </si>
   <si>
-    <t>Filusz Marzena</t>
+    <t>p. Misiąg, j. niemiecki z 25.05.2026</t>
   </si>
   <si>
     <t>Obsługa klienta</t>
@@ -573,6 +588,9 @@
     <t>1FC</t>
   </si>
   <si>
+    <t>Rozwój kompetencji zawodowych - matematyka w działalności gospodarczej</t>
+  </si>
+  <si>
     <t>1FA</t>
   </si>
   <si>
@@ -594,9 +612,6 @@
     <t>Marketing w działalności handlowej</t>
   </si>
   <si>
-    <t>3TFA</t>
-  </si>
-  <si>
     <t>2CA</t>
   </si>
   <si>
@@ -615,6 +630,18 @@
     <t>Wójcik Kamil</t>
   </si>
   <si>
+    <t>4TFB|CH</t>
+  </si>
+  <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
+    <t>4TFB|dz1</t>
+  </si>
+  <si>
+    <t>4TFB|dz2</t>
+  </si>
+  <si>
     <t>Pietrycha Małgorzata</t>
   </si>
   <si>
@@ -630,15 +657,15 @@
     <t>sg3</t>
   </si>
   <si>
-    <t>3TFB</t>
-  </si>
-  <si>
     <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
   </si>
   <si>
     <t>2WA</t>
   </si>
   <si>
+    <t>p. Wojciechowski, j. angielski za lekcję 8</t>
+  </si>
+  <si>
     <t>3TFB|JA1</t>
   </si>
   <si>
@@ -651,6 +678,18 @@
     <t>28.05.2026</t>
   </si>
   <si>
+    <t>sg6</t>
+  </si>
+  <si>
+    <t>przygotowania Konkurs im. Cierplikowskiego</t>
+  </si>
+  <si>
+    <t>Dalach Krystyna</t>
+  </si>
+  <si>
+    <t>sg1</t>
+  </si>
+  <si>
     <t>p. Hudziec, chemia za lekcję 7</t>
   </si>
   <si>
@@ -660,6 +699,18 @@
     <t>29.05.2026</t>
   </si>
   <si>
+    <t>3TFB|JA2</t>
+  </si>
+  <si>
+    <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Jaworska Edyta</t>
+  </si>
+  <si>
     <t>Świerzewicz Katarzyna</t>
   </si>
   <si>
@@ -669,6 +720,12 @@
     <t>42</t>
   </si>
   <si>
+    <t>2TFB|DZ</t>
+  </si>
+  <si>
+    <t>2TH|DZ</t>
+  </si>
+  <si>
     <t>Danielewski Paweł</t>
   </si>
   <si>
@@ -687,18 +744,21 @@
     <t>1CB|JA1</t>
   </si>
   <si>
+    <t>Podstawy fryzjerstwa</t>
+  </si>
+  <si>
     <t>Kruk Marcin</t>
   </si>
   <si>
+    <t>1CB|JA2</t>
+  </si>
+  <si>
     <t>1FC|JA2</t>
   </si>
   <si>
     <t>Edukacja dla bezpieczeństwa</t>
   </si>
   <si>
-    <t>Płatek Krzysztof</t>
-  </si>
-  <si>
     <t>1FC|JA1</t>
   </si>
   <si>
@@ -717,6 +777,9 @@
     <t>2FB|CH</t>
   </si>
   <si>
+    <t>sg2</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -792,9 +855,27 @@
     <t>zajęcia socjoterapeutyczne</t>
   </si>
   <si>
+    <t>14:15-15:00</t>
+  </si>
+  <si>
+    <t>Mateusz Wisiński - 1TH - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>matematyka</t>
+  </si>
+  <si>
     <t>15:05-16:00</t>
   </si>
   <si>
+    <t>12:25-15:40</t>
+  </si>
+  <si>
+    <t>Projektowanie fryzur- cztery godziny co piatek od 20.02.2026r.</t>
+  </si>
+  <si>
+    <t>15:45-16:30</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -847,9 +928,6 @@
   </si>
   <si>
     <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>Jaworska Edyta</t>
   </si>
   <si>
     <t>Marzec Renata</t>
@@ -1311,7 +1389,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{cb10051d-bf4d-4863-9db9-038ba902a32d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd768827-b297-44e9-8255-181f3892200f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1332,15 +1410,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{7c7c1aca-f1b4-473f-8866-25922a6bc57b}">
-  <dimension ref="A1:I181"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{49eacd9a-69b0-4d6e-b67e-24622ac054db}">
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="14.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="25.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="10.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="56.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="68.4285714285714" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="28.1428571428571" customWidth="1"/>
     <col min="8" max="8" width="56.1428571428571" customWidth="1"/>
@@ -3327,25 +3405,25 @@
         <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D69" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E69" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="G69" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="H69" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15">
@@ -3359,7 +3437,7 @@
         <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E70" t="s">
         <v>62</v>
@@ -3368,13 +3446,13 @@
         <v>37</v>
       </c>
       <c r="G70" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H70" t="s">
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15">
@@ -3385,25 +3463,25 @@
         <v>72</v>
       </c>
       <c r="C71" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E71" t="s">
-        <v>145</v>
+        <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G71" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="H71" t="s">
         <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15">
@@ -3414,25 +3492,25 @@
         <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E72" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="F72" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="G72" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s">
         <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15">
@@ -3446,7 +3524,7 @@
         <v>70</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="E73" t="s">
         <v>54</v>
@@ -3461,7 +3539,7 @@
         <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15">
@@ -3469,28 +3547,28 @@
         <v>121</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D74" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="E74" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F74" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G74" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="H74" t="s">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15">
@@ -3501,19 +3579,19 @@
         <v>86</v>
       </c>
       <c r="C75" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="G75" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
         <v>18</v>
@@ -3530,22 +3608,22 @@
         <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E76" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F76" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="G76" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="H76" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="I76" t="s">
         <v>26</v>
@@ -3559,25 +3637,25 @@
         <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="E77" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="F77" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H77" t="s">
         <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15">
@@ -3585,28 +3663,28 @@
         <v>121</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -3614,22 +3692,22 @@
         <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F79" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="G79" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="H79" t="s">
         <v>18</v>
@@ -3646,25 +3724,25 @@
         <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="E80" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>158</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
         <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15">
@@ -3672,22 +3750,22 @@
         <v>121</v>
       </c>
       <c r="B81" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="E81" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F81" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="G81" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="H81" t="s">
         <v>18</v>
@@ -3701,28 +3779,28 @@
         <v>121</v>
       </c>
       <c r="B82" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F82" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="G82" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="H82" t="s">
         <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15">
@@ -3733,25 +3811,25 @@
         <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G83" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="H83" t="s">
         <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15">
@@ -3762,25 +3840,25 @@
         <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D84" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="E84" t="s">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="F84" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G84" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15">
@@ -3788,28 +3866,28 @@
         <v>121</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
         <v>38</v>
       </c>
       <c r="D85" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="E85" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
         <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15">
@@ -3817,51 +3895,51 @@
         <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C86" t="s">
         <v>70</v>
       </c>
       <c r="D86" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="F86" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G86" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H86" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E87" t="s">
         <v>87</v>
       </c>
       <c r="F87" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G87" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s">
         <v>18</v>
@@ -3872,28 +3950,28 @@
     </row>
     <row r="88" spans="1:9" ht="15">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E88" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="F88" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="G88" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="H88" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="I88" t="s">
         <v>26</v>
@@ -3901,22 +3979,22 @@
     </row>
     <row r="89" spans="1:9" ht="15">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F89" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s">
         <v>24</v>
@@ -3930,28 +4008,28 @@
     </row>
     <row r="90" spans="1:9" ht="15">
       <c r="A90" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="D90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F90" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="G90" t="s">
         <v>24</v>
       </c>
       <c r="H90" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I90" t="s">
         <v>26</v>
@@ -3959,65 +4037,65 @@
     </row>
     <row r="91" spans="1:9" ht="15">
       <c r="A91" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="D91" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E91" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G91" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="H91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15">
       <c r="A92" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="G92" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15">
       <c r="A93" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
@@ -4026,7 +4104,7 @@
         <v>122</v>
       </c>
       <c r="D93" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E93" t="s">
         <v>124</v>
@@ -4046,7 +4124,7 @@
     </row>
     <row r="94" spans="1:9" ht="15">
       <c r="A94" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
@@ -4055,7 +4133,7 @@
         <v>122</v>
       </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E94" t="s">
         <v>124</v>
@@ -4075,25 +4153,25 @@
     </row>
     <row r="95" spans="1:9" ht="15">
       <c r="A95" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="D95" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="E95" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="F95" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G95" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="H95" t="s">
         <v>18</v>
@@ -4104,115 +4182,115 @@
     </row>
     <row r="96" spans="1:9" ht="15">
       <c r="A96" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="D96" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="E96" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="G96" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="H96" t="s">
         <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15">
       <c r="A97" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B97" t="s">
         <v>33</v>
       </c>
       <c r="C97" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="E97" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F97" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G97" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15">
       <c r="A98" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B98" t="s">
         <v>33</v>
       </c>
       <c r="C98" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="D98" t="s">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="E98" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F98" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G98" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="H98" t="s">
         <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15">
       <c r="A99" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B99" t="s">
         <v>33</v>
       </c>
       <c r="C99" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="D99" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="F99" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
         <v>26</v>
@@ -4220,28 +4298,28 @@
     </row>
     <row r="100" spans="1:9" ht="15">
       <c r="A100" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B100" t="s">
         <v>33</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D100" t="s">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="E100" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="G100" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="I100" t="s">
         <v>26</v>
@@ -4249,170 +4327,170 @@
     </row>
     <row r="101" spans="1:9" ht="15">
       <c r="A101" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s">
         <v>33</v>
       </c>
       <c r="C101" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>50</v>
       </c>
       <c r="E101" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F101" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G101" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="H101" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15">
       <c r="A102" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B102" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="E102" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="F102" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="G102" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I102" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15">
       <c r="A103" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B103" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="D103" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="E103" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H103" t="s">
         <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15">
       <c r="A104" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B104" t="s">
         <v>41</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D104" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="E104" t="s">
         <v>101</v>
       </c>
       <c r="F104" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G104" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H104" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15">
       <c r="A105" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B105" t="s">
         <v>41</v>
       </c>
       <c r="C105" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="D105" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="E105" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F105" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G105" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H105" t="s">
         <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B106" t="s">
         <v>41</v>
       </c>
       <c r="C106" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D106" t="s">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="E106" t="s">
-        <v>54</v>
+        <v>188</v>
       </c>
       <c r="F106" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H106" t="s">
         <v>18</v>
@@ -4423,28 +4501,28 @@
     </row>
     <row r="107" spans="1:9" ht="15">
       <c r="A107" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
         <v>41</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E107" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F107" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="G107" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="H107" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="I107" t="s">
         <v>26</v>
@@ -4452,25 +4530,25 @@
     </row>
     <row r="108" spans="1:9" ht="15">
       <c r="A108" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B108" t="s">
         <v>41</v>
       </c>
       <c r="C108" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="E108" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="F108" t="s">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="G108" t="s">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="H108" t="s">
         <v>18</v>
@@ -4481,25 +4559,25 @@
     </row>
     <row r="109" spans="1:9" ht="15">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B109" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C109" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="D109" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="E109" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="F109" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G109" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H109" t="s">
         <v>18</v>
@@ -4510,54 +4588,54 @@
     </row>
     <row r="110" spans="1:9" ht="15">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B110" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C110" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E110" t="s">
-        <v>187</v>
+        <v>22</v>
       </c>
       <c r="F110" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G110" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H110" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B111" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C111" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D111" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="E111" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="F111" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="G111" t="s">
-        <v>52</v>
+        <v>194</v>
       </c>
       <c r="H111" t="s">
         <v>18</v>
@@ -4568,199 +4646,199 @@
     </row>
     <row r="112" spans="1:9" ht="15">
       <c r="A112" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B112" t="s">
         <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D112" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="F112" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="H112" t="s">
         <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B113" t="s">
         <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="D113" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="E113" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="F113" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="H113" t="s">
         <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15">
       <c r="A114" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B114" t="s">
         <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D114" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="E114" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F114" t="s">
-        <v>194</v>
+        <v>115</v>
       </c>
       <c r="G114" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15">
       <c r="A115" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B115" t="s">
         <v>51</v>
       </c>
       <c r="C115" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="G115" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="H115" t="s">
         <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
       <c r="A116" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B116" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="D116" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="E116" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="F116" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="G116" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="H116" t="s">
         <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15">
       <c r="A117" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B117" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C117" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E117" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="F117" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G117" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="H117" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I117" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C118" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D118" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F118" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="G118" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="H118" t="s">
         <v>18</v>
@@ -4771,25 +4849,25 @@
     </row>
     <row r="119" spans="1:9" ht="15">
       <c r="A119" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B119" t="s">
         <v>72</v>
       </c>
       <c r="C119" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D119" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="E119" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="F119" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="G119" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H119" t="s">
         <v>18</v>
@@ -4800,25 +4878,25 @@
     </row>
     <row r="120" spans="1:9" ht="15">
       <c r="A120" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B120" t="s">
         <v>72</v>
       </c>
       <c r="C120" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="D120" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E120" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F120" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G120" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4829,312 +4907,312 @@
     </row>
     <row r="121" spans="1:9" ht="15">
       <c r="A121" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B121" t="s">
         <v>72</v>
       </c>
       <c r="C121" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="D121" t="s">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="E121" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="F121" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="H121" t="s">
         <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15">
       <c r="A122" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B122" t="s">
         <v>72</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D122" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E122" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="F122" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G122" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="H122" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15">
       <c r="A123" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B123" t="s">
         <v>72</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D123" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="E123" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F123" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G123" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15">
       <c r="A124" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="E124" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F124" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G124" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="H124" t="s">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15">
       <c r="A125" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B125" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C125" t="s">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="D125" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E125" t="s">
         <v>62</v>
       </c>
       <c r="F125" t="s">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="G125" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15">
       <c r="A126" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B126" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C126" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="D126" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E126" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>201</v>
+        <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
         <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15">
       <c r="A127" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B127" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="E127" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="F127" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G127" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="H127" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I127" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15">
       <c r="A128" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C128" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D128" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="E128" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F128" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="G128" t="s">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="H128" t="s">
         <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
       <c r="A129" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B129" t="s">
         <v>86</v>
       </c>
       <c r="C129" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D129" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="E129" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F129" t="s">
         <v>79</v>
       </c>
       <c r="G129" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="H129" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="I129" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
       <c r="A130" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B130" t="s">
         <v>86</v>
       </c>
       <c r="C130" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
       <c r="D130" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E130" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="G130" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="H130" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
       <c r="A131" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B131" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C131" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="D131" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E131" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F131" t="s">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="G131" t="s">
         <v>88</v>
@@ -5148,25 +5226,25 @@
     </row>
     <row r="132" spans="1:9" ht="15">
       <c r="A132" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B132" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C132" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="D132" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="E132" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F132" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="G132" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5177,57 +5255,57 @@
     </row>
     <row r="133" spans="1:9" ht="15">
       <c r="A133" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B133" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C133" t="s">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E133" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F133" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="G133" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s">
         <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15">
       <c r="A134" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B134" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C134" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="E134" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="F134" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="H134" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I134" t="s">
         <v>32</v>
@@ -5235,28 +5313,28 @@
     </row>
     <row r="135" spans="1:9" ht="15">
       <c r="A135" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B135" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="E135" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="F135" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="G135" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="H135" t="s">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="I135" t="s">
         <v>26</v>
@@ -5264,22 +5342,22 @@
     </row>
     <row r="136" spans="1:9" ht="15">
       <c r="A136" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B136" t="s">
         <v>93</v>
       </c>
       <c r="C136" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D136" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="E136" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="F136" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="G136" t="s">
         <v>88</v>
@@ -5293,51 +5371,51 @@
     </row>
     <row r="137" spans="1:9" ht="15">
       <c r="A137" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B137" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C137" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="D137" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="E137" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F137" t="s">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="G137" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15">
       <c r="A138" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B138" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D138" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="E138" t="s">
         <v>62</v>
       </c>
       <c r="F138" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G138" t="s">
         <v>88</v>
@@ -5351,83 +5429,83 @@
     </row>
     <row r="139" spans="1:9" ht="15">
       <c r="A139" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B139" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C139" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="D139" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="E139" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F139" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="G139" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="H139" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="I139" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15">
       <c r="A140" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B140" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C140" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="D140" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E140" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F140" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="G140" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H140" t="s">
         <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15">
       <c r="A141" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B141" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C141" t="s">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="D141" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="E141" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="F141" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="G141" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="H141" t="s">
         <v>18</v>
@@ -5438,86 +5516,86 @@
     </row>
     <row r="142" spans="1:9" ht="15">
       <c r="A142" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B142" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C142" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="E142" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F142" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G142" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H142" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I142" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15">
       <c r="A143" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B143" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C143" t="s">
         <v>70</v>
       </c>
       <c r="D143" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="E143" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F143" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G143" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H143" t="s">
         <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15">
       <c r="A144" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B144" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C144" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D144" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E144" t="s">
         <v>87</v>
       </c>
       <c r="F144" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G144" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H144" t="s">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
         <v>26</v>
@@ -5525,54 +5603,54 @@
     </row>
     <row r="145" spans="1:9" ht="15">
       <c r="A145" t="s">
+        <v>172</v>
+      </c>
+      <c r="B145" t="s">
+        <v>104</v>
+      </c>
+      <c r="C145" t="s">
         <v>208</v>
       </c>
-      <c r="B145" t="s">
-        <v>72</v>
-      </c>
-      <c r="C145" t="s">
-        <v>70</v>
-      </c>
       <c r="D145" t="s">
+        <v>209</v>
+      </c>
+      <c r="E145" t="s">
+        <v>62</v>
+      </c>
+      <c r="F145" t="s">
         <v>210</v>
       </c>
-      <c r="E145" t="s">
-        <v>111</v>
-      </c>
-      <c r="F145" t="s">
-        <v>135</v>
-      </c>
       <c r="G145" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="H145" t="s">
         <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15">
       <c r="A146" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B146" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C146" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="E146" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F146" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="G146" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
@@ -5583,54 +5661,54 @@
     </row>
     <row r="147" spans="1:9" ht="15">
       <c r="A147" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B147" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C147" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D147" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F147" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G147" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H147" t="s">
         <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15">
       <c r="A148" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="B148" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C148" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="D148" t="s">
-        <v>66</v>
+        <v>216</v>
       </c>
       <c r="E148" t="s">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="F148" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="G148" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="H148" t="s">
         <v>18</v>
@@ -5641,57 +5719,57 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B149" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="E149" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F149" t="s">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="G149" t="s">
-        <v>178</v>
+        <v>24</v>
       </c>
       <c r="H149" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I149" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B150" t="s">
         <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D150" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="E150" t="s">
-        <v>213</v>
+        <v>62</v>
       </c>
       <c r="F150" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G150" t="s">
         <v>24</v>
       </c>
       <c r="H150" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I150" t="s">
         <v>26</v>
@@ -5699,28 +5777,28 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B151" t="s">
         <v>33</v>
       </c>
       <c r="C151" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="D151" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="E151" t="s">
-        <v>213</v>
+        <v>62</v>
       </c>
       <c r="F151" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G151" t="s">
         <v>24</v>
       </c>
       <c r="H151" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I151" t="s">
         <v>26</v>
@@ -5728,57 +5806,57 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B152" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C152" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="D152" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="E152" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F152" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="G152" t="s">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="H152" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I152" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B153" t="s">
         <v>41</v>
       </c>
       <c r="C153" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="D153" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E153" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F153" t="s">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="G153" t="s">
         <v>24</v>
       </c>
       <c r="H153" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I153" t="s">
         <v>26</v>
@@ -5786,141 +5864,141 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B154" t="s">
         <v>41</v>
       </c>
       <c r="C154" t="s">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="D154" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
       <c r="E154" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F154" t="s">
-        <v>16</v>
+        <v>221</v>
       </c>
       <c r="G154" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H154" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I154" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B155" t="s">
         <v>41</v>
       </c>
       <c r="C155" t="s">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="D155" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="E155" t="s">
-        <v>219</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>214</v>
+        <v>16</v>
       </c>
       <c r="G155" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B156" t="s">
         <v>51</v>
       </c>
       <c r="C156" t="s">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="D156" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="H156" t="s">
         <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B157" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C157" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="D157" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="E157" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F157" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G157" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="H157" t="s">
-        <v>18</v>
+        <v>222</v>
       </c>
       <c r="I157" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B158" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C158" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D158" t="s">
-        <v>149</v>
+        <v>223</v>
       </c>
       <c r="E158" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="F158" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="G158" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
@@ -5931,25 +6009,25 @@
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B159" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C159" t="s">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="D159" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="E159" t="s">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="F159" t="s">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="G159" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H159" t="s">
         <v>18</v>
@@ -5960,54 +6038,54 @@
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B160" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C160" t="s">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="E160" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F160" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G160" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B161" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C161" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D161" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="E161" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="F161" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="G161" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="H161" t="s">
         <v>18</v>
@@ -6018,54 +6096,54 @@
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B162" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C162" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D162" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="E162" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="F162" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="G162" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="H162" t="s">
         <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B163" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C163" t="s">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="D163" t="s">
-        <v>218</v>
+        <v>151</v>
       </c>
       <c r="E163" t="s">
-        <v>219</v>
+        <v>111</v>
       </c>
       <c r="F163" t="s">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="G163" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
@@ -6076,231 +6154,231 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B164" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C164" t="s">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="D164" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="E164" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F164" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G164" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B165" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D165" t="s">
-        <v>66</v>
+        <v>225</v>
       </c>
       <c r="E165" t="s">
-        <v>111</v>
+        <v>226</v>
       </c>
       <c r="F165" t="s">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="G165" t="s">
-        <v>49</v>
+        <v>228</v>
       </c>
       <c r="H165" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I165" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B166" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="C166" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="D166" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="E166" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="F166" t="s">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="G166" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B167" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C167" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D167" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E167" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="F167" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G167" t="s">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="H167" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I167" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B168" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C168" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D168" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E168" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="F168" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G168" t="s">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="H168" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B169" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C169" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="D169" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E169" t="s">
+        <v>226</v>
+      </c>
+      <c r="F169" t="s">
+        <v>227</v>
+      </c>
+      <c r="G169" t="s">
+        <v>228</v>
+      </c>
+      <c r="H169" t="s">
         <v>219</v>
       </c>
-      <c r="F169" t="s">
-        <v>214</v>
-      </c>
-      <c r="G169" t="s">
-        <v>59</v>
-      </c>
-      <c r="H169" t="s">
-        <v>18</v>
-      </c>
       <c r="I169" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B170" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C170" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="D170" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="E170" t="s">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="F170" t="s">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="H170" t="s">
         <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B171" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C171" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D171" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="E171" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="F171" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="G171" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H171" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I171" t="s">
         <v>32</v>
@@ -6308,83 +6386,83 @@
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B172" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C172" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="D172" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="E172" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="F172" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="G172" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="H172" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I172" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B173" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C173" t="s">
+        <v>112</v>
+      </c>
+      <c r="D173" t="s">
+        <v>225</v>
+      </c>
+      <c r="E173" t="s">
+        <v>226</v>
+      </c>
+      <c r="F173" t="s">
         <v>227</v>
       </c>
-      <c r="D173" t="s">
+      <c r="G173" t="s">
         <v>228</v>
       </c>
-      <c r="E173" t="s">
-        <v>87</v>
-      </c>
-      <c r="F173" t="s">
-        <v>100</v>
-      </c>
-      <c r="G173" t="s">
-        <v>229</v>
-      </c>
       <c r="H173" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I173" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B174" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C174" t="s">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="D174" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="E174" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F174" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G174" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="H174" t="s">
         <v>18</v>
@@ -6395,28 +6473,28 @@
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B175" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C175" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="D175" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E175" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F175" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="G175" t="s">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="H175" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I175" t="s">
         <v>32</v>
@@ -6424,83 +6502,83 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B176" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C176" t="s">
-        <v>206</v>
+        <v>60</v>
       </c>
       <c r="D176" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="E176" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="F176" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="G176" t="s">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B177" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C177" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="D177" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E177" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F177" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G177" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
       </c>
       <c r="I177" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B178" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="C178" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D178" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E178" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
       <c r="F178" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="G178" t="s">
-        <v>197</v>
+        <v>59</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
@@ -6511,28 +6589,28 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B179" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C179" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="D179" t="s">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="E179" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F179" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="G179" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="H179" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I179" t="s">
         <v>32</v>
@@ -6540,28 +6618,28 @@
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B180" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="C180" t="s">
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="D180" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E180" t="s">
         <v>62</v>
       </c>
       <c r="F180" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="G180" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="H180" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="I180" t="s">
         <v>32</v>
@@ -6569,30 +6647,1306 @@
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B181" t="s">
+        <v>51</v>
+      </c>
+      <c r="C181" t="s">
+        <v>208</v>
+      </c>
+      <c r="D181" t="s">
+        <v>239</v>
+      </c>
+      <c r="E181" t="s">
+        <v>62</v>
+      </c>
+      <c r="F181" t="s">
+        <v>210</v>
+      </c>
+      <c r="G181" t="s">
+        <v>155</v>
+      </c>
+      <c r="H181" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="15">
+      <c r="A182" t="s">
+        <v>224</v>
+      </c>
+      <c r="B182" t="s">
+        <v>51</v>
+      </c>
+      <c r="C182" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" t="s">
+        <v>225</v>
+      </c>
+      <c r="E182" t="s">
+        <v>226</v>
+      </c>
+      <c r="F182" t="s">
+        <v>227</v>
+      </c>
+      <c r="G182" t="s">
+        <v>228</v>
+      </c>
+      <c r="H182" t="s">
+        <v>219</v>
+      </c>
+      <c r="I182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="15">
+      <c r="A183" t="s">
+        <v>224</v>
+      </c>
+      <c r="B183" t="s">
+        <v>51</v>
+      </c>
+      <c r="C183" t="s">
+        <v>77</v>
+      </c>
+      <c r="D183" t="s">
+        <v>158</v>
+      </c>
+      <c r="E183" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" t="s">
+        <v>17</v>
+      </c>
+      <c r="H183" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="15">
+      <c r="A184" t="s">
+        <v>224</v>
+      </c>
+      <c r="B184" t="s">
+        <v>51</v>
+      </c>
+      <c r="C184" t="s">
+        <v>164</v>
+      </c>
+      <c r="D184" t="s">
+        <v>116</v>
+      </c>
+      <c r="E184" t="s">
+        <v>240</v>
+      </c>
+      <c r="F184" t="s">
+        <v>163</v>
+      </c>
+      <c r="G184" t="s">
+        <v>24</v>
+      </c>
+      <c r="H184" t="s">
+        <v>219</v>
+      </c>
+      <c r="I184" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="15">
+      <c r="A185" t="s">
+        <v>224</v>
+      </c>
+      <c r="B185" t="s">
+        <v>51</v>
+      </c>
+      <c r="C185" t="s">
+        <v>60</v>
+      </c>
+      <c r="D185" t="s">
+        <v>149</v>
+      </c>
+      <c r="E185" t="s">
+        <v>36</v>
+      </c>
+      <c r="F185" t="s">
+        <v>152</v>
+      </c>
+      <c r="G185" t="s">
+        <v>241</v>
+      </c>
+      <c r="H185" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="15">
+      <c r="A186" t="s">
+        <v>224</v>
+      </c>
+      <c r="B186" t="s">
+        <v>51</v>
+      </c>
+      <c r="C186" t="s">
+        <v>229</v>
+      </c>
+      <c r="D186" t="s">
+        <v>237</v>
+      </c>
+      <c r="E186" t="s">
+        <v>238</v>
+      </c>
+      <c r="F186" t="s">
+        <v>231</v>
+      </c>
+      <c r="G186" t="s">
+        <v>59</v>
+      </c>
+      <c r="H186" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="15">
+      <c r="A187" t="s">
+        <v>224</v>
+      </c>
+      <c r="B187" t="s">
+        <v>72</v>
+      </c>
+      <c r="C187" t="s">
+        <v>131</v>
+      </c>
+      <c r="D187" t="s">
+        <v>242</v>
+      </c>
+      <c r="E187" t="s">
+        <v>62</v>
+      </c>
+      <c r="F187" t="s">
+        <v>175</v>
+      </c>
+      <c r="G187" t="s">
+        <v>136</v>
+      </c>
+      <c r="H187" t="s">
+        <v>219</v>
+      </c>
+      <c r="I187" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="15">
+      <c r="A188" t="s">
+        <v>224</v>
+      </c>
+      <c r="B188" t="s">
+        <v>72</v>
+      </c>
+      <c r="C188" t="s">
+        <v>220</v>
+      </c>
+      <c r="D188" t="s">
+        <v>186</v>
+      </c>
+      <c r="E188" t="s">
+        <v>62</v>
+      </c>
+      <c r="F188" t="s">
+        <v>221</v>
+      </c>
+      <c r="G188" t="s">
+        <v>64</v>
+      </c>
+      <c r="H188" t="s">
+        <v>219</v>
+      </c>
+      <c r="I188" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="15">
+      <c r="A189" t="s">
+        <v>224</v>
+      </c>
+      <c r="B189" t="s">
+        <v>72</v>
+      </c>
+      <c r="C189" t="s">
+        <v>208</v>
+      </c>
+      <c r="D189" t="s">
+        <v>239</v>
+      </c>
+      <c r="E189" t="s">
+        <v>62</v>
+      </c>
+      <c r="F189" t="s">
+        <v>210</v>
+      </c>
+      <c r="G189" t="s">
+        <v>155</v>
+      </c>
+      <c r="H189" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="15">
+      <c r="A190" t="s">
+        <v>224</v>
+      </c>
+      <c r="B190" t="s">
+        <v>72</v>
+      </c>
+      <c r="C190" t="s">
+        <v>112</v>
+      </c>
+      <c r="D190" t="s">
+        <v>225</v>
+      </c>
+      <c r="E190" t="s">
+        <v>226</v>
+      </c>
+      <c r="F190" t="s">
+        <v>227</v>
+      </c>
+      <c r="G190" t="s">
+        <v>228</v>
+      </c>
+      <c r="H190" t="s">
+        <v>219</v>
+      </c>
+      <c r="I190" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="15">
+      <c r="A191" t="s">
+        <v>224</v>
+      </c>
+      <c r="B191" t="s">
+        <v>72</v>
+      </c>
+      <c r="C191" t="s">
+        <v>77</v>
+      </c>
+      <c r="D191" t="s">
+        <v>158</v>
+      </c>
+      <c r="E191" t="s">
+        <v>193</v>
+      </c>
+      <c r="F191" t="s">
+        <v>30</v>
+      </c>
+      <c r="G191" t="s">
+        <v>31</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="15">
+      <c r="A192" t="s">
+        <v>224</v>
+      </c>
+      <c r="B192" t="s">
+        <v>72</v>
+      </c>
+      <c r="C192" t="s">
+        <v>164</v>
+      </c>
+      <c r="D192" t="s">
+        <v>170</v>
+      </c>
+      <c r="E192" t="s">
+        <v>82</v>
+      </c>
+      <c r="F192" t="s">
+        <v>79</v>
+      </c>
+      <c r="G192" t="s">
+        <v>107</v>
+      </c>
+      <c r="H192" t="s">
+        <v>219</v>
+      </c>
+      <c r="I192" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15">
+      <c r="A193" t="s">
+        <v>224</v>
+      </c>
+      <c r="B193" t="s">
+        <v>72</v>
+      </c>
+      <c r="C193" t="s">
+        <v>60</v>
+      </c>
+      <c r="D193" t="s">
+        <v>118</v>
+      </c>
+      <c r="E193" t="s">
+        <v>101</v>
+      </c>
+      <c r="F193" t="s">
+        <v>83</v>
+      </c>
+      <c r="G193" t="s">
+        <v>88</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15">
+      <c r="A194" t="s">
+        <v>224</v>
+      </c>
+      <c r="B194" t="s">
+        <v>72</v>
+      </c>
+      <c r="C194" t="s">
+        <v>229</v>
+      </c>
+      <c r="D194" t="s">
+        <v>237</v>
+      </c>
+      <c r="E194" t="s">
+        <v>238</v>
+      </c>
+      <c r="F194" t="s">
+        <v>231</v>
+      </c>
+      <c r="G194" t="s">
+        <v>59</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15">
+      <c r="A195" t="s">
+        <v>224</v>
+      </c>
+      <c r="B195" t="s">
+        <v>86</v>
+      </c>
+      <c r="C195" t="s">
+        <v>131</v>
+      </c>
+      <c r="D195" t="s">
+        <v>242</v>
+      </c>
+      <c r="E195" t="s">
+        <v>62</v>
+      </c>
+      <c r="F195" t="s">
+        <v>175</v>
+      </c>
+      <c r="G195" t="s">
+        <v>136</v>
+      </c>
+      <c r="H195" t="s">
+        <v>219</v>
+      </c>
+      <c r="I195" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15">
+      <c r="A196" t="s">
+        <v>224</v>
+      </c>
+      <c r="B196" t="s">
+        <v>86</v>
+      </c>
+      <c r="C196" t="s">
+        <v>220</v>
+      </c>
+      <c r="D196" t="s">
+        <v>186</v>
+      </c>
+      <c r="E196" t="s">
+        <v>62</v>
+      </c>
+      <c r="F196" t="s">
+        <v>221</v>
+      </c>
+      <c r="G196" t="s">
+        <v>64</v>
+      </c>
+      <c r="H196" t="s">
+        <v>219</v>
+      </c>
+      <c r="I196" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15">
+      <c r="A197" t="s">
+        <v>224</v>
+      </c>
+      <c r="B197" t="s">
+        <v>86</v>
+      </c>
+      <c r="C197" t="s">
+        <v>208</v>
+      </c>
+      <c r="D197" t="s">
+        <v>239</v>
+      </c>
+      <c r="E197" t="s">
+        <v>62</v>
+      </c>
+      <c r="F197" t="s">
+        <v>210</v>
+      </c>
+      <c r="G197" t="s">
+        <v>155</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15">
+      <c r="A198" t="s">
+        <v>224</v>
+      </c>
+      <c r="B198" t="s">
+        <v>86</v>
+      </c>
+      <c r="C198" t="s">
+        <v>150</v>
+      </c>
+      <c r="D198" t="s">
+        <v>158</v>
+      </c>
+      <c r="E198" t="s">
+        <v>15</v>
+      </c>
+      <c r="F198" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" t="s">
+        <v>17</v>
+      </c>
+      <c r="H198" t="s">
+        <v>18</v>
+      </c>
+      <c r="I198" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15">
+      <c r="A199" t="s">
+        <v>224</v>
+      </c>
+      <c r="B199" t="s">
+        <v>86</v>
+      </c>
+      <c r="C199" t="s">
+        <v>112</v>
+      </c>
+      <c r="D199" t="s">
+        <v>225</v>
+      </c>
+      <c r="E199" t="s">
+        <v>226</v>
+      </c>
+      <c r="F199" t="s">
+        <v>227</v>
+      </c>
+      <c r="G199" t="s">
+        <v>228</v>
+      </c>
+      <c r="H199" t="s">
+        <v>219</v>
+      </c>
+      <c r="I199" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15">
+      <c r="A200" t="s">
+        <v>224</v>
+      </c>
+      <c r="B200" t="s">
+        <v>86</v>
+      </c>
+      <c r="C200" t="s">
+        <v>77</v>
+      </c>
+      <c r="D200" t="s">
+        <v>66</v>
+      </c>
+      <c r="E200" t="s">
+        <v>111</v>
+      </c>
+      <c r="F200" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" t="s">
+        <v>49</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15">
+      <c r="A201" t="s">
+        <v>224</v>
+      </c>
+      <c r="B201" t="s">
+        <v>86</v>
+      </c>
+      <c r="C201" t="s">
+        <v>164</v>
+      </c>
+      <c r="D201" t="s">
+        <v>116</v>
+      </c>
+      <c r="E201" t="s">
+        <v>82</v>
+      </c>
+      <c r="F201" t="s">
+        <v>148</v>
+      </c>
+      <c r="G201" t="s">
+        <v>107</v>
+      </c>
+      <c r="H201" t="s">
+        <v>219</v>
+      </c>
+      <c r="I201" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15">
+      <c r="A202" t="s">
+        <v>224</v>
+      </c>
+      <c r="B202" t="s">
+        <v>86</v>
+      </c>
+      <c r="C202" t="s">
+        <v>60</v>
+      </c>
+      <c r="D202" t="s">
+        <v>196</v>
+      </c>
+      <c r="E202" t="s">
+        <v>54</v>
+      </c>
+      <c r="F202" t="s">
+        <v>83</v>
+      </c>
+      <c r="G202" t="s">
+        <v>52</v>
+      </c>
+      <c r="H202" t="s">
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15">
+      <c r="A203" t="s">
+        <v>224</v>
+      </c>
+      <c r="B203" t="s">
+        <v>86</v>
+      </c>
+      <c r="C203" t="s">
+        <v>38</v>
+      </c>
+      <c r="D203" t="s">
+        <v>243</v>
+      </c>
+      <c r="E203" t="s">
+        <v>244</v>
+      </c>
+      <c r="F203" t="s">
+        <v>58</v>
+      </c>
+      <c r="G203" t="s">
+        <v>203</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15">
+      <c r="A204" t="s">
+        <v>224</v>
+      </c>
+      <c r="B204" t="s">
+        <v>86</v>
+      </c>
+      <c r="C204" t="s">
+        <v>38</v>
+      </c>
+      <c r="D204" t="s">
+        <v>245</v>
+      </c>
+      <c r="E204" t="s">
+        <v>244</v>
+      </c>
+      <c r="F204" t="s">
+        <v>58</v>
+      </c>
+      <c r="G204" t="s">
+        <v>203</v>
+      </c>
+      <c r="H204" t="s">
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="15">
+      <c r="A205" t="s">
+        <v>224</v>
+      </c>
+      <c r="B205" t="s">
+        <v>86</v>
+      </c>
+      <c r="C205" t="s">
+        <v>229</v>
+      </c>
+      <c r="D205" t="s">
+        <v>237</v>
+      </c>
+      <c r="E205" t="s">
+        <v>238</v>
+      </c>
+      <c r="F205" t="s">
+        <v>231</v>
+      </c>
+      <c r="G205" t="s">
+        <v>59</v>
+      </c>
+      <c r="H205" t="s">
+        <v>18</v>
+      </c>
+      <c r="I205" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="15">
+      <c r="A206" t="s">
+        <v>224</v>
+      </c>
+      <c r="B206" t="s">
+        <v>93</v>
+      </c>
+      <c r="C206" t="s">
+        <v>131</v>
+      </c>
+      <c r="D206" t="s">
+        <v>242</v>
+      </c>
+      <c r="E206" t="s">
+        <v>62</v>
+      </c>
+      <c r="F206" t="s">
+        <v>175</v>
+      </c>
+      <c r="G206" t="s">
+        <v>136</v>
+      </c>
+      <c r="H206" t="s">
+        <v>219</v>
+      </c>
+      <c r="I206" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="15">
+      <c r="A207" t="s">
+        <v>224</v>
+      </c>
+      <c r="B207" t="s">
+        <v>93</v>
+      </c>
+      <c r="C207" t="s">
+        <v>220</v>
+      </c>
+      <c r="D207" t="s">
+        <v>186</v>
+      </c>
+      <c r="E207" t="s">
+        <v>62</v>
+      </c>
+      <c r="F207" t="s">
+        <v>221</v>
+      </c>
+      <c r="G207" t="s">
+        <v>64</v>
+      </c>
+      <c r="H207" t="s">
+        <v>219</v>
+      </c>
+      <c r="I207" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="15">
+      <c r="A208" t="s">
+        <v>224</v>
+      </c>
+      <c r="B208" t="s">
+        <v>93</v>
+      </c>
+      <c r="C208" t="s">
+        <v>150</v>
+      </c>
+      <c r="D208" t="s">
+        <v>158</v>
+      </c>
+      <c r="E208" t="s">
+        <v>111</v>
+      </c>
+      <c r="F208" t="s">
+        <v>63</v>
+      </c>
+      <c r="G208" t="s">
+        <v>49</v>
+      </c>
+      <c r="H208" t="s">
+        <v>18</v>
+      </c>
+      <c r="I208" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="15">
+      <c r="A209" t="s">
+        <v>224</v>
+      </c>
+      <c r="B209" t="s">
+        <v>93</v>
+      </c>
+      <c r="C209" t="s">
+        <v>164</v>
+      </c>
+      <c r="D209" t="s">
+        <v>116</v>
+      </c>
+      <c r="E209" t="s">
+        <v>111</v>
+      </c>
+      <c r="F209" t="s">
+        <v>163</v>
+      </c>
+      <c r="G209" t="s">
+        <v>136</v>
+      </c>
+      <c r="H209" t="s">
+        <v>219</v>
+      </c>
+      <c r="I209" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="15">
+      <c r="A210" t="s">
+        <v>224</v>
+      </c>
+      <c r="B210" t="s">
+        <v>93</v>
+      </c>
+      <c r="C210" t="s">
+        <v>60</v>
+      </c>
+      <c r="D210" t="s">
+        <v>187</v>
+      </c>
+      <c r="E210" t="s">
+        <v>82</v>
+      </c>
+      <c r="F210" t="s">
+        <v>97</v>
+      </c>
+      <c r="G210" t="s">
+        <v>98</v>
+      </c>
+      <c r="H210" t="s">
+        <v>18</v>
+      </c>
+      <c r="I210" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="15">
+      <c r="A211" t="s">
+        <v>224</v>
+      </c>
+      <c r="B211" t="s">
+        <v>93</v>
+      </c>
+      <c r="C211" t="s">
+        <v>38</v>
+      </c>
+      <c r="D211" t="s">
+        <v>196</v>
+      </c>
+      <c r="E211" t="s">
+        <v>246</v>
+      </c>
+      <c r="F211" t="s">
+        <v>58</v>
+      </c>
+      <c r="G211" t="s">
+        <v>59</v>
+      </c>
+      <c r="H211" t="s">
+        <v>18</v>
+      </c>
+      <c r="I211" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="15">
+      <c r="A212" t="s">
+        <v>224</v>
+      </c>
+      <c r="B212" t="s">
+        <v>93</v>
+      </c>
+      <c r="C212" t="s">
+        <v>229</v>
+      </c>
+      <c r="D212" t="s">
+        <v>96</v>
+      </c>
+      <c r="E212" t="s">
+        <v>105</v>
+      </c>
+      <c r="F212" t="s">
+        <v>231</v>
+      </c>
+      <c r="G212" t="s">
+        <v>88</v>
+      </c>
+      <c r="H212" t="s">
+        <v>18</v>
+      </c>
+      <c r="I212" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="15">
+      <c r="A213" t="s">
+        <v>224</v>
+      </c>
+      <c r="B213" t="s">
+        <v>93</v>
+      </c>
+      <c r="C213" t="s">
+        <v>247</v>
+      </c>
+      <c r="D213" t="s">
+        <v>248</v>
+      </c>
+      <c r="E213" t="s">
+        <v>87</v>
+      </c>
+      <c r="F213" t="s">
+        <v>100</v>
+      </c>
+      <c r="G213" t="s">
+        <v>249</v>
+      </c>
+      <c r="H213" t="s">
+        <v>18</v>
+      </c>
+      <c r="I213" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="15">
+      <c r="A214" t="s">
+        <v>224</v>
+      </c>
+      <c r="B214" t="s">
+        <v>104</v>
+      </c>
+      <c r="C214" t="s">
+        <v>220</v>
+      </c>
+      <c r="D214" t="s">
+        <v>189</v>
+      </c>
+      <c r="E214" t="s">
+        <v>15</v>
+      </c>
+      <c r="F214" t="s">
+        <v>16</v>
+      </c>
+      <c r="G214" t="s">
+        <v>103</v>
+      </c>
+      <c r="H214" t="s">
+        <v>219</v>
+      </c>
+      <c r="I214" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="15">
+      <c r="A215" t="s">
+        <v>224</v>
+      </c>
+      <c r="B215" t="s">
+        <v>104</v>
+      </c>
+      <c r="C215" t="s">
+        <v>208</v>
+      </c>
+      <c r="D215" t="s">
+        <v>250</v>
+      </c>
+      <c r="E215" t="s">
+        <v>62</v>
+      </c>
+      <c r="F215" t="s">
+        <v>251</v>
+      </c>
+      <c r="G215" t="s">
+        <v>155</v>
+      </c>
+      <c r="H215" t="s">
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="15">
+      <c r="A216" t="s">
+        <v>224</v>
+      </c>
+      <c r="B216" t="s">
+        <v>104</v>
+      </c>
+      <c r="C216" t="s">
+        <v>112</v>
+      </c>
+      <c r="D216" t="s">
+        <v>149</v>
+      </c>
+      <c r="E216" t="s">
+        <v>111</v>
+      </c>
+      <c r="F216" t="s">
+        <v>63</v>
+      </c>
+      <c r="G216" t="s">
+        <v>88</v>
+      </c>
+      <c r="H216" t="s">
+        <v>219</v>
+      </c>
+      <c r="I216" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="15">
+      <c r="A217" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" t="s">
+        <v>104</v>
+      </c>
+      <c r="C217" t="s">
+        <v>164</v>
+      </c>
+      <c r="D217" t="s">
+        <v>187</v>
+      </c>
+      <c r="E217" t="s">
+        <v>36</v>
+      </c>
+      <c r="F217" t="s">
+        <v>163</v>
+      </c>
+      <c r="G217" t="s">
+        <v>241</v>
+      </c>
+      <c r="H217" t="s">
+        <v>219</v>
+      </c>
+      <c r="I217" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="15">
+      <c r="A218" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" t="s">
+        <v>104</v>
+      </c>
+      <c r="C218" t="s">
+        <v>38</v>
+      </c>
+      <c r="D218" t="s">
+        <v>66</v>
+      </c>
+      <c r="E218" t="s">
+        <v>101</v>
+      </c>
+      <c r="F218" t="s">
+        <v>58</v>
+      </c>
+      <c r="G218" t="s">
+        <v>102</v>
+      </c>
+      <c r="H218" t="s">
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="15">
+      <c r="A219" t="s">
+        <v>224</v>
+      </c>
+      <c r="B219" t="s">
+        <v>104</v>
+      </c>
+      <c r="C219" t="s">
+        <v>215</v>
+      </c>
+      <c r="D219" t="s">
+        <v>216</v>
+      </c>
+      <c r="E219" t="s">
+        <v>145</v>
+      </c>
+      <c r="F219" t="s">
+        <v>152</v>
+      </c>
+      <c r="G219" t="s">
+        <v>165</v>
+      </c>
+      <c r="H219" t="s">
+        <v>18</v>
+      </c>
+      <c r="I219" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="15">
+      <c r="A220" t="s">
+        <v>224</v>
+      </c>
+      <c r="B220" t="s">
+        <v>104</v>
+      </c>
+      <c r="C220" t="s">
+        <v>247</v>
+      </c>
+      <c r="D220" t="s">
+        <v>248</v>
+      </c>
+      <c r="E220" t="s">
+        <v>87</v>
+      </c>
+      <c r="F220" t="s">
+        <v>100</v>
+      </c>
+      <c r="G220" t="s">
+        <v>249</v>
+      </c>
+      <c r="H220" t="s">
+        <v>18</v>
+      </c>
+      <c r="I220" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="15">
+      <c r="A221" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" t="s">
+        <v>113</v>
+      </c>
+      <c r="C221" t="s">
+        <v>208</v>
+      </c>
+      <c r="D221" t="s">
+        <v>250</v>
+      </c>
+      <c r="E221" t="s">
+        <v>62</v>
+      </c>
+      <c r="F221" t="s">
+        <v>251</v>
+      </c>
+      <c r="G221" t="s">
+        <v>155</v>
+      </c>
+      <c r="H221" t="s">
+        <v>18</v>
+      </c>
+      <c r="I221" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="15">
+      <c r="A222" t="s">
+        <v>224</v>
+      </c>
+      <c r="B222" t="s">
+        <v>113</v>
+      </c>
+      <c r="C222" t="s">
+        <v>112</v>
+      </c>
+      <c r="D222" t="s">
+        <v>149</v>
+      </c>
+      <c r="E222" t="s">
+        <v>111</v>
+      </c>
+      <c r="F222" t="s">
+        <v>63</v>
+      </c>
+      <c r="G222" t="s">
+        <v>88</v>
+      </c>
+      <c r="H222" t="s">
+        <v>219</v>
+      </c>
+      <c r="I222" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="15">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+      <c r="B223" t="s">
+        <v>113</v>
+      </c>
+      <c r="C223" t="s">
+        <v>60</v>
+      </c>
+      <c r="D223" t="s">
+        <v>116</v>
+      </c>
+      <c r="E223" t="s">
+        <v>101</v>
+      </c>
+      <c r="F223" t="s">
+        <v>100</v>
+      </c>
+      <c r="G223" t="s">
+        <v>102</v>
+      </c>
+      <c r="H223" t="s">
+        <v>18</v>
+      </c>
+      <c r="I223" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="15">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" t="s">
         <v>117</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C224" t="s">
+        <v>208</v>
+      </c>
+      <c r="D224" t="s">
+        <v>250</v>
+      </c>
+      <c r="E224" t="s">
+        <v>62</v>
+      </c>
+      <c r="F224" t="s">
+        <v>251</v>
+      </c>
+      <c r="G224" t="s">
+        <v>155</v>
+      </c>
+      <c r="H224" t="s">
+        <v>18</v>
+      </c>
+      <c r="I224" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="15">
+      <c r="A225" t="s">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>117</v>
+      </c>
+      <c r="C225" t="s">
         <v>60</v>
       </c>
-      <c r="D181" t="s">
-        <v>228</v>
-      </c>
-      <c r="E181" t="s">
+      <c r="D225" t="s">
+        <v>248</v>
+      </c>
+      <c r="E225" t="s">
         <v>101</v>
       </c>
-      <c r="F181" t="s">
+      <c r="F225" t="s">
         <v>100</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G225" t="s">
         <v>102</v>
       </c>
-      <c r="H181" t="s">
-        <v>18</v>
-      </c>
-      <c r="I181" t="s">
+      <c r="H225" t="s">
+        <v>18</v>
+      </c>
+      <c r="I225" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6604,18 +7958,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{99993fb3-164c-4a0f-b3f8-aac9cd3736ec}">
-  <dimension ref="A1:I11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5fb1f090-a174-4d68-ae27-489d674321f9}">
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
     <col min="3" max="3" width="18.5714285714286" customWidth="1"/>
     <col min="4" max="4" width="50.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="24.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="55.5714285714286" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="11.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="40.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6624,16 +7978,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -6653,13 +8007,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -6682,19 +8036,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F3" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G3" t="s">
         <v>136</v>
@@ -6711,16 +8065,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -6740,19 +8094,19 @@
         <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G5" t="s">
         <v>136</v>
@@ -6769,19 +8123,19 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="E6" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G6" t="s">
         <v>136</v>
@@ -6798,19 +8152,19 @@
         <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F7" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G7" t="s">
         <v>136</v>
@@ -6824,16 +8178,16 @@
     </row>
     <row r="8" spans="1:9" ht="15">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -6853,22 +8207,22 @@
     </row>
     <row r="9" spans="1:9" ht="15">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="E9" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="F9" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G9" t="s">
         <v>136</v>
@@ -6882,19 +8236,19 @@
     </row>
     <row r="10" spans="1:9" ht="15">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -6911,30 +8265,117 @@
     </row>
     <row r="11" spans="1:9" ht="15">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="E11" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
         <v>136</v>
       </c>
       <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15">
+      <c r="A12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" t="s">
+        <v>136</v>
+      </c>
+      <c r="H12" t="s">
         <v>25</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15">
+      <c r="A13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" t="s">
+        <v>282</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" t="s">
+        <v>219</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15">
+      <c r="A14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" t="s">
+        <v>219</v>
+      </c>
+      <c r="I14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6946,16 +8387,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{de62a0cd-f96a-4c06-9e53-196ffa59af86}">
-  <dimension ref="A1:F57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8d8b1b34-9adf-49d0-930e-1b3ca8e9545f}">
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="21.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="15.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="40.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -6963,13 +8404,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -6983,13 +8424,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
@@ -7003,13 +8444,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
         <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E3" t="s">
         <v>76</v>
@@ -7023,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -7043,13 +8484,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E5" t="s">
         <v>46</v>
@@ -7063,13 +8504,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -7083,13 +8524,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
         <v>102</v>
@@ -7103,13 +8544,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E8" t="s">
         <v>143</v>
@@ -7123,16 +8564,16 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C9" t="s">
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -7143,13 +8584,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
@@ -7163,13 +8604,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -7183,16 +8624,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -7203,13 +8644,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -7223,13 +8664,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E14" t="s">
         <v>46</v>
@@ -7243,16 +8684,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E15" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -7263,16 +8704,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -7283,13 +8724,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E17" t="s">
         <v>112</v>
@@ -7303,13 +8744,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -7323,16 +8764,16 @@
         <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E19" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -7343,16 +8784,16 @@
         <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -7363,16 +8804,16 @@
         <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D21" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E21" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -7383,13 +8824,13 @@
         <v>121</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="C22" t="s">
         <v>77</v>
       </c>
       <c r="D22" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E22" t="s">
         <v>142</v>
@@ -7403,13 +8844,13 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
         <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E23" t="s">
         <v>56</v>
@@ -7423,13 +8864,13 @@
         <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C24" t="s">
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E24" t="s">
         <v>52</v>
@@ -7443,16 +8884,16 @@
         <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D25" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -7463,13 +8904,13 @@
         <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C26" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="D26" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E26" t="s">
         <v>102</v>
@@ -7483,13 +8924,13 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E27" t="s">
         <v>56</v>
@@ -7503,16 +8944,16 @@
         <v>121</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C28" t="s">
         <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E28" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -7523,16 +8964,16 @@
         <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="D29" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E29" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -7543,13 +8984,13 @@
         <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C30" t="s">
         <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
         <v>98</v>
@@ -7563,13 +9004,13 @@
         <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C31" t="s">
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
@@ -7583,16 +9024,16 @@
         <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E32" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="F32" t="s">
         <v>18</v>
@@ -7603,13 +9044,13 @@
         <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -7620,16 +9061,16 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E34" t="s">
         <v>26</v>
@@ -7640,16 +9081,16 @@
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C35" t="s">
         <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
@@ -7660,16 +9101,16 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C36" t="s">
         <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E36" t="s">
         <v>26</v>
@@ -7680,16 +9121,16 @@
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C37" t="s">
         <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -7700,16 +9141,16 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B38" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C38" t="s">
         <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -7720,16 +9161,16 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C39" t="s">
         <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="E39" t="s">
         <v>26</v>
@@ -7740,16 +9181,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B40" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C40" t="s">
         <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="E40" t="s">
         <v>26</v>
@@ -7760,16 +9201,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B41" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
         <v>26</v>
@@ -7780,16 +9221,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E42" t="s">
         <v>26</v>
@@ -7800,16 +9241,16 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="C43" t="s">
         <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -7820,16 +9261,16 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C44" t="s">
         <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
         <v>26</v>
@@ -7840,16 +9281,16 @@
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="C45" t="s">
         <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
@@ -7860,16 +9301,16 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="C46" t="s">
         <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
@@ -7880,56 +9321,56 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="C47" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="E47" t="s">
         <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E48" t="s">
         <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C49" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D49" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="E49" t="s">
         <v>26</v>
@@ -7940,16 +9381,16 @@
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="C50" t="s">
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E50" t="s">
         <v>26</v>
@@ -7960,16 +9401,16 @@
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D51" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
@@ -7980,16 +9421,16 @@
     </row>
     <row r="52" spans="1:6" ht="15">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="E52" t="s">
         <v>26</v>
@@ -8000,16 +9441,16 @@
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="D53" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="E53" t="s">
         <v>26</v>
@@ -8020,16 +9461,16 @@
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
@@ -8040,16 +9481,16 @@
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C55" t="s">
         <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="E55" t="s">
         <v>26</v>
@@ -8060,16 +9501,16 @@
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B56" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="E56" t="s">
         <v>26</v>
@@ -8080,21 +9521,121 @@
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B57" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="C57" t="s">
-        <v>199</v>
+        <v>60</v>
       </c>
       <c r="D57" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="E57" t="s">
         <v>26</v>
       </c>
       <c r="F57" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="s">
+        <v>296</v>
+      </c>
+      <c r="C58" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E58" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15">
+      <c r="A59" t="s">
+        <v>224</v>
+      </c>
+      <c r="B59" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15">
+      <c r="A60" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" t="s">
+        <v>296</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15">
+      <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
+        <v>298</v>
+      </c>
+      <c r="C61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D61" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15">
+      <c r="A62" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" t="s">
+        <v>208</v>
+      </c>
+      <c r="D62" t="s">
+        <v>290</v>
+      </c>
+      <c r="E62" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2525" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2909" uniqueCount="324">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -615,6 +615,9 @@
     <t>2CA</t>
   </si>
   <si>
+    <t>p. Nowak Damiana, historia za piątek 29 maja</t>
+  </si>
+  <si>
     <t>3TH|JA2</t>
   </si>
   <si>
@@ -657,7 +660,10 @@
     <t>sg3</t>
   </si>
   <si>
-    <t>matematyka przeniesiona na środę 27.05.2026, lekcja 6, sala 3</t>
+    <t>3TFB|JA1</t>
+  </si>
+  <si>
+    <t>3TFB|JA2</t>
   </si>
   <si>
     <t>2WA</t>
@@ -666,9 +672,6 @@
     <t>p. Wojciechowski, j. angielski za lekcję 8</t>
   </si>
   <si>
-    <t>3TFB|JA1</t>
-  </si>
-  <si>
     <t>Wakat1 j. niemiecki</t>
   </si>
   <si>
@@ -690,18 +693,48 @@
     <t>sg1</t>
   </si>
   <si>
+    <t>Ostrowska Ewa</t>
+  </si>
+  <si>
+    <t>1CB</t>
+  </si>
+  <si>
+    <t>Organizacja sprzedaży</t>
+  </si>
+  <si>
+    <t>1WB</t>
+  </si>
+  <si>
+    <t>egzaminy zawodowe</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>p. Hudziec, chemia za lekcję 7</t>
   </si>
   <si>
     <t>3FB</t>
   </si>
   <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1WA</t>
+  </si>
+  <si>
+    <t>Przedsiębiorca w handlu</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>p. Leńczowska, RKZ za lekcję 10</t>
+  </si>
+  <si>
     <t>29.05.2026</t>
   </si>
   <si>
-    <t>3TFB|JA2</t>
-  </si>
-  <si>
     <t>Zajęcia praktyczne - wykonywanie usług fryzjerskich</t>
   </si>
   <si>
@@ -717,9 +750,6 @@
     <t>Rozwój kompetencji zawodowych - Zasady zdrowego żywienia</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>2TFB|DZ</t>
   </si>
   <si>
@@ -735,7 +765,7 @@
     <t>1CB|relu</t>
   </si>
   <si>
-    <t>1K</t>
+    <t>konkurs im. Cierplikowskiego</t>
   </si>
   <si>
     <t>Technologia gastronomiczna z towaroznawstwem</t>
@@ -762,9 +792,6 @@
     <t>1FC|JA1</t>
   </si>
   <si>
-    <t>Technika w produkcji cukierniczej</t>
-  </si>
-  <si>
     <t>Wakat2 matematyka</t>
   </si>
   <si>
@@ -780,6 +807,12 @@
     <t>sg2</t>
   </si>
   <si>
+    <t>1FA|JA1</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
     <t>Godzina</t>
   </si>
   <si>
@@ -867,15 +900,36 @@
     <t>15:05-16:00</t>
   </si>
   <si>
+    <t>16:30-18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nikodem Gieysztor - 2CA - indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>18:00-18:45</t>
+  </si>
+  <si>
     <t>12:25-15:40</t>
   </si>
   <si>
     <t>Projektowanie fryzur- cztery godziny co piatek od 20.02.2026r.</t>
   </si>
   <si>
+    <t>12:40-14:10</t>
+  </si>
+  <si>
+    <t>Marcel Wiśniewski - 1WA - indywidualne nauczanie</t>
+  </si>
+  <si>
     <t>15:45-16:30</t>
   </si>
   <si>
+    <t>18:55-20:25</t>
+  </si>
+  <si>
+    <t>Matematyka, fizyka</t>
+  </si>
+  <si>
     <t>Miejsce dyżuru</t>
   </si>
   <si>
@@ -915,9 +969,6 @@
     <t>14:00-14:05</t>
   </si>
   <si>
-    <t>Ostrowska Ewa</t>
-  </si>
-  <si>
     <t>14:50-14:55</t>
   </si>
   <si>
@@ -927,19 +978,22 @@
     <t>17:20-17:25</t>
   </si>
   <si>
-    <t>Jarek Zbigniew</t>
-  </si>
-  <si>
-    <t>Marzec Renata</t>
+    <t>07:55-08:00</t>
+  </si>
+  <si>
+    <t>Smereka Alicja</t>
+  </si>
+  <si>
+    <t>Doliński Mirosław</t>
   </si>
   <si>
     <t>15:40-15:45</t>
   </si>
   <si>
-    <t>16:30-16:35</t>
-  </si>
-  <si>
-    <t>07:55-08:00</t>
+    <t>Stępień Krystyna</t>
+  </si>
+  <si>
+    <t>Piątek-Pawłowska Bożena</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{bd768827-b297-44e9-8255-181f3892200f}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fd65d982-9525-4b24-809b-b17ad4d43f6c}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1410,8 +1464,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{49eacd9a-69b0-4d6e-b67e-24622ac054db}">
-  <dimension ref="A1:I225"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e03ba48e-0eb0-4188-941f-7513145081ff}">
+  <dimension ref="A1:I270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -3672,19 +3726,19 @@
         <v>147</v>
       </c>
       <c r="E78" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F78" t="s">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G78" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
         <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15">
@@ -4745,19 +4799,19 @@
         <v>196</v>
       </c>
       <c r="E115" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F115" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G115" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="H115" t="s">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15">
@@ -4771,7 +4825,7 @@
         <v>176</v>
       </c>
       <c r="D116" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E116" t="s">
         <v>145</v>
@@ -4800,13 +4854,13 @@
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E117" t="s">
         <v>22</v>
       </c>
       <c r="F117" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G117" t="s">
         <v>76</v>
@@ -4887,7 +4941,7 @@
         <v>173</v>
       </c>
       <c r="D120" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E120" t="s">
         <v>62</v>
@@ -4896,7 +4950,7 @@
         <v>175</v>
       </c>
       <c r="G120" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H120" t="s">
         <v>18</v>
@@ -4974,7 +5028,7 @@
         <v>38</v>
       </c>
       <c r="D123" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E123" t="s">
         <v>62</v>
@@ -4983,7 +5037,7 @@
         <v>58</v>
       </c>
       <c r="G123" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H123" t="s">
         <v>18</v>
@@ -5003,7 +5057,7 @@
         <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E124" t="s">
         <v>62</v>
@@ -5012,7 +5066,7 @@
         <v>58</v>
       </c>
       <c r="G124" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H124" t="s">
         <v>18</v>
@@ -5032,7 +5086,7 @@
         <v>38</v>
       </c>
       <c r="D125" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E125" t="s">
         <v>62</v>
@@ -5041,7 +5095,7 @@
         <v>58</v>
       </c>
       <c r="G125" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H125" t="s">
         <v>18</v>
@@ -5058,10 +5112,10 @@
         <v>72</v>
       </c>
       <c r="C126" t="s">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
@@ -5073,7 +5127,7 @@
         <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
@@ -5087,22 +5141,22 @@
         <v>72</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D127" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E127" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F127" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G127" t="s">
-        <v>17</v>
+        <v>207</v>
       </c>
       <c r="H127" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
@@ -5113,28 +5167,28 @@
         <v>172</v>
       </c>
       <c r="B128" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C128" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D128" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E128" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="F128" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="H128" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15">
@@ -5145,25 +5199,25 @@
         <v>86</v>
       </c>
       <c r="C129" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="E129" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="G129" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="H129" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15">
@@ -5174,25 +5228,25 @@
         <v>86</v>
       </c>
       <c r="C130" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="D130" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E130" t="s">
         <v>62</v>
       </c>
       <c r="F130" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="G130" t="s">
-        <v>201</v>
+        <v>88</v>
       </c>
       <c r="H130" t="s">
         <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15">
@@ -5203,25 +5257,25 @@
         <v>86</v>
       </c>
       <c r="C131" t="s">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="D131" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="E131" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F131" t="s">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="G131" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H131" t="s">
         <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15">
@@ -5232,19 +5286,19 @@
         <v>86</v>
       </c>
       <c r="C132" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="E132" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F132" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="G132" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H132" t="s">
         <v>18</v>
@@ -5261,22 +5315,22 @@
         <v>86</v>
       </c>
       <c r="C133" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="E133" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="H133" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I133" t="s">
         <v>32</v>
@@ -5290,25 +5344,25 @@
         <v>86</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D134" t="s">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="E134" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="F134" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="G134" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="H134" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15">
@@ -5322,22 +5376,22 @@
         <v>70</v>
       </c>
       <c r="D135" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="E135" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="F135" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G135" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="H135" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15">
@@ -5351,7 +5405,7 @@
         <v>73</v>
       </c>
       <c r="D136" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E136" t="s">
         <v>87</v>
@@ -5380,7 +5434,7 @@
         <v>173</v>
       </c>
       <c r="D137" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E137" t="s">
         <v>62</v>
@@ -5389,7 +5443,7 @@
         <v>175</v>
       </c>
       <c r="G137" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H137" t="s">
         <v>18</v>
@@ -5406,16 +5460,16 @@
         <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E138" t="s">
         <v>62</v>
       </c>
       <c r="F138" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G138" t="s">
         <v>88</v>
@@ -5450,7 +5504,7 @@
         <v>136</v>
       </c>
       <c r="H139" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I139" t="s">
         <v>26</v>
@@ -5525,7 +5579,7 @@
         <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E142" t="s">
         <v>22</v>
@@ -5609,16 +5663,16 @@
         <v>104</v>
       </c>
       <c r="C145" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D145" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E145" t="s">
         <v>62</v>
       </c>
       <c r="F145" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G145" t="s">
         <v>88</v>
@@ -5644,19 +5698,19 @@
         <v>106</v>
       </c>
       <c r="E146" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="F146" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="G146" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H146" t="s">
         <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15">
@@ -5696,10 +5750,10 @@
         <v>113</v>
       </c>
       <c r="C148" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D148" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E148" t="s">
         <v>145</v>
@@ -5719,7 +5773,7 @@
     </row>
     <row r="149" spans="1:9" ht="15">
       <c r="A149" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B149" t="s">
         <v>12</v>
@@ -5728,19 +5782,19 @@
         <v>131</v>
       </c>
       <c r="D149" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E149" t="s">
         <v>62</v>
       </c>
       <c r="F149" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G149" t="s">
         <v>24</v>
       </c>
       <c r="H149" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I149" t="s">
         <v>26</v>
@@ -5748,28 +5802,28 @@
     </row>
     <row r="150" spans="1:9" ht="15">
       <c r="A150" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B150" t="s">
         <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>220</v>
+        <v>73</v>
       </c>
       <c r="D150" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="E150" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F150" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="G150" t="s">
         <v>24</v>
       </c>
       <c r="H150" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
         <v>26</v>
@@ -5777,28 +5831,28 @@
     </row>
     <row r="151" spans="1:9" ht="15">
       <c r="A151" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B151" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="D151" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="E151" t="s">
         <v>62</v>
       </c>
       <c r="F151" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G151" t="s">
         <v>24</v>
       </c>
       <c r="H151" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I151" t="s">
         <v>26</v>
@@ -5806,28 +5860,28 @@
     </row>
     <row r="152" spans="1:9" ht="15">
       <c r="A152" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B152" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D152" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E152" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F152" t="s">
-        <v>221</v>
+        <v>37</v>
       </c>
       <c r="G152" t="s">
         <v>24</v>
       </c>
       <c r="H152" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I152" t="s">
         <v>26</v>
@@ -5835,28 +5889,28 @@
     </row>
     <row r="153" spans="1:9" ht="15">
       <c r="A153" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B153" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D153" t="s">
-        <v>205</v>
+        <v>106</v>
       </c>
       <c r="E153" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F153" t="s">
-        <v>218</v>
+        <v>45</v>
       </c>
       <c r="G153" t="s">
         <v>24</v>
       </c>
       <c r="H153" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I153" t="s">
         <v>26</v>
@@ -5864,28 +5918,28 @@
     </row>
     <row r="154" spans="1:9" ht="15">
       <c r="A154" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B154" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C154" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="D154" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="E154" t="s">
         <v>62</v>
       </c>
       <c r="F154" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G154" t="s">
         <v>24</v>
       </c>
       <c r="H154" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I154" t="s">
         <v>26</v>
@@ -5893,231 +5947,231 @@
     </row>
     <row r="155" spans="1:9" ht="15">
       <c r="A155" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B155" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C155" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D155" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F155" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="H155" t="s">
         <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15">
       <c r="A156" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B156" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C156" t="s">
-        <v>70</v>
+        <v>221</v>
       </c>
       <c r="D156" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="E156" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
-        <v>16</v>
+        <v>222</v>
       </c>
       <c r="G156" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="H156" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I156" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15">
       <c r="A157" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B157" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C157" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D157" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E157" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F157" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="G157" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I157" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15">
       <c r="A158" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B158" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C158" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D158" t="s">
-        <v>223</v>
+        <v>50</v>
       </c>
       <c r="E158" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F158" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="G158" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H158" t="s">
         <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15">
       <c r="A159" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B159" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C159" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D159" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="E159" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F159" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="G159" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="H159" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I159" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15">
       <c r="A160" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C160" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D160" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="E160" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="F160" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="H160" t="s">
         <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15">
       <c r="A161" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B161" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C161" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="D161" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E161" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F161" t="s">
-        <v>63</v>
+        <v>222</v>
       </c>
       <c r="G161" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="H161" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I161" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15">
       <c r="A162" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B162" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C162" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D162" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E162" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="F162" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G162" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
       <c r="H162" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="I162" t="s">
         <v>32</v>
@@ -6125,25 +6179,25 @@
     </row>
     <row r="163" spans="1:9" ht="15">
       <c r="A163" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B163" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="C163" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="D163" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="E163" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="F163" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="G163" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="H163" t="s">
         <v>18</v>
@@ -6154,25 +6208,25 @@
     </row>
     <row r="164" spans="1:9" ht="15">
       <c r="A164" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B164" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="C164" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="D164" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="E164" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F164" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="G164" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="H164" t="s">
         <v>18</v>
@@ -6183,86 +6237,86 @@
     </row>
     <row r="165" spans="1:9" ht="15">
       <c r="A165" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C165" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D165" t="s">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="E165" t="s">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="F165" t="s">
-        <v>227</v>
+        <v>23</v>
       </c>
       <c r="G165" t="s">
-        <v>228</v>
+        <v>20</v>
       </c>
       <c r="H165" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15">
       <c r="A166" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C166" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="D166" t="s">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="E166" t="s">
-        <v>230</v>
+        <v>44</v>
       </c>
       <c r="F166" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="G166" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
       <c r="A167" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B167" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C167" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="D167" t="s">
-        <v>232</v>
+        <v>35</v>
       </c>
       <c r="E167" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F167" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="G167" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="H167" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I167" t="s">
         <v>32</v>
@@ -6270,86 +6324,86 @@
     </row>
     <row r="168" spans="1:9" ht="15">
       <c r="A168" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B168" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C168" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="D168" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="E168" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F168" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="G168" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="H168" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15">
       <c r="A169" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B169" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C169" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="D169" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="E169" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="F169" t="s">
+        <v>30</v>
+      </c>
+      <c r="G169" t="s">
+        <v>88</v>
+      </c>
+      <c r="H169" t="s">
         <v>227</v>
       </c>
-      <c r="G169" t="s">
-        <v>228</v>
-      </c>
-      <c r="H169" t="s">
-        <v>219</v>
-      </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15">
       <c r="A170" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B170" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C170" t="s">
+        <v>38</v>
+      </c>
+      <c r="D170" t="s">
+        <v>50</v>
+      </c>
+      <c r="E170" t="s">
+        <v>87</v>
+      </c>
+      <c r="F170" t="s">
+        <v>58</v>
+      </c>
+      <c r="G170" t="s">
+        <v>136</v>
+      </c>
+      <c r="H170" t="s">
         <v>229</v>
-      </c>
-      <c r="D170" t="s">
-        <v>96</v>
-      </c>
-      <c r="E170" t="s">
-        <v>230</v>
-      </c>
-      <c r="F170" t="s">
-        <v>231</v>
-      </c>
-      <c r="G170" t="s">
-        <v>24</v>
-      </c>
-      <c r="H170" t="s">
-        <v>18</v>
       </c>
       <c r="I170" t="s">
         <v>26</v>
@@ -6357,57 +6411,57 @@
     </row>
     <row r="171" spans="1:9" ht="15">
       <c r="A171" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B171" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C171" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="D171" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="E171" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F171" t="s">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="G171" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="H171" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15">
       <c r="A172" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B172" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C172" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="D172" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E172" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F172" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="G172" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="H172" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I172" t="s">
         <v>32</v>
@@ -6415,86 +6469,86 @@
     </row>
     <row r="173" spans="1:9" ht="15">
       <c r="A173" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B173" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C173" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D173" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E173" t="s">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="F173" t="s">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="G173" t="s">
-        <v>228</v>
+        <v>59</v>
       </c>
       <c r="H173" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15">
       <c r="A174" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B174" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C174" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="D174" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="E174" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="F174" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="G174" t="s">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="H174" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="I174" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15">
       <c r="A175" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B175" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C175" t="s">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="D175" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E175" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="F175" t="s">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="G175" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="H175" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I175" t="s">
         <v>32</v>
@@ -6502,83 +6556,83 @@
     </row>
     <row r="176" spans="1:9" ht="15">
       <c r="A176" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B176" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C176" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="D176" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="F176" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="G176" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15">
       <c r="A177" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B177" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="C177" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D177" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="E177" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F177" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G177" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H177" t="s">
         <v>18</v>
       </c>
       <c r="I177" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15">
       <c r="A178" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B178" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C178" t="s">
-        <v>229</v>
+        <v>150</v>
       </c>
       <c r="D178" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="E178" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="F178" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="G178" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="H178" t="s">
         <v>18</v>
@@ -6589,173 +6643,173 @@
     </row>
     <row r="179" spans="1:9" ht="15">
       <c r="A179" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B179" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C179" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="D179" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="E179" t="s">
-        <v>62</v>
+        <v>193</v>
       </c>
       <c r="F179" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="G179" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H179" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I179" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15">
       <c r="A180" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B180" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C180" t="s">
-        <v>131</v>
+        <v>223</v>
       </c>
       <c r="D180" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E180" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F180" t="s">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="G180" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H180" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15">
       <c r="A181" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B181" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C181" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D181" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="E181" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F181" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="G181" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="H181" t="s">
         <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15">
       <c r="A182" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B182" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C182" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="D182" t="s">
-        <v>225</v>
+        <v>66</v>
       </c>
       <c r="E182" t="s">
-        <v>226</v>
+        <v>36</v>
       </c>
       <c r="F182" t="s">
-        <v>227</v>
+        <v>37</v>
       </c>
       <c r="G182" t="s">
-        <v>228</v>
+        <v>34</v>
       </c>
       <c r="H182" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15">
       <c r="A183" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B183" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C183" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D183" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E183" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="F183" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G183" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="H183" t="s">
         <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15">
       <c r="A184" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B184" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C184" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="D184" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="E184" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="F184" t="s">
-        <v>163</v>
+        <v>30</v>
       </c>
       <c r="G184" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="H184" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I184" t="s">
         <v>26</v>
@@ -6763,257 +6817,257 @@
     </row>
     <row r="185" spans="1:9" ht="15">
       <c r="A185" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B185" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C185" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="D185" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="E185" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="F185" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="G185" t="s">
-        <v>241</v>
+        <v>24</v>
       </c>
       <c r="H185" t="s">
         <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
       <c r="A186" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B186" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C186" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="D186" t="s">
-        <v>237</v>
+        <v>177</v>
       </c>
       <c r="E186" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F186" t="s">
-        <v>231</v>
+        <v>45</v>
       </c>
       <c r="G186" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="H186" t="s">
         <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15">
       <c r="A187" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B187" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C187" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="D187" t="s">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="E187" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F187" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="G187" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H187" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15">
       <c r="A188" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B188" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C188" t="s">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="D188" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E188" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F188" t="s">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="G188" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H188" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I188" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="15">
       <c r="A189" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B189" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C189" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D189" t="s">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="E189" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F189" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="G189" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="H189" t="s">
-        <v>18</v>
+        <v>235</v>
       </c>
       <c r="I189" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15">
       <c r="A190" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B190" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C190" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="D190" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="E190" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F190" t="s">
-        <v>227</v>
+        <v>45</v>
       </c>
       <c r="G190" t="s">
-        <v>228</v>
+        <v>88</v>
       </c>
       <c r="H190" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I190" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15">
       <c r="A191" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B191" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="C191" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="D191" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E191" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="F191" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="G191" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="H191" t="s">
         <v>18</v>
       </c>
       <c r="I191" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B192" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C192" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="D192" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="E192" t="s">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="F192" t="s">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="G192" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="H192" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I192" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B193" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D193" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E193" t="s">
-        <v>101</v>
+        <v>241</v>
       </c>
       <c r="F193" t="s">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="G193" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="H193" t="s">
         <v>18</v>
@@ -7024,28 +7078,28 @@
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B194" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C194" t="s">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="D194" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E194" t="s">
-        <v>238</v>
+        <v>62</v>
       </c>
       <c r="F194" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="G194" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H194" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I194" t="s">
         <v>32</v>
@@ -7053,16 +7107,16 @@
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B195" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C195" t="s">
         <v>131</v>
       </c>
       <c r="D195" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E195" t="s">
         <v>62</v>
@@ -7071,39 +7125,39 @@
         <v>175</v>
       </c>
       <c r="G195" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="H195" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I195" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B196" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C196" t="s">
+        <v>112</v>
+      </c>
+      <c r="D196" t="s">
+        <v>213</v>
+      </c>
+      <c r="E196" t="s">
+        <v>237</v>
+      </c>
+      <c r="F196" t="s">
+        <v>238</v>
+      </c>
+      <c r="G196" t="s">
+        <v>239</v>
+      </c>
+      <c r="H196" t="s">
         <v>220</v>
-      </c>
-      <c r="D196" t="s">
-        <v>186</v>
-      </c>
-      <c r="E196" t="s">
-        <v>62</v>
-      </c>
-      <c r="F196" t="s">
-        <v>221</v>
-      </c>
-      <c r="G196" t="s">
-        <v>64</v>
-      </c>
-      <c r="H196" t="s">
-        <v>219</v>
       </c>
       <c r="I196" t="s">
         <v>19</v>
@@ -7111,144 +7165,144 @@
     </row>
     <row r="197" spans="1:9" ht="15">
       <c r="A197" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B197" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C197" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D197" t="s">
-        <v>239</v>
+        <v>96</v>
       </c>
       <c r="E197" t="s">
-        <v>62</v>
+        <v>241</v>
       </c>
       <c r="F197" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="G197" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="H197" t="s">
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
       <c r="A198" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B198" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C198" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D198" t="s">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="E198" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F198" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="G198" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="H198" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I198" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B199" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C199" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D199" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E199" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="F199" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="G199" t="s">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="H199" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I199" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B200" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C200" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D200" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="E200" t="s">
-        <v>111</v>
+        <v>237</v>
       </c>
       <c r="F200" t="s">
-        <v>63</v>
+        <v>238</v>
       </c>
       <c r="G200" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="H200" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I200" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B201" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C201" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D201" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E201" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="F201" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="G201" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="H201" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I201" t="s">
         <v>32</v>
@@ -7256,28 +7310,28 @@
     </row>
     <row r="202" spans="1:9" ht="15">
       <c r="A202" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B202" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C202" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D202" t="s">
-        <v>196</v>
+        <v>74</v>
       </c>
       <c r="E202" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="F202" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="G202" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="H202" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I202" t="s">
         <v>32</v>
@@ -7285,54 +7339,54 @@
     </row>
     <row r="203" spans="1:9" ht="15">
       <c r="A203" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B203" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C203" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D203" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E203" t="s">
-        <v>244</v>
+        <v>101</v>
       </c>
       <c r="F203" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G203" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="H203" t="s">
         <v>18</v>
       </c>
       <c r="I203" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="15">
       <c r="A204" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B204" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C204" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D204" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E204" t="s">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="F204" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G204" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="H204" t="s">
         <v>18</v>
@@ -7343,28 +7397,28 @@
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B205" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C205" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="D205" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E205" t="s">
-        <v>238</v>
+        <v>110</v>
       </c>
       <c r="F205" t="s">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="G205" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="H205" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="I205" t="s">
         <v>32</v>
@@ -7372,86 +7426,86 @@
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B206" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="C206" t="s">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="D206" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E206" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="F206" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="G206" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="H206" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I206" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B207" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C207" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="D207" t="s">
-        <v>186</v>
+        <v>242</v>
       </c>
       <c r="E207" t="s">
         <v>62</v>
       </c>
       <c r="F207" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="G207" t="s">
         <v>64</v>
       </c>
       <c r="H207" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I207" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B208" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C208" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D208" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="E208" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F208" t="s">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="G208" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H208" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I208" t="s">
         <v>32</v>
@@ -7459,115 +7513,115 @@
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B209" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C209" t="s">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="D209" t="s">
-        <v>116</v>
+        <v>249</v>
       </c>
       <c r="E209" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="F209" t="s">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="G209" t="s">
-        <v>136</v>
+        <v>42</v>
       </c>
       <c r="H209" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I209" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B210" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C210" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D210" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E210" t="s">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="F210" t="s">
-        <v>97</v>
+        <v>238</v>
       </c>
       <c r="G210" t="s">
-        <v>98</v>
+        <v>239</v>
       </c>
       <c r="H210" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I210" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B211" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C211" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D211" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="E211" t="s">
-        <v>246</v>
+        <v>15</v>
       </c>
       <c r="F211" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G211" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="H211" t="s">
         <v>18</v>
       </c>
       <c r="I211" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B212" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C212" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="D212" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E212" t="s">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="F212" t="s">
-        <v>231</v>
+        <v>163</v>
       </c>
       <c r="G212" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="H212" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I212" t="s">
         <v>26</v>
@@ -7575,25 +7629,25 @@
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B213" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C213" t="s">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="D213" t="s">
-        <v>248</v>
+        <v>149</v>
       </c>
       <c r="E213" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F213" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="G213" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H213" t="s">
         <v>18</v>
@@ -7604,16 +7658,16 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B214" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C214" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="D214" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E214" t="s">
         <v>15</v>
@@ -7622,10 +7676,10 @@
         <v>16</v>
       </c>
       <c r="G214" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="H214" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="I214" t="s">
         <v>19</v>
@@ -7633,25 +7687,25 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B215" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C215" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D215" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="E215" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="F215" t="s">
-        <v>251</v>
+        <v>58</v>
       </c>
       <c r="G215" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="H215" t="s">
         <v>18</v>
@@ -7662,83 +7716,83 @@
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B216" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C216" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D216" t="s">
-        <v>149</v>
+        <v>252</v>
       </c>
       <c r="E216" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="F216" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G216" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="H216" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I216" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B217" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C217" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="D217" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E217" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="F217" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="G217" t="s">
-        <v>241</v>
+        <v>64</v>
       </c>
       <c r="H217" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I217" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B218" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C218" t="s">
-        <v>38</v>
+        <v>209</v>
       </c>
       <c r="D218" t="s">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="E218" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="F218" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G218" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="H218" t="s">
         <v>18</v>
@@ -7749,54 +7803,54 @@
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B219" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C219" t="s">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="D219" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E219" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="F219" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="G219" t="s">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="H219" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I219" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B220" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C220" t="s">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="D220" t="s">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="E220" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="F220" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G220" t="s">
-        <v>249</v>
+        <v>31</v>
       </c>
       <c r="H220" t="s">
         <v>18</v>
@@ -7807,28 +7861,28 @@
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B221" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C221" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="D221" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="E221" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F221" t="s">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="G221" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="H221" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I221" t="s">
         <v>32</v>
@@ -7836,28 +7890,28 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B222" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C222" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D222" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="E222" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F222" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="G222" t="s">
         <v>88</v>
       </c>
       <c r="H222" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I222" t="s">
         <v>26</v>
@@ -7865,28 +7919,28 @@
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B223" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C223" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D223" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="E223" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="F223" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="G223" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="H223" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="I223" t="s">
         <v>32</v>
@@ -7894,25 +7948,25 @@
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B224" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="C224" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D224" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="E224" t="s">
-        <v>62</v>
+        <v>248</v>
       </c>
       <c r="F224" t="s">
-        <v>251</v>
+        <v>58</v>
       </c>
       <c r="G224" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="H224" t="s">
         <v>18</v>
@@ -7923,31 +7977,1336 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B225" t="s">
+        <v>86</v>
+      </c>
+      <c r="C225" t="s">
+        <v>131</v>
+      </c>
+      <c r="D225" t="s">
+        <v>252</v>
+      </c>
+      <c r="E225" t="s">
+        <v>67</v>
+      </c>
+      <c r="F225" t="s">
+        <v>83</v>
+      </c>
+      <c r="G225" t="s">
+        <v>42</v>
+      </c>
+      <c r="H225" t="s">
+        <v>220</v>
+      </c>
+      <c r="I225" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="15">
+      <c r="A226" t="s">
+        <v>236</v>
+      </c>
+      <c r="B226" t="s">
+        <v>86</v>
+      </c>
+      <c r="C226" t="s">
+        <v>221</v>
+      </c>
+      <c r="D226" t="s">
+        <v>186</v>
+      </c>
+      <c r="E226" t="s">
+        <v>62</v>
+      </c>
+      <c r="F226" t="s">
+        <v>222</v>
+      </c>
+      <c r="G226" t="s">
+        <v>64</v>
+      </c>
+      <c r="H226" t="s">
+        <v>220</v>
+      </c>
+      <c r="I226" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="15">
+      <c r="A227" t="s">
+        <v>236</v>
+      </c>
+      <c r="B227" t="s">
+        <v>86</v>
+      </c>
+      <c r="C227" t="s">
+        <v>209</v>
+      </c>
+      <c r="D227" t="s">
+        <v>249</v>
+      </c>
+      <c r="E227" t="s">
+        <v>67</v>
+      </c>
+      <c r="F227" t="s">
+        <v>83</v>
+      </c>
+      <c r="G227" t="s">
+        <v>42</v>
+      </c>
+      <c r="H227" t="s">
+        <v>18</v>
+      </c>
+      <c r="I227" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="15">
+      <c r="A228" t="s">
+        <v>236</v>
+      </c>
+      <c r="B228" t="s">
+        <v>86</v>
+      </c>
+      <c r="C228" t="s">
+        <v>150</v>
+      </c>
+      <c r="D228" t="s">
+        <v>158</v>
+      </c>
+      <c r="E228" t="s">
+        <v>87</v>
+      </c>
+      <c r="F228" t="s">
+        <v>152</v>
+      </c>
+      <c r="G228" t="s">
+        <v>88</v>
+      </c>
+      <c r="H228" t="s">
+        <v>18</v>
+      </c>
+      <c r="I228" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="15">
+      <c r="A229" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" t="s">
+        <v>86</v>
+      </c>
+      <c r="C229" t="s">
+        <v>112</v>
+      </c>
+      <c r="D229" t="s">
+        <v>213</v>
+      </c>
+      <c r="E229" t="s">
+        <v>237</v>
+      </c>
+      <c r="F229" t="s">
+        <v>238</v>
+      </c>
+      <c r="G229" t="s">
+        <v>239</v>
+      </c>
+      <c r="H229" t="s">
+        <v>220</v>
+      </c>
+      <c r="I229" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="15">
+      <c r="A230" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" t="s">
+        <v>86</v>
+      </c>
+      <c r="C230" t="s">
+        <v>77</v>
+      </c>
+      <c r="D230" t="s">
+        <v>66</v>
+      </c>
+      <c r="E230" t="s">
+        <v>54</v>
+      </c>
+      <c r="F230" t="s">
+        <v>146</v>
+      </c>
+      <c r="G230" t="s">
+        <v>52</v>
+      </c>
+      <c r="H230" t="s">
+        <v>18</v>
+      </c>
+      <c r="I230" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="15">
+      <c r="A231" t="s">
+        <v>236</v>
+      </c>
+      <c r="B231" t="s">
+        <v>86</v>
+      </c>
+      <c r="C231" t="s">
+        <v>164</v>
+      </c>
+      <c r="D231" t="s">
+        <v>116</v>
+      </c>
+      <c r="E231" t="s">
+        <v>82</v>
+      </c>
+      <c r="F231" t="s">
+        <v>148</v>
+      </c>
+      <c r="G231" t="s">
+        <v>107</v>
+      </c>
+      <c r="H231" t="s">
+        <v>220</v>
+      </c>
+      <c r="I231" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="15">
+      <c r="A232" t="s">
+        <v>236</v>
+      </c>
+      <c r="B232" t="s">
+        <v>86</v>
+      </c>
+      <c r="C232" t="s">
+        <v>60</v>
+      </c>
+      <c r="D232" t="s">
+        <v>196</v>
+      </c>
+      <c r="E232" t="s">
+        <v>101</v>
+      </c>
+      <c r="F232" t="s">
+        <v>83</v>
+      </c>
+      <c r="G232" t="s">
+        <v>88</v>
+      </c>
+      <c r="H232" t="s">
+        <v>18</v>
+      </c>
+      <c r="I232" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="15">
+      <c r="A233" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" t="s">
+        <v>86</v>
+      </c>
+      <c r="C233" t="s">
+        <v>38</v>
+      </c>
+      <c r="D233" t="s">
+        <v>253</v>
+      </c>
+      <c r="E233" t="s">
+        <v>254</v>
+      </c>
+      <c r="F233" t="s">
+        <v>58</v>
+      </c>
+      <c r="G233" t="s">
+        <v>204</v>
+      </c>
+      <c r="H233" t="s">
+        <v>18</v>
+      </c>
+      <c r="I233" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15">
+      <c r="A234" t="s">
+        <v>236</v>
+      </c>
+      <c r="B234" t="s">
+        <v>86</v>
+      </c>
+      <c r="C234" t="s">
+        <v>38</v>
+      </c>
+      <c r="D234" t="s">
+        <v>255</v>
+      </c>
+      <c r="E234" t="s">
+        <v>254</v>
+      </c>
+      <c r="F234" t="s">
+        <v>58</v>
+      </c>
+      <c r="G234" t="s">
+        <v>204</v>
+      </c>
+      <c r="H234" t="s">
+        <v>18</v>
+      </c>
+      <c r="I234" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="15">
+      <c r="A235" t="s">
+        <v>236</v>
+      </c>
+      <c r="B235" t="s">
+        <v>86</v>
+      </c>
+      <c r="C235" t="s">
+        <v>240</v>
+      </c>
+      <c r="D235" t="s">
+        <v>231</v>
+      </c>
+      <c r="E235" t="s">
+        <v>248</v>
+      </c>
+      <c r="F235" t="s">
+        <v>55</v>
+      </c>
+      <c r="G235" t="s">
+        <v>59</v>
+      </c>
+      <c r="H235" t="s">
+        <v>18</v>
+      </c>
+      <c r="I235" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="15">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+      <c r="B236" t="s">
+        <v>93</v>
+      </c>
+      <c r="C236" t="s">
+        <v>131</v>
+      </c>
+      <c r="D236" t="s">
+        <v>252</v>
+      </c>
+      <c r="E236" t="s">
+        <v>54</v>
+      </c>
+      <c r="F236" t="s">
+        <v>83</v>
+      </c>
+      <c r="G236" t="s">
+        <v>80</v>
+      </c>
+      <c r="H236" t="s">
+        <v>220</v>
+      </c>
+      <c r="I236" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="15">
+      <c r="A237" t="s">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>93</v>
+      </c>
+      <c r="C237" t="s">
+        <v>73</v>
+      </c>
+      <c r="D237" t="s">
+        <v>170</v>
+      </c>
+      <c r="E237" t="s">
+        <v>87</v>
+      </c>
+      <c r="F237" t="s">
+        <v>79</v>
+      </c>
+      <c r="G237" t="s">
+        <v>88</v>
+      </c>
+      <c r="H237" t="s">
+        <v>18</v>
+      </c>
+      <c r="I237" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="15">
+      <c r="A238" t="s">
+        <v>236</v>
+      </c>
+      <c r="B238" t="s">
+        <v>93</v>
+      </c>
+      <c r="C238" t="s">
+        <v>221</v>
+      </c>
+      <c r="D238" t="s">
+        <v>186</v>
+      </c>
+      <c r="E238" t="s">
+        <v>62</v>
+      </c>
+      <c r="F238" t="s">
+        <v>222</v>
+      </c>
+      <c r="G238" t="s">
+        <v>64</v>
+      </c>
+      <c r="H238" t="s">
+        <v>220</v>
+      </c>
+      <c r="I238" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="15">
+      <c r="A239" t="s">
+        <v>236</v>
+      </c>
+      <c r="B239" t="s">
+        <v>93</v>
+      </c>
+      <c r="C239" t="s">
+        <v>244</v>
+      </c>
+      <c r="D239" t="s">
+        <v>78</v>
+      </c>
+      <c r="E239" t="s">
+        <v>67</v>
+      </c>
+      <c r="F239" t="s">
+        <v>228</v>
+      </c>
+      <c r="G239" t="s">
+        <v>42</v>
+      </c>
+      <c r="H239" t="s">
+        <v>247</v>
+      </c>
+      <c r="I239" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="15">
+      <c r="A240" t="s">
+        <v>236</v>
+      </c>
+      <c r="B240" t="s">
+        <v>93</v>
+      </c>
+      <c r="C240" t="s">
+        <v>150</v>
+      </c>
+      <c r="D240" t="s">
+        <v>158</v>
+      </c>
+      <c r="E240" t="s">
+        <v>87</v>
+      </c>
+      <c r="F240" t="s">
+        <v>152</v>
+      </c>
+      <c r="G240" t="s">
+        <v>88</v>
+      </c>
+      <c r="H240" t="s">
+        <v>18</v>
+      </c>
+      <c r="I240" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="15">
+      <c r="A241" t="s">
+        <v>236</v>
+      </c>
+      <c r="B241" t="s">
+        <v>93</v>
+      </c>
+      <c r="C241" t="s">
+        <v>251</v>
+      </c>
+      <c r="D241" t="s">
+        <v>149</v>
+      </c>
+      <c r="E241" t="s">
+        <v>36</v>
+      </c>
+      <c r="F241" t="s">
+        <v>130</v>
+      </c>
+      <c r="G241" t="s">
+        <v>88</v>
+      </c>
+      <c r="H241" t="s">
+        <v>247</v>
+      </c>
+      <c r="I241" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="15">
+      <c r="A242" t="s">
+        <v>236</v>
+      </c>
+      <c r="B242" t="s">
+        <v>93</v>
+      </c>
+      <c r="C242" t="s">
+        <v>164</v>
+      </c>
+      <c r="D242" t="s">
+        <v>116</v>
+      </c>
+      <c r="E242" t="s">
+        <v>111</v>
+      </c>
+      <c r="F242" t="s">
+        <v>163</v>
+      </c>
+      <c r="G242" t="s">
+        <v>136</v>
+      </c>
+      <c r="H242" t="s">
+        <v>220</v>
+      </c>
+      <c r="I242" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="15">
+      <c r="A243" t="s">
+        <v>236</v>
+      </c>
+      <c r="B243" t="s">
+        <v>93</v>
+      </c>
+      <c r="C243" t="s">
+        <v>60</v>
+      </c>
+      <c r="D243" t="s">
+        <v>187</v>
+      </c>
+      <c r="E243" t="s">
+        <v>82</v>
+      </c>
+      <c r="F243" t="s">
+        <v>97</v>
+      </c>
+      <c r="G243" t="s">
+        <v>98</v>
+      </c>
+      <c r="H243" t="s">
+        <v>18</v>
+      </c>
+      <c r="I243" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="15">
+      <c r="A244" t="s">
+        <v>236</v>
+      </c>
+      <c r="B244" t="s">
+        <v>93</v>
+      </c>
+      <c r="C244" t="s">
+        <v>38</v>
+      </c>
+      <c r="D244" t="s">
+        <v>196</v>
+      </c>
+      <c r="E244" t="s">
+        <v>87</v>
+      </c>
+      <c r="F244" t="s">
+        <v>58</v>
+      </c>
+      <c r="G244" t="s">
+        <v>88</v>
+      </c>
+      <c r="H244" t="s">
+        <v>18</v>
+      </c>
+      <c r="I244" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="15">
+      <c r="A245" t="s">
+        <v>236</v>
+      </c>
+      <c r="B245" t="s">
+        <v>93</v>
+      </c>
+      <c r="C245" t="s">
+        <v>240</v>
+      </c>
+      <c r="D245" t="s">
+        <v>96</v>
+      </c>
+      <c r="E245" t="s">
+        <v>105</v>
+      </c>
+      <c r="F245" t="s">
+        <v>228</v>
+      </c>
+      <c r="G245" t="s">
+        <v>88</v>
+      </c>
+      <c r="H245" t="s">
+        <v>18</v>
+      </c>
+      <c r="I245" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="15">
+      <c r="A246" t="s">
+        <v>236</v>
+      </c>
+      <c r="B246" t="s">
+        <v>93</v>
+      </c>
+      <c r="C246" t="s">
+        <v>256</v>
+      </c>
+      <c r="D246" t="s">
+        <v>257</v>
+      </c>
+      <c r="E246" t="s">
+        <v>87</v>
+      </c>
+      <c r="F246" t="s">
+        <v>100</v>
+      </c>
+      <c r="G246" t="s">
+        <v>258</v>
+      </c>
+      <c r="H246" t="s">
+        <v>18</v>
+      </c>
+      <c r="I246" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="15">
+      <c r="A247" t="s">
+        <v>236</v>
+      </c>
+      <c r="B247" t="s">
+        <v>104</v>
+      </c>
+      <c r="C247" t="s">
+        <v>73</v>
+      </c>
+      <c r="D247" t="s">
+        <v>226</v>
+      </c>
+      <c r="E247" t="s">
+        <v>87</v>
+      </c>
+      <c r="F247" t="s">
+        <v>79</v>
+      </c>
+      <c r="G247" t="s">
+        <v>88</v>
+      </c>
+      <c r="H247" t="s">
+        <v>18</v>
+      </c>
+      <c r="I247" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="15">
+      <c r="A248" t="s">
+        <v>236</v>
+      </c>
+      <c r="B248" t="s">
+        <v>104</v>
+      </c>
+      <c r="C248" t="s">
+        <v>221</v>
+      </c>
+      <c r="D248" t="s">
+        <v>189</v>
+      </c>
+      <c r="E248" t="s">
+        <v>15</v>
+      </c>
+      <c r="F248" t="s">
+        <v>16</v>
+      </c>
+      <c r="G248" t="s">
+        <v>103</v>
+      </c>
+      <c r="H248" t="s">
+        <v>220</v>
+      </c>
+      <c r="I248" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="15">
+      <c r="A249" t="s">
+        <v>236</v>
+      </c>
+      <c r="B249" t="s">
+        <v>104</v>
+      </c>
+      <c r="C249" t="s">
+        <v>209</v>
+      </c>
+      <c r="D249" t="s">
+        <v>259</v>
+      </c>
+      <c r="E249" t="s">
+        <v>62</v>
+      </c>
+      <c r="F249" t="s">
+        <v>260</v>
+      </c>
+      <c r="G249" t="s">
+        <v>88</v>
+      </c>
+      <c r="H249" t="s">
+        <v>18</v>
+      </c>
+      <c r="I249" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="15">
+      <c r="A250" t="s">
+        <v>236</v>
+      </c>
+      <c r="B250" t="s">
+        <v>104</v>
+      </c>
+      <c r="C250" t="s">
+        <v>244</v>
+      </c>
+      <c r="D250" t="s">
+        <v>158</v>
+      </c>
+      <c r="E250" t="s">
+        <v>111</v>
+      </c>
+      <c r="F250" t="s">
+        <v>130</v>
+      </c>
+      <c r="G250" t="s">
+        <v>88</v>
+      </c>
+      <c r="H250" t="s">
+        <v>247</v>
+      </c>
+      <c r="I250" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="15">
+      <c r="A251" t="s">
+        <v>236</v>
+      </c>
+      <c r="B251" t="s">
+        <v>104</v>
+      </c>
+      <c r="C251" t="s">
+        <v>112</v>
+      </c>
+      <c r="D251" t="s">
+        <v>149</v>
+      </c>
+      <c r="E251" t="s">
+        <v>111</v>
+      </c>
+      <c r="F251" t="s">
+        <v>63</v>
+      </c>
+      <c r="G251" t="s">
+        <v>88</v>
+      </c>
+      <c r="H251" t="s">
+        <v>220</v>
+      </c>
+      <c r="I251" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="15">
+      <c r="A252" t="s">
+        <v>236</v>
+      </c>
+      <c r="B252" t="s">
+        <v>104</v>
+      </c>
+      <c r="C252" t="s">
+        <v>164</v>
+      </c>
+      <c r="D252" t="s">
+        <v>187</v>
+      </c>
+      <c r="E252" t="s">
+        <v>67</v>
+      </c>
+      <c r="F252" t="s">
+        <v>228</v>
+      </c>
+      <c r="G252" t="s">
+        <v>42</v>
+      </c>
+      <c r="H252" t="s">
+        <v>220</v>
+      </c>
+      <c r="I252" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="15">
+      <c r="A253" t="s">
+        <v>236</v>
+      </c>
+      <c r="B253" t="s">
+        <v>104</v>
+      </c>
+      <c r="C253" t="s">
+        <v>38</v>
+      </c>
+      <c r="D253" t="s">
+        <v>66</v>
+      </c>
+      <c r="E253" t="s">
+        <v>101</v>
+      </c>
+      <c r="F253" t="s">
+        <v>58</v>
+      </c>
+      <c r="G253" t="s">
+        <v>102</v>
+      </c>
+      <c r="H253" t="s">
+        <v>18</v>
+      </c>
+      <c r="I253" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="15">
+      <c r="A254" t="s">
+        <v>236</v>
+      </c>
+      <c r="B254" t="s">
+        <v>104</v>
+      </c>
+      <c r="C254" t="s">
+        <v>49</v>
+      </c>
+      <c r="D254" t="s">
+        <v>116</v>
+      </c>
+      <c r="E254" t="s">
+        <v>36</v>
+      </c>
+      <c r="F254" t="s">
+        <v>37</v>
+      </c>
+      <c r="G254" t="s">
+        <v>34</v>
+      </c>
+      <c r="H254" t="s">
+        <v>247</v>
+      </c>
+      <c r="I254" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="15">
+      <c r="A255" t="s">
+        <v>236</v>
+      </c>
+      <c r="B255" t="s">
+        <v>104</v>
+      </c>
+      <c r="C255" t="s">
+        <v>216</v>
+      </c>
+      <c r="D255" t="s">
+        <v>217</v>
+      </c>
+      <c r="E255" t="s">
+        <v>145</v>
+      </c>
+      <c r="F255" t="s">
+        <v>152</v>
+      </c>
+      <c r="G255" t="s">
+        <v>165</v>
+      </c>
+      <c r="H255" t="s">
+        <v>18</v>
+      </c>
+      <c r="I255" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15">
+      <c r="A256" t="s">
+        <v>236</v>
+      </c>
+      <c r="B256" t="s">
+        <v>104</v>
+      </c>
+      <c r="C256" t="s">
+        <v>256</v>
+      </c>
+      <c r="D256" t="s">
+        <v>257</v>
+      </c>
+      <c r="E256" t="s">
+        <v>87</v>
+      </c>
+      <c r="F256" t="s">
+        <v>100</v>
+      </c>
+      <c r="G256" t="s">
+        <v>258</v>
+      </c>
+      <c r="H256" t="s">
+        <v>18</v>
+      </c>
+      <c r="I256" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15">
+      <c r="A257" t="s">
+        <v>236</v>
+      </c>
+      <c r="B257" t="s">
+        <v>113</v>
+      </c>
+      <c r="C257" t="s">
+        <v>73</v>
+      </c>
+      <c r="D257" t="s">
+        <v>231</v>
+      </c>
+      <c r="E257" t="s">
+        <v>87</v>
+      </c>
+      <c r="F257" t="s">
+        <v>79</v>
+      </c>
+      <c r="G257" t="s">
+        <v>88</v>
+      </c>
+      <c r="H257" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="15">
+      <c r="A258" t="s">
+        <v>236</v>
+      </c>
+      <c r="B258" t="s">
+        <v>113</v>
+      </c>
+      <c r="C258" t="s">
+        <v>209</v>
+      </c>
+      <c r="D258" t="s">
+        <v>259</v>
+      </c>
+      <c r="E258" t="s">
+        <v>62</v>
+      </c>
+      <c r="F258" t="s">
+        <v>260</v>
+      </c>
+      <c r="G258" t="s">
+        <v>88</v>
+      </c>
+      <c r="H258" t="s">
+        <v>18</v>
+      </c>
+      <c r="I258" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="15">
+      <c r="A259" t="s">
+        <v>236</v>
+      </c>
+      <c r="B259" t="s">
+        <v>113</v>
+      </c>
+      <c r="C259" t="s">
+        <v>244</v>
+      </c>
+      <c r="D259" t="s">
+        <v>158</v>
+      </c>
+      <c r="E259" t="s">
+        <v>111</v>
+      </c>
+      <c r="F259" t="s">
+        <v>130</v>
+      </c>
+      <c r="G259" t="s">
+        <v>88</v>
+      </c>
+      <c r="H259" t="s">
+        <v>247</v>
+      </c>
+      <c r="I259" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="15">
+      <c r="A260" t="s">
+        <v>236</v>
+      </c>
+      <c r="B260" t="s">
+        <v>113</v>
+      </c>
+      <c r="C260" t="s">
+        <v>112</v>
+      </c>
+      <c r="D260" t="s">
+        <v>149</v>
+      </c>
+      <c r="E260" t="s">
+        <v>111</v>
+      </c>
+      <c r="F260" t="s">
+        <v>63</v>
+      </c>
+      <c r="G260" t="s">
+        <v>88</v>
+      </c>
+      <c r="H260" t="s">
+        <v>220</v>
+      </c>
+      <c r="I260" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="15">
+      <c r="A261" t="s">
+        <v>236</v>
+      </c>
+      <c r="B261" t="s">
+        <v>113</v>
+      </c>
+      <c r="C261" t="s">
+        <v>60</v>
+      </c>
+      <c r="D261" t="s">
+        <v>116</v>
+      </c>
+      <c r="E261" t="s">
+        <v>101</v>
+      </c>
+      <c r="F261" t="s">
+        <v>100</v>
+      </c>
+      <c r="G261" t="s">
+        <v>102</v>
+      </c>
+      <c r="H261" t="s">
+        <v>18</v>
+      </c>
+      <c r="I261" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="15">
+      <c r="A262" t="s">
+        <v>236</v>
+      </c>
+      <c r="B262" t="s">
+        <v>113</v>
+      </c>
+      <c r="C262" t="s">
+        <v>49</v>
+      </c>
+      <c r="D262" t="s">
+        <v>261</v>
+      </c>
+      <c r="E262" t="s">
+        <v>54</v>
+      </c>
+      <c r="F262" t="s">
+        <v>148</v>
+      </c>
+      <c r="G262" t="s">
+        <v>262</v>
+      </c>
+      <c r="H262" t="s">
+        <v>247</v>
+      </c>
+      <c r="I262" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="15">
+      <c r="A263" t="s">
+        <v>236</v>
+      </c>
+      <c r="B263" t="s">
+        <v>113</v>
+      </c>
+      <c r="C263" t="s">
+        <v>49</v>
+      </c>
+      <c r="D263" t="s">
+        <v>186</v>
+      </c>
+      <c r="E263" t="s">
+        <v>54</v>
+      </c>
+      <c r="F263" t="s">
+        <v>148</v>
+      </c>
+      <c r="G263" t="s">
+        <v>262</v>
+      </c>
+      <c r="H263" t="s">
+        <v>247</v>
+      </c>
+      <c r="I263" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="15">
+      <c r="A264" t="s">
+        <v>236</v>
+      </c>
+      <c r="B264" t="s">
         <v>117</v>
       </c>
-      <c r="C225" t="s">
+      <c r="C264" t="s">
+        <v>73</v>
+      </c>
+      <c r="D264" t="s">
+        <v>78</v>
+      </c>
+      <c r="E264" t="s">
+        <v>87</v>
+      </c>
+      <c r="F264" t="s">
+        <v>79</v>
+      </c>
+      <c r="G264" t="s">
+        <v>88</v>
+      </c>
+      <c r="H264" t="s">
+        <v>18</v>
+      </c>
+      <c r="I264" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="15">
+      <c r="A265" t="s">
+        <v>236</v>
+      </c>
+      <c r="B265" t="s">
+        <v>117</v>
+      </c>
+      <c r="C265" t="s">
+        <v>209</v>
+      </c>
+      <c r="D265" t="s">
+        <v>259</v>
+      </c>
+      <c r="E265" t="s">
+        <v>62</v>
+      </c>
+      <c r="F265" t="s">
+        <v>260</v>
+      </c>
+      <c r="G265" t="s">
+        <v>88</v>
+      </c>
+      <c r="H265" t="s">
+        <v>18</v>
+      </c>
+      <c r="I265" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="15">
+      <c r="A266" t="s">
+        <v>236</v>
+      </c>
+      <c r="B266" t="s">
+        <v>117</v>
+      </c>
+      <c r="C266" t="s">
         <v>60</v>
       </c>
-      <c r="D225" t="s">
-        <v>248</v>
-      </c>
-      <c r="E225" t="s">
+      <c r="D266" t="s">
+        <v>257</v>
+      </c>
+      <c r="E266" t="s">
         <v>101</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F266" t="s">
         <v>100</v>
       </c>
-      <c r="G225" t="s">
+      <c r="G266" t="s">
         <v>102</v>
       </c>
-      <c r="H225" t="s">
-        <v>18</v>
-      </c>
-      <c r="I225" t="s">
-        <v>32</v>
+      <c r="H266" t="s">
+        <v>18</v>
+      </c>
+      <c r="I266" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="15">
+      <c r="A267" t="s">
+        <v>236</v>
+      </c>
+      <c r="B267" t="s">
+        <v>117</v>
+      </c>
+      <c r="C267" t="s">
+        <v>223</v>
+      </c>
+      <c r="D267" t="s">
+        <v>116</v>
+      </c>
+      <c r="E267" t="s">
+        <v>87</v>
+      </c>
+      <c r="F267" t="s">
+        <v>130</v>
+      </c>
+      <c r="G267" t="s">
+        <v>136</v>
+      </c>
+      <c r="H267" t="s">
+        <v>18</v>
+      </c>
+      <c r="I267" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="15">
+      <c r="A268" t="s">
+        <v>236</v>
+      </c>
+      <c r="B268" t="s">
+        <v>117</v>
+      </c>
+      <c r="C268" t="s">
+        <v>49</v>
+      </c>
+      <c r="D268" t="s">
+        <v>189</v>
+      </c>
+      <c r="E268" t="s">
+        <v>67</v>
+      </c>
+      <c r="F268" t="s">
+        <v>90</v>
+      </c>
+      <c r="G268" t="s">
+        <v>91</v>
+      </c>
+      <c r="H268" t="s">
+        <v>247</v>
+      </c>
+      <c r="I268" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="15">
+      <c r="A269" t="s">
+        <v>236</v>
+      </c>
+      <c r="B269" t="s">
+        <v>119</v>
+      </c>
+      <c r="C269" t="s">
+        <v>73</v>
+      </c>
+      <c r="D269" t="s">
+        <v>106</v>
+      </c>
+      <c r="E269" t="s">
+        <v>87</v>
+      </c>
+      <c r="F269" t="s">
+        <v>79</v>
+      </c>
+      <c r="G269" t="s">
+        <v>88</v>
+      </c>
+      <c r="H269" t="s">
+        <v>18</v>
+      </c>
+      <c r="I269" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="15">
+      <c r="A270" t="s">
+        <v>236</v>
+      </c>
+      <c r="B270" t="s">
+        <v>119</v>
+      </c>
+      <c r="C270" t="s">
+        <v>223</v>
+      </c>
+      <c r="D270" t="s">
+        <v>189</v>
+      </c>
+      <c r="E270" t="s">
+        <v>87</v>
+      </c>
+      <c r="F270" t="s">
+        <v>130</v>
+      </c>
+      <c r="G270" t="s">
+        <v>136</v>
+      </c>
+      <c r="H270" t="s">
+        <v>18</v>
+      </c>
+      <c r="I270" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -7958,8 +9317,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{5fb1f090-a174-4d68-ae27-489d674321f9}">
-  <dimension ref="A1:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{25316d17-a719-4878-b296-81dea5740b7d}">
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -7978,16 +9337,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -8007,13 +9366,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -8036,19 +9395,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G3" t="s">
         <v>136</v>
@@ -8065,16 +9424,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -8094,19 +9453,19 @@
         <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G5" t="s">
         <v>136</v>
@@ -8123,19 +9482,19 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G6" t="s">
         <v>136</v>
@@ -8152,19 +9511,19 @@
         <v>121</v>
       </c>
       <c r="B7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" t="s">
         <v>270</v>
       </c>
-      <c r="C7" t="s">
-        <v>259</v>
-      </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E7" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F7" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G7" t="s">
         <v>136</v>
@@ -8181,13 +9540,13 @@
         <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -8210,19 +9569,19 @@
         <v>172</v>
       </c>
       <c r="B9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" t="s">
         <v>273</v>
-      </c>
-      <c r="C9" t="s">
-        <v>259</v>
-      </c>
-      <c r="D9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F9" t="s">
-        <v>262</v>
       </c>
       <c r="G9" t="s">
         <v>136</v>
@@ -8239,16 +9598,16 @@
         <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C10" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D10" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -8268,16 +9627,16 @@
         <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -8297,19 +9656,19 @@
         <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F12" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="G12" t="s">
         <v>136</v>
@@ -8323,19 +9682,19 @@
     </row>
     <row r="13" spans="1:9" ht="15">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E13" t="s">
-        <v>282</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -8344,7 +9703,7 @@
         <v>136</v>
       </c>
       <c r="H13" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -8352,19 +9711,19 @@
     </row>
     <row r="14" spans="1:9" ht="15">
       <c r="A14" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C14" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -8373,9 +9732,154 @@
         <v>136</v>
       </c>
       <c r="H14" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15">
+      <c r="A15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="A16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>283</v>
+      </c>
+      <c r="E16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
+        <v>297</v>
+      </c>
+      <c r="C17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" t="s">
+        <v>298</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="A18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" t="s">
+        <v>220</v>
+      </c>
+      <c r="I18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="A19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D19" t="s">
+        <v>298</v>
+      </c>
+      <c r="E19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -8387,16 +9891,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8d8b1b34-9adf-49d0-930e-1b3ca8e9545f}">
-  <dimension ref="A1:F62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f9969701-3163-4685-bd2b-4905d5711021}">
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="11.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="28.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="19.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="35.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="40.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="27.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="56.25" customHeight="1">
@@ -8404,13 +9908,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -8424,13 +9928,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
@@ -8444,13 +9948,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
         <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E3" t="s">
         <v>76</v>
@@ -8464,13 +9968,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -8484,13 +9988,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E5" t="s">
         <v>46</v>
@@ -8504,13 +10008,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C6" t="s">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -8524,13 +10028,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E7" t="s">
         <v>102</v>
@@ -8544,13 +10048,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E8" t="s">
         <v>143</v>
@@ -8564,13 +10068,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -8584,13 +10088,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
@@ -8604,13 +10108,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -8624,13 +10128,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="E12" t="s">
         <v>194</v>
@@ -8644,13 +10148,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -8664,13 +10168,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E14" t="s">
         <v>46</v>
@@ -8684,16 +10188,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E15" t="s">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -8704,16 +10208,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -8724,13 +10228,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="C17" t="s">
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="E17" t="s">
         <v>112</v>
@@ -8744,13 +10248,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -8761,19 +10265,19 @@
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -8781,19 +10285,19 @@
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E20" t="s">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -8801,19 +10305,19 @@
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C21" t="s">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
         <v>18</v>
@@ -8821,19 +10325,19 @@
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="E22" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -8841,19 +10345,19 @@
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>320</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -8861,19 +10365,19 @@
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -8881,19 +10385,19 @@
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -8901,19 +10405,19 @@
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
-        <v>302</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -8921,19 +10425,19 @@
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -8941,19 +10445,19 @@
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E28" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -8961,19 +10465,19 @@
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C29" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>18</v>
@@ -8981,19 +10485,19 @@
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
         <v>18</v>
@@ -9001,19 +10505,19 @@
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="F31" t="s">
         <v>18</v>
@@ -9021,39 +10525,39 @@
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="E32" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
+        <v>309</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
         <v>304</v>
       </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>290</v>
-      </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
         <v>18</v>
@@ -9061,39 +10565,39 @@
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B35" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>322</v>
       </c>
       <c r="D35" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>323</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -9101,39 +10605,39 @@
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F37" t="s">
         <v>18</v>
@@ -9141,19 +10645,19 @@
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -9161,39 +10665,39 @@
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C40" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="F40" t="s">
         <v>18</v>
@@ -9201,39 +10705,39 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B42" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
-        <v>173</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F42" t="s">
         <v>18</v>
@@ -9241,19 +10745,19 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B43" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -9261,39 +10765,39 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>319</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -9301,19 +10805,19 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
       <c r="D46" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F46" t="s">
         <v>18</v>
@@ -9321,79 +10825,79 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F47" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B48" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F48" t="s">
-        <v>219</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="D50" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F50" t="s">
         <v>18</v>
@@ -9401,241 +10905,21 @@
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="C51" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D51" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15">
-      <c r="A52" t="s">
-        <v>224</v>
-      </c>
-      <c r="B52" t="s">
-        <v>289</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" t="s">
-        <v>299</v>
-      </c>
-      <c r="E52" t="s">
-        <v>26</v>
-      </c>
-      <c r="F52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15">
-      <c r="A53" t="s">
-        <v>224</v>
-      </c>
-      <c r="B53" t="s">
-        <v>289</v>
-      </c>
-      <c r="C53" t="s">
-        <v>229</v>
-      </c>
-      <c r="D53" t="s">
-        <v>287</v>
-      </c>
-      <c r="E53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15">
-      <c r="A54" t="s">
-        <v>224</v>
-      </c>
-      <c r="B54" t="s">
-        <v>291</v>
-      </c>
-      <c r="C54" t="s">
-        <v>77</v>
-      </c>
-      <c r="D54" t="s">
-        <v>286</v>
-      </c>
-      <c r="E54" t="s">
-        <v>26</v>
-      </c>
-      <c r="F54" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15">
-      <c r="A55" t="s">
-        <v>224</v>
-      </c>
-      <c r="B55" t="s">
-        <v>291</v>
-      </c>
-      <c r="C55" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" t="s">
-        <v>292</v>
-      </c>
-      <c r="E55" t="s">
-        <v>26</v>
-      </c>
-      <c r="F55" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15">
-      <c r="A56" t="s">
-        <v>224</v>
-      </c>
-      <c r="B56" t="s">
-        <v>293</v>
-      </c>
-      <c r="C56" t="s">
-        <v>229</v>
-      </c>
-      <c r="D56" t="s">
-        <v>295</v>
-      </c>
-      <c r="E56" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15">
-      <c r="A57" t="s">
-        <v>224</v>
-      </c>
-      <c r="B57" t="s">
-        <v>294</v>
-      </c>
-      <c r="C57" t="s">
-        <v>60</v>
-      </c>
-      <c r="D57" t="s">
-        <v>292</v>
-      </c>
-      <c r="E57" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15">
-      <c r="A58" t="s">
-        <v>224</v>
-      </c>
-      <c r="B58" t="s">
-        <v>296</v>
-      </c>
-      <c r="C58" t="s">
-        <v>131</v>
-      </c>
-      <c r="D58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E58" t="s">
-        <v>26</v>
-      </c>
-      <c r="F58" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15">
-      <c r="A59" t="s">
-        <v>224</v>
-      </c>
-      <c r="B59" t="s">
-        <v>296</v>
-      </c>
-      <c r="C59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" t="s">
-        <v>295</v>
-      </c>
-      <c r="E59" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15">
-      <c r="A60" t="s">
-        <v>224</v>
-      </c>
-      <c r="B60" t="s">
-        <v>296</v>
-      </c>
-      <c r="C60" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" t="s">
-        <v>299</v>
-      </c>
-      <c r="E60" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15">
-      <c r="A61" t="s">
-        <v>224</v>
-      </c>
-      <c r="B61" t="s">
-        <v>298</v>
-      </c>
-      <c r="C61" t="s">
-        <v>220</v>
-      </c>
-      <c r="D61" t="s">
-        <v>287</v>
-      </c>
-      <c r="E61" t="s">
-        <v>26</v>
-      </c>
-      <c r="F61" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15">
-      <c r="A62" t="s">
-        <v>224</v>
-      </c>
-      <c r="B62" t="s">
-        <v>304</v>
-      </c>
-      <c r="C62" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" t="s">
-        <v>290</v>
-      </c>
-      <c r="E62" t="s">
-        <v>26</v>
-      </c>
-      <c r="F62" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2909" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="325">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -729,7 +729,10 @@
     <t>2B</t>
   </si>
   <si>
-    <t>p. Leńczowska, RKZ za lekcję 10</t>
+    <t>Rozwój kompetencji zawodowych - Fryzjerstwo naturalne</t>
+  </si>
+  <si>
+    <t>09</t>
   </si>
   <si>
     <t>29.05.2026</t>
@@ -1443,7 +1446,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{fd65d982-9525-4b24-809b-b17ad4d43f6c}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{0d6d9055-3ad0-44e9-9dea-4e8b2a607c8f}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1464,8 +1467,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e03ba48e-0eb0-4188-941f-7513145081ff}">
-  <dimension ref="A1:I270"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c07b6150-fc30-4118-bb5a-ef82f76a6df2}">
+  <dimension ref="A1:I271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -6278,19 +6281,19 @@
         <v>198</v>
       </c>
       <c r="E166" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="G166" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H166" t="s">
         <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15">
@@ -6423,13 +6426,13 @@
         <v>198</v>
       </c>
       <c r="E171" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F171" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G171" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H171" t="s">
         <v>18</v>
@@ -6568,13 +6571,13 @@
         <v>198</v>
       </c>
       <c r="E176" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F176" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="G176" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="H176" t="s">
         <v>18</v>
@@ -6951,10 +6954,10 @@
         <v>79</v>
       </c>
       <c r="G189" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H189" t="s">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="I189" t="s">
         <v>26</v>
@@ -6997,16 +7000,16 @@
         <v>117</v>
       </c>
       <c r="C191" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="D191" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="E191" t="s">
-        <v>87</v>
+        <v>235</v>
       </c>
       <c r="F191" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="G191" t="s">
         <v>88</v>
@@ -7020,94 +7023,94 @@
     </row>
     <row r="192" spans="1:9" ht="15">
       <c r="A192" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="B192" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="C192" t="s">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="D192" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="E192" t="s">
-        <v>237</v>
+        <v>87</v>
       </c>
       <c r="F192" t="s">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="G192" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="H192" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15">
       <c r="A193" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B193" t="s">
         <v>12</v>
       </c>
       <c r="C193" t="s">
+        <v>112</v>
+      </c>
+      <c r="D193" t="s">
+        <v>213</v>
+      </c>
+      <c r="E193" t="s">
+        <v>238</v>
+      </c>
+      <c r="F193" t="s">
+        <v>239</v>
+      </c>
+      <c r="G193" t="s">
         <v>240</v>
       </c>
-      <c r="D193" t="s">
-        <v>96</v>
-      </c>
-      <c r="E193" t="s">
-        <v>241</v>
-      </c>
-      <c r="F193" t="s">
-        <v>228</v>
-      </c>
-      <c r="G193" t="s">
-        <v>24</v>
-      </c>
       <c r="H193" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I193" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15">
       <c r="A194" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B194" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C194" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D194" t="s">
+        <v>96</v>
+      </c>
+      <c r="E194" t="s">
         <v>242</v>
       </c>
-      <c r="E194" t="s">
-        <v>62</v>
-      </c>
       <c r="F194" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="G194" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="H194" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15">
       <c r="A195" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B195" t="s">
         <v>33</v>
@@ -7136,94 +7139,94 @@
     </row>
     <row r="196" spans="1:9" ht="15">
       <c r="A196" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B196" t="s">
         <v>33</v>
       </c>
       <c r="C196" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D196" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="E196" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="F196" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="G196" t="s">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="H196" t="s">
         <v>220</v>
       </c>
       <c r="I196" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15">
       <c r="A197" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B197" t="s">
         <v>33</v>
       </c>
       <c r="C197" t="s">
+        <v>112</v>
+      </c>
+      <c r="D197" t="s">
+        <v>213</v>
+      </c>
+      <c r="E197" t="s">
+        <v>238</v>
+      </c>
+      <c r="F197" t="s">
+        <v>239</v>
+      </c>
+      <c r="G197" t="s">
         <v>240</v>
       </c>
-      <c r="D197" t="s">
-        <v>96</v>
-      </c>
-      <c r="E197" t="s">
-        <v>241</v>
-      </c>
-      <c r="F197" t="s">
-        <v>228</v>
-      </c>
-      <c r="G197" t="s">
-        <v>24</v>
-      </c>
       <c r="H197" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I197" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
       <c r="A198" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B198" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C198" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D198" t="s">
+        <v>96</v>
+      </c>
+      <c r="E198" t="s">
         <v>242</v>
       </c>
-      <c r="E198" t="s">
-        <v>62</v>
-      </c>
       <c r="F198" t="s">
-        <v>175</v>
+        <v>228</v>
       </c>
       <c r="G198" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="H198" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I198" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
       <c r="A199" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B199" t="s">
         <v>41</v>
@@ -7252,86 +7255,86 @@
     </row>
     <row r="200" spans="1:9" ht="15">
       <c r="A200" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B200" t="s">
         <v>41</v>
       </c>
       <c r="C200" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D200" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="E200" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="F200" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="G200" t="s">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="H200" t="s">
         <v>220</v>
       </c>
       <c r="I200" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15">
       <c r="A201" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B201" t="s">
         <v>41</v>
       </c>
       <c r="C201" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D201" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="E201" t="s">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="F201" t="s">
-        <v>63</v>
+        <v>239</v>
       </c>
       <c r="G201" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H201" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I201" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="15">
       <c r="A202" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B202" t="s">
         <v>41</v>
       </c>
       <c r="C202" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D202" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="E202" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="F202" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="G202" t="s">
-        <v>107</v>
+        <v>245</v>
       </c>
       <c r="H202" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I202" t="s">
         <v>32</v>
@@ -7339,36 +7342,36 @@
     </row>
     <row r="203" spans="1:9" ht="15">
       <c r="A203" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B203" t="s">
         <v>41</v>
       </c>
       <c r="C203" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D203" t="s">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="E203" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F203" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="G203" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="H203" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I203" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="15">
       <c r="A204" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B204" t="s">
         <v>41</v>
@@ -7380,74 +7383,74 @@
         <v>246</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="F204" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="G204" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H204" t="s">
         <v>18</v>
       </c>
       <c r="I204" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B205" t="s">
         <v>41</v>
       </c>
       <c r="C205" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D205" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="E205" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="G205" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H205" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I205" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B206" t="s">
         <v>41</v>
       </c>
       <c r="C206" t="s">
-        <v>240</v>
+        <v>49</v>
       </c>
       <c r="D206" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E206" t="s">
+        <v>110</v>
+      </c>
+      <c r="F206" t="s">
+        <v>83</v>
+      </c>
+      <c r="G206" t="s">
+        <v>42</v>
+      </c>
+      <c r="H206" t="s">
         <v>248</v>
-      </c>
-      <c r="F206" t="s">
-        <v>58</v>
-      </c>
-      <c r="G206" t="s">
-        <v>59</v>
-      </c>
-      <c r="H206" t="s">
-        <v>18</v>
       </c>
       <c r="I206" t="s">
         <v>32</v>
@@ -7455,28 +7458,28 @@
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B207" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C207" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D207" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="E207" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="F207" t="s">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="G207" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H207" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I207" t="s">
         <v>32</v>
@@ -7484,7 +7487,7 @@
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B208" t="s">
         <v>51</v>
@@ -7513,28 +7516,28 @@
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B209" t="s">
         <v>51</v>
       </c>
       <c r="C209" t="s">
-        <v>209</v>
+        <v>131</v>
       </c>
       <c r="D209" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E209" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F209" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="G209" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H209" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I209" t="s">
         <v>32</v>
@@ -7542,57 +7545,57 @@
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B210" t="s">
         <v>51</v>
       </c>
       <c r="C210" t="s">
-        <v>112</v>
+        <v>209</v>
       </c>
       <c r="D210" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="E210" t="s">
-        <v>237</v>
+        <v>67</v>
       </c>
       <c r="F210" t="s">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="G210" t="s">
-        <v>239</v>
+        <v>42</v>
       </c>
       <c r="H210" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I210" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B211" t="s">
         <v>51</v>
       </c>
       <c r="C211" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D211" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="E211" t="s">
-        <v>15</v>
+        <v>238</v>
       </c>
       <c r="F211" t="s">
-        <v>16</v>
+        <v>239</v>
       </c>
       <c r="G211" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="H211" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I211" t="s">
         <v>19</v>
@@ -7600,170 +7603,170 @@
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B212" t="s">
         <v>51</v>
       </c>
       <c r="C212" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D212" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="E212" t="s">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="F212" t="s">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c r="G212" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H212" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I212" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B213" t="s">
         <v>51</v>
       </c>
       <c r="C213" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D213" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="E213" t="s">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="F213" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="G213" t="s">
-        <v>251</v>
+        <v>24</v>
       </c>
       <c r="H213" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I213" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B214" t="s">
         <v>51</v>
       </c>
       <c r="C214" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D214" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E214" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F214" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G214" t="s">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="H214" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I214" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B215" t="s">
         <v>51</v>
       </c>
       <c r="C215" t="s">
-        <v>240</v>
+        <v>49</v>
       </c>
       <c r="D215" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="E215" t="s">
+        <v>15</v>
+      </c>
+      <c r="F215" t="s">
+        <v>16</v>
+      </c>
+      <c r="G215" t="s">
+        <v>17</v>
+      </c>
+      <c r="H215" t="s">
         <v>248</v>
       </c>
-      <c r="F215" t="s">
-        <v>58</v>
-      </c>
-      <c r="G215" t="s">
-        <v>59</v>
-      </c>
-      <c r="H215" t="s">
-        <v>18</v>
-      </c>
       <c r="I215" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B216" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C216" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D216" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E216" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="F216" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G216" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H216" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I216" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B217" t="s">
         <v>72</v>
       </c>
       <c r="C217" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="D217" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="E217" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F217" t="s">
-        <v>222</v>
+        <v>83</v>
       </c>
       <c r="G217" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="H217" t="s">
         <v>220</v>
@@ -7774,115 +7777,115 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B218" t="s">
         <v>72</v>
       </c>
       <c r="C218" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D218" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="E218" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F218" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="G218" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H218" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I218" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B219" t="s">
         <v>72</v>
       </c>
       <c r="C219" t="s">
-        <v>112</v>
+        <v>209</v>
       </c>
       <c r="D219" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="E219" t="s">
-        <v>237</v>
+        <v>67</v>
       </c>
       <c r="F219" t="s">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="G219" t="s">
-        <v>239</v>
+        <v>42</v>
       </c>
       <c r="H219" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B220" t="s">
         <v>72</v>
       </c>
       <c r="C220" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D220" t="s">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="E220" t="s">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="F220" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="G220" t="s">
-        <v>31</v>
+        <v>240</v>
       </c>
       <c r="H220" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I220" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B221" t="s">
         <v>72</v>
       </c>
       <c r="C221" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D221" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E221" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="F221" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="G221" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="H221" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I221" t="s">
         <v>32</v>
@@ -7890,86 +7893,86 @@
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B222" t="s">
         <v>72</v>
       </c>
       <c r="C222" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D222" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="E222" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F222" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G222" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H222" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I222" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B223" t="s">
         <v>72</v>
       </c>
       <c r="C223" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D223" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="E223" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="F223" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="G223" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I223" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B224" t="s">
         <v>72</v>
       </c>
       <c r="C224" t="s">
-        <v>240</v>
+        <v>49</v>
       </c>
       <c r="D224" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="E224" t="s">
+        <v>168</v>
+      </c>
+      <c r="F224" t="s">
+        <v>152</v>
+      </c>
+      <c r="G224" t="s">
+        <v>169</v>
+      </c>
+      <c r="H224" t="s">
         <v>248</v>
-      </c>
-      <c r="F224" t="s">
-        <v>58</v>
-      </c>
-      <c r="G224" t="s">
-        <v>59</v>
-      </c>
-      <c r="H224" t="s">
-        <v>18</v>
       </c>
       <c r="I224" t="s">
         <v>32</v>
@@ -7977,28 +7980,28 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B225" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C225" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D225" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E225" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="F225" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G225" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H225" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I225" t="s">
         <v>32</v>
@@ -8006,57 +8009,57 @@
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B226" t="s">
         <v>86</v>
       </c>
       <c r="C226" t="s">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="D226" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="E226" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F226" t="s">
-        <v>222</v>
+        <v>83</v>
       </c>
       <c r="G226" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="H226" t="s">
         <v>220</v>
       </c>
       <c r="I226" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B227" t="s">
         <v>86</v>
       </c>
       <c r="C227" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D227" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="E227" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F227" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="G227" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H227" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I227" t="s">
         <v>19</v>
@@ -8064,115 +8067,115 @@
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B228" t="s">
         <v>86</v>
       </c>
       <c r="C228" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="D228" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="E228" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F228" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="G228" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="H228" t="s">
         <v>18</v>
       </c>
       <c r="I228" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B229" t="s">
         <v>86</v>
       </c>
       <c r="C229" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="D229" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="E229" t="s">
-        <v>237</v>
+        <v>87</v>
       </c>
       <c r="F229" t="s">
-        <v>238</v>
+        <v>152</v>
       </c>
       <c r="G229" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="H229" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I229" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B230" t="s">
         <v>86</v>
       </c>
       <c r="C230" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D230" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="E230" t="s">
-        <v>54</v>
+        <v>238</v>
       </c>
       <c r="F230" t="s">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="G230" t="s">
-        <v>52</v>
+        <v>240</v>
       </c>
       <c r="H230" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I230" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B231" t="s">
         <v>86</v>
       </c>
       <c r="C231" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="D231" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="E231" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="F231" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G231" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="H231" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I231" t="s">
         <v>32</v>
@@ -8180,65 +8183,65 @@
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B232" t="s">
         <v>86</v>
       </c>
       <c r="C232" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D232" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="E232" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="F232" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="G232" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H232" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I232" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B233" t="s">
         <v>86</v>
       </c>
       <c r="C233" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D233" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="E233" t="s">
-        <v>254</v>
+        <v>101</v>
       </c>
       <c r="F233" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="G233" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="H233" t="s">
         <v>18</v>
       </c>
       <c r="I233" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B234" t="s">
         <v>86</v>
@@ -8247,10 +8250,10 @@
         <v>38</v>
       </c>
       <c r="D234" t="s">
+        <v>254</v>
+      </c>
+      <c r="E234" t="s">
         <v>255</v>
-      </c>
-      <c r="E234" t="s">
-        <v>254</v>
       </c>
       <c r="F234" t="s">
         <v>58</v>
@@ -8267,57 +8270,57 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B235" t="s">
         <v>86</v>
       </c>
       <c r="C235" t="s">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="D235" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E235" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F235" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G235" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="H235" t="s">
         <v>18</v>
       </c>
       <c r="I235" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B236" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C236" t="s">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="D236" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E236" t="s">
-        <v>54</v>
+        <v>249</v>
       </c>
       <c r="F236" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="G236" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H236" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I236" t="s">
         <v>32</v>
@@ -8325,144 +8328,144 @@
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B237" t="s">
         <v>93</v>
       </c>
       <c r="C237" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="D237" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="E237" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F237" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G237" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H237" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I237" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B238" t="s">
         <v>93</v>
       </c>
       <c r="C238" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="D238" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="E238" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F238" t="s">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="G238" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H238" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I238" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B239" t="s">
         <v>93</v>
       </c>
       <c r="C239" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="D239" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="E239" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F239" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G239" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H239" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="I239" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B240" t="s">
         <v>93</v>
       </c>
       <c r="C240" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="D240" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="E240" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F240" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="G240" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="H240" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I240" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B241" t="s">
         <v>93</v>
       </c>
       <c r="C241" t="s">
-        <v>251</v>
+        <v>150</v>
       </c>
       <c r="D241" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E241" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="F241" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="G241" t="s">
         <v>88</v>
       </c>
       <c r="H241" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I241" t="s">
         <v>26</v>
@@ -8470,28 +8473,28 @@
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B242" t="s">
         <v>93</v>
       </c>
       <c r="C242" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="D242" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="E242" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="F242" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="G242" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="H242" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="I242" t="s">
         <v>26</v>
@@ -8499,80 +8502,80 @@
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B243" t="s">
         <v>93</v>
       </c>
       <c r="C243" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="D243" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="E243" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="F243" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="G243" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="H243" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I243" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B244" t="s">
         <v>93</v>
       </c>
       <c r="C244" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D244" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E244" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F244" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="G244" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H244" t="s">
         <v>18</v>
       </c>
       <c r="I244" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B245" t="s">
         <v>93</v>
       </c>
       <c r="C245" t="s">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="D245" t="s">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="E245" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F245" t="s">
-        <v>228</v>
+        <v>58</v>
       </c>
       <c r="G245" t="s">
         <v>88</v>
@@ -8586,144 +8589,144 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B246" t="s">
         <v>93</v>
       </c>
       <c r="C246" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D246" t="s">
-        <v>257</v>
+        <v>96</v>
       </c>
       <c r="E246" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F246" t="s">
-        <v>100</v>
+        <v>228</v>
       </c>
       <c r="G246" t="s">
-        <v>258</v>
+        <v>88</v>
       </c>
       <c r="H246" t="s">
         <v>18</v>
       </c>
       <c r="I246" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B247" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C247" t="s">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="D247" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="E247" t="s">
         <v>87</v>
       </c>
       <c r="F247" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G247" t="s">
-        <v>88</v>
+        <v>259</v>
       </c>
       <c r="H247" t="s">
         <v>18</v>
       </c>
       <c r="I247" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B248" t="s">
         <v>104</v>
       </c>
       <c r="C248" t="s">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="D248" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E248" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F248" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G248" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H248" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I248" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B249" t="s">
         <v>104</v>
       </c>
       <c r="C249" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D249" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="E249" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F249" t="s">
-        <v>260</v>
+        <v>16</v>
       </c>
       <c r="G249" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H249" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I249" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B250" t="s">
         <v>104</v>
       </c>
       <c r="C250" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="D250" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="E250" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F250" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="G250" t="s">
         <v>88</v>
       </c>
       <c r="H250" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I250" t="s">
         <v>26</v>
@@ -8731,28 +8734,28 @@
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B251" t="s">
         <v>104</v>
       </c>
       <c r="C251" t="s">
-        <v>112</v>
+        <v>245</v>
       </c>
       <c r="D251" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E251" t="s">
         <v>111</v>
       </c>
       <c r="F251" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="G251" t="s">
         <v>88</v>
       </c>
       <c r="H251" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="I251" t="s">
         <v>26</v>
@@ -8760,57 +8763,57 @@
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B252" t="s">
         <v>104</v>
       </c>
       <c r="C252" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="D252" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="E252" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F252" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="G252" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="H252" t="s">
         <v>220</v>
       </c>
       <c r="I252" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B253" t="s">
         <v>104</v>
       </c>
       <c r="C253" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="D253" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="E253" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="F253" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="G253" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="H253" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I253" t="s">
         <v>32</v>
@@ -8818,28 +8821,28 @@
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B254" t="s">
         <v>104</v>
       </c>
       <c r="C254" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D254" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="E254" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="F254" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G254" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="H254" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I254" t="s">
         <v>32</v>
@@ -8847,54 +8850,54 @@
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B255" t="s">
         <v>104</v>
       </c>
       <c r="C255" t="s">
-        <v>216</v>
+        <v>49</v>
       </c>
       <c r="D255" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="E255" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="F255" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="G255" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="H255" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I255" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B256" t="s">
         <v>104</v>
       </c>
       <c r="C256" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="D256" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="E256" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="F256" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="G256" t="s">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="H256" t="s">
         <v>18</v>
@@ -8905,51 +8908,51 @@
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B257" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C257" t="s">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="D257" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="E257" t="s">
         <v>87</v>
       </c>
       <c r="F257" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G257" t="s">
-        <v>88</v>
+        <v>259</v>
       </c>
       <c r="H257" t="s">
         <v>18</v>
       </c>
       <c r="I257" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B258" t="s">
         <v>113</v>
       </c>
       <c r="C258" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="D258" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="E258" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F258" t="s">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="G258" t="s">
         <v>88</v>
@@ -8963,28 +8966,28 @@
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B259" t="s">
         <v>113</v>
       </c>
       <c r="C259" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="D259" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="E259" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F259" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="G259" t="s">
         <v>88</v>
       </c>
       <c r="H259" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I259" t="s">
         <v>26</v>
@@ -8992,28 +8995,28 @@
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B260" t="s">
         <v>113</v>
       </c>
       <c r="C260" t="s">
-        <v>112</v>
+        <v>245</v>
       </c>
       <c r="D260" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E260" t="s">
         <v>111</v>
       </c>
       <c r="F260" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="G260" t="s">
         <v>88</v>
       </c>
       <c r="H260" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="I260" t="s">
         <v>26</v>
@@ -9021,57 +9024,57 @@
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B261" t="s">
         <v>113</v>
       </c>
       <c r="C261" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D261" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="E261" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F261" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G261" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H261" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="I261" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B262" t="s">
         <v>113</v>
       </c>
       <c r="C262" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D262" t="s">
-        <v>261</v>
+        <v>116</v>
       </c>
       <c r="E262" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F262" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="G262" t="s">
-        <v>262</v>
+        <v>102</v>
       </c>
       <c r="H262" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I262" t="s">
         <v>32</v>
@@ -9079,7 +9082,7 @@
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B263" t="s">
         <v>113</v>
@@ -9088,7 +9091,7 @@
         <v>49</v>
       </c>
       <c r="D263" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="E263" t="s">
         <v>54</v>
@@ -9097,62 +9100,62 @@
         <v>148</v>
       </c>
       <c r="G263" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H263" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I263" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B264" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C264" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D264" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="E264" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F264" t="s">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="G264" t="s">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="H264" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I264" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B265" t="s">
         <v>117</v>
       </c>
       <c r="C265" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="D265" t="s">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="E265" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F265" t="s">
-        <v>260</v>
+        <v>79</v>
       </c>
       <c r="G265" t="s">
         <v>88</v>
@@ -9166,146 +9169,175 @@
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B266" t="s">
         <v>117</v>
       </c>
       <c r="C266" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="D266" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E266" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="F266" t="s">
-        <v>100</v>
+        <v>261</v>
       </c>
       <c r="G266" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H266" t="s">
         <v>18</v>
       </c>
       <c r="I266" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B267" t="s">
         <v>117</v>
       </c>
       <c r="C267" t="s">
-        <v>223</v>
+        <v>60</v>
       </c>
       <c r="D267" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="E267" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F267" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G267" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="H267" t="s">
         <v>18</v>
       </c>
       <c r="I267" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B268" t="s">
         <v>117</v>
       </c>
       <c r="C268" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="D268" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="E268" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="F268" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="G268" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H268" t="s">
-        <v>247</v>
+        <v>18</v>
       </c>
       <c r="I268" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B269" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C269" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="D269" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="E269" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F269" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G269" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H269" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I269" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B270" t="s">
         <v>119</v>
       </c>
       <c r="C270" t="s">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="D270" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="E270" t="s">
         <v>87</v>
       </c>
       <c r="F270" t="s">
+        <v>79</v>
+      </c>
+      <c r="G270" t="s">
+        <v>88</v>
+      </c>
+      <c r="H270" t="s">
+        <v>18</v>
+      </c>
+      <c r="I270" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="15">
+      <c r="A271" t="s">
+        <v>237</v>
+      </c>
+      <c r="B271" t="s">
+        <v>119</v>
+      </c>
+      <c r="C271" t="s">
+        <v>223</v>
+      </c>
+      <c r="D271" t="s">
+        <v>189</v>
+      </c>
+      <c r="E271" t="s">
+        <v>87</v>
+      </c>
+      <c r="F271" t="s">
         <v>130</v>
       </c>
-      <c r="G270" t="s">
-        <v>136</v>
-      </c>
-      <c r="H270" t="s">
-        <v>18</v>
-      </c>
-      <c r="I270" t="s">
+      <c r="G271" t="s">
+        <v>88</v>
+      </c>
+      <c r="H271" t="s">
+        <v>18</v>
+      </c>
+      <c r="I271" t="s">
         <v>26</v>
       </c>
     </row>
@@ -9317,7 +9349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{25316d17-a719-4878-b296-81dea5740b7d}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c1512344-6745-4507-872f-956b0ab9cc08}">
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9337,16 +9369,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -9366,13 +9398,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
@@ -9395,19 +9427,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G3" t="s">
         <v>136</v>
@@ -9424,16 +9456,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -9453,19 +9485,19 @@
         <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G5" t="s">
         <v>136</v>
@@ -9482,19 +9514,19 @@
         <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G6" t="s">
         <v>136</v>
@@ -9511,19 +9543,19 @@
         <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" t="s">
         <v>136</v>
@@ -9540,13 +9572,13 @@
         <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
@@ -9569,19 +9601,19 @@
         <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G9" t="s">
         <v>136</v>
@@ -9598,16 +9630,16 @@
         <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -9627,16 +9659,16 @@
         <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C11" t="s">
         <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -9656,19 +9688,19 @@
         <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G12" t="s">
         <v>136</v>
@@ -9685,13 +9717,13 @@
         <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E13" t="s">
         <v>87</v>
@@ -9714,16 +9746,16 @@
         <v>218</v>
       </c>
       <c r="B14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C14" t="s">
         <v>223</v>
       </c>
       <c r="D14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -9743,13 +9775,13 @@
         <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
         <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -9769,19 +9801,19 @@
     </row>
     <row r="16" spans="1:9" ht="15">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
         <v>164</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -9798,16 +9830,16 @@
     </row>
     <row r="17" spans="1:9" ht="15">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C17" t="s">
         <v>223</v>
       </c>
       <c r="D17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E17" t="s">
         <v>87</v>
@@ -9827,16 +9859,16 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
         <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E18" t="s">
         <v>193</v>
@@ -9856,19 +9888,19 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C19" t="s">
         <v>223</v>
       </c>
       <c r="D19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F19" t="s">
         <v>18</v>
@@ -9891,7 +9923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f9969701-3163-4685-bd2b-4905d5711021}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f41ec723-1409-4631-bff1-eede89fdf299}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9908,13 +9940,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -9928,13 +9960,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
         <v>56</v>
@@ -9948,13 +9980,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
         <v>143</v>
       </c>
       <c r="D3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
         <v>76</v>
@@ -9968,13 +10000,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
         <v>69</v>
@@ -9988,13 +10020,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
         <v>46</v>
@@ -10008,13 +10040,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -10028,13 +10060,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E7" t="s">
         <v>102</v>
@@ -10048,13 +10080,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E8" t="s">
         <v>143</v>
@@ -10068,13 +10100,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
         <v>165</v>
@@ -10088,13 +10120,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
         <v>46</v>
@@ -10108,13 +10140,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
@@ -10128,13 +10160,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
         <v>194</v>
@@ -10148,13 +10180,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C13" t="s">
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -10168,13 +10200,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E14" t="s">
         <v>46</v>
@@ -10188,13 +10220,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C15" t="s">
         <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E15" t="s">
         <v>223</v>
@@ -10208,13 +10240,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E16" t="s">
         <v>223</v>
@@ -10228,13 +10260,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C17" t="s">
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E17" t="s">
         <v>112</v>
@@ -10248,13 +10280,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E18" t="s">
         <v>26</v>
@@ -10268,13 +10300,13 @@
         <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
@@ -10288,16 +10320,16 @@
         <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C20" t="s">
         <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F20" t="s">
         <v>18</v>
@@ -10308,13 +10340,13 @@
         <v>172</v>
       </c>
       <c r="B21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C21" t="s">
         <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E21" t="s">
         <v>56</v>
@@ -10328,13 +10360,13 @@
         <v>172</v>
       </c>
       <c r="B22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C22" t="s">
         <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E22" t="s">
         <v>131</v>
@@ -10348,16 +10380,16 @@
         <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C23" t="s">
         <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -10368,13 +10400,13 @@
         <v>172</v>
       </c>
       <c r="B24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E24" t="s">
         <v>46</v>
@@ -10388,13 +10420,13 @@
         <v>172</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C25" t="s">
         <v>173</v>
       </c>
       <c r="D25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E25" t="s">
         <v>42</v>
@@ -10408,13 +10440,13 @@
         <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C26" t="s">
         <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
@@ -10428,13 +10460,13 @@
         <v>218</v>
       </c>
       <c r="B27" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E27" t="s">
         <v>165</v>
@@ -10448,13 +10480,13 @@
         <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C28" t="s">
         <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E28" t="s">
         <v>26</v>
@@ -10468,13 +10500,13 @@
         <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s">
         <v>223</v>
       </c>
       <c r="D29" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E29" t="s">
         <v>26</v>
@@ -10488,13 +10520,13 @@
         <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" t="s">
         <v>176</v>
       </c>
       <c r="D30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
@@ -10508,13 +10540,13 @@
         <v>218</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C31" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E31" t="s">
         <v>155</v>
@@ -10528,16 +10560,16 @@
         <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F32" t="s">
         <v>227</v>
@@ -10548,13 +10580,13 @@
         <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" t="s">
         <v>176</v>
       </c>
       <c r="D33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E33" t="s">
         <v>56</v>
@@ -10568,13 +10600,13 @@
         <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" t="s">
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
@@ -10588,16 +10620,16 @@
         <v>218</v>
       </c>
       <c r="B35" t="s">
+        <v>312</v>
+      </c>
+      <c r="C35" t="s">
+        <v>323</v>
+      </c>
+      <c r="D35" t="s">
         <v>311</v>
       </c>
-      <c r="C35" t="s">
-        <v>322</v>
-      </c>
-      <c r="D35" t="s">
-        <v>310</v>
-      </c>
       <c r="E35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F35" t="s">
         <v>18</v>
@@ -10608,13 +10640,13 @@
         <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E36" t="s">
         <v>13</v>
@@ -10628,13 +10660,13 @@
         <v>218</v>
       </c>
       <c r="B37" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C37" t="s">
         <v>176</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E37" t="s">
         <v>80</v>
@@ -10648,13 +10680,13 @@
         <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C38" t="s">
         <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E38" t="s">
         <v>84</v>
@@ -10668,13 +10700,13 @@
         <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C39" t="s">
         <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E39" t="s">
         <v>91</v>
@@ -10685,16 +10717,16 @@
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C40" t="s">
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E40" t="s">
         <v>169</v>
@@ -10705,16 +10737,16 @@
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C41" t="s">
         <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
@@ -10725,16 +10757,16 @@
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C42" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E42" t="s">
         <v>42</v>
@@ -10745,19 +10777,19 @@
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C43" t="s">
         <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -10765,39 +10797,39 @@
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C44" t="s">
         <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E44" t="s">
         <v>202</v>
       </c>
       <c r="F44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s">
         <v>73</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E45" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F45" t="s">
         <v>18</v>
@@ -10805,16 +10837,16 @@
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B46" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E46" t="s">
         <v>80</v>
@@ -10825,16 +10857,16 @@
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C47" t="s">
         <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E47" t="s">
         <v>42</v>
@@ -10845,16 +10877,16 @@
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C48" t="s">
         <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E48" t="s">
         <v>42</v>
@@ -10865,36 +10897,36 @@
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C49" t="s">
         <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E49" t="s">
         <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B50" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C50" t="s">
         <v>223</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E50" t="s">
         <v>80</v>
@@ -10905,16 +10937,16 @@
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C51" t="s">
         <v>223</v>
       </c>
       <c r="D51" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3659" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="344">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -687,9 +687,6 @@
     <t>Bokuniewicz Sylwia</t>
   </si>
   <si>
-    <t>p. Nowaczyk, j. angielski za lekcję 9</t>
-  </si>
-  <si>
     <t>3TFA|reln</t>
   </si>
   <si>
@@ -708,9 +705,6 @@
     <t>1WB|JN2</t>
   </si>
   <si>
-    <t>p. Nowaczyk, j. angielski przeniesiony na lekcję 9</t>
-  </si>
-  <si>
     <t>Młynarczyk Paweł</t>
   </si>
   <si>
@@ -732,6 +726,9 @@
     <t>1FC|JA2</t>
   </si>
   <si>
+    <t>Płatek Krzysztof</t>
+  </si>
+  <si>
     <t>2CA</t>
   </si>
   <si>
@@ -741,14 +738,18 @@
     <t>37</t>
   </si>
   <si>
-    <t xml:space="preserve">egzaminy zawodowe - delegacja
-</t>
+    <t>delegowanie Elektroenergetyk, p. Filipek, j. polski za lekcję 7</t>
+  </si>
+  <si>
+    <t>egzaminy zawodowe - delegacja
+p. Bujanowska, matematyka za lekcję 9</t>
   </si>
   <si>
     <t>1FC</t>
   </si>
   <si>
-    <t>4TFB|JA2</t>
+    <t>delegowanie Elektroenergetyk,
+p. Damiana Nowak, historia za lekcję 9</t>
   </si>
   <si>
     <t>1WA</t>
@@ -766,21 +767,21 @@
     <t>11.06.2026</t>
   </si>
   <si>
+    <t>1FA</t>
+  </si>
+  <si>
+    <t>delegowanie na egzaminy zawodowe</t>
+  </si>
+  <si>
+    <t>Nowaczyk Agnieszka</t>
+  </si>
+  <si>
+    <t>delegowanie w EZN - szkoła publiczna</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - Fryzjerstwo naturalne</t>
   </si>
   <si>
-    <t>1FA</t>
-  </si>
-  <si>
-    <t>delegowanie na egzaminy zawodowe</t>
-  </si>
-  <si>
-    <t>Nowaczyk Agnieszka</t>
-  </si>
-  <si>
-    <t>delegowanie w EZN - szkoła publiczna</t>
-  </si>
-  <si>
     <t>09</t>
   </si>
   <si>
@@ -793,9 +794,24 @@
     <t>1FB|JA2</t>
   </si>
   <si>
+    <t>3TFB|JA2</t>
+  </si>
+  <si>
+    <t>Danielewski Paweł</t>
+  </si>
+  <si>
+    <t>1WA|reln</t>
+  </si>
+  <si>
+    <t>1WA|relu</t>
+  </si>
+  <si>
     <t>1FB|JA1</t>
   </si>
   <si>
+    <t>szkolenie ARAW, p. Biczysko, fizyka za lekcję 8</t>
+  </si>
+  <si>
     <t>1WA|JN1</t>
   </si>
   <si>
@@ -808,12 +824,12 @@
     <t>1CB|JA2</t>
   </si>
   <si>
-    <t>Rozwój kompetencji zawodowych - barber</t>
-  </si>
-  <si>
     <t>1S|JA2</t>
   </si>
   <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -1021,13 +1037,7 @@
     <t>14:50-14:55</t>
   </si>
   <si>
-    <t>Danielewski Paweł</t>
-  </si>
-  <si>
     <t>15:40-15:45</t>
-  </si>
-  <si>
-    <t>Płatek Krzysztof</t>
   </si>
   <si>
     <t>16:30-16:35</t>
@@ -1495,7 +1505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{e2350b8a-57fd-4a57-a341-dda8ea4db638}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8b965003-cf4b-4d92-8515-d29ba4c8e9f2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1516,8 +1526,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{59ecb008-ea55-453a-9e13-e80424f3b05e}">
-  <dimension ref="A1:I326"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{663f94aa-d6b2-4992-8822-d1af5aacee36}">
+  <dimension ref="A1:I331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -1527,7 +1537,7 @@
     <col min="5" max="5" width="55.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="7.42857142857143" customWidth="1"/>
     <col min="7" max="7" width="27.8571428571429" customWidth="1"/>
-    <col min="8" max="8" width="44.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="64.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6594,7 +6604,7 @@
         <v>136</v>
       </c>
       <c r="F175" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="G175" t="s">
         <v>197</v>
@@ -6881,19 +6891,19 @@
         <v>119</v>
       </c>
       <c r="E185" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F185" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="G185" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H185" t="s">
-        <v>221</v>
+        <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15">
@@ -6913,7 +6923,7 @@
         <v>136</v>
       </c>
       <c r="F186" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="G186" t="s">
         <v>197</v>
@@ -6936,10 +6946,10 @@
         <v>27</v>
       </c>
       <c r="D187" t="s">
+        <v>221</v>
+      </c>
+      <c r="E187" t="s">
         <v>222</v>
-      </c>
-      <c r="E187" t="s">
-        <v>223</v>
       </c>
       <c r="F187" t="s">
         <v>30</v>
@@ -6965,7 +6975,7 @@
         <v>27</v>
       </c>
       <c r="D188" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E188" t="s">
         <v>83</v>
@@ -7032,7 +7042,7 @@
         <v>135</v>
       </c>
       <c r="G190" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H190" t="s">
         <v>31</v>
@@ -7058,7 +7068,7 @@
         <v>62</v>
       </c>
       <c r="F191" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="G191" t="s">
         <v>158</v>
@@ -7168,7 +7178,7 @@
         <v>165</v>
       </c>
       <c r="D195" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E195" t="s">
         <v>103</v>
@@ -7197,7 +7207,7 @@
         <v>13</v>
       </c>
       <c r="D196" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E196" t="s">
         <v>103</v>
@@ -7235,13 +7245,13 @@
         <v>63</v>
       </c>
       <c r="G197" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="H197" t="s">
         <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15">
@@ -7261,16 +7271,16 @@
         <v>62</v>
       </c>
       <c r="F198" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="G198" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H198" t="s">
-        <v>228</v>
+        <v>18</v>
       </c>
       <c r="I198" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15">
@@ -7313,7 +7323,7 @@
         <v>13</v>
       </c>
       <c r="D200" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E200" t="s">
         <v>182</v>
@@ -7322,7 +7332,7 @@
         <v>74</v>
       </c>
       <c r="G200" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H200" t="s">
         <v>18</v>
@@ -7449,7 +7459,7 @@
     </row>
     <row r="205" spans="1:9" ht="15">
       <c r="A205" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B205" t="s">
         <v>12</v>
@@ -7478,7 +7488,7 @@
     </row>
     <row r="206" spans="1:9" ht="15">
       <c r="A206" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B206" t="s">
         <v>12</v>
@@ -7496,7 +7506,7 @@
         <v>44</v>
       </c>
       <c r="G206" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H206" t="s">
         <v>31</v>
@@ -7507,7 +7517,7 @@
     </row>
     <row r="207" spans="1:9" ht="15">
       <c r="A207" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B207" t="s">
         <v>12</v>
@@ -7516,7 +7526,7 @@
         <v>175</v>
       </c>
       <c r="D207" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E207" t="s">
         <v>177</v>
@@ -7536,7 +7546,7 @@
     </row>
     <row r="208" spans="1:9" ht="15">
       <c r="A208" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B208" t="s">
         <v>12</v>
@@ -7545,7 +7555,7 @@
         <v>175</v>
       </c>
       <c r="D208" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E208" t="s">
         <v>177</v>
@@ -7565,7 +7575,7 @@
     </row>
     <row r="209" spans="1:9" ht="15">
       <c r="A209" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B209" t="s">
         <v>12</v>
@@ -7574,7 +7584,7 @@
         <v>175</v>
       </c>
       <c r="D209" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E209" t="s">
         <v>177</v>
@@ -7594,7 +7604,7 @@
     </row>
     <row r="210" spans="1:9" ht="15">
       <c r="A210" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B210" t="s">
         <v>12</v>
@@ -7603,7 +7613,7 @@
         <v>175</v>
       </c>
       <c r="D210" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E210" t="s">
         <v>177</v>
@@ -7623,7 +7633,7 @@
     </row>
     <row r="211" spans="1:9" ht="15">
       <c r="A211" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B211" t="s">
         <v>50</v>
@@ -7652,57 +7662,57 @@
     </row>
     <row r="212" spans="1:9" ht="15">
       <c r="A212" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B212" t="s">
         <v>50</v>
       </c>
       <c r="C212" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D212" t="s">
-        <v>202</v>
+        <v>57</v>
       </c>
       <c r="E212" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F212" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G212" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H212" t="s">
         <v>18</v>
       </c>
       <c r="I212" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15">
       <c r="A213" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B213" t="s">
         <v>50</v>
       </c>
       <c r="C213" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D213" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E213" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="F213" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G213" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H213" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I213" t="s">
         <v>19</v>
@@ -7710,25 +7720,25 @@
     </row>
     <row r="214" spans="1:9" ht="15">
       <c r="A214" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B214" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C214" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D214" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="E214" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F214" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="G214" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H214" t="s">
         <v>31</v>
@@ -7739,54 +7749,54 @@
     </row>
     <row r="215" spans="1:9" ht="15">
       <c r="A215" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B215" t="s">
         <v>71</v>
       </c>
       <c r="C215" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="D215" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="E215" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="F215" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="G215" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="H215" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I215" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="15">
       <c r="A216" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B216" t="s">
         <v>71</v>
       </c>
       <c r="C216" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="D216" t="s">
-        <v>235</v>
+        <v>126</v>
       </c>
       <c r="E216" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="F216" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="G216" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H216" t="s">
         <v>18</v>
@@ -7797,28 +7807,28 @@
     </row>
     <row r="217" spans="1:9" ht="15">
       <c r="A217" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B217" t="s">
         <v>71</v>
       </c>
       <c r="C217" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D217" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="E217" t="s">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="F217" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G217" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H217" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I217" t="s">
         <v>19</v>
@@ -7826,28 +7836,28 @@
     </row>
     <row r="218" spans="1:9" ht="15">
       <c r="A218" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B218" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C218" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D218" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E218" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="F218" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="G218" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H218" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I218" t="s">
         <v>19</v>
@@ -7855,57 +7865,57 @@
     </row>
     <row r="219" spans="1:9" ht="15">
       <c r="A219" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B219" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C219" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="D219" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="E219" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F219" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="G219" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="H219" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15">
       <c r="A220" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B220" t="s">
         <v>86</v>
       </c>
       <c r="C220" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="D220" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E220" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="F220" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="G220" t="s">
         <v>17</v>
       </c>
       <c r="H220" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I220" t="s">
         <v>19</v>
@@ -7913,115 +7923,115 @@
     </row>
     <row r="221" spans="1:9" ht="15">
       <c r="A221" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B221" t="s">
         <v>86</v>
       </c>
       <c r="C221" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="D221" t="s">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="E221" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="F221" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="G221" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="H221" t="s">
         <v>18</v>
       </c>
       <c r="I221" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="15">
       <c r="A222" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B222" t="s">
         <v>86</v>
       </c>
       <c r="C222" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D222" t="s">
-        <v>126</v>
+        <v>235</v>
       </c>
       <c r="E222" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="F222" t="s">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="G222" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H222" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I222" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15">
       <c r="A223" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B223" t="s">
         <v>86</v>
       </c>
       <c r="C223" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D223" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="E223" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F223" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="G223" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="H223" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I223" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="15">
       <c r="A224" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B224" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C224" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D224" t="s">
-        <v>236</v>
+        <v>123</v>
       </c>
       <c r="E224" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="F224" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="G224" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H224" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I224" t="s">
         <v>19</v>
@@ -8029,144 +8039,144 @@
     </row>
     <row r="225" spans="1:9" ht="15">
       <c r="A225" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="D225" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="E225" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="F225" t="s">
-        <v>44</v>
+        <v>189</v>
       </c>
       <c r="G225" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="H225" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I225" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="15">
       <c r="A226" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B226" t="s">
         <v>108</v>
       </c>
       <c r="C226" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D226" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="E226" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="F226" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="G226" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="H226" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I226" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="15">
       <c r="A227" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B227" t="s">
         <v>108</v>
       </c>
       <c r="C227" t="s">
-        <v>161</v>
+        <v>32</v>
       </c>
       <c r="D227" t="s">
-        <v>235</v>
+        <v>28</v>
       </c>
       <c r="E227" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="F227" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="G227" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H227" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I227" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="228" spans="1:9" ht="15">
       <c r="A228" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B228" t="s">
         <v>108</v>
       </c>
       <c r="C228" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="E228" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F228" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="G228" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H228" t="s">
         <v>18</v>
       </c>
       <c r="I228" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="15">
       <c r="A229" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B229" t="s">
         <v>108</v>
       </c>
       <c r="C229" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D229" t="s">
-        <v>28</v>
+        <v>201</v>
       </c>
       <c r="E229" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F229" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G229" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H229" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I229" t="s">
         <v>19</v>
@@ -8174,28 +8184,28 @@
     </row>
     <row r="230" spans="1:9" ht="15">
       <c r="A230" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C230" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D230" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E230" t="s">
-        <v>58</v>
+        <v>236</v>
       </c>
       <c r="F230" t="s">
-        <v>59</v>
+        <v>237</v>
       </c>
       <c r="G230" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H230" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I230" t="s">
         <v>19</v>
@@ -8203,25 +8213,25 @@
     </row>
     <row r="231" spans="1:9" ht="15">
       <c r="A231" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B231" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C231" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="D231" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E231" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="F231" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="G231" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H231" t="s">
         <v>18</v>
@@ -8232,28 +8242,28 @@
     </row>
     <row r="232" spans="1:9" ht="15">
       <c r="A232" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B232" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C232" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D232" t="s">
-        <v>201</v>
+        <v>28</v>
       </c>
       <c r="E232" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F232" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G232" t="s">
         <v>131</v>
       </c>
       <c r="H232" t="s">
-        <v>31</v>
+        <v>238</v>
       </c>
       <c r="I232" t="s">
         <v>19</v>
@@ -8261,57 +8271,57 @@
     </row>
     <row r="233" spans="1:9" ht="15">
       <c r="A233" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B233" t="s">
         <v>120</v>
       </c>
       <c r="C233" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D233" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="E233" t="s">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="F233" t="s">
-        <v>238</v>
+        <v>84</v>
       </c>
       <c r="G233" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H233" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I233" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15">
       <c r="A234" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B234" t="s">
         <v>120</v>
       </c>
       <c r="C234" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D234" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E234" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F234" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="G234" t="s">
         <v>131</v>
       </c>
       <c r="H234" t="s">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="I234" t="s">
         <v>19</v>
@@ -8319,28 +8329,28 @@
     </row>
     <row r="235" spans="1:9" ht="15">
       <c r="A235" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B235" t="s">
         <v>120</v>
       </c>
       <c r="C235" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="D235" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="E235" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F235" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H235" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I235" t="s">
         <v>19</v>
@@ -8348,28 +8358,28 @@
     </row>
     <row r="236" spans="1:9" ht="15">
       <c r="A236" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B236" t="s">
         <v>120</v>
       </c>
       <c r="C236" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D236" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="E236" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="F236" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G236" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H236" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I236" t="s">
         <v>19</v>
@@ -8377,28 +8387,28 @@
     </row>
     <row r="237" spans="1:9" ht="15">
       <c r="A237" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B237" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C237" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="D237" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="E237" t="s">
-        <v>151</v>
+        <v>236</v>
       </c>
       <c r="F237" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="G237" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H237" t="s">
-        <v>239</v>
+        <v>31</v>
       </c>
       <c r="I237" t="s">
         <v>19</v>
@@ -8406,25 +8416,25 @@
     </row>
     <row r="238" spans="1:9" ht="15">
       <c r="A238" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B238" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C238" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="D238" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E238" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="F238" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="G238" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H238" t="s">
         <v>18</v>
@@ -8435,57 +8445,57 @@
     </row>
     <row r="239" spans="1:9" ht="15">
       <c r="A239" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B239" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C239" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D239" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="E239" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F239" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G239" t="s">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="H239" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I239" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15">
       <c r="A240" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B240" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C240" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D240" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="E240" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F240" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G240" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H240" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I240" t="s">
         <v>19</v>
@@ -8493,28 +8503,28 @@
     </row>
     <row r="241" spans="1:9" ht="15">
       <c r="A241" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B241" t="s">
         <v>132</v>
       </c>
       <c r="C241" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="D241" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="E241" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="F241" t="s">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="G241" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H241" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="I241" t="s">
         <v>19</v>
@@ -8522,57 +8532,57 @@
     </row>
     <row r="242" spans="1:9" ht="15">
       <c r="A242" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B242" t="s">
         <v>132</v>
       </c>
       <c r="C242" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="D242" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E242" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="F242" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="G242" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="H242" t="s">
         <v>18</v>
       </c>
       <c r="I242" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="15">
       <c r="A243" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B243" t="s">
         <v>132</v>
       </c>
       <c r="C243" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="D243" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="E243" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F243" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G243" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H243" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I243" t="s">
         <v>19</v>
@@ -8580,28 +8590,28 @@
     </row>
     <row r="244" spans="1:9" ht="15">
       <c r="A244" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B244" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C244" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D244" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="E244" t="s">
-        <v>136</v>
+        <v>236</v>
       </c>
       <c r="F244" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="G244" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H244" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I244" t="s">
         <v>19</v>
@@ -8609,25 +8619,25 @@
     </row>
     <row r="245" spans="1:9" ht="15">
       <c r="A245" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B245" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C245" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D245" t="s">
-        <v>241</v>
+        <v>57</v>
       </c>
       <c r="E245" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="F245" t="s">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="G245" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H245" t="s">
         <v>18</v>
@@ -8638,28 +8648,28 @@
     </row>
     <row r="246" spans="1:9" ht="15">
       <c r="A246" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B246" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C246" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D246" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E246" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="F246" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="G246" t="s">
         <v>131</v>
       </c>
       <c r="H246" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I246" t="s">
         <v>19</v>
@@ -8667,28 +8677,28 @@
     </row>
     <row r="247" spans="1:9" ht="15">
       <c r="A247" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B247" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C247" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="D247" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="E247" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F247" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G247" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H247" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I247" t="s">
         <v>19</v>
@@ -8696,28 +8706,28 @@
     </row>
     <row r="248" spans="1:9" ht="15">
       <c r="A248" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B248" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C248" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D248" t="s">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E248" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="F248" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G248" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H248" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I248" t="s">
         <v>19</v>
@@ -8725,28 +8735,28 @@
     </row>
     <row r="249" spans="1:9" ht="15">
       <c r="A249" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B249" t="s">
         <v>142</v>
       </c>
       <c r="C249" t="s">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="D249" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="E249" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="F249" t="s">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="G249" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H249" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="I249" t="s">
         <v>19</v>
@@ -8754,57 +8764,57 @@
     </row>
     <row r="250" spans="1:9" ht="15">
       <c r="A250" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B250" t="s">
         <v>142</v>
       </c>
       <c r="C250" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="D250" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="E250" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="F250" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="G250" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="H250" t="s">
         <v>18</v>
       </c>
       <c r="I250" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="15">
       <c r="A251" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B251" t="s">
         <v>142</v>
       </c>
       <c r="C251" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="D251" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="E251" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F251" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="G251" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H251" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I251" t="s">
         <v>19</v>
@@ -8812,28 +8822,28 @@
     </row>
     <row r="252" spans="1:9" ht="15">
       <c r="A252" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B252" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C252" t="s">
-        <v>32</v>
+        <v>138</v>
       </c>
       <c r="D252" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E252" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F252" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G252" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H252" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I252" t="s">
         <v>19</v>
@@ -8841,28 +8851,28 @@
     </row>
     <row r="253" spans="1:9" ht="15">
       <c r="A253" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B253" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C253" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D253" t="s">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="E253" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F253" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G253" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H253" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I253" t="s">
         <v>19</v>
@@ -8870,57 +8880,57 @@
     </row>
     <row r="254" spans="1:9" ht="15">
       <c r="A254" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B254" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C254" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D254" t="s">
-        <v>93</v>
+        <v>245</v>
       </c>
       <c r="E254" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="F254" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="G254" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="H254" t="s">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="I254" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B255" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="C255" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="D255" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E255" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F255" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G255" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H255" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I255" t="s">
         <v>19</v>
@@ -8928,57 +8938,57 @@
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B256" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="C256" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D256" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="E256" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="F256" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G256" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="H256" t="s">
         <v>31</v>
       </c>
       <c r="I256" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B257" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="C257" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="D257" t="s">
-        <v>243</v>
+        <v>28</v>
       </c>
       <c r="E257" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F257" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G257" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H257" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I257" t="s">
         <v>19</v>
@@ -8986,60 +8996,60 @@
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B258" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="C258" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D258" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E258" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F258" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="G258" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H258" t="s">
         <v>31</v>
       </c>
       <c r="I258" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B259" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="C259" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="D259" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="E259" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F259" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="G259" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="H259" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I259" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="15">
@@ -9047,22 +9057,22 @@
         <v>246</v>
       </c>
       <c r="B260" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="C260" t="s">
         <v>32</v>
       </c>
       <c r="D260" t="s">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="E260" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="F260" t="s">
         <v>40</v>
       </c>
       <c r="G260" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H260" t="s">
         <v>35</v>
@@ -9076,28 +9086,28 @@
         <v>246</v>
       </c>
       <c r="B261" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C261" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D261" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="E261" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F261" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="G261" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="H261" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I261" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="15">
@@ -9105,28 +9115,28 @@
         <v>246</v>
       </c>
       <c r="B262" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="C262" t="s">
         <v>32</v>
       </c>
       <c r="D262" t="s">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="E262" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F262" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G262" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="H262" t="s">
         <v>35</v>
       </c>
       <c r="I262" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15">
@@ -9134,28 +9144,28 @@
         <v>246</v>
       </c>
       <c r="B263" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C263" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D263" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="E263" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="F263" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G263" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="H263" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I263" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15">
@@ -9163,28 +9173,28 @@
         <v>246</v>
       </c>
       <c r="B264" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="C264" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D264" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E264" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F264" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G264" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H264" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I264" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="15">
@@ -9192,28 +9202,28 @@
         <v>246</v>
       </c>
       <c r="B265" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="C265" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D265" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E265" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F265" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="G265" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="H265" t="s">
         <v>18</v>
       </c>
       <c r="I265" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="15">
@@ -9221,28 +9231,28 @@
         <v>246</v>
       </c>
       <c r="B266" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C266" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D266" t="s">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="E266" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="F266" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="G266" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="H266" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I266" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15">
@@ -9250,28 +9260,28 @@
         <v>246</v>
       </c>
       <c r="B267" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C267" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="D267" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="E267" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F267" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G267" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H267" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I267" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15">
@@ -9279,7 +9289,7 @@
         <v>246</v>
       </c>
       <c r="B268" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C268" t="s">
         <v>51</v>
@@ -9294,7 +9304,7 @@
         <v>49</v>
       </c>
       <c r="G268" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H268" t="s">
         <v>31</v>
@@ -9308,25 +9318,25 @@
         <v>246</v>
       </c>
       <c r="B269" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C269" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D269" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E269" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="F269" t="s">
         <v>40</v>
       </c>
       <c r="G269" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H269" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I269" t="s">
         <v>19</v>
@@ -9337,13 +9347,13 @@
         <v>246</v>
       </c>
       <c r="B270" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C270" t="s">
         <v>60</v>
       </c>
       <c r="D270" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="E270" t="s">
         <v>62</v>
@@ -9352,13 +9362,13 @@
         <v>63</v>
       </c>
       <c r="G270" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="H270" t="s">
         <v>18</v>
       </c>
       <c r="I270" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="15">
@@ -9366,28 +9376,28 @@
         <v>246</v>
       </c>
       <c r="B271" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C271" t="s">
         <v>139</v>
       </c>
       <c r="D271" t="s">
-        <v>143</v>
+        <v>218</v>
       </c>
       <c r="E271" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="F271" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G271" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="H271" t="s">
         <v>31</v>
       </c>
       <c r="I271" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="15">
@@ -9395,7 +9405,7 @@
         <v>246</v>
       </c>
       <c r="B272" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C272" t="s">
         <v>51</v>
@@ -9410,7 +9420,7 @@
         <v>49</v>
       </c>
       <c r="G272" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H272" t="s">
         <v>31</v>
@@ -9424,7 +9434,7 @@
         <v>246</v>
       </c>
       <c r="B273" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C273" t="s">
         <v>32</v>
@@ -9439,7 +9449,7 @@
         <v>40</v>
       </c>
       <c r="G273" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H273" t="s">
         <v>35</v>
@@ -9453,28 +9463,28 @@
         <v>246</v>
       </c>
       <c r="B274" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C274" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="D274" t="s">
-        <v>97</v>
+        <v>247</v>
       </c>
       <c r="E274" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="F274" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="G274" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="H274" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I274" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="15">
@@ -9482,22 +9492,22 @@
         <v>246</v>
       </c>
       <c r="B275" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C275" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="D275" t="s">
-        <v>218</v>
+        <v>52</v>
       </c>
       <c r="E275" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="F275" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="G275" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H275" t="s">
         <v>31</v>
@@ -9511,25 +9521,25 @@
         <v>246</v>
       </c>
       <c r="B276" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C276" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D276" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E276" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F276" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G276" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H276" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I276" t="s">
         <v>19</v>
@@ -9540,25 +9550,25 @@
         <v>246</v>
       </c>
       <c r="B277" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C277" t="s">
-        <v>32</v>
+        <v>249</v>
       </c>
       <c r="D277" t="s">
-        <v>240</v>
+        <v>172</v>
       </c>
       <c r="E277" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="F277" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="G277" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H277" t="s">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="I277" t="s">
         <v>19</v>
@@ -9569,28 +9579,28 @@
         <v>246</v>
       </c>
       <c r="B278" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C278" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="D278" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="E278" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F278" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="G278" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H278" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="I278" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="15">
@@ -9598,25 +9608,25 @@
         <v>246</v>
       </c>
       <c r="B279" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C279" t="s">
-        <v>51</v>
+        <v>197</v>
       </c>
       <c r="D279" t="s">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="E279" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F279" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G279" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H279" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
       <c r="I279" t="s">
         <v>19</v>
@@ -9627,13 +9637,13 @@
         <v>246</v>
       </c>
       <c r="B280" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C280" t="s">
         <v>37</v>
       </c>
       <c r="D280" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E280" t="s">
         <v>55</v>
@@ -9642,7 +9652,7 @@
         <v>40</v>
       </c>
       <c r="G280" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
@@ -9656,13 +9666,13 @@
         <v>246</v>
       </c>
       <c r="B281" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C281" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D281" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E281" t="s">
         <v>129</v>
@@ -9671,10 +9681,10 @@
         <v>91</v>
       </c>
       <c r="G281" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H281" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I281" t="s">
         <v>19</v>
@@ -9688,19 +9698,19 @@
         <v>145</v>
       </c>
       <c r="C282" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D282" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E282" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F282" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G282" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="H282" t="s">
         <v>18</v>
@@ -9714,7 +9724,7 @@
         <v>246</v>
       </c>
       <c r="B283" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C283" t="s">
         <v>197</v>
@@ -9729,10 +9739,10 @@
         <v>30</v>
       </c>
       <c r="G283" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H283" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I283" t="s">
         <v>19</v>
@@ -9743,25 +9753,25 @@
         <v>246</v>
       </c>
       <c r="B284" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C284" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D284" t="s">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="E284" t="s">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="F284" t="s">
-        <v>40</v>
+        <v>252</v>
       </c>
       <c r="G284" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H284" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I284" t="s">
         <v>19</v>
@@ -9772,25 +9782,25 @@
         <v>246</v>
       </c>
       <c r="B285" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C285" t="s">
-        <v>250</v>
+        <v>37</v>
       </c>
       <c r="D285" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="E285" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="F285" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="G285" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H285" t="s">
-        <v>251</v>
+        <v>18</v>
       </c>
       <c r="I285" t="s">
         <v>19</v>
@@ -9801,25 +9811,25 @@
         <v>246</v>
       </c>
       <c r="B286" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C286" t="s">
-        <v>60</v>
+        <v>249</v>
       </c>
       <c r="D286" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="E286" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="F286" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="G286" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H286" t="s">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="I286" t="s">
         <v>19</v>
@@ -9830,7 +9840,7 @@
         <v>246</v>
       </c>
       <c r="B287" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C287" t="s">
         <v>197</v>
@@ -9845,10 +9855,10 @@
         <v>30</v>
       </c>
       <c r="G287" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H287" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I287" t="s">
         <v>19</v>
@@ -9859,25 +9869,25 @@
         <v>246</v>
       </c>
       <c r="B288" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C288" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D288" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="E288" t="s">
-        <v>247</v>
+        <v>55</v>
       </c>
       <c r="F288" t="s">
-        <v>252</v>
+        <v>40</v>
       </c>
       <c r="G288" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H288" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I288" t="s">
         <v>19</v>
@@ -9888,25 +9898,25 @@
         <v>246</v>
       </c>
       <c r="B289" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C289" t="s">
-        <v>37</v>
+        <v>197</v>
       </c>
       <c r="D289" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="E289" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F289" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G289" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H289" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="I289" t="s">
         <v>19</v>
@@ -9917,25 +9927,25 @@
         <v>246</v>
       </c>
       <c r="B290" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="C290" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="D290" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E290" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="F290" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="G290" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H290" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I290" t="s">
         <v>19</v>
@@ -9943,28 +9953,28 @@
     </row>
     <row r="291" spans="1:9" ht="15">
       <c r="A291" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B291" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="C291" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="D291" t="s">
-        <v>157</v>
+        <v>255</v>
       </c>
       <c r="E291" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="F291" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="G291" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H291" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="I291" t="s">
         <v>19</v>
@@ -9972,86 +9982,86 @@
     </row>
     <row r="292" spans="1:9" ht="15">
       <c r="A292" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B292" t="s">
-        <v>155</v>
+        <v>12</v>
       </c>
       <c r="C292" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D292" t="s">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="E292" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F292" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G292" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="H292" t="s">
         <v>18</v>
       </c>
       <c r="I292" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15">
       <c r="A293" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B293" t="s">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="C293" t="s">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="D293" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="E293" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F293" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G293" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="H293" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="I293" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="15">
       <c r="A294" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B294" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="C294" t="s">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="D294" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="E294" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F294" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G294" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H294" t="s">
-        <v>249</v>
+        <v>31</v>
       </c>
       <c r="I294" t="s">
         <v>19</v>
@@ -10062,28 +10072,28 @@
         <v>254</v>
       </c>
       <c r="B295" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="C295" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D295" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E295" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F295" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="G295" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H295" t="s">
         <v>18</v>
       </c>
       <c r="I295" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="15">
@@ -10091,7 +10101,7 @@
         <v>254</v>
       </c>
       <c r="B296" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C296" t="s">
         <v>51</v>
@@ -10106,7 +10116,7 @@
         <v>49</v>
       </c>
       <c r="G296" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H296" t="s">
         <v>31</v>
@@ -10123,25 +10133,25 @@
         <v>71</v>
       </c>
       <c r="C297" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D297" t="s">
-        <v>202</v>
+        <v>66</v>
       </c>
       <c r="E297" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F297" t="s">
         <v>49</v>
       </c>
       <c r="G297" t="s">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="H297" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I297" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="15">
@@ -10152,22 +10162,22 @@
         <v>71</v>
       </c>
       <c r="C298" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="D298" t="s">
-        <v>66</v>
+        <v>258</v>
       </c>
       <c r="E298" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="F298" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G298" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H298" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I298" t="s">
         <v>19</v>
@@ -10184,22 +10194,22 @@
         <v>139</v>
       </c>
       <c r="D299" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E299" t="s">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="F299" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="G299" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H299" t="s">
         <v>31</v>
       </c>
       <c r="I299" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15">
@@ -10210,25 +10220,25 @@
         <v>86</v>
       </c>
       <c r="C300" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D300" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
       <c r="E300" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="F300" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G300" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="H300" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I300" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="15">
@@ -10239,25 +10249,25 @@
         <v>86</v>
       </c>
       <c r="C301" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D301" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="E301" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F301" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G301" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="H301" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I301" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="302" spans="1:9" ht="15">
@@ -10268,25 +10278,25 @@
         <v>86</v>
       </c>
       <c r="C302" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="D302" t="s">
-        <v>218</v>
+        <v>130</v>
       </c>
       <c r="E302" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F302" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G302" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="H302" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I302" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="15">
@@ -10294,28 +10304,28 @@
         <v>254</v>
       </c>
       <c r="B303" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C303" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="D303" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="E303" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="F303" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="G303" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="H303" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I303" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="15">
@@ -10326,25 +10336,25 @@
         <v>108</v>
       </c>
       <c r="C304" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D304" t="s">
-        <v>202</v>
+        <v>260</v>
       </c>
       <c r="E304" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="F304" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="G304" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="H304" t="s">
         <v>18</v>
       </c>
       <c r="I304" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305" spans="1:9" ht="15">
@@ -10355,25 +10365,25 @@
         <v>108</v>
       </c>
       <c r="C305" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="D305" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="E305" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="F305" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G305" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="H305" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I305" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="15">
@@ -10381,28 +10391,28 @@
         <v>254</v>
       </c>
       <c r="B306" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C306" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D306" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="E306" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F306" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="G306" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="H306" t="s">
         <v>18</v>
       </c>
       <c r="I306" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="307" spans="1:9" ht="15">
@@ -10410,25 +10420,25 @@
         <v>254</v>
       </c>
       <c r="B307" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C307" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="D307" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="E307" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="F307" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="G307" t="s">
         <v>131</v>
       </c>
       <c r="H307" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="I307" t="s">
         <v>19</v>
@@ -10442,25 +10452,25 @@
         <v>120</v>
       </c>
       <c r="C308" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D308" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="E308" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="F308" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G308" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="H308" t="s">
         <v>18</v>
       </c>
       <c r="I308" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="15">
@@ -10471,25 +10481,25 @@
         <v>120</v>
       </c>
       <c r="C309" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D309" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E309" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="F309" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="G309" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="H309" t="s">
         <v>18</v>
       </c>
       <c r="I309" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15">
@@ -10497,25 +10507,25 @@
         <v>254</v>
       </c>
       <c r="B310" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C310" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D310" t="s">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="E310" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="F310" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="G310" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="H310" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I310" t="s">
         <v>19</v>
@@ -10526,28 +10536,28 @@
         <v>254</v>
       </c>
       <c r="B311" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C311" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D311" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="E311" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F311" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="G311" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H311" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I311" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="312" spans="1:9" ht="15">
@@ -10555,28 +10565,28 @@
         <v>254</v>
       </c>
       <c r="B312" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C312" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D312" t="s">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="E312" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F312" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="G312" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="H312" t="s">
         <v>18</v>
       </c>
       <c r="I312" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="15">
@@ -10587,25 +10597,25 @@
         <v>132</v>
       </c>
       <c r="C313" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D313" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E313" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F313" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G313" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="H313" t="s">
         <v>18</v>
       </c>
       <c r="I313" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="314" spans="1:9" ht="15">
@@ -10616,25 +10626,25 @@
         <v>132</v>
       </c>
       <c r="C314" t="s">
-        <v>258</v>
+        <v>51</v>
       </c>
       <c r="D314" t="s">
-        <v>259</v>
+        <v>52</v>
       </c>
       <c r="E314" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="F314" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="G314" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="H314" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I314" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="15">
@@ -10642,28 +10652,28 @@
         <v>254</v>
       </c>
       <c r="B315" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C315" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D315" t="s">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="E315" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="F315" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="G315" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H315" t="s">
         <v>18</v>
       </c>
       <c r="I315" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="316" spans="1:9" ht="15">
@@ -10671,28 +10681,28 @@
         <v>254</v>
       </c>
       <c r="B316" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C316" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D316" t="s">
-        <v>52</v>
+        <v>235</v>
       </c>
       <c r="E316" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="F316" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G316" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="H316" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I316" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="15">
@@ -10700,28 +10710,28 @@
         <v>254</v>
       </c>
       <c r="B317" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C317" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="D317" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="E317" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F317" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G317" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="H317" t="s">
         <v>18</v>
       </c>
       <c r="I317" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15">
@@ -10732,25 +10742,25 @@
         <v>142</v>
       </c>
       <c r="C318" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D318" t="s">
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="E318" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="F318" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="G318" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="H318" t="s">
         <v>18</v>
       </c>
       <c r="I318" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="15">
@@ -10761,22 +10771,22 @@
         <v>142</v>
       </c>
       <c r="C319" t="s">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="D319" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="E319" t="s">
-        <v>261</v>
+        <v>136</v>
       </c>
       <c r="F319" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="G319" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="H319" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I319" t="s">
         <v>19</v>
@@ -10790,25 +10800,25 @@
         <v>142</v>
       </c>
       <c r="C320" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="D320" t="s">
-        <v>245</v>
+        <v>52</v>
       </c>
       <c r="E320" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="F320" t="s">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="G320" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="H320" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I320" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="15">
@@ -10819,19 +10829,19 @@
         <v>142</v>
       </c>
       <c r="C321" t="s">
-        <v>258</v>
+        <v>37</v>
       </c>
       <c r="D321" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="E321" t="s">
         <v>62</v>
       </c>
       <c r="F321" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G321" t="s">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="H321" t="s">
         <v>18</v>
@@ -10845,28 +10855,28 @@
         <v>254</v>
       </c>
       <c r="B322" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C322" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="D322" t="s">
-        <v>262</v>
+        <v>57</v>
       </c>
       <c r="E322" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="F322" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="G322" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="H322" t="s">
         <v>18</v>
       </c>
       <c r="I322" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="323" spans="1:9" ht="15">
@@ -10874,28 +10884,28 @@
         <v>254</v>
       </c>
       <c r="B323" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C323" t="s">
         <v>139</v>
       </c>
       <c r="D323" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="E323" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="F323" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G323" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="H323" t="s">
         <v>31</v>
       </c>
       <c r="I323" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="15">
@@ -10903,28 +10913,28 @@
         <v>254</v>
       </c>
       <c r="B324" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C324" t="s">
-        <v>13</v>
+        <v>244</v>
       </c>
       <c r="D324" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="E324" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F324" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G324" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="H324" t="s">
         <v>18</v>
       </c>
       <c r="I324" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="325" spans="1:9" ht="15">
@@ -10932,28 +10942,28 @@
         <v>254</v>
       </c>
       <c r="B325" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C325" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="D325" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E325" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="F325" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G325" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="H325" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I325" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="15">
@@ -10961,27 +10971,172 @@
         <v>254</v>
       </c>
       <c r="B326" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C326" t="s">
         <v>13</v>
       </c>
       <c r="D326" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E326" t="s">
+        <v>83</v>
+      </c>
+      <c r="F326" t="s">
+        <v>84</v>
+      </c>
+      <c r="G326" t="s">
+        <v>267</v>
+      </c>
+      <c r="H326" t="s">
+        <v>18</v>
+      </c>
+      <c r="I326" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="15">
+      <c r="A327" t="s">
+        <v>254</v>
+      </c>
+      <c r="B327" t="s">
+        <v>145</v>
+      </c>
+      <c r="C327" t="s">
+        <v>20</v>
+      </c>
+      <c r="D327" t="s">
+        <v>96</v>
+      </c>
+      <c r="E327" t="s">
+        <v>136</v>
+      </c>
+      <c r="F327" t="s">
+        <v>148</v>
+      </c>
+      <c r="G327" t="s">
+        <v>118</v>
+      </c>
+      <c r="H327" t="s">
+        <v>18</v>
+      </c>
+      <c r="I327" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="15">
+      <c r="A328" t="s">
+        <v>254</v>
+      </c>
+      <c r="B328" t="s">
+        <v>145</v>
+      </c>
+      <c r="C328" t="s">
+        <v>139</v>
+      </c>
+      <c r="D328" t="s">
+        <v>247</v>
+      </c>
+      <c r="E328" t="s">
+        <v>83</v>
+      </c>
+      <c r="F328" t="s">
+        <v>84</v>
+      </c>
+      <c r="G328" t="s">
+        <v>267</v>
+      </c>
+      <c r="H328" t="s">
+        <v>18</v>
+      </c>
+      <c r="I328" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="15">
+      <c r="A329" t="s">
+        <v>254</v>
+      </c>
+      <c r="B329" t="s">
+        <v>153</v>
+      </c>
+      <c r="C329" t="s">
+        <v>13</v>
+      </c>
+      <c r="D329" t="s">
+        <v>268</v>
+      </c>
+      <c r="E329" t="s">
         <v>15</v>
       </c>
-      <c r="F326" t="s">
+      <c r="F329" t="s">
         <v>167</v>
       </c>
-      <c r="G326" t="s">
-        <v>17</v>
-      </c>
-      <c r="H326" t="s">
-        <v>18</v>
-      </c>
-      <c r="I326" t="s">
+      <c r="G329" t="s">
+        <v>118</v>
+      </c>
+      <c r="H329" t="s">
+        <v>18</v>
+      </c>
+      <c r="I329" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="15">
+      <c r="A330" t="s">
+        <v>254</v>
+      </c>
+      <c r="B330" t="s">
+        <v>153</v>
+      </c>
+      <c r="C330" t="s">
+        <v>139</v>
+      </c>
+      <c r="D330" t="s">
+        <v>247</v>
+      </c>
+      <c r="E330" t="s">
+        <v>136</v>
+      </c>
+      <c r="F330" t="s">
+        <v>49</v>
+      </c>
+      <c r="G330" t="s">
+        <v>257</v>
+      </c>
+      <c r="H330" t="s">
+        <v>31</v>
+      </c>
+      <c r="I330" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="15">
+      <c r="A331" t="s">
+        <v>254</v>
+      </c>
+      <c r="B331" t="s">
+        <v>155</v>
+      </c>
+      <c r="C331" t="s">
+        <v>13</v>
+      </c>
+      <c r="D331" t="s">
+        <v>269</v>
+      </c>
+      <c r="E331" t="s">
+        <v>15</v>
+      </c>
+      <c r="F331" t="s">
+        <v>167</v>
+      </c>
+      <c r="G331" t="s">
+        <v>118</v>
+      </c>
+      <c r="H331" t="s">
+        <v>18</v>
+      </c>
+      <c r="I331" t="s">
         <v>19</v>
       </c>
     </row>
@@ -10993,7 +11148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1ab6f500-0f01-4890-b680-3ba28fd6ade7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8703a655-295b-4735-bc55-695cf79229b5}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11013,16 +11168,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -11042,13 +11197,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C2" t="s">
         <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
         <v>62</v>
@@ -11071,13 +11226,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
         <v>77</v>
@@ -11100,16 +11255,16 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C4" t="s">
         <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -11129,16 +11284,16 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E5" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
@@ -11158,13 +11313,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
@@ -11187,19 +11342,19 @@
         <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D7" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G7" t="s">
         <v>131</v>
@@ -11216,16 +11371,16 @@
         <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
         <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
@@ -11245,16 +11400,16 @@
         <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
         <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E9" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -11274,16 +11429,16 @@
         <v>160</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C10" t="s">
         <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
@@ -11303,16 +11458,16 @@
         <v>160</v>
       </c>
       <c r="B11" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C11" t="s">
         <v>190</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
@@ -11332,16 +11487,16 @@
         <v>160</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C12" t="s">
         <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E12" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
@@ -11361,13 +11516,13 @@
         <v>160</v>
       </c>
       <c r="B13" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E13" t="s">
         <v>77</v>
@@ -11390,16 +11545,16 @@
         <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -11419,16 +11574,16 @@
         <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C15" t="s">
         <v>138</v>
       </c>
       <c r="D15" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -11448,16 +11603,16 @@
         <v>160</v>
       </c>
       <c r="B16" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C16" t="s">
         <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E16" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
@@ -11477,16 +11632,16 @@
         <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C17" t="s">
         <v>165</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E17" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F17" t="s">
         <v>18</v>
@@ -11503,19 +11658,19 @@
     </row>
     <row r="18" spans="1:9" ht="15">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C18" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D18" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E18" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -11532,16 +11687,16 @@
     </row>
     <row r="19" spans="1:9" ht="15">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -11561,19 +11716,19 @@
     </row>
     <row r="20" spans="1:9" ht="15">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F20" t="s">
         <v>44</v>
@@ -11593,13 +11748,13 @@
         <v>246</v>
       </c>
       <c r="B21" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C21" t="s">
         <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
         <v>77</v>
@@ -11622,13 +11777,13 @@
         <v>246</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -11651,13 +11806,13 @@
         <v>246</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E23" t="s">
         <v>77</v>
@@ -11680,16 +11835,16 @@
         <v>254</v>
       </c>
       <c r="B24" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C24" t="s">
         <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -11709,16 +11864,16 @@
         <v>254</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
         <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F25" t="s">
         <v>18</v>
@@ -11738,13 +11893,13 @@
         <v>254</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
@@ -11767,13 +11922,13 @@
         <v>254</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C27" t="s">
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E27" t="s">
         <v>43</v>
@@ -11799,8 +11954,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{1c460449-6426-4351-890c-8d6fb14f82db}">
-  <dimension ref="A1:F80"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{202b42ba-880b-46f8-b697-8b85aa14a738}">
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -11816,13 +11971,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -11836,13 +11991,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -11856,13 +12011,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -11876,13 +12031,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E4" t="s">
         <v>75</v>
@@ -11896,13 +12051,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -11916,13 +12071,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
         <v>194</v>
@@ -11936,13 +12091,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C7" t="s">
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E7" t="s">
         <v>116</v>
@@ -11956,13 +12111,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -11976,13 +12131,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C9" t="s">
         <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E9" t="s">
         <v>75</v>
@@ -11996,13 +12151,13 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C10" t="s">
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E10" t="s">
         <v>92</v>
@@ -12016,13 +12171,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
         <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E11" t="s">
         <v>104</v>
@@ -12036,13 +12191,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
         <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E12" t="s">
         <v>81</v>
@@ -12056,13 +12211,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C13" t="s">
         <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E13" t="s">
         <v>190</v>
@@ -12076,13 +12231,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E14" t="s">
         <v>107</v>
@@ -12096,13 +12251,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C15" t="s">
         <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
@@ -12116,13 +12271,13 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
         <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E16" t="s">
         <v>187</v>
@@ -12136,13 +12291,13 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C17" t="s">
         <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E17" t="s">
         <v>165</v>
@@ -12156,13 +12311,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E18" t="s">
         <v>24</v>
@@ -12176,13 +12331,13 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -12196,13 +12351,13 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C20" t="s">
         <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E20" t="s">
         <v>101</v>
@@ -12216,13 +12371,13 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C21" t="s">
         <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E21" t="s">
         <v>85</v>
@@ -12236,13 +12391,13 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C22" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E22" t="s">
         <v>199</v>
@@ -12256,13 +12411,13 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E23" t="s">
         <v>206</v>
@@ -12276,16 +12431,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
         <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E24" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="F24" t="s">
         <v>31</v>
@@ -12296,16 +12451,16 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E25" t="s">
-        <v>334</v>
+        <v>234</v>
       </c>
       <c r="F25" t="s">
         <v>31</v>
@@ -12316,16 +12471,16 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -12336,13 +12491,13 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -12356,13 +12511,13 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s">
         <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -12376,13 +12531,13 @@
         <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C29" t="s">
         <v>165</v>
       </c>
       <c r="D29" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E29" t="s">
         <v>199</v>
@@ -12396,13 +12551,13 @@
         <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C30" t="s">
         <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -12416,13 +12571,13 @@
         <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C31" t="s">
         <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -12436,13 +12591,13 @@
         <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E32" t="s">
         <v>111</v>
@@ -12456,13 +12611,13 @@
         <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C33" t="s">
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E33" t="s">
         <v>199</v>
@@ -12476,13 +12631,13 @@
         <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C34" t="s">
         <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -12496,13 +12651,13 @@
         <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C35" t="s">
         <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E35" t="s">
         <v>101</v>
@@ -12516,13 +12671,13 @@
         <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E36" t="s">
         <v>194</v>
@@ -12536,13 +12691,13 @@
         <v>160</v>
       </c>
       <c r="B37" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C37" t="s">
         <v>169</v>
       </c>
       <c r="D37" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E37" t="s">
         <v>81</v>
@@ -12556,13 +12711,13 @@
         <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C38" t="s">
         <v>190</v>
       </c>
       <c r="D38" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E38" t="s">
         <v>137</v>
@@ -12576,13 +12731,13 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C39" t="s">
         <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E39" t="s">
         <v>199</v>
@@ -12596,13 +12751,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E40" t="s">
         <v>217</v>
@@ -12616,13 +12771,13 @@
         <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E41" t="s">
         <v>115</v>
@@ -12636,13 +12791,13 @@
         <v>160</v>
       </c>
       <c r="B42" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E42" t="s">
         <v>197</v>
@@ -12656,13 +12811,13 @@
         <v>160</v>
       </c>
       <c r="B43" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E43" t="s">
         <v>206</v>
@@ -12676,13 +12831,13 @@
         <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C44" t="s">
         <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E44" t="s">
         <v>144</v>
@@ -12696,13 +12851,13 @@
         <v>160</v>
       </c>
       <c r="B45" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C45" t="s">
         <v>190</v>
       </c>
       <c r="D45" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E45" t="s">
         <v>92</v>
@@ -12716,13 +12871,13 @@
         <v>160</v>
       </c>
       <c r="B46" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C46" t="s">
         <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E46" t="s">
         <v>104</v>
@@ -12736,16 +12891,16 @@
         <v>160</v>
       </c>
       <c r="B47" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C47" t="s">
         <v>169</v>
       </c>
       <c r="D47" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E47" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F47" t="s">
         <v>171</v>
@@ -12756,13 +12911,13 @@
         <v>160</v>
       </c>
       <c r="B48" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E48" t="s">
         <v>111</v>
@@ -12776,13 +12931,13 @@
         <v>160</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C49" t="s">
         <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E49" t="s">
         <v>81</v>
@@ -12796,13 +12951,13 @@
         <v>160</v>
       </c>
       <c r="B50" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C50" t="s">
         <v>165</v>
       </c>
       <c r="D50" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E50" t="s">
         <v>104</v>
@@ -12816,13 +12971,13 @@
         <v>160</v>
       </c>
       <c r="B51" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E51" t="s">
         <v>203</v>
@@ -12836,13 +12991,13 @@
         <v>160</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C52" t="s">
         <v>138</v>
       </c>
       <c r="D52" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -12856,16 +13011,16 @@
         <v>160</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C53" t="s">
         <v>187</v>
       </c>
       <c r="D53" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E53" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F53" t="s">
         <v>18</v>
@@ -12876,16 +13031,16 @@
         <v>160</v>
       </c>
       <c r="B54" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C54" t="s">
         <v>115</v>
       </c>
       <c r="D54" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E54" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F54" t="s">
         <v>18</v>
@@ -12896,13 +13051,13 @@
         <v>160</v>
       </c>
       <c r="B55" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s">
         <v>139</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E55" t="s">
         <v>184</v>
@@ -12916,13 +13071,13 @@
         <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C56" t="s">
         <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E56" t="s">
         <v>104</v>
@@ -12936,16 +13091,16 @@
         <v>160</v>
       </c>
       <c r="B57" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C57" t="s">
         <v>165</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E57" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F57" t="s">
         <v>18</v>
@@ -12956,16 +13111,16 @@
         <v>160</v>
       </c>
       <c r="B58" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C58" t="s">
         <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
@@ -12976,16 +13131,16 @@
         <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E59" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F59" t="s">
         <v>31</v>
@@ -12996,13 +13151,13 @@
         <v>160</v>
       </c>
       <c r="B60" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
@@ -13013,19 +13168,19 @@
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C61" t="s">
         <v>161</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="F61" t="s">
         <v>18</v>
@@ -13033,19 +13188,19 @@
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B62" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
@@ -13053,19 +13208,19 @@
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B63" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C63" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -13073,39 +13228,39 @@
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B64" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D64" t="s">
         <v>325</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>342</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B65" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="F65" t="s">
         <v>35</v>
@@ -13116,19 +13271,19 @@
         <v>246</v>
       </c>
       <c r="B66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C66" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
@@ -13136,13 +13291,13 @@
         <v>246</v>
       </c>
       <c r="B67" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C67" t="s">
         <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
@@ -13156,19 +13311,19 @@
         <v>246</v>
       </c>
       <c r="B68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D68" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
@@ -13176,19 +13331,19 @@
         <v>246</v>
       </c>
       <c r="B69" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C69" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
@@ -13196,13 +13351,13 @@
         <v>246</v>
       </c>
       <c r="B70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D70" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
@@ -13216,19 +13371,19 @@
         <v>246</v>
       </c>
       <c r="B71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15">
@@ -13236,19 +13391,19 @@
         <v>246</v>
       </c>
       <c r="B72" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15">
@@ -13256,19 +13411,19 @@
         <v>246</v>
       </c>
       <c r="B73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="D73" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
@@ -13276,19 +13431,19 @@
         <v>246</v>
       </c>
       <c r="B74" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="D74" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>35</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
@@ -13296,19 +13451,19 @@
         <v>246</v>
       </c>
       <c r="B75" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C75" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15">
@@ -13316,19 +13471,19 @@
         <v>246</v>
       </c>
       <c r="B76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C76" t="s">
-        <v>250</v>
+        <v>37</v>
       </c>
       <c r="D76" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>251</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15">
@@ -13336,19 +13491,19 @@
         <v>246</v>
       </c>
       <c r="B77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="D77" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15">
@@ -13356,19 +13511,19 @@
         <v>246</v>
       </c>
       <c r="B78" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>197</v>
       </c>
       <c r="D78" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15">
@@ -13376,38 +13531,118 @@
         <v>246</v>
       </c>
       <c r="B79" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="D79" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" t="s">
+        <v>246</v>
+      </c>
+      <c r="B80" t="s">
+        <v>343</v>
+      </c>
+      <c r="C80" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" t="s">
+        <v>330</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15">
+      <c r="A81" t="s">
         <v>254</v>
       </c>
-      <c r="B80" t="s">
-        <v>336</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B81" t="s">
+        <v>322</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" t="s">
+        <v>323</v>
+      </c>
+      <c r="E81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15">
+      <c r="A82" t="s">
+        <v>254</v>
+      </c>
+      <c r="B82" t="s">
+        <v>326</v>
+      </c>
+      <c r="C82" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" t="s">
+        <v>323</v>
+      </c>
+      <c r="E82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15">
+      <c r="A83" t="s">
+        <v>254</v>
+      </c>
+      <c r="B83" t="s">
+        <v>335</v>
+      </c>
+      <c r="C83" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" t="s">
+        <v>334</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15">
+      <c r="A84" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" t="s">
+        <v>339</v>
+      </c>
+      <c r="C84" t="s">
         <v>13</v>
       </c>
-      <c r="D80" t="s">
-        <v>320</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="D84" t="s">
+        <v>325</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
         <v>18</v>
       </c>
     </row>

--- a/InformacjeOZastepstwach.xlsx
+++ b/InformacjeOZastepstwach.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="349">
   <si>
     <t>Rok szkolny: 2025/2026</t>
   </si>
@@ -755,6 +755,9 @@
     <t>1WA</t>
   </si>
   <si>
+    <t>Zając Ewa</t>
+  </si>
+  <si>
     <t>1CB</t>
   </si>
   <si>
@@ -779,6 +782,12 @@
     <t>delegowanie w EZN - szkoła publiczna</t>
   </si>
   <si>
+    <t>1K|JA1</t>
+  </si>
+  <si>
+    <t>delegowanie egzaminy w EZN Braniborska</t>
+  </si>
+  <si>
     <t>Rozwój kompetencji zawodowych - Fryzjerstwo naturalne</t>
   </si>
   <si>
@@ -827,9 +836,6 @@
     <t>1S|JA2</t>
   </si>
   <si>
-    <t>Zając Ewa</t>
-  </si>
-  <si>
     <t>1CB|JA1</t>
   </si>
   <si>
@@ -975,6 +981,15 @@
   </si>
   <si>
     <t>13:15-14:00</t>
+  </si>
+  <si>
+    <t>08:00-08:45</t>
+  </si>
+  <si>
+    <t>Patryk Migdalski - ICA indywidualne nauczanie</t>
+  </si>
+  <si>
+    <t>chemia</t>
   </si>
   <si>
     <t>12:25-15:40</t>
@@ -1505,7 +1520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{8b965003-cf4b-4d92-8515-d29ba4c8e9f2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{a1de5ad7-7491-4f7b-b2bb-f077e1a8d7e4}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1526,8 +1541,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{663f94aa-d6b2-4992-8822-d1af5aacee36}">
-  <dimension ref="A1:I331"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{2be42f63-6cef-4cc3-9757-accce9ca3dcf}">
+  <dimension ref="A1:I337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.4285714285714" customWidth="1"/>
@@ -8776,19 +8791,19 @@
         <v>242</v>
       </c>
       <c r="E250" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F250" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="G250" t="s">
-        <v>116</v>
+        <v>243</v>
       </c>
       <c r="H250" t="s">
         <v>18</v>
       </c>
       <c r="I250" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="15">
@@ -8831,7 +8846,7 @@
         <v>138</v>
       </c>
       <c r="D252" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E252" t="s">
         <v>62</v>
@@ -8886,10 +8901,10 @@
         <v>145</v>
       </c>
       <c r="C254" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D254" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E254" t="s">
         <v>58</v>
@@ -8909,7 +8924,7 @@
     </row>
     <row r="255" spans="1:9" ht="15">
       <c r="A255" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B255" t="s">
         <v>12</v>
@@ -8938,7 +8953,7 @@
     </row>
     <row r="256" spans="1:9" ht="15">
       <c r="A256" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B256" t="s">
         <v>50</v>
@@ -8967,7 +8982,7 @@
     </row>
     <row r="257" spans="1:9" ht="15">
       <c r="A257" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B257" t="s">
         <v>50</v>
@@ -8996,7 +9011,7 @@
     </row>
     <row r="258" spans="1:9" ht="15">
       <c r="A258" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B258" t="s">
         <v>71</v>
@@ -9025,7 +9040,7 @@
     </row>
     <row r="259" spans="1:9" ht="15">
       <c r="A259" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B259" t="s">
         <v>71</v>
@@ -9054,7 +9069,7 @@
     </row>
     <row r="260" spans="1:9" ht="15">
       <c r="A260" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B260" t="s">
         <v>71</v>
@@ -9083,7 +9098,7 @@
     </row>
     <row r="261" spans="1:9" ht="15">
       <c r="A261" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B261" t="s">
         <v>71</v>
@@ -9112,7 +9127,7 @@
     </row>
     <row r="262" spans="1:9" ht="15">
       <c r="A262" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B262" t="s">
         <v>86</v>
@@ -9141,7 +9156,7 @@
     </row>
     <row r="263" spans="1:9" ht="15">
       <c r="A263" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B263" t="s">
         <v>86</v>
@@ -9170,7 +9185,7 @@
     </row>
     <row r="264" spans="1:9" ht="15">
       <c r="A264" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B264" t="s">
         <v>108</v>
@@ -9199,7 +9214,7 @@
     </row>
     <row r="265" spans="1:9" ht="15">
       <c r="A265" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B265" t="s">
         <v>108</v>
@@ -9208,7 +9223,7 @@
         <v>37</v>
       </c>
       <c r="D265" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E265" t="s">
         <v>67</v>
@@ -9228,7 +9243,7 @@
     </row>
     <row r="266" spans="1:9" ht="15">
       <c r="A266" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B266" t="s">
         <v>108</v>
@@ -9257,7 +9272,7 @@
     </row>
     <row r="267" spans="1:9" ht="15">
       <c r="A267" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B267" t="s">
         <v>108</v>
@@ -9286,7 +9301,7 @@
     </row>
     <row r="268" spans="1:9" ht="15">
       <c r="A268" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B268" t="s">
         <v>120</v>
@@ -9315,7 +9330,7 @@
     </row>
     <row r="269" spans="1:9" ht="15">
       <c r="A269" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B269" t="s">
         <v>120</v>
@@ -9344,7 +9359,7 @@
     </row>
     <row r="270" spans="1:9" ht="15">
       <c r="A270" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B270" t="s">
         <v>120</v>
@@ -9373,7 +9388,7 @@
     </row>
     <row r="271" spans="1:9" ht="15">
       <c r="A271" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B271" t="s">
         <v>120</v>
@@ -9402,7 +9417,7 @@
     </row>
     <row r="272" spans="1:9" ht="15">
       <c r="A272" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B272" t="s">
         <v>132</v>
@@ -9431,7 +9446,7 @@
     </row>
     <row r="273" spans="1:9" ht="15">
       <c r="A273" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B273" t="s">
         <v>132</v>
@@ -9460,7 +9475,7 @@
     </row>
     <row r="274" spans="1:9" ht="15">
       <c r="A274" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B274" t="s">
         <v>142</v>
@@ -9469,7 +9484,7 @@
         <v>197</v>
       </c>
       <c r="D274" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E274" t="s">
         <v>94</v>
@@ -9481,7 +9496,7 @@
         <v>105</v>
       </c>
       <c r="H274" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I274" t="s">
         <v>36</v>
@@ -9489,7 +9504,7 @@
     </row>
     <row r="275" spans="1:9" ht="15">
       <c r="A275" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B275" t="s">
         <v>142</v>
@@ -9518,7 +9533,7 @@
     </row>
     <row r="276" spans="1:9" ht="15">
       <c r="A276" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B276" t="s">
         <v>142</v>
@@ -9547,13 +9562,13 @@
     </row>
     <row r="277" spans="1:9" ht="15">
       <c r="A277" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B277" t="s">
         <v>142</v>
       </c>
       <c r="C277" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D277" t="s">
         <v>172</v>
@@ -9568,7 +9583,7 @@
         <v>118</v>
       </c>
       <c r="H277" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I277" t="s">
         <v>19</v>
@@ -9576,7 +9591,7 @@
     </row>
     <row r="278" spans="1:9" ht="15">
       <c r="A278" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B278" t="s">
         <v>145</v>
@@ -9605,7 +9620,7 @@
     </row>
     <row r="279" spans="1:9" ht="15">
       <c r="A279" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B279" t="s">
         <v>145</v>
@@ -9626,7 +9641,7 @@
         <v>118</v>
       </c>
       <c r="H279" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I279" t="s">
         <v>19</v>
@@ -9634,7 +9649,7 @@
     </row>
     <row r="280" spans="1:9" ht="15">
       <c r="A280" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B280" t="s">
         <v>145</v>
@@ -9663,13 +9678,13 @@
     </row>
     <row r="281" spans="1:9" ht="15">
       <c r="A281" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B281" t="s">
         <v>145</v>
       </c>
       <c r="C281" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D281" t="s">
         <v>154</v>
@@ -9684,7 +9699,7 @@
         <v>118</v>
       </c>
       <c r="H281" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I281" t="s">
         <v>19</v>
@@ -9692,7 +9707,7 @@
     </row>
     <row r="282" spans="1:9" ht="15">
       <c r="A282" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B282" t="s">
         <v>145</v>
@@ -9721,28 +9736,28 @@
     </row>
     <row r="283" spans="1:9" ht="15">
       <c r="A283" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B283" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C283" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="D283" t="s">
-        <v>157</v>
+        <v>252</v>
       </c>
       <c r="E283" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="F283" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="G283" t="s">
         <v>118</v>
       </c>
       <c r="H283" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I283" t="s">
         <v>19</v>
@@ -9750,28 +9765,28 @@
     </row>
     <row r="284" spans="1:9" ht="15">
       <c r="A284" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B284" t="s">
         <v>153</v>
       </c>
       <c r="C284" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="D284" t="s">
-        <v>247</v>
+        <v>157</v>
       </c>
       <c r="E284" t="s">
-        <v>251</v>
+        <v>95</v>
       </c>
       <c r="F284" t="s">
-        <v>252</v>
+        <v>30</v>
       </c>
       <c r="G284" t="s">
         <v>118</v>
       </c>
       <c r="H284" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="I284" t="s">
         <v>19</v>
@@ -9779,28 +9794,28 @@
     </row>
     <row r="285" spans="1:9" ht="15">
       <c r="A285" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B285" t="s">
         <v>153</v>
       </c>
       <c r="C285" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D285" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="E285" t="s">
-        <v>55</v>
+        <v>254</v>
       </c>
       <c r="F285" t="s">
-        <v>40</v>
+        <v>255</v>
       </c>
       <c r="G285" t="s">
         <v>118</v>
       </c>
       <c r="H285" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I285" t="s">
         <v>19</v>
@@ -9808,28 +9823,28 @@
     </row>
     <row r="286" spans="1:9" ht="15">
       <c r="A286" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B286" t="s">
         <v>153</v>
       </c>
       <c r="C286" t="s">
-        <v>249</v>
+        <v>37</v>
       </c>
       <c r="D286" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="E286" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="F286" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="G286" t="s">
         <v>118</v>
       </c>
       <c r="H286" t="s">
-        <v>250</v>
+        <v>18</v>
       </c>
       <c r="I286" t="s">
         <v>19</v>
@@ -9837,28 +9852,28 @@
     </row>
     <row r="287" spans="1:9" ht="15">
       <c r="A287" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B287" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C287" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="D287" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E287" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="F287" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G287" t="s">
         <v>118</v>
       </c>
       <c r="H287" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I287" t="s">
         <v>19</v>
@@ -9866,28 +9881,28 @@
     </row>
     <row r="288" spans="1:9" ht="15">
       <c r="A288" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B288" t="s">
         <v>155</v>
       </c>
       <c r="C288" t="s">
-        <v>37</v>
+        <v>197</v>
       </c>
       <c r="D288" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="E288" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F288" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c